--- a/app/download_dir/system_files/шали_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шали_по каждому размеру.xlsx
@@ -13895,7 +13895,7 @@
   </mergeCells>
   <dataValidations count="11">
     <dataValidation sqref="I7:I1045" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>Справочники!$G$2:$G$5</formula1>
+      <formula1>Справочники!$G$2:$G$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="G7:G1045" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="textLength" errorStyle="stop" operator="lessThan">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>РОСТ</t>
+          <t>ДЛИНА-ШИРИНА</t>
         </is>
       </c>
       <c r="H4" s="72" t="inlineStr">
@@ -14128,11 +14128,7 @@
           <t>Детск.</t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr">
-        <is>
-          <t>ДЛИНА-ШИРИНА</t>
-        </is>
-      </c>
+      <c r="G5" s="42" t="n"/>
       <c r="H5" s="72" t="inlineStr">
         <is>
           <t>АЗЕРБАЙДЖАН</t>
@@ -16572,7 +16568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="B2:E110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.77" customWidth="1" style="42" min="2" max="2"/>
@@ -16581,7 +16577,6 @@
     <col width="29.63" customWidth="1" style="42" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="12.75" customHeight="1" s="69">
       <c r="B2" s="75" t="inlineStr">
         <is>
@@ -16593,11 +16588,7 @@
           <t>тип размера РОССИЯ</t>
         </is>
       </c>
-      <c r="D2" s="75" t="inlineStr">
-        <is>
-          <t>тип размера РОСТ</t>
-        </is>
-      </c>
+      <c r="D2" s="75" t="n"/>
       <c r="E2" s="75" t="inlineStr">
         <is>
           <t>Тип размера МЕЖДУНАРОДНЫЙ</t>
@@ -16615,11 +16606,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="D3" s="76" t="inlineStr">
-        <is>
-          <t>50-56</t>
-        </is>
-      </c>
+      <c r="D3" s="76" t="n"/>
       <c r="E3" s="42" t="inlineStr">
         <is>
           <t>2XS</t>
@@ -16637,11 +16624,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>56-62</t>
-        </is>
-      </c>
+      <c r="D4" s="42" t="n"/>
       <c r="E4" s="76" t="inlineStr">
         <is>
           <t>XS</t>
@@ -16651,7 +16634,7 @@
     <row r="5" ht="12.75" customHeight="1" s="69">
       <c r="B5" s="50" t="inlineStr">
         <is>
-          <t>РОСТ</t>
+          <t>ДЛИНА-ШИРИНА</t>
         </is>
       </c>
       <c r="C5" s="76" t="inlineStr">
@@ -16659,11 +16642,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62-68 </t>
-        </is>
-      </c>
+      <c r="D5" s="76" t="n"/>
       <c r="E5" s="76" t="inlineStr">
         <is>
           <t>S</t>
@@ -16671,21 +16650,13 @@
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="69">
-      <c r="B6" s="50" t="inlineStr">
-        <is>
-          <t>ДЛИНА-ШИРИНА</t>
-        </is>
-      </c>
+      <c r="B6" s="50" t="n"/>
       <c r="C6" s="76" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68-74 </t>
-        </is>
-      </c>
+      <c r="D6" s="76" t="n"/>
       <c r="E6" s="76" t="inlineStr">
         <is>
           <t>M</t>
@@ -16698,11 +16669,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="76" t="inlineStr">
-        <is>
-          <t>74-80</t>
-        </is>
-      </c>
+      <c r="D7" s="76" t="n"/>
       <c r="E7" s="76" t="inlineStr">
         <is>
           <t>L</t>
@@ -16715,11 +16682,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="76" t="inlineStr">
-        <is>
-          <t>80-86</t>
-        </is>
-      </c>
+      <c r="D8" s="76" t="n"/>
       <c r="E8" s="76" t="inlineStr">
         <is>
           <t>XL</t>
@@ -16732,11 +16695,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>86-92</t>
-        </is>
-      </c>
+      <c r="D9" s="42" t="n"/>
       <c r="E9" s="76" t="inlineStr">
         <is>
           <t>XXL</t>
@@ -16749,11 +16708,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="D10" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92-98 </t>
-        </is>
-      </c>
+      <c r="D10" s="76" t="n"/>
       <c r="E10" s="76" t="inlineStr">
         <is>
           <t>XXXL</t>
@@ -16766,11 +16721,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98-104 </t>
-        </is>
-      </c>
+      <c r="D11" s="76" t="n"/>
       <c r="E11" s="76" t="inlineStr">
         <is>
           <t>4XL</t>
@@ -16783,11 +16734,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104-110 </t>
-        </is>
-      </c>
+      <c r="D12" s="76" t="n"/>
       <c r="E12" s="76" t="inlineStr">
         <is>
           <t>5XL</t>
@@ -16800,11 +16747,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110-116 </t>
-        </is>
-      </c>
+      <c r="D13" s="76" t="n"/>
       <c r="E13" s="76" t="inlineStr">
         <is>
           <t>6XL</t>
@@ -16817,11 +16760,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116-122 </t>
-        </is>
-      </c>
+      <c r="D14" s="76" t="n"/>
       <c r="E14" s="76" t="inlineStr">
         <is>
           <t>7XL</t>
@@ -16834,11 +16773,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122-128 </t>
-        </is>
-      </c>
+      <c r="D15" s="76" t="n"/>
       <c r="E15" s="76" t="inlineStr">
         <is>
           <t>8XL</t>
@@ -16851,11 +16786,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128-134 </t>
-        </is>
-      </c>
+      <c r="D16" s="76" t="n"/>
       <c r="E16" s="76" t="inlineStr">
         <is>
           <t>9XL</t>
@@ -16868,11 +16799,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134-140 </t>
-        </is>
-      </c>
+      <c r="D17" s="76" t="n"/>
       <c r="E17" s="76" t="inlineStr">
         <is>
           <t>10XL</t>
@@ -16885,11 +16812,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="D18" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140-146 </t>
-        </is>
-      </c>
+      <c r="D18" s="76" t="n"/>
       <c r="E18" s="76" t="inlineStr">
         <is>
           <t>11XL</t>
@@ -16902,11 +16825,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="D19" s="76" t="inlineStr">
-        <is>
-          <t>146-152</t>
-        </is>
-      </c>
+      <c r="D19" s="76" t="n"/>
       <c r="E19" s="76" t="inlineStr">
         <is>
           <t>12XL</t>
@@ -16919,11 +16838,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="D20" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152-158 </t>
-        </is>
-      </c>
+      <c r="D20" s="76" t="n"/>
       <c r="E20" s="76" t="inlineStr">
         <is>
           <t>13XL</t>
@@ -16936,11 +16851,7 @@
           <t>54</t>
         </is>
       </c>
-      <c r="D21" s="76" t="inlineStr">
-        <is>
-          <t>158-164</t>
-        </is>
-      </c>
+      <c r="D21" s="76" t="n"/>
       <c r="E21" s="76" t="inlineStr">
         <is>
           <t>14XL</t>

--- a/app/download_dir/system_files/шали_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шали_по каждому размеру.xlsx
@@ -14784,7 +14784,7 @@
     <row r="44" ht="13.5" customHeight="1" s="69">
       <c r="D44" s="42" t="inlineStr">
         <is>
-          <t>ШАРФ</t>
+          <t>ШАРФ-СНУД</t>
         </is>
       </c>
       <c r="E44" s="42" t="inlineStr">
@@ -16568,7 +16568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:E110"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.77" customWidth="1" style="42" min="2" max="2"/>
@@ -16577,6 +16577,7 @@
     <col width="29.63" customWidth="1" style="42" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="12.75" customHeight="1" s="69">
       <c r="B2" s="75" t="inlineStr">
         <is>
@@ -17927,7 +17928,7 @@
     <row r="58" ht="15" customHeight="1" s="69">
       <c r="A58" s="79" t="inlineStr">
         <is>
-          <t>&lt;4000000049&gt; ШАРФ</t>
+          <t>&lt;4000000049&gt; ШАРФ-СНУД</t>
         </is>
       </c>
     </row>

--- a/app/download_dir/system_files/шали_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шали_по каждому размеру.xlsx
@@ -245,7 +245,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -497,6 +497,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -878,19 +881,19 @@
   <dimension ref="A1:AMJ1045"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.43359375" defaultRowHeight="12" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="13.82" customWidth="1" style="42" min="1" max="1"/>
-    <col width="72.34" customWidth="1" style="42" min="2" max="2"/>
+    <col width="13.82" customWidth="1" style="75" min="1" max="1"/>
+    <col width="72.34" customWidth="1" style="75" min="2" max="2"/>
     <col width="47.36" customWidth="1" style="43" min="3" max="3"/>
     <col width="34.53" customWidth="1" style="43" min="4" max="5"/>
     <col width="22.7" customWidth="1" style="43" min="6" max="8"/>
     <col width="24.67" customWidth="1" style="43" min="9" max="9"/>
     <col width="22.7" customWidth="1" style="43" min="10" max="10"/>
     <col width="25.83" customWidth="1" style="43" min="11" max="11"/>
-    <col width="22.7" customWidth="1" style="42" min="12" max="12"/>
+    <col width="22.7" customWidth="1" style="75" min="12" max="12"/>
     <col width="11.35" customWidth="1" style="43" min="14" max="14"/>
-    <col width="17.78" customWidth="1" style="42" min="15" max="15"/>
-    <col width="16" customWidth="1" style="42" min="16" max="16"/>
-    <col width="25.96" customWidth="1" style="42" min="17" max="17"/>
+    <col width="17.78" customWidth="1" style="75" min="15" max="15"/>
+    <col width="16" customWidth="1" style="75" min="16" max="16"/>
+    <col width="25.96" customWidth="1" style="75" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="64.5" customFormat="1" customHeight="1" s="44">
@@ -975,12 +978,12 @@
 ( например 23.10.2023)</t>
         </is>
       </c>
-      <c r="AME1" s="42" t="n"/>
-      <c r="AMF1" s="42" t="n"/>
-      <c r="AMG1" s="42" t="n"/>
-      <c r="AMH1" s="42" t="n"/>
-      <c r="AMI1" s="42" t="n"/>
-      <c r="AMJ1" s="42" t="n"/>
+      <c r="AME1" s="75" t="n"/>
+      <c r="AMF1" s="75" t="n"/>
+      <c r="AMG1" s="75" t="n"/>
+      <c r="AMH1" s="75" t="n"/>
+      <c r="AMI1" s="75" t="n"/>
+      <c r="AMJ1" s="75" t="n"/>
     </row>
     <row r="2" ht="12.75" customFormat="1" customHeight="1" s="44">
       <c r="A2" s="51" t="inlineStr">
@@ -1048,12 +1051,12 @@
       <c r="O2" s="50" t="n"/>
       <c r="P2" s="50" t="n"/>
       <c r="Q2" s="50" t="n"/>
-      <c r="AME2" s="42" t="n"/>
-      <c r="AMF2" s="42" t="n"/>
-      <c r="AMG2" s="42" t="n"/>
-      <c r="AMH2" s="42" t="n"/>
-      <c r="AMI2" s="42" t="n"/>
-      <c r="AMJ2" s="42" t="n"/>
+      <c r="AME2" s="75" t="n"/>
+      <c r="AMF2" s="75" t="n"/>
+      <c r="AMG2" s="75" t="n"/>
+      <c r="AMH2" s="75" t="n"/>
+      <c r="AMI2" s="75" t="n"/>
+      <c r="AMJ2" s="75" t="n"/>
     </row>
     <row r="3" ht="12.75" customFormat="1" customHeight="1" s="44">
       <c r="A3" s="51" t="inlineStr">
@@ -1121,12 +1124,12 @@
       <c r="O3" s="50" t="n"/>
       <c r="P3" s="50" t="n"/>
       <c r="Q3" s="50" t="n"/>
-      <c r="AME3" s="42" t="n"/>
-      <c r="AMF3" s="42" t="n"/>
-      <c r="AMG3" s="42" t="n"/>
-      <c r="AMH3" s="42" t="n"/>
-      <c r="AMI3" s="42" t="n"/>
-      <c r="AMJ3" s="42" t="n"/>
+      <c r="AME3" s="75" t="n"/>
+      <c r="AMF3" s="75" t="n"/>
+      <c r="AMG3" s="75" t="n"/>
+      <c r="AMH3" s="75" t="n"/>
+      <c r="AMI3" s="75" t="n"/>
+      <c r="AMJ3" s="75" t="n"/>
     </row>
     <row r="4" ht="12.75" customFormat="1" customHeight="1" s="44">
       <c r="A4" s="52" t="n"/>
@@ -1190,12 +1193,12 @@
       <c r="O4" s="50" t="n"/>
       <c r="P4" s="50" t="n"/>
       <c r="Q4" s="50" t="n"/>
-      <c r="AME4" s="42" t="n"/>
-      <c r="AMF4" s="42" t="n"/>
-      <c r="AMG4" s="42" t="n"/>
-      <c r="AMH4" s="42" t="n"/>
-      <c r="AMI4" s="42" t="n"/>
-      <c r="AMJ4" s="42" t="n"/>
+      <c r="AME4" s="75" t="n"/>
+      <c r="AMF4" s="75" t="n"/>
+      <c r="AMG4" s="75" t="n"/>
+      <c r="AMH4" s="75" t="n"/>
+      <c r="AMI4" s="75" t="n"/>
+      <c r="AMJ4" s="75" t="n"/>
     </row>
     <row r="5" ht="21.75" customFormat="1" customHeight="1" s="44">
       <c r="A5" s="52" t="n"/>
@@ -1219,12 +1222,12 @@
       <c r="O5" s="54" t="n"/>
       <c r="P5" s="54" t="n"/>
       <c r="Q5" s="54" t="n"/>
-      <c r="AME5" s="42" t="n"/>
-      <c r="AMF5" s="42" t="n"/>
-      <c r="AMG5" s="42" t="n"/>
-      <c r="AMH5" s="42" t="n"/>
-      <c r="AMI5" s="42" t="n"/>
-      <c r="AMJ5" s="42" t="n"/>
+      <c r="AME5" s="75" t="n"/>
+      <c r="AMF5" s="75" t="n"/>
+      <c r="AMG5" s="75" t="n"/>
+      <c r="AMH5" s="75" t="n"/>
+      <c r="AMI5" s="75" t="n"/>
+      <c r="AMJ5" s="75" t="n"/>
     </row>
     <row r="6" ht="202.5" customFormat="1" customHeight="1" s="44">
       <c r="A6" s="55" t="inlineStr">
@@ -1309,12 +1312,12 @@
       </c>
       <c r="P6" s="60" t="n"/>
       <c r="Q6" s="47" t="n"/>
-      <c r="AME6" s="42" t="n"/>
-      <c r="AMF6" s="42" t="n"/>
-      <c r="AMG6" s="42" t="n"/>
-      <c r="AMH6" s="42" t="n"/>
-      <c r="AMI6" s="42" t="n"/>
-      <c r="AMJ6" s="42" t="n"/>
+      <c r="AME6" s="75" t="n"/>
+      <c r="AMF6" s="75" t="n"/>
+      <c r="AMG6" s="75" t="n"/>
+      <c r="AMH6" s="75" t="n"/>
+      <c r="AMI6" s="75" t="n"/>
+      <c r="AMJ6" s="75" t="n"/>
     </row>
     <row r="7" ht="17.25" customFormat="1" customHeight="1" s="61">
       <c r="A7" s="50" t="inlineStr">
@@ -1412,12 +1415,12 @@
       <c r="Z7" s="50" t="n"/>
       <c r="AA7" s="50" t="n"/>
       <c r="AB7" s="50" t="n"/>
-      <c r="AME7" s="42" t="n"/>
-      <c r="AMF7" s="42" t="n"/>
-      <c r="AMG7" s="42" t="n"/>
-      <c r="AMH7" s="42" t="n"/>
-      <c r="AMI7" s="42" t="n"/>
-      <c r="AMJ7" s="42" t="n"/>
+      <c r="AME7" s="75" t="n"/>
+      <c r="AMF7" s="75" t="n"/>
+      <c r="AMG7" s="75" t="n"/>
+      <c r="AMH7" s="75" t="n"/>
+      <c r="AMI7" s="75" t="n"/>
+      <c r="AMJ7" s="75" t="n"/>
     </row>
     <row r="8" ht="17.25" customFormat="1" customHeight="1" s="61">
       <c r="A8" s="50" t="inlineStr">
@@ -1503,12 +1506,12 @@
       <c r="Z8" s="50" t="n"/>
       <c r="AA8" s="50" t="n"/>
       <c r="AB8" s="50" t="n"/>
-      <c r="AME8" s="42" t="n"/>
-      <c r="AMF8" s="42" t="n"/>
-      <c r="AMG8" s="42" t="n"/>
-      <c r="AMH8" s="42" t="n"/>
-      <c r="AMI8" s="42" t="n"/>
-      <c r="AMJ8" s="42" t="n"/>
+      <c r="AME8" s="75" t="n"/>
+      <c r="AMF8" s="75" t="n"/>
+      <c r="AMG8" s="75" t="n"/>
+      <c r="AMH8" s="75" t="n"/>
+      <c r="AMI8" s="75" t="n"/>
+      <c r="AMJ8" s="75" t="n"/>
     </row>
     <row r="9" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B9" s="62">
@@ -1529,12 +1532,12 @@
       <c r="O9" s="68" t="n"/>
       <c r="P9" s="61" t="n"/>
       <c r="Q9" s="61" t="n"/>
-      <c r="AME9" s="42" t="n"/>
-      <c r="AMF9" s="42" t="n"/>
-      <c r="AMG9" s="42" t="n"/>
-      <c r="AMH9" s="42" t="n"/>
-      <c r="AMI9" s="42" t="n"/>
-      <c r="AMJ9" s="42" t="n"/>
+      <c r="AME9" s="75" t="n"/>
+      <c r="AMF9" s="75" t="n"/>
+      <c r="AMG9" s="75" t="n"/>
+      <c r="AMH9" s="75" t="n"/>
+      <c r="AMI9" s="75" t="n"/>
+      <c r="AMJ9" s="75" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B10" s="62">
@@ -1555,12 +1558,12 @@
       <c r="O10" s="68" t="n"/>
       <c r="P10" s="61" t="n"/>
       <c r="Q10" s="61" t="n"/>
-      <c r="AME10" s="42" t="n"/>
-      <c r="AMF10" s="42" t="n"/>
-      <c r="AMG10" s="42" t="n"/>
-      <c r="AMH10" s="42" t="n"/>
-      <c r="AMI10" s="42" t="n"/>
-      <c r="AMJ10" s="42" t="n"/>
+      <c r="AME10" s="75" t="n"/>
+      <c r="AMF10" s="75" t="n"/>
+      <c r="AMG10" s="75" t="n"/>
+      <c r="AMH10" s="75" t="n"/>
+      <c r="AMI10" s="75" t="n"/>
+      <c r="AMJ10" s="75" t="n"/>
     </row>
     <row r="11" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B11" s="62">
@@ -1581,12 +1584,12 @@
       <c r="O11" s="68" t="n"/>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="61" t="n"/>
-      <c r="AME11" s="42" t="n"/>
-      <c r="AMF11" s="42" t="n"/>
-      <c r="AMG11" s="42" t="n"/>
-      <c r="AMH11" s="42" t="n"/>
-      <c r="AMI11" s="42" t="n"/>
-      <c r="AMJ11" s="42" t="n"/>
+      <c r="AME11" s="75" t="n"/>
+      <c r="AMF11" s="75" t="n"/>
+      <c r="AMG11" s="75" t="n"/>
+      <c r="AMH11" s="75" t="n"/>
+      <c r="AMI11" s="75" t="n"/>
+      <c r="AMJ11" s="75" t="n"/>
     </row>
     <row r="12" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B12" s="62">
@@ -1607,12 +1610,12 @@
       <c r="O12" s="68" t="n"/>
       <c r="P12" s="61" t="n"/>
       <c r="Q12" s="61" t="n"/>
-      <c r="AME12" s="42" t="n"/>
-      <c r="AMF12" s="42" t="n"/>
-      <c r="AMG12" s="42" t="n"/>
-      <c r="AMH12" s="42" t="n"/>
-      <c r="AMI12" s="42" t="n"/>
-      <c r="AMJ12" s="42" t="n"/>
+      <c r="AME12" s="75" t="n"/>
+      <c r="AMF12" s="75" t="n"/>
+      <c r="AMG12" s="75" t="n"/>
+      <c r="AMH12" s="75" t="n"/>
+      <c r="AMI12" s="75" t="n"/>
+      <c r="AMJ12" s="75" t="n"/>
     </row>
     <row r="13" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B13" s="62">
@@ -1633,12 +1636,12 @@
       <c r="O13" s="68" t="n"/>
       <c r="P13" s="61" t="n"/>
       <c r="Q13" s="61" t="n"/>
-      <c r="AME13" s="42" t="n"/>
-      <c r="AMF13" s="42" t="n"/>
-      <c r="AMG13" s="42" t="n"/>
-      <c r="AMH13" s="42" t="n"/>
-      <c r="AMI13" s="42" t="n"/>
-      <c r="AMJ13" s="42" t="n"/>
+      <c r="AME13" s="75" t="n"/>
+      <c r="AMF13" s="75" t="n"/>
+      <c r="AMG13" s="75" t="n"/>
+      <c r="AMH13" s="75" t="n"/>
+      <c r="AMI13" s="75" t="n"/>
+      <c r="AMJ13" s="75" t="n"/>
     </row>
     <row r="14" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B14" s="62">
@@ -1659,12 +1662,12 @@
       <c r="O14" s="68" t="n"/>
       <c r="P14" s="61" t="n"/>
       <c r="Q14" s="61" t="n"/>
-      <c r="AME14" s="42" t="n"/>
-      <c r="AMF14" s="42" t="n"/>
-      <c r="AMG14" s="42" t="n"/>
-      <c r="AMH14" s="42" t="n"/>
-      <c r="AMI14" s="42" t="n"/>
-      <c r="AMJ14" s="42" t="n"/>
+      <c r="AME14" s="75" t="n"/>
+      <c r="AMF14" s="75" t="n"/>
+      <c r="AMG14" s="75" t="n"/>
+      <c r="AMH14" s="75" t="n"/>
+      <c r="AMI14" s="75" t="n"/>
+      <c r="AMJ14" s="75" t="n"/>
     </row>
     <row r="15" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B15" s="62">
@@ -1685,12 +1688,12 @@
       <c r="O15" s="68" t="n"/>
       <c r="P15" s="61" t="n"/>
       <c r="Q15" s="61" t="n"/>
-      <c r="AME15" s="42" t="n"/>
-      <c r="AMF15" s="42" t="n"/>
-      <c r="AMG15" s="42" t="n"/>
-      <c r="AMH15" s="42" t="n"/>
-      <c r="AMI15" s="42" t="n"/>
-      <c r="AMJ15" s="42" t="n"/>
+      <c r="AME15" s="75" t="n"/>
+      <c r="AMF15" s="75" t="n"/>
+      <c r="AMG15" s="75" t="n"/>
+      <c r="AMH15" s="75" t="n"/>
+      <c r="AMI15" s="75" t="n"/>
+      <c r="AMJ15" s="75" t="n"/>
     </row>
     <row r="16" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B16" s="62">
@@ -1711,12 +1714,12 @@
       <c r="O16" s="68" t="n"/>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="61" t="n"/>
-      <c r="AME16" s="42" t="n"/>
-      <c r="AMF16" s="42" t="n"/>
-      <c r="AMG16" s="42" t="n"/>
-      <c r="AMH16" s="42" t="n"/>
-      <c r="AMI16" s="42" t="n"/>
-      <c r="AMJ16" s="42" t="n"/>
+      <c r="AME16" s="75" t="n"/>
+      <c r="AMF16" s="75" t="n"/>
+      <c r="AMG16" s="75" t="n"/>
+      <c r="AMH16" s="75" t="n"/>
+      <c r="AMI16" s="75" t="n"/>
+      <c r="AMJ16" s="75" t="n"/>
     </row>
     <row r="17" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B17" s="62">
@@ -1737,12 +1740,12 @@
       <c r="O17" s="68" t="n"/>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="61" t="n"/>
-      <c r="AME17" s="42" t="n"/>
-      <c r="AMF17" s="42" t="n"/>
-      <c r="AMG17" s="42" t="n"/>
-      <c r="AMH17" s="42" t="n"/>
-      <c r="AMI17" s="42" t="n"/>
-      <c r="AMJ17" s="42" t="n"/>
+      <c r="AME17" s="75" t="n"/>
+      <c r="AMF17" s="75" t="n"/>
+      <c r="AMG17" s="75" t="n"/>
+      <c r="AMH17" s="75" t="n"/>
+      <c r="AMI17" s="75" t="n"/>
+      <c r="AMJ17" s="75" t="n"/>
     </row>
     <row r="18" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B18" s="62">
@@ -1763,12 +1766,12 @@
       <c r="O18" s="68" t="n"/>
       <c r="P18" s="61" t="n"/>
       <c r="Q18" s="61" t="n"/>
-      <c r="AME18" s="42" t="n"/>
-      <c r="AMF18" s="42" t="n"/>
-      <c r="AMG18" s="42" t="n"/>
-      <c r="AMH18" s="42" t="n"/>
-      <c r="AMI18" s="42" t="n"/>
-      <c r="AMJ18" s="42" t="n"/>
+      <c r="AME18" s="75" t="n"/>
+      <c r="AMF18" s="75" t="n"/>
+      <c r="AMG18" s="75" t="n"/>
+      <c r="AMH18" s="75" t="n"/>
+      <c r="AMI18" s="75" t="n"/>
+      <c r="AMJ18" s="75" t="n"/>
     </row>
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B19" s="62">
@@ -1789,12 +1792,12 @@
       <c r="O19" s="68" t="n"/>
       <c r="P19" s="61" t="n"/>
       <c r="Q19" s="61" t="n"/>
-      <c r="AME19" s="42" t="n"/>
-      <c r="AMF19" s="42" t="n"/>
-      <c r="AMG19" s="42" t="n"/>
-      <c r="AMH19" s="42" t="n"/>
-      <c r="AMI19" s="42" t="n"/>
-      <c r="AMJ19" s="42" t="n"/>
+      <c r="AME19" s="75" t="n"/>
+      <c r="AMF19" s="75" t="n"/>
+      <c r="AMG19" s="75" t="n"/>
+      <c r="AMH19" s="75" t="n"/>
+      <c r="AMI19" s="75" t="n"/>
+      <c r="AMJ19" s="75" t="n"/>
     </row>
     <row r="20" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B20" s="62">
@@ -1815,12 +1818,12 @@
       <c r="O20" s="68" t="n"/>
       <c r="P20" s="61" t="n"/>
       <c r="Q20" s="61" t="n"/>
-      <c r="AME20" s="42" t="n"/>
-      <c r="AMF20" s="42" t="n"/>
-      <c r="AMG20" s="42" t="n"/>
-      <c r="AMH20" s="42" t="n"/>
-      <c r="AMI20" s="42" t="n"/>
-      <c r="AMJ20" s="42" t="n"/>
+      <c r="AME20" s="75" t="n"/>
+      <c r="AMF20" s="75" t="n"/>
+      <c r="AMG20" s="75" t="n"/>
+      <c r="AMH20" s="75" t="n"/>
+      <c r="AMI20" s="75" t="n"/>
+      <c r="AMJ20" s="75" t="n"/>
     </row>
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B21" s="62">
@@ -1841,12 +1844,12 @@
       <c r="O21" s="68" t="n"/>
       <c r="P21" s="61" t="n"/>
       <c r="Q21" s="61" t="n"/>
-      <c r="AME21" s="42" t="n"/>
-      <c r="AMF21" s="42" t="n"/>
-      <c r="AMG21" s="42" t="n"/>
-      <c r="AMH21" s="42" t="n"/>
-      <c r="AMI21" s="42" t="n"/>
-      <c r="AMJ21" s="42" t="n"/>
+      <c r="AME21" s="75" t="n"/>
+      <c r="AMF21" s="75" t="n"/>
+      <c r="AMG21" s="75" t="n"/>
+      <c r="AMH21" s="75" t="n"/>
+      <c r="AMI21" s="75" t="n"/>
+      <c r="AMJ21" s="75" t="n"/>
     </row>
     <row r="22" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B22" s="62">
@@ -1867,12 +1870,12 @@
       <c r="O22" s="68" t="n"/>
       <c r="P22" s="61" t="n"/>
       <c r="Q22" s="61" t="n"/>
-      <c r="AME22" s="42" t="n"/>
-      <c r="AMF22" s="42" t="n"/>
-      <c r="AMG22" s="42" t="n"/>
-      <c r="AMH22" s="42" t="n"/>
-      <c r="AMI22" s="42" t="n"/>
-      <c r="AMJ22" s="42" t="n"/>
+      <c r="AME22" s="75" t="n"/>
+      <c r="AMF22" s="75" t="n"/>
+      <c r="AMG22" s="75" t="n"/>
+      <c r="AMH22" s="75" t="n"/>
+      <c r="AMI22" s="75" t="n"/>
+      <c r="AMJ22" s="75" t="n"/>
     </row>
     <row r="23" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B23" s="62">
@@ -1893,12 +1896,12 @@
       <c r="O23" s="68" t="n"/>
       <c r="P23" s="61" t="n"/>
       <c r="Q23" s="61" t="n"/>
-      <c r="AME23" s="42" t="n"/>
-      <c r="AMF23" s="42" t="n"/>
-      <c r="AMG23" s="42" t="n"/>
-      <c r="AMH23" s="42" t="n"/>
-      <c r="AMI23" s="42" t="n"/>
-      <c r="AMJ23" s="42" t="n"/>
+      <c r="AME23" s="75" t="n"/>
+      <c r="AMF23" s="75" t="n"/>
+      <c r="AMG23" s="75" t="n"/>
+      <c r="AMH23" s="75" t="n"/>
+      <c r="AMI23" s="75" t="n"/>
+      <c r="AMJ23" s="75" t="n"/>
     </row>
     <row r="24" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B24" s="62">
@@ -1919,12 +1922,12 @@
       <c r="O24" s="68" t="n"/>
       <c r="P24" s="61" t="n"/>
       <c r="Q24" s="61" t="n"/>
-      <c r="AME24" s="42" t="n"/>
-      <c r="AMF24" s="42" t="n"/>
-      <c r="AMG24" s="42" t="n"/>
-      <c r="AMH24" s="42" t="n"/>
-      <c r="AMI24" s="42" t="n"/>
-      <c r="AMJ24" s="42" t="n"/>
+      <c r="AME24" s="75" t="n"/>
+      <c r="AMF24" s="75" t="n"/>
+      <c r="AMG24" s="75" t="n"/>
+      <c r="AMH24" s="75" t="n"/>
+      <c r="AMI24" s="75" t="n"/>
+      <c r="AMJ24" s="75" t="n"/>
     </row>
     <row r="25" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B25" s="62">
@@ -1945,12 +1948,12 @@
       <c r="O25" s="68" t="n"/>
       <c r="P25" s="61" t="n"/>
       <c r="Q25" s="61" t="n"/>
-      <c r="AME25" s="42" t="n"/>
-      <c r="AMF25" s="42" t="n"/>
-      <c r="AMG25" s="42" t="n"/>
-      <c r="AMH25" s="42" t="n"/>
-      <c r="AMI25" s="42" t="n"/>
-      <c r="AMJ25" s="42" t="n"/>
+      <c r="AME25" s="75" t="n"/>
+      <c r="AMF25" s="75" t="n"/>
+      <c r="AMG25" s="75" t="n"/>
+      <c r="AMH25" s="75" t="n"/>
+      <c r="AMI25" s="75" t="n"/>
+      <c r="AMJ25" s="75" t="n"/>
     </row>
     <row r="26" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B26" s="62">
@@ -1971,12 +1974,12 @@
       <c r="O26" s="68" t="n"/>
       <c r="P26" s="61" t="n"/>
       <c r="Q26" s="61" t="n"/>
-      <c r="AME26" s="42" t="n"/>
-      <c r="AMF26" s="42" t="n"/>
-      <c r="AMG26" s="42" t="n"/>
-      <c r="AMH26" s="42" t="n"/>
-      <c r="AMI26" s="42" t="n"/>
-      <c r="AMJ26" s="42" t="n"/>
+      <c r="AME26" s="75" t="n"/>
+      <c r="AMF26" s="75" t="n"/>
+      <c r="AMG26" s="75" t="n"/>
+      <c r="AMH26" s="75" t="n"/>
+      <c r="AMI26" s="75" t="n"/>
+      <c r="AMJ26" s="75" t="n"/>
     </row>
     <row r="27" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B27" s="62">
@@ -1997,12 +2000,12 @@
       <c r="O27" s="68" t="n"/>
       <c r="P27" s="61" t="n"/>
       <c r="Q27" s="61" t="n"/>
-      <c r="AME27" s="42" t="n"/>
-      <c r="AMF27" s="42" t="n"/>
-      <c r="AMG27" s="42" t="n"/>
-      <c r="AMH27" s="42" t="n"/>
-      <c r="AMI27" s="42" t="n"/>
-      <c r="AMJ27" s="42" t="n"/>
+      <c r="AME27" s="75" t="n"/>
+      <c r="AMF27" s="75" t="n"/>
+      <c r="AMG27" s="75" t="n"/>
+      <c r="AMH27" s="75" t="n"/>
+      <c r="AMI27" s="75" t="n"/>
+      <c r="AMJ27" s="75" t="n"/>
     </row>
     <row r="28" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B28" s="62">
@@ -2023,12 +2026,12 @@
       <c r="O28" s="68" t="n"/>
       <c r="P28" s="61" t="n"/>
       <c r="Q28" s="61" t="n"/>
-      <c r="AME28" s="42" t="n"/>
-      <c r="AMF28" s="42" t="n"/>
-      <c r="AMG28" s="42" t="n"/>
-      <c r="AMH28" s="42" t="n"/>
-      <c r="AMI28" s="42" t="n"/>
-      <c r="AMJ28" s="42" t="n"/>
+      <c r="AME28" s="75" t="n"/>
+      <c r="AMF28" s="75" t="n"/>
+      <c r="AMG28" s="75" t="n"/>
+      <c r="AMH28" s="75" t="n"/>
+      <c r="AMI28" s="75" t="n"/>
+      <c r="AMJ28" s="75" t="n"/>
     </row>
     <row r="29" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B29" s="62">
@@ -2049,12 +2052,12 @@
       <c r="O29" s="68" t="n"/>
       <c r="P29" s="61" t="n"/>
       <c r="Q29" s="61" t="n"/>
-      <c r="AME29" s="42" t="n"/>
-      <c r="AMF29" s="42" t="n"/>
-      <c r="AMG29" s="42" t="n"/>
-      <c r="AMH29" s="42" t="n"/>
-      <c r="AMI29" s="42" t="n"/>
-      <c r="AMJ29" s="42" t="n"/>
+      <c r="AME29" s="75" t="n"/>
+      <c r="AMF29" s="75" t="n"/>
+      <c r="AMG29" s="75" t="n"/>
+      <c r="AMH29" s="75" t="n"/>
+      <c r="AMI29" s="75" t="n"/>
+      <c r="AMJ29" s="75" t="n"/>
     </row>
     <row r="30" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B30" s="62">
@@ -2075,12 +2078,12 @@
       <c r="O30" s="68" t="n"/>
       <c r="P30" s="61" t="n"/>
       <c r="Q30" s="61" t="n"/>
-      <c r="AME30" s="42" t="n"/>
-      <c r="AMF30" s="42" t="n"/>
-      <c r="AMG30" s="42" t="n"/>
-      <c r="AMH30" s="42" t="n"/>
-      <c r="AMI30" s="42" t="n"/>
-      <c r="AMJ30" s="42" t="n"/>
+      <c r="AME30" s="75" t="n"/>
+      <c r="AMF30" s="75" t="n"/>
+      <c r="AMG30" s="75" t="n"/>
+      <c r="AMH30" s="75" t="n"/>
+      <c r="AMI30" s="75" t="n"/>
+      <c r="AMJ30" s="75" t="n"/>
     </row>
     <row r="31" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B31" s="62">
@@ -2101,12 +2104,12 @@
       <c r="O31" s="68" t="n"/>
       <c r="P31" s="61" t="n"/>
       <c r="Q31" s="61" t="n"/>
-      <c r="AME31" s="42" t="n"/>
-      <c r="AMF31" s="42" t="n"/>
-      <c r="AMG31" s="42" t="n"/>
-      <c r="AMH31" s="42" t="n"/>
-      <c r="AMI31" s="42" t="n"/>
-      <c r="AMJ31" s="42" t="n"/>
+      <c r="AME31" s="75" t="n"/>
+      <c r="AMF31" s="75" t="n"/>
+      <c r="AMG31" s="75" t="n"/>
+      <c r="AMH31" s="75" t="n"/>
+      <c r="AMI31" s="75" t="n"/>
+      <c r="AMJ31" s="75" t="n"/>
     </row>
     <row r="32" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B32" s="62">
@@ -2127,12 +2130,12 @@
       <c r="O32" s="68" t="n"/>
       <c r="P32" s="61" t="n"/>
       <c r="Q32" s="61" t="n"/>
-      <c r="AME32" s="42" t="n"/>
-      <c r="AMF32" s="42" t="n"/>
-      <c r="AMG32" s="42" t="n"/>
-      <c r="AMH32" s="42" t="n"/>
-      <c r="AMI32" s="42" t="n"/>
-      <c r="AMJ32" s="42" t="n"/>
+      <c r="AME32" s="75" t="n"/>
+      <c r="AMF32" s="75" t="n"/>
+      <c r="AMG32" s="75" t="n"/>
+      <c r="AMH32" s="75" t="n"/>
+      <c r="AMI32" s="75" t="n"/>
+      <c r="AMJ32" s="75" t="n"/>
     </row>
     <row r="33" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B33" s="62">
@@ -2153,12 +2156,12 @@
       <c r="O33" s="68" t="n"/>
       <c r="P33" s="61" t="n"/>
       <c r="Q33" s="61" t="n"/>
-      <c r="AME33" s="42" t="n"/>
-      <c r="AMF33" s="42" t="n"/>
-      <c r="AMG33" s="42" t="n"/>
-      <c r="AMH33" s="42" t="n"/>
-      <c r="AMI33" s="42" t="n"/>
-      <c r="AMJ33" s="42" t="n"/>
+      <c r="AME33" s="75" t="n"/>
+      <c r="AMF33" s="75" t="n"/>
+      <c r="AMG33" s="75" t="n"/>
+      <c r="AMH33" s="75" t="n"/>
+      <c r="AMI33" s="75" t="n"/>
+      <c r="AMJ33" s="75" t="n"/>
     </row>
     <row r="34" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B34" s="62">
@@ -2179,12 +2182,12 @@
       <c r="O34" s="68" t="n"/>
       <c r="P34" s="61" t="n"/>
       <c r="Q34" s="61" t="n"/>
-      <c r="AME34" s="42" t="n"/>
-      <c r="AMF34" s="42" t="n"/>
-      <c r="AMG34" s="42" t="n"/>
-      <c r="AMH34" s="42" t="n"/>
-      <c r="AMI34" s="42" t="n"/>
-      <c r="AMJ34" s="42" t="n"/>
+      <c r="AME34" s="75" t="n"/>
+      <c r="AMF34" s="75" t="n"/>
+      <c r="AMG34" s="75" t="n"/>
+      <c r="AMH34" s="75" t="n"/>
+      <c r="AMI34" s="75" t="n"/>
+      <c r="AMJ34" s="75" t="n"/>
     </row>
     <row r="35" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B35" s="62">
@@ -2205,12 +2208,12 @@
       <c r="O35" s="68" t="n"/>
       <c r="P35" s="61" t="n"/>
       <c r="Q35" s="61" t="n"/>
-      <c r="AME35" s="42" t="n"/>
-      <c r="AMF35" s="42" t="n"/>
-      <c r="AMG35" s="42" t="n"/>
-      <c r="AMH35" s="42" t="n"/>
-      <c r="AMI35" s="42" t="n"/>
-      <c r="AMJ35" s="42" t="n"/>
+      <c r="AME35" s="75" t="n"/>
+      <c r="AMF35" s="75" t="n"/>
+      <c r="AMG35" s="75" t="n"/>
+      <c r="AMH35" s="75" t="n"/>
+      <c r="AMI35" s="75" t="n"/>
+      <c r="AMJ35" s="75" t="n"/>
     </row>
     <row r="36" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B36" s="62">
@@ -2231,12 +2234,12 @@
       <c r="O36" s="68" t="n"/>
       <c r="P36" s="61" t="n"/>
       <c r="Q36" s="61" t="n"/>
-      <c r="AME36" s="42" t="n"/>
-      <c r="AMF36" s="42" t="n"/>
-      <c r="AMG36" s="42" t="n"/>
-      <c r="AMH36" s="42" t="n"/>
-      <c r="AMI36" s="42" t="n"/>
-      <c r="AMJ36" s="42" t="n"/>
+      <c r="AME36" s="75" t="n"/>
+      <c r="AMF36" s="75" t="n"/>
+      <c r="AMG36" s="75" t="n"/>
+      <c r="AMH36" s="75" t="n"/>
+      <c r="AMI36" s="75" t="n"/>
+      <c r="AMJ36" s="75" t="n"/>
     </row>
     <row r="37" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B37" s="62">
@@ -2257,12 +2260,12 @@
       <c r="O37" s="68" t="n"/>
       <c r="P37" s="61" t="n"/>
       <c r="Q37" s="61" t="n"/>
-      <c r="AME37" s="42" t="n"/>
-      <c r="AMF37" s="42" t="n"/>
-      <c r="AMG37" s="42" t="n"/>
-      <c r="AMH37" s="42" t="n"/>
-      <c r="AMI37" s="42" t="n"/>
-      <c r="AMJ37" s="42" t="n"/>
+      <c r="AME37" s="75" t="n"/>
+      <c r="AMF37" s="75" t="n"/>
+      <c r="AMG37" s="75" t="n"/>
+      <c r="AMH37" s="75" t="n"/>
+      <c r="AMI37" s="75" t="n"/>
+      <c r="AMJ37" s="75" t="n"/>
     </row>
     <row r="38" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B38" s="62">
@@ -2283,12 +2286,12 @@
       <c r="O38" s="68" t="n"/>
       <c r="P38" s="61" t="n"/>
       <c r="Q38" s="61" t="n"/>
-      <c r="AME38" s="42" t="n"/>
-      <c r="AMF38" s="42" t="n"/>
-      <c r="AMG38" s="42" t="n"/>
-      <c r="AMH38" s="42" t="n"/>
-      <c r="AMI38" s="42" t="n"/>
-      <c r="AMJ38" s="42" t="n"/>
+      <c r="AME38" s="75" t="n"/>
+      <c r="AMF38" s="75" t="n"/>
+      <c r="AMG38" s="75" t="n"/>
+      <c r="AMH38" s="75" t="n"/>
+      <c r="AMI38" s="75" t="n"/>
+      <c r="AMJ38" s="75" t="n"/>
     </row>
     <row r="39" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B39" s="62">
@@ -2309,12 +2312,12 @@
       <c r="O39" s="68" t="n"/>
       <c r="P39" s="61" t="n"/>
       <c r="Q39" s="61" t="n"/>
-      <c r="AME39" s="42" t="n"/>
-      <c r="AMF39" s="42" t="n"/>
-      <c r="AMG39" s="42" t="n"/>
-      <c r="AMH39" s="42" t="n"/>
-      <c r="AMI39" s="42" t="n"/>
-      <c r="AMJ39" s="42" t="n"/>
+      <c r="AME39" s="75" t="n"/>
+      <c r="AMF39" s="75" t="n"/>
+      <c r="AMG39" s="75" t="n"/>
+      <c r="AMH39" s="75" t="n"/>
+      <c r="AMI39" s="75" t="n"/>
+      <c r="AMJ39" s="75" t="n"/>
     </row>
     <row r="40" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B40" s="62">
@@ -2335,12 +2338,12 @@
       <c r="O40" s="68" t="n"/>
       <c r="P40" s="61" t="n"/>
       <c r="Q40" s="61" t="n"/>
-      <c r="AME40" s="42" t="n"/>
-      <c r="AMF40" s="42" t="n"/>
-      <c r="AMG40" s="42" t="n"/>
-      <c r="AMH40" s="42" t="n"/>
-      <c r="AMI40" s="42" t="n"/>
-      <c r="AMJ40" s="42" t="n"/>
+      <c r="AME40" s="75" t="n"/>
+      <c r="AMF40" s="75" t="n"/>
+      <c r="AMG40" s="75" t="n"/>
+      <c r="AMH40" s="75" t="n"/>
+      <c r="AMI40" s="75" t="n"/>
+      <c r="AMJ40" s="75" t="n"/>
     </row>
     <row r="41" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B41" s="62">
@@ -2361,12 +2364,12 @@
       <c r="O41" s="68" t="n"/>
       <c r="P41" s="61" t="n"/>
       <c r="Q41" s="61" t="n"/>
-      <c r="AME41" s="42" t="n"/>
-      <c r="AMF41" s="42" t="n"/>
-      <c r="AMG41" s="42" t="n"/>
-      <c r="AMH41" s="42" t="n"/>
-      <c r="AMI41" s="42" t="n"/>
-      <c r="AMJ41" s="42" t="n"/>
+      <c r="AME41" s="75" t="n"/>
+      <c r="AMF41" s="75" t="n"/>
+      <c r="AMG41" s="75" t="n"/>
+      <c r="AMH41" s="75" t="n"/>
+      <c r="AMI41" s="75" t="n"/>
+      <c r="AMJ41" s="75" t="n"/>
     </row>
     <row r="42" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B42" s="62">
@@ -2387,12 +2390,12 @@
       <c r="O42" s="68" t="n"/>
       <c r="P42" s="61" t="n"/>
       <c r="Q42" s="61" t="n"/>
-      <c r="AME42" s="42" t="n"/>
-      <c r="AMF42" s="42" t="n"/>
-      <c r="AMG42" s="42" t="n"/>
-      <c r="AMH42" s="42" t="n"/>
-      <c r="AMI42" s="42" t="n"/>
-      <c r="AMJ42" s="42" t="n"/>
+      <c r="AME42" s="75" t="n"/>
+      <c r="AMF42" s="75" t="n"/>
+      <c r="AMG42" s="75" t="n"/>
+      <c r="AMH42" s="75" t="n"/>
+      <c r="AMI42" s="75" t="n"/>
+      <c r="AMJ42" s="75" t="n"/>
     </row>
     <row r="43" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B43" s="62">
@@ -2413,12 +2416,12 @@
       <c r="O43" s="68" t="n"/>
       <c r="P43" s="61" t="n"/>
       <c r="Q43" s="61" t="n"/>
-      <c r="AME43" s="42" t="n"/>
-      <c r="AMF43" s="42" t="n"/>
-      <c r="AMG43" s="42" t="n"/>
-      <c r="AMH43" s="42" t="n"/>
-      <c r="AMI43" s="42" t="n"/>
-      <c r="AMJ43" s="42" t="n"/>
+      <c r="AME43" s="75" t="n"/>
+      <c r="AMF43" s="75" t="n"/>
+      <c r="AMG43" s="75" t="n"/>
+      <c r="AMH43" s="75" t="n"/>
+      <c r="AMI43" s="75" t="n"/>
+      <c r="AMJ43" s="75" t="n"/>
     </row>
     <row r="44" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B44" s="62">
@@ -2439,12 +2442,12 @@
       <c r="O44" s="68" t="n"/>
       <c r="P44" s="61" t="n"/>
       <c r="Q44" s="61" t="n"/>
-      <c r="AME44" s="42" t="n"/>
-      <c r="AMF44" s="42" t="n"/>
-      <c r="AMG44" s="42" t="n"/>
-      <c r="AMH44" s="42" t="n"/>
-      <c r="AMI44" s="42" t="n"/>
-      <c r="AMJ44" s="42" t="n"/>
+      <c r="AME44" s="75" t="n"/>
+      <c r="AMF44" s="75" t="n"/>
+      <c r="AMG44" s="75" t="n"/>
+      <c r="AMH44" s="75" t="n"/>
+      <c r="AMI44" s="75" t="n"/>
+      <c r="AMJ44" s="75" t="n"/>
     </row>
     <row r="45" ht="17.25" customFormat="1" customHeight="1" s="50">
       <c r="B45" s="62">
@@ -2465,12 +2468,12 @@
       <c r="O45" s="68" t="n"/>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="61" t="n"/>
-      <c r="AME45" s="42" t="n"/>
-      <c r="AMF45" s="42" t="n"/>
-      <c r="AMG45" s="42" t="n"/>
-      <c r="AMH45" s="42" t="n"/>
-      <c r="AMI45" s="42" t="n"/>
-      <c r="AMJ45" s="42" t="n"/>
+      <c r="AME45" s="75" t="n"/>
+      <c r="AMF45" s="75" t="n"/>
+      <c r="AMG45" s="75" t="n"/>
+      <c r="AMH45" s="75" t="n"/>
+      <c r="AMI45" s="75" t="n"/>
+      <c r="AMJ45" s="75" t="n"/>
     </row>
     <row r="46" ht="12.75" customHeight="1" s="69">
       <c r="F46" s="65" t="n"/>
@@ -13965,18 +13968,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I246"/>
+  <dimension ref="A1:R1700"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.43359375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="24.67" customWidth="1" style="42" min="1" max="1"/>
-    <col width="49.34" customWidth="1" style="42" min="2" max="2"/>
-    <col width="37.18" customWidth="1" style="42" min="4" max="4"/>
-    <col width="24.58" customWidth="1" style="42" min="5" max="5"/>
-    <col width="27.73" customWidth="1" style="42" min="6" max="6"/>
-    <col width="19.5" customWidth="1" style="42" min="7" max="7"/>
-    <col width="71.98" customWidth="1" style="42" min="8" max="8"/>
-    <col width="34.52" customWidth="1" style="42" min="9" max="9"/>
-    <col width="11.52" customWidth="1" style="42" min="1024" max="1024"/>
+    <col width="24.67" customWidth="1" style="75" min="1" max="1"/>
+    <col width="49.34" customWidth="1" style="75" min="2" max="2"/>
+    <col width="37.18" customWidth="1" style="75" min="4" max="4"/>
+    <col width="24.58" customWidth="1" style="75" min="5" max="5"/>
+    <col width="27.73" customWidth="1" style="75" min="6" max="6"/>
+    <col width="19.5" customWidth="1" style="75" min="7" max="7"/>
+    <col width="71.98" customWidth="1" style="75" min="8" max="8"/>
+    <col width="34.52" customWidth="1" style="75" min="9" max="9"/>
+    <col width="20" customWidth="1" style="69" min="18" max="18"/>
+    <col width="11.52" customWidth="1" style="75" min="1024" max="1024"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" s="69">
@@ -14016,24 +14020,29 @@
           <t>Тип разрешительной документации</t>
         </is>
       </c>
+      <c r="R1" s="75" t="inlineStr">
+        <is>
+          <t>Вес в граммах</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" s="69">
-      <c r="D2" s="42" t="inlineStr">
+      <c r="D2" s="75" t="inlineStr">
         <is>
           <t>АРАФАТКА</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="75" t="inlineStr">
         <is>
           <t>БЕЖЕВЫЙ</t>
         </is>
       </c>
-      <c r="F2" s="42" t="inlineStr">
+      <c r="F2" s="75" t="inlineStr">
         <is>
           <t>Жен.</t>
         </is>
       </c>
-      <c r="G2" s="42" t="inlineStr">
+      <c r="G2" s="75" t="inlineStr">
         <is>
           <t>РОССИЯ</t>
         </is>
@@ -14060,22 +14069,22 @@
           <t>Значение атрибута</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="75" t="inlineStr">
         <is>
           <t>БАБОЧКА</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>БЕЖЕВЫЙ МЕЛАНЖ</t>
         </is>
       </c>
-      <c r="F3" s="42" t="inlineStr">
+      <c r="F3" s="75" t="inlineStr">
         <is>
           <t>Муж.</t>
         </is>
       </c>
-      <c r="G3" s="42" t="inlineStr">
+      <c r="G3" s="75" t="inlineStr">
         <is>
           <t>МЕЖДУНАРОДНЫЙ</t>
         </is>
@@ -14092,22 +14101,22 @@
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1" s="69">
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="75" t="inlineStr">
         <is>
           <t>БАНТ</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="75" t="inlineStr">
         <is>
           <t>БЕЖЕВЫЙ/ЗЕЛЕНЫЙ</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="75" t="inlineStr">
         <is>
           <t>Унисекс</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="75" t="inlineStr">
         <is>
           <t>ДЛИНА-ШИРИНА</t>
         </is>
@@ -14119,17 +14128,17 @@
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1" s="69">
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="75" t="inlineStr">
         <is>
           <t>БАСКА</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="75" t="inlineStr">
         <is>
           <t>БЕЖЕВЫЙ/СИНИЙ</t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="75" t="inlineStr">
         <is>
           <t>Детск.</t>
         </is>
@@ -14140,13 +14149,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="69">
-      <c r="D6" s="42" t="inlineStr">
+    <row r="6" ht="160" customHeight="1" s="69">
+      <c r="D6" s="75" t="inlineStr">
         <is>
           <t>БАФФ</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="75" t="inlineStr">
         <is>
           <t>БЕЛО-ЗЕЛЕНЫЙ</t>
         </is>
@@ -14156,14 +14165,19 @@
           <t>АЛАНДСКИЕ ОСТРОВА</t>
         </is>
       </c>
+      <c r="R6" s="86" t="inlineStr">
+        <is>
+          <t>Обязательное поле: общий вес позиции, целое число больше 0. Просьба указать актуальный вес товара в ГРАММАХ для отчетности РОСПРИРОДНАДЗОР.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="13.5" customHeight="1" s="69">
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="75" t="inlineStr">
         <is>
           <t>ВОРОТНИК</t>
         </is>
       </c>
-      <c r="E7" s="42" t="inlineStr">
+      <c r="E7" s="75" t="inlineStr">
         <is>
           <t>БЕЛО-КОРИЧНЕВЫЙ</t>
         </is>
@@ -14175,12 +14189,12 @@
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1" s="69">
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="75" t="inlineStr">
         <is>
           <t>ВОРОТНИК-ГАЛСТУК</t>
         </is>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="75" t="inlineStr">
         <is>
           <t>БЕЛО-РОЗОВЫЙ</t>
         </is>
@@ -14192,12 +14206,12 @@
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1" s="69">
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="75" t="inlineStr">
         <is>
           <t>ВУАЛЬ</t>
         </is>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="75" t="inlineStr">
         <is>
           <t>БЕЛЫЙ</t>
         </is>
@@ -14209,12 +14223,12 @@
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1" s="69">
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="75" t="inlineStr">
         <is>
           <t>ГАЛСТУК</t>
         </is>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="75" t="inlineStr">
         <is>
           <t>БЕЛЫЙ/БЕЖЕВЫЙ</t>
         </is>
@@ -14226,12 +14240,12 @@
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1" s="69">
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="75" t="inlineStr">
         <is>
           <t>ГАЛСТУК-БАБОЧКА</t>
         </is>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="75" t="inlineStr">
         <is>
           <t>БЕЛЫЙ/СЕРЫЙ</t>
         </is>
@@ -14243,12 +14257,12 @@
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1" s="69">
-      <c r="D12" s="42" t="inlineStr">
+      <c r="D12" s="75" t="inlineStr">
         <is>
           <t>ГЕЙТОР</t>
         </is>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="75" t="inlineStr">
         <is>
           <t>БЕЛЫЙ/СИНИЙ</t>
         </is>
@@ -14260,12 +14274,12 @@
       </c>
     </row>
     <row r="13" ht="13.5" customHeight="1" s="69">
-      <c r="D13" s="42" t="inlineStr">
+      <c r="D13" s="75" t="inlineStr">
         <is>
           <t>ГОРЖЕТКА</t>
         </is>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E13" s="75" t="inlineStr">
         <is>
           <t>БИРЮЗОВЫЙ</t>
         </is>
@@ -14277,12 +14291,12 @@
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="69">
-      <c r="D14" s="42" t="inlineStr">
+      <c r="D14" s="75" t="inlineStr">
         <is>
           <t>ГЮЙС</t>
         </is>
       </c>
-      <c r="E14" s="42" t="inlineStr">
+      <c r="E14" s="75" t="inlineStr">
         <is>
           <t>БОРДОВО-РЫЖИЙ</t>
         </is>
@@ -14294,12 +14308,12 @@
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="69">
-      <c r="D15" s="42" t="inlineStr">
+      <c r="D15" s="75" t="inlineStr">
         <is>
           <t>ЖАБО</t>
         </is>
       </c>
-      <c r="E15" s="42" t="inlineStr">
+      <c r="E15" s="75" t="inlineStr">
         <is>
           <t>БОРДОВЫЙ</t>
         </is>
@@ -14311,12 +14325,12 @@
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="69">
-      <c r="D16" s="42" t="inlineStr">
+      <c r="D16" s="75" t="inlineStr">
         <is>
           <t>КАШНЕ</t>
         </is>
       </c>
-      <c r="E16" s="42" t="inlineStr">
+      <c r="E16" s="75" t="inlineStr">
         <is>
           <t>БРОНЗОВЫЙ</t>
         </is>
@@ -14328,12 +14342,12 @@
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1" s="69">
-      <c r="D17" s="42" t="inlineStr">
+      <c r="D17" s="75" t="inlineStr">
         <is>
           <t>МАНИШКА</t>
         </is>
       </c>
-      <c r="E17" s="42" t="inlineStr">
+      <c r="E17" s="75" t="inlineStr">
         <is>
           <t>ВАНИЛЬ</t>
         </is>
@@ -14345,12 +14359,12 @@
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1" s="69">
-      <c r="D18" s="42" t="inlineStr">
+      <c r="D18" s="75" t="inlineStr">
         <is>
           <t>МАНТИЛЬЯ</t>
         </is>
       </c>
-      <c r="E18" s="42" t="inlineStr">
+      <c r="E18" s="75" t="inlineStr">
         <is>
           <t>ВИШНЯ</t>
         </is>
@@ -14362,12 +14376,12 @@
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1" s="69">
-      <c r="D19" s="42" t="inlineStr">
+      <c r="D19" s="75" t="inlineStr">
         <is>
           <t>МАСКА</t>
         </is>
       </c>
-      <c r="E19" s="42" t="inlineStr">
+      <c r="E19" s="75" t="inlineStr">
         <is>
           <t>ГОЛУБОЙ</t>
         </is>
@@ -14379,12 +14393,12 @@
       </c>
     </row>
     <row r="20" ht="13.5" customHeight="1" s="69">
-      <c r="D20" s="42" t="inlineStr">
+      <c r="D20" s="75" t="inlineStr">
         <is>
           <t>НАГРУДНИК</t>
         </is>
       </c>
-      <c r="E20" s="42" t="inlineStr">
+      <c r="E20" s="75" t="inlineStr">
         <is>
           <t>ГОРЧИЧНЫЙ</t>
         </is>
@@ -14396,12 +14410,12 @@
       </c>
     </row>
     <row r="21" ht="13.5" customHeight="1" s="69">
-      <c r="D21" s="42" t="inlineStr">
+      <c r="D21" s="75" t="inlineStr">
         <is>
           <t>НАМАЗНИК</t>
         </is>
       </c>
-      <c r="E21" s="42" t="inlineStr">
+      <c r="E21" s="75" t="inlineStr">
         <is>
           <t>ГРАФИТОВЫЙ</t>
         </is>
@@ -14413,12 +14427,12 @@
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1" s="69">
-      <c r="D22" s="42" t="inlineStr">
+      <c r="D22" s="75" t="inlineStr">
         <is>
           <t>ПАЛАНТИН</t>
         </is>
       </c>
-      <c r="E22" s="42" t="inlineStr">
+      <c r="E22" s="75" t="inlineStr">
         <is>
           <t>ЖЁЛТЫЙ</t>
         </is>
@@ -14430,12 +14444,12 @@
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1" s="69">
-      <c r="D23" s="42" t="inlineStr">
+      <c r="D23" s="75" t="inlineStr">
         <is>
           <t>ПАРЕО</t>
         </is>
       </c>
-      <c r="E23" s="42" t="inlineStr">
+      <c r="E23" s="75" t="inlineStr">
         <is>
           <t>ЗЕЛЁНЫЙ</t>
         </is>
@@ -14447,12 +14461,12 @@
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="69">
-      <c r="D24" s="42" t="inlineStr">
+      <c r="D24" s="75" t="inlineStr">
         <is>
           <t>ПАШЕ</t>
         </is>
       </c>
-      <c r="E24" s="42" t="inlineStr">
+      <c r="E24" s="75" t="inlineStr">
         <is>
           <t>ЗОЛОТИСТЫЙ</t>
         </is>
@@ -14464,12 +14478,12 @@
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1" s="69">
-      <c r="D25" s="42" t="inlineStr">
+      <c r="D25" s="75" t="inlineStr">
         <is>
           <t>ПЕЛЕРИНА</t>
         </is>
       </c>
-      <c r="E25" s="42" t="inlineStr">
+      <c r="E25" s="75" t="inlineStr">
         <is>
           <t>ЗОЛОТОЙ</t>
         </is>
@@ -14481,12 +14495,12 @@
       </c>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="69">
-      <c r="D26" s="42" t="inlineStr">
+      <c r="D26" s="75" t="inlineStr">
         <is>
           <t>ПЛАТОК ГОЛОВНОЙ</t>
         </is>
       </c>
-      <c r="E26" s="42" t="inlineStr">
+      <c r="E26" s="75" t="inlineStr">
         <is>
           <t>ИЗУМРУДНЫЙ</t>
         </is>
@@ -14498,12 +14512,12 @@
       </c>
     </row>
     <row r="27" ht="13.5" customHeight="1" s="69">
-      <c r="D27" s="42" t="inlineStr">
+      <c r="D27" s="75" t="inlineStr">
         <is>
           <t>ПЛАТОК НОСОВОЙ</t>
         </is>
       </c>
-      <c r="E27" s="42" t="inlineStr">
+      <c r="E27" s="75" t="inlineStr">
         <is>
           <t>КАПУЧИНО</t>
         </is>
@@ -14515,12 +14529,12 @@
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="69">
-      <c r="D28" s="42" t="inlineStr">
+      <c r="D28" s="75" t="inlineStr">
         <is>
           <t>ПЛАТОК ШЕЙНЫЙ</t>
         </is>
       </c>
-      <c r="E28" s="42" t="inlineStr">
+      <c r="E28" s="75" t="inlineStr">
         <is>
           <t>КИРПИЧНЫЙ</t>
         </is>
@@ -14532,12 +14546,12 @@
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1" s="69">
-      <c r="D29" s="42" t="inlineStr">
+      <c r="D29" s="75" t="inlineStr">
         <is>
           <t>ПОВЯЗКА НА ГОЛОВУ</t>
         </is>
       </c>
-      <c r="E29" s="42" t="inlineStr">
+      <c r="E29" s="75" t="inlineStr">
         <is>
           <t>КОРАЛЛОВЫЙ</t>
         </is>
@@ -14549,12 +14563,12 @@
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" s="69">
-      <c r="D30" s="42" t="inlineStr">
+      <c r="D30" s="75" t="inlineStr">
         <is>
           <t>ПОДТЯЖКИ</t>
         </is>
       </c>
-      <c r="E30" s="42" t="inlineStr">
+      <c r="E30" s="75" t="inlineStr">
         <is>
           <t>КОРИЧНЕВЫЙ</t>
         </is>
@@ -14566,12 +14580,12 @@
       </c>
     </row>
     <row r="31" ht="13.5" customHeight="1" s="69">
-      <c r="D31" s="42" t="inlineStr">
+      <c r="D31" s="75" t="inlineStr">
         <is>
           <t>ПОРТУПЕЯ</t>
         </is>
       </c>
-      <c r="E31" s="42" t="inlineStr">
+      <c r="E31" s="75" t="inlineStr">
         <is>
           <t>КОФЕЙНЫЙ</t>
         </is>
@@ -14583,12 +14597,12 @@
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1" s="69">
-      <c r="D32" s="42" t="inlineStr">
+      <c r="D32" s="75" t="inlineStr">
         <is>
           <t>ПОЯС</t>
         </is>
       </c>
-      <c r="E32" s="42" t="inlineStr">
+      <c r="E32" s="75" t="inlineStr">
         <is>
           <t>КРАСНО-КОРИЧНЕВЫЙ</t>
         </is>
@@ -14600,12 +14614,12 @@
       </c>
     </row>
     <row r="33" ht="13.5" customHeight="1" s="69">
-      <c r="D33" s="42" t="inlineStr">
+      <c r="D33" s="75" t="inlineStr">
         <is>
           <t>РЕМЕНЬ</t>
         </is>
       </c>
-      <c r="E33" s="42" t="inlineStr">
+      <c r="E33" s="75" t="inlineStr">
         <is>
           <t>КРАСНЫЙ</t>
         </is>
@@ -14617,12 +14631,12 @@
       </c>
     </row>
     <row r="34" ht="13.5" customHeight="1" s="69">
-      <c r="D34" s="42" t="inlineStr">
+      <c r="D34" s="75" t="inlineStr">
         <is>
           <t>РУКАВА</t>
         </is>
       </c>
-      <c r="E34" s="42" t="inlineStr">
+      <c r="E34" s="75" t="inlineStr">
         <is>
           <t>КРЕМОВЫЙ</t>
         </is>
@@ -14634,12 +14648,12 @@
       </c>
     </row>
     <row r="35" ht="13.5" customHeight="1" s="69">
-      <c r="D35" s="42" t="inlineStr">
+      <c r="D35" s="75" t="inlineStr">
         <is>
           <t>ХИДЖАБ</t>
         </is>
       </c>
-      <c r="E35" s="42" t="inlineStr">
+      <c r="E35" s="75" t="inlineStr">
         <is>
           <t>ЛАВАНДОВЫЙ</t>
         </is>
@@ -14651,12 +14665,12 @@
       </c>
     </row>
     <row r="36" ht="13.5" customHeight="1" s="69">
-      <c r="D36" s="42" t="inlineStr">
+      <c r="D36" s="75" t="inlineStr">
         <is>
           <t>ШАЛЬ</t>
         </is>
       </c>
-      <c r="E36" s="42" t="inlineStr">
+      <c r="E36" s="75" t="inlineStr">
         <is>
           <t>ЛАЙМ</t>
         </is>
@@ -14668,12 +14682,12 @@
       </c>
     </row>
     <row r="37" ht="13.5" customHeight="1" s="69">
-      <c r="D37" s="42" t="inlineStr">
+      <c r="D37" s="75" t="inlineStr">
         <is>
           <t>ШАРФ-СНУД</t>
         </is>
       </c>
-      <c r="E37" s="42" t="inlineStr">
+      <c r="E37" s="75" t="inlineStr">
         <is>
           <t>ЛЕОПАРД</t>
         </is>
@@ -14690,7 +14704,7 @@
           <t>ГАЛСТУК-БАНТ</t>
         </is>
       </c>
-      <c r="E38" s="42" t="inlineStr">
+      <c r="E38" s="75" t="inlineStr">
         <is>
           <t>МАЛИНОВЫЙ</t>
         </is>
@@ -14702,7 +14716,7 @@
       </c>
     </row>
     <row r="39" ht="13.5" customHeight="1" s="69">
-      <c r="E39" s="42" t="inlineStr">
+      <c r="E39" s="75" t="inlineStr">
         <is>
           <t>МЕДНЫЙ</t>
         </is>
@@ -14714,7 +14728,7 @@
       </c>
     </row>
     <row r="40" ht="13.5" customHeight="1" s="69">
-      <c r="E40" s="42" t="inlineStr">
+      <c r="E40" s="75" t="inlineStr">
         <is>
           <t>МОЛОЧНЫЙ</t>
         </is>
@@ -14726,7 +14740,7 @@
       </c>
     </row>
     <row r="41" ht="13.5" customHeight="1" s="69">
-      <c r="E41" s="42" t="inlineStr">
+      <c r="E41" s="75" t="inlineStr">
         <is>
           <t>МЯТНЫЙ</t>
         </is>
@@ -14738,7 +14752,7 @@
       </c>
     </row>
     <row r="42" ht="13.5" customHeight="1" s="69">
-      <c r="E42" s="42" t="inlineStr">
+      <c r="E42" s="75" t="inlineStr">
         <is>
           <t>НАТУРАЛЬНЫЙ</t>
         </is>
@@ -14750,7 +14764,7 @@
       </c>
     </row>
     <row r="43" ht="13.5" customHeight="1" s="69">
-      <c r="E43" s="42" t="inlineStr">
+      <c r="E43" s="75" t="inlineStr">
         <is>
           <t>НИКЕЛЬ</t>
         </is>
@@ -14762,7 +14776,7 @@
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1" s="69">
-      <c r="E44" s="42" t="inlineStr">
+      <c r="E44" s="75" t="inlineStr">
         <is>
           <t>ОЛИВКОВО-БЕЛЫЙ</t>
         </is>
@@ -14774,7 +14788,7 @@
       </c>
     </row>
     <row r="45" ht="13.5" customHeight="1" s="69">
-      <c r="E45" s="42" t="inlineStr">
+      <c r="E45" s="75" t="inlineStr">
         <is>
           <t>ОЛИВКОВЫЙ</t>
         </is>
@@ -14786,7 +14800,7 @@
       </c>
     </row>
     <row r="46" ht="13.5" customHeight="1" s="69">
-      <c r="E46" s="42" t="inlineStr">
+      <c r="E46" s="75" t="inlineStr">
         <is>
           <t>ОРАНЖЕВЫЙ</t>
         </is>
@@ -14798,7 +14812,7 @@
       </c>
     </row>
     <row r="47" ht="13.5" customHeight="1" s="69">
-      <c r="E47" s="42" t="inlineStr">
+      <c r="E47" s="75" t="inlineStr">
         <is>
           <t>ПЕРЛАМУТРОВЫЙ</t>
         </is>
@@ -14810,7 +14824,7 @@
       </c>
     </row>
     <row r="48" ht="13.5" customHeight="1" s="69">
-      <c r="E48" s="42" t="inlineStr">
+      <c r="E48" s="75" t="inlineStr">
         <is>
           <t>ПЕРСИКОВЫЙ</t>
         </is>
@@ -14822,7 +14836,7 @@
       </c>
     </row>
     <row r="49" ht="13.5" customHeight="1" s="69">
-      <c r="E49" s="42" t="inlineStr">
+      <c r="E49" s="75" t="inlineStr">
         <is>
           <t>ПЕСОЧНЫЙ</t>
         </is>
@@ -14834,7 +14848,7 @@
       </c>
     </row>
     <row r="50" ht="13.5" customHeight="1" s="69">
-      <c r="E50" s="42" t="inlineStr">
+      <c r="E50" s="75" t="inlineStr">
         <is>
           <t>ПРОЗРАЧНЫЙ</t>
         </is>
@@ -14846,7 +14860,7 @@
       </c>
     </row>
     <row r="51" ht="13.5" customHeight="1" s="69">
-      <c r="E51" s="42" t="inlineStr">
+      <c r="E51" s="75" t="inlineStr">
         <is>
           <t>ПУРПУРНЫЙ</t>
         </is>
@@ -14858,7 +14872,7 @@
       </c>
     </row>
     <row r="52" ht="13.5" customHeight="1" s="69">
-      <c r="E52" s="42" t="inlineStr">
+      <c r="E52" s="75" t="inlineStr">
         <is>
           <t>РАЗНОЦВЕТНЫЙ</t>
         </is>
@@ -14870,7 +14884,7 @@
       </c>
     </row>
     <row r="53" ht="13.5" customHeight="1" s="69">
-      <c r="E53" s="42" t="inlineStr">
+      <c r="E53" s="75" t="inlineStr">
         <is>
           <t>РОЗОВО-БЕЖЕВЫЙ</t>
         </is>
@@ -14882,7 +14896,7 @@
       </c>
     </row>
     <row r="54" ht="13.5" customHeight="1" s="69">
-      <c r="E54" s="42" t="inlineStr">
+      <c r="E54" s="75" t="inlineStr">
         <is>
           <t>РОЗОВЫЙ</t>
         </is>
@@ -14894,7 +14908,7 @@
       </c>
     </row>
     <row r="55" ht="13.5" customHeight="1" s="69">
-      <c r="E55" s="42" t="inlineStr">
+      <c r="E55" s="75" t="inlineStr">
         <is>
           <t>РЫЖЕ-КОРИЧНЕВЫЙ</t>
         </is>
@@ -14906,7 +14920,7 @@
       </c>
     </row>
     <row r="56" ht="13.5" customHeight="1" s="69">
-      <c r="E56" s="42" t="inlineStr">
+      <c r="E56" s="75" t="inlineStr">
         <is>
           <t>РЫЖИЙ</t>
         </is>
@@ -14918,7 +14932,7 @@
       </c>
     </row>
     <row r="57" ht="13.5" customHeight="1" s="69">
-      <c r="E57" s="42" t="inlineStr">
+      <c r="E57" s="75" t="inlineStr">
         <is>
           <t>САЛАТОВЫЙ</t>
         </is>
@@ -14930,7 +14944,7 @@
       </c>
     </row>
     <row r="58" ht="13.5" customHeight="1" s="69">
-      <c r="E58" s="42" t="inlineStr">
+      <c r="E58" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-БЕЖЕВЫЙ</t>
         </is>
@@ -14942,7 +14956,7 @@
       </c>
     </row>
     <row r="59" ht="13.5" customHeight="1" s="69">
-      <c r="E59" s="42" t="inlineStr">
+      <c r="E59" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-ЗЕЛЕНЫЙ</t>
         </is>
@@ -14954,7 +14968,7 @@
       </c>
     </row>
     <row r="60" ht="13.5" customHeight="1" s="69">
-      <c r="E60" s="42" t="inlineStr">
+      <c r="E60" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-КОРИЧНЕВЫЙ</t>
         </is>
@@ -14966,7 +14980,7 @@
       </c>
     </row>
     <row r="61" ht="13.5" customHeight="1" s="69">
-      <c r="E61" s="42" t="inlineStr">
+      <c r="E61" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-РОЗОВЫЙ</t>
         </is>
@@ -14978,7 +14992,7 @@
       </c>
     </row>
     <row r="62" ht="13.5" customHeight="1" s="69">
-      <c r="E62" s="42" t="inlineStr">
+      <c r="E62" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-СЕРЫЙ</t>
         </is>
@@ -14990,7 +15004,7 @@
       </c>
     </row>
     <row r="63" ht="13.5" customHeight="1" s="69">
-      <c r="E63" s="42" t="inlineStr">
+      <c r="E63" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-СЕРЫЙ МЕЛАНЖ</t>
         </is>
@@ -15002,7 +15016,7 @@
       </c>
     </row>
     <row r="64" ht="13.5" customHeight="1" s="69">
-      <c r="E64" s="42" t="inlineStr">
+      <c r="E64" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-СИНИЙ</t>
         </is>
@@ -15014,7 +15028,7 @@
       </c>
     </row>
     <row r="65" ht="13.5" customHeight="1" s="69">
-      <c r="E65" s="42" t="inlineStr">
+      <c r="E65" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-ФИОЛЕТОВЫЙ</t>
         </is>
@@ -15026,7 +15040,7 @@
       </c>
     </row>
     <row r="66" ht="13.5" customHeight="1" s="69">
-      <c r="E66" s="42" t="inlineStr">
+      <c r="E66" s="75" t="inlineStr">
         <is>
           <t>СЕРЕБРЯНЫЙ</t>
         </is>
@@ -15038,7 +15052,7 @@
       </c>
     </row>
     <row r="67" ht="13.5" customHeight="1" s="69">
-      <c r="E67" s="42" t="inlineStr">
+      <c r="E67" s="75" t="inlineStr">
         <is>
           <t>СЕРО-БЕЖЕВЫЙ</t>
         </is>
@@ -15050,7 +15064,7 @@
       </c>
     </row>
     <row r="68" ht="13.5" customHeight="1" s="69">
-      <c r="E68" s="42" t="inlineStr">
+      <c r="E68" s="75" t="inlineStr">
         <is>
           <t>СЕРО-ГОЛУБОЙ</t>
         </is>
@@ -15062,7 +15076,7 @@
       </c>
     </row>
     <row r="69" ht="13.5" customHeight="1" s="69">
-      <c r="E69" s="42" t="inlineStr">
+      <c r="E69" s="75" t="inlineStr">
         <is>
           <t>СЕРО-ЖЕЛТЫЙ</t>
         </is>
@@ -15074,7 +15088,7 @@
       </c>
     </row>
     <row r="70" ht="13.5" customHeight="1" s="69">
-      <c r="E70" s="42" t="inlineStr">
+      <c r="E70" s="75" t="inlineStr">
         <is>
           <t>СЕРЫЙ</t>
         </is>
@@ -15086,7 +15100,7 @@
       </c>
     </row>
     <row r="71" ht="13.5" customHeight="1" s="69">
-      <c r="E71" s="42" t="inlineStr">
+      <c r="E71" s="75" t="inlineStr">
         <is>
           <t>СЕРЫЙ МЕЛАНЖ</t>
         </is>
@@ -15098,7 +15112,7 @@
       </c>
     </row>
     <row r="72" ht="13.5" customHeight="1" s="69">
-      <c r="E72" s="42" t="inlineStr">
+      <c r="E72" s="75" t="inlineStr">
         <is>
           <t>СИНИЙ</t>
         </is>
@@ -15110,7 +15124,7 @@
       </c>
     </row>
     <row r="73" ht="13.5" customHeight="1" s="69">
-      <c r="E73" s="42" t="inlineStr">
+      <c r="E73" s="75" t="inlineStr">
         <is>
           <t>СИРЕНЕВЫЙ/ЛИЛОВЫЙ</t>
         </is>
@@ -15122,7 +15136,7 @@
       </c>
     </row>
     <row r="74" ht="13.5" customHeight="1" s="69">
-      <c r="E74" s="42" t="inlineStr">
+      <c r="E74" s="75" t="inlineStr">
         <is>
           <t>СЛИВОВЫЙ</t>
         </is>
@@ -15134,7 +15148,7 @@
       </c>
     </row>
     <row r="75" ht="13.5" customHeight="1" s="69">
-      <c r="E75" s="42" t="inlineStr">
+      <c r="E75" s="75" t="inlineStr">
         <is>
           <t>СЛОНОВАЯ КОСТЬ</t>
         </is>
@@ -15146,7 +15160,7 @@
       </c>
     </row>
     <row r="76" ht="13.5" customHeight="1" s="69">
-      <c r="E76" s="42" t="inlineStr">
+      <c r="E76" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-БЕЖЕВЫЙ</t>
         </is>
@@ -15158,7 +15172,7 @@
       </c>
     </row>
     <row r="77" ht="13.5" customHeight="1" s="69">
-      <c r="E77" s="42" t="inlineStr">
+      <c r="E77" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-ЗЕЛЕНЫЙ</t>
         </is>
@@ -15170,7 +15184,7 @@
       </c>
     </row>
     <row r="78" ht="13.5" customHeight="1" s="69">
-      <c r="E78" s="42" t="inlineStr">
+      <c r="E78" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-КОРИЧНЕВЫЙ</t>
         </is>
@@ -15182,7 +15196,7 @@
       </c>
     </row>
     <row r="79" ht="13.5" customHeight="1" s="69">
-      <c r="E79" s="42" t="inlineStr">
+      <c r="E79" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-РОЗОВЫЙ</t>
         </is>
@@ -15194,7 +15208,7 @@
       </c>
     </row>
     <row r="80" ht="13.5" customHeight="1" s="69">
-      <c r="E80" s="42" t="inlineStr">
+      <c r="E80" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-СЕРЫЙ</t>
         </is>
@@ -15206,7 +15220,7 @@
       </c>
     </row>
     <row r="81" ht="13.5" customHeight="1" s="69">
-      <c r="E81" s="42" t="inlineStr">
+      <c r="E81" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-СЕРЫЙ МЕЛАНЖ</t>
         </is>
@@ -15218,7 +15232,7 @@
       </c>
     </row>
     <row r="82" ht="13.5" customHeight="1" s="69">
-      <c r="E82" s="42" t="inlineStr">
+      <c r="E82" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-СИНИЙ</t>
         </is>
@@ -15230,7 +15244,7 @@
       </c>
     </row>
     <row r="83" ht="13.5" customHeight="1" s="69">
-      <c r="E83" s="42" t="inlineStr">
+      <c r="E83" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-ФИОЛЕТОВЫЙ</t>
         </is>
@@ -15242,7 +15256,7 @@
       </c>
     </row>
     <row r="84" ht="13.5" customHeight="1" s="69">
-      <c r="E84" s="42" t="inlineStr">
+      <c r="E84" s="75" t="inlineStr">
         <is>
           <t>ТЕРРАКОТОВЫЙ</t>
         </is>
@@ -15254,7 +15268,7 @@
       </c>
     </row>
     <row r="85" ht="13.5" customHeight="1" s="69">
-      <c r="E85" s="42" t="inlineStr">
+      <c r="E85" s="75" t="inlineStr">
         <is>
           <t>ФИОЛЕТОВЫЙ</t>
         </is>
@@ -15266,7 +15280,7 @@
       </c>
     </row>
     <row r="86" ht="13.5" customHeight="1" s="69">
-      <c r="E86" s="42" t="inlineStr">
+      <c r="E86" s="75" t="inlineStr">
         <is>
           <t>ФИСТАШКОВЫЙ</t>
         </is>
@@ -15278,7 +15292,7 @@
       </c>
     </row>
     <row r="87" ht="13.5" customHeight="1" s="69">
-      <c r="E87" s="42" t="inlineStr">
+      <c r="E87" s="75" t="inlineStr">
         <is>
           <t>ФУКСИЯ</t>
         </is>
@@ -15290,7 +15304,7 @@
       </c>
     </row>
     <row r="88" ht="13.5" customHeight="1" s="69">
-      <c r="E88" s="42" t="inlineStr">
+      <c r="E88" s="75" t="inlineStr">
         <is>
           <t>ХАКИ</t>
         </is>
@@ -15302,7 +15316,7 @@
       </c>
     </row>
     <row r="89" ht="13.5" customHeight="1" s="69">
-      <c r="E89" s="42" t="inlineStr">
+      <c r="E89" s="75" t="inlineStr">
         <is>
           <t>ХАКИ/ОЛИВКОВЫЙ</t>
         </is>
@@ -15314,7 +15328,7 @@
       </c>
     </row>
     <row r="90" ht="13.5" customHeight="1" s="69">
-      <c r="E90" s="42" t="inlineStr">
+      <c r="E90" s="75" t="inlineStr">
         <is>
           <t>ЧЕРНЫЙ</t>
         </is>
@@ -15326,7 +15340,7 @@
       </c>
     </row>
     <row r="91" ht="13.5" customHeight="1" s="69">
-      <c r="E91" s="42" t="inlineStr">
+      <c r="E91" s="75" t="inlineStr">
         <is>
           <t>ЧЕРНЫЙ/БЕЛЫЙ</t>
         </is>
@@ -15338,7 +15352,7 @@
       </c>
     </row>
     <row r="92" ht="13.5" customHeight="1" s="69">
-      <c r="E92" s="42" t="inlineStr">
+      <c r="E92" s="75" t="inlineStr">
         <is>
           <t>ЧЕРНЫЙ/ЗОЛОТИСТЫЙ</t>
         </is>
@@ -15350,7 +15364,7 @@
       </c>
     </row>
     <row r="93" ht="13.5" customHeight="1" s="69">
-      <c r="E93" s="42" t="inlineStr">
+      <c r="E93" s="75" t="inlineStr">
         <is>
           <t>ЧЕРНЫЙ/СЕРЫЙ</t>
         </is>
@@ -15362,7 +15376,7 @@
       </c>
     </row>
     <row r="94" ht="13.5" customHeight="1" s="69">
-      <c r="E94" s="42" t="inlineStr">
+      <c r="E94" s="75" t="inlineStr">
         <is>
           <t>ШОКОЛАДНЫЙ</t>
         </is>
@@ -15374,7 +15388,7 @@
       </c>
     </row>
     <row r="95" ht="13.5" customHeight="1" s="69">
-      <c r="E95" s="42" t="inlineStr">
+      <c r="E95" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-ЖЕЛТЫЙ</t>
         </is>
@@ -15386,7 +15400,7 @@
       </c>
     </row>
     <row r="96" ht="13.5" customHeight="1" s="69">
-      <c r="E96" s="42" t="inlineStr">
+      <c r="E96" s="75" t="inlineStr">
         <is>
           <t>ТЕМНО-ЖЕЛТЫЙ</t>
         </is>
@@ -15398,7 +15412,7 @@
       </c>
     </row>
     <row r="97" ht="13.5" customHeight="1" s="69">
-      <c r="E97" s="42" t="inlineStr">
+      <c r="E97" s="75" t="inlineStr">
         <is>
           <t>ЛИЛОВЫЙ</t>
         </is>
@@ -15410,7 +15424,7 @@
       </c>
     </row>
     <row r="98" ht="13.5" customHeight="1" s="69">
-      <c r="E98" s="42" t="inlineStr">
+      <c r="E98" s="75" t="inlineStr">
         <is>
           <t>СЕРЫЙ/ЗЕЛЕНЫЙ</t>
         </is>
@@ -15422,7 +15436,7 @@
       </c>
     </row>
     <row r="99" ht="13.5" customHeight="1" s="69">
-      <c r="E99" s="42" t="inlineStr">
+      <c r="E99" s="75" t="inlineStr">
         <is>
           <t>СИНЕ-ЗЕЛЕНЫЙ</t>
         </is>
@@ -15434,7 +15448,7 @@
       </c>
     </row>
     <row r="100" ht="13.5" customHeight="1" s="69">
-      <c r="E100" s="42" t="inlineStr">
+      <c r="E100" s="75" t="inlineStr">
         <is>
           <t>БЕЛО-ГОЛУБОЙ</t>
         </is>
@@ -15446,7 +15460,7 @@
       </c>
     </row>
     <row r="101" ht="13.5" customHeight="1" s="69">
-      <c r="E101" s="42" t="inlineStr">
+      <c r="E101" s="75" t="inlineStr">
         <is>
           <t>БЕЛО-СИНИЙ</t>
         </is>
@@ -15458,7 +15472,7 @@
       </c>
     </row>
     <row r="102" ht="13.5" customHeight="1" s="69">
-      <c r="E102" s="42" t="inlineStr">
+      <c r="E102" s="75" t="inlineStr">
         <is>
           <t>СВЕТЛО-ГОЛУБОЙ</t>
         </is>
@@ -15470,7 +15484,7 @@
       </c>
     </row>
     <row r="103" ht="13.5" customHeight="1" s="69">
-      <c r="E103" s="42" t="inlineStr">
+      <c r="E103" s="75" t="inlineStr">
         <is>
           <t>ЗЕЛЕНЫЙ МЕЛАНЖ</t>
         </is>
@@ -15482,7 +15496,7 @@
       </c>
     </row>
     <row r="104" ht="13.5" customHeight="1" s="69">
-      <c r="E104" s="42" t="inlineStr">
+      <c r="E104" s="75" t="inlineStr">
         <is>
           <t>ЖЕЛТЫЙ МЕЛАНЖ</t>
         </is>
@@ -15494,7 +15508,7 @@
       </c>
     </row>
     <row r="105" ht="13.5" customHeight="1" s="69">
-      <c r="E105" s="42" t="inlineStr">
+      <c r="E105" s="75" t="inlineStr">
         <is>
           <t>СИНИЙ МЕЛАНЖ</t>
         </is>
@@ -15506,7 +15520,7 @@
       </c>
     </row>
     <row r="106" ht="13.5" customHeight="1" s="69">
-      <c r="E106" s="42" t="inlineStr">
+      <c r="E106" s="75" t="inlineStr">
         <is>
           <t>КРАСНЫЙ МЕЛАНЖ</t>
         </is>
@@ -15518,7 +15532,7 @@
       </c>
     </row>
     <row r="107" ht="13.5" customHeight="1" s="69">
-      <c r="E107" s="42" t="inlineStr">
+      <c r="E107" s="75" t="inlineStr">
         <is>
           <t>РОЗОВЫЙ МЕЛАНЖ</t>
         </is>
@@ -15530,7 +15544,7 @@
       </c>
     </row>
     <row r="108" ht="13.5" customHeight="1" s="69">
-      <c r="E108" s="42" t="inlineStr">
+      <c r="E108" s="75" t="inlineStr">
         <is>
           <t>ФИОЛЕТОВЫЙ МЕЛАНЖ</t>
         </is>
@@ -15542,7 +15556,7 @@
       </c>
     </row>
     <row r="109" ht="13.5" customHeight="1" s="69">
-      <c r="E109" s="42" t="inlineStr">
+      <c r="E109" s="75" t="inlineStr">
         <is>
           <t>ЖЕЛТО-ЗЕЛЕНЫЙ</t>
         </is>
@@ -15554,7 +15568,7 @@
       </c>
     </row>
     <row r="110" ht="13.5" customHeight="1" s="69">
-      <c r="E110" s="42" t="inlineStr">
+      <c r="E110" s="75" t="inlineStr">
         <is>
           <t>МЕЛАНЖ</t>
         </is>
@@ -15566,7 +15580,7 @@
       </c>
     </row>
     <row r="111" ht="13.5" customHeight="1" s="69">
-      <c r="E111" s="42" t="inlineStr">
+      <c r="E111" s="75" t="inlineStr">
         <is>
           <t>СЕРО-ЗЕЛЕНЫЙ</t>
         </is>
@@ -15578,7 +15592,7 @@
       </c>
     </row>
     <row r="112" ht="13.5" customHeight="1" s="69">
-      <c r="E112" s="42" t="inlineStr">
+      <c r="E112" s="75" t="inlineStr">
         <is>
           <t>СЕРО-ЗЕЛЁНЫЙ</t>
         </is>
@@ -15590,7 +15604,7 @@
       </c>
     </row>
     <row r="113" ht="13.5" customHeight="1" s="69">
-      <c r="E113" s="42" t="inlineStr">
+      <c r="E113" s="75" t="inlineStr">
         <is>
           <t>КАМУФЛЯЖНЫЙ</t>
         </is>
@@ -16516,6 +16530,1460 @@
     <row r="246" ht="13.5" customHeight="1" s="69">
       <c r="H246" s="72" t="n"/>
     </row>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
+    <row r="1200"/>
+    <row r="1201"/>
+    <row r="1202"/>
+    <row r="1203"/>
+    <row r="1204"/>
+    <row r="1205"/>
+    <row r="1206"/>
+    <row r="1207"/>
+    <row r="1208"/>
+    <row r="1209"/>
+    <row r="1210"/>
+    <row r="1211"/>
+    <row r="1212"/>
+    <row r="1213"/>
+    <row r="1214"/>
+    <row r="1215"/>
+    <row r="1216"/>
+    <row r="1217"/>
+    <row r="1218"/>
+    <row r="1219"/>
+    <row r="1220"/>
+    <row r="1221"/>
+    <row r="1222"/>
+    <row r="1223"/>
+    <row r="1224"/>
+    <row r="1225"/>
+    <row r="1226"/>
+    <row r="1227"/>
+    <row r="1228"/>
+    <row r="1229"/>
+    <row r="1230"/>
+    <row r="1231"/>
+    <row r="1232"/>
+    <row r="1233"/>
+    <row r="1234"/>
+    <row r="1235"/>
+    <row r="1236"/>
+    <row r="1237"/>
+    <row r="1238"/>
+    <row r="1239"/>
+    <row r="1240"/>
+    <row r="1241"/>
+    <row r="1242"/>
+    <row r="1243"/>
+    <row r="1244"/>
+    <row r="1245"/>
+    <row r="1246"/>
+    <row r="1247"/>
+    <row r="1248"/>
+    <row r="1249"/>
+    <row r="1250"/>
+    <row r="1251"/>
+    <row r="1252"/>
+    <row r="1253"/>
+    <row r="1254"/>
+    <row r="1255"/>
+    <row r="1256"/>
+    <row r="1257"/>
+    <row r="1258"/>
+    <row r="1259"/>
+    <row r="1260"/>
+    <row r="1261"/>
+    <row r="1262"/>
+    <row r="1263"/>
+    <row r="1264"/>
+    <row r="1265"/>
+    <row r="1266"/>
+    <row r="1267"/>
+    <row r="1268"/>
+    <row r="1269"/>
+    <row r="1270"/>
+    <row r="1271"/>
+    <row r="1272"/>
+    <row r="1273"/>
+    <row r="1274"/>
+    <row r="1275"/>
+    <row r="1276"/>
+    <row r="1277"/>
+    <row r="1278"/>
+    <row r="1279"/>
+    <row r="1280"/>
+    <row r="1281"/>
+    <row r="1282"/>
+    <row r="1283"/>
+    <row r="1284"/>
+    <row r="1285"/>
+    <row r="1286"/>
+    <row r="1287"/>
+    <row r="1288"/>
+    <row r="1289"/>
+    <row r="1290"/>
+    <row r="1291"/>
+    <row r="1292"/>
+    <row r="1293"/>
+    <row r="1294"/>
+    <row r="1295"/>
+    <row r="1296"/>
+    <row r="1297"/>
+    <row r="1298"/>
+    <row r="1299"/>
+    <row r="1300"/>
+    <row r="1301"/>
+    <row r="1302"/>
+    <row r="1303"/>
+    <row r="1304"/>
+    <row r="1305"/>
+    <row r="1306"/>
+    <row r="1307"/>
+    <row r="1308"/>
+    <row r="1309"/>
+    <row r="1310"/>
+    <row r="1311"/>
+    <row r="1312"/>
+    <row r="1313"/>
+    <row r="1314"/>
+    <row r="1315"/>
+    <row r="1316"/>
+    <row r="1317"/>
+    <row r="1318"/>
+    <row r="1319"/>
+    <row r="1320"/>
+    <row r="1321"/>
+    <row r="1322"/>
+    <row r="1323"/>
+    <row r="1324"/>
+    <row r="1325"/>
+    <row r="1326"/>
+    <row r="1327"/>
+    <row r="1328"/>
+    <row r="1329"/>
+    <row r="1330"/>
+    <row r="1331"/>
+    <row r="1332"/>
+    <row r="1333"/>
+    <row r="1334"/>
+    <row r="1335"/>
+    <row r="1336"/>
+    <row r="1337"/>
+    <row r="1338"/>
+    <row r="1339"/>
+    <row r="1340"/>
+    <row r="1341"/>
+    <row r="1342"/>
+    <row r="1343"/>
+    <row r="1344"/>
+    <row r="1345"/>
+    <row r="1346"/>
+    <row r="1347"/>
+    <row r="1348"/>
+    <row r="1349"/>
+    <row r="1350"/>
+    <row r="1351"/>
+    <row r="1352"/>
+    <row r="1353"/>
+    <row r="1354"/>
+    <row r="1355"/>
+    <row r="1356"/>
+    <row r="1357"/>
+    <row r="1358"/>
+    <row r="1359"/>
+    <row r="1360"/>
+    <row r="1361"/>
+    <row r="1362"/>
+    <row r="1363"/>
+    <row r="1364"/>
+    <row r="1365"/>
+    <row r="1366"/>
+    <row r="1367"/>
+    <row r="1368"/>
+    <row r="1369"/>
+    <row r="1370"/>
+    <row r="1371"/>
+    <row r="1372"/>
+    <row r="1373"/>
+    <row r="1374"/>
+    <row r="1375"/>
+    <row r="1376"/>
+    <row r="1377"/>
+    <row r="1378"/>
+    <row r="1379"/>
+    <row r="1380"/>
+    <row r="1381"/>
+    <row r="1382"/>
+    <row r="1383"/>
+    <row r="1384"/>
+    <row r="1385"/>
+    <row r="1386"/>
+    <row r="1387"/>
+    <row r="1388"/>
+    <row r="1389"/>
+    <row r="1390"/>
+    <row r="1391"/>
+    <row r="1392"/>
+    <row r="1393"/>
+    <row r="1394"/>
+    <row r="1395"/>
+    <row r="1396"/>
+    <row r="1397"/>
+    <row r="1398"/>
+    <row r="1399"/>
+    <row r="1400"/>
+    <row r="1401"/>
+    <row r="1402"/>
+    <row r="1403"/>
+    <row r="1404"/>
+    <row r="1405"/>
+    <row r="1406"/>
+    <row r="1407"/>
+    <row r="1408"/>
+    <row r="1409"/>
+    <row r="1410"/>
+    <row r="1411"/>
+    <row r="1412"/>
+    <row r="1413"/>
+    <row r="1414"/>
+    <row r="1415"/>
+    <row r="1416"/>
+    <row r="1417"/>
+    <row r="1418"/>
+    <row r="1419"/>
+    <row r="1420"/>
+    <row r="1421"/>
+    <row r="1422"/>
+    <row r="1423"/>
+    <row r="1424"/>
+    <row r="1425"/>
+    <row r="1426"/>
+    <row r="1427"/>
+    <row r="1428"/>
+    <row r="1429"/>
+    <row r="1430"/>
+    <row r="1431"/>
+    <row r="1432"/>
+    <row r="1433"/>
+    <row r="1434"/>
+    <row r="1435"/>
+    <row r="1436"/>
+    <row r="1437"/>
+    <row r="1438"/>
+    <row r="1439"/>
+    <row r="1440"/>
+    <row r="1441"/>
+    <row r="1442"/>
+    <row r="1443"/>
+    <row r="1444"/>
+    <row r="1445"/>
+    <row r="1446"/>
+    <row r="1447"/>
+    <row r="1448"/>
+    <row r="1449"/>
+    <row r="1450"/>
+    <row r="1451"/>
+    <row r="1452"/>
+    <row r="1453"/>
+    <row r="1454"/>
+    <row r="1455"/>
+    <row r="1456"/>
+    <row r="1457"/>
+    <row r="1458"/>
+    <row r="1459"/>
+    <row r="1460"/>
+    <row r="1461"/>
+    <row r="1462"/>
+    <row r="1463"/>
+    <row r="1464"/>
+    <row r="1465"/>
+    <row r="1466"/>
+    <row r="1467"/>
+    <row r="1468"/>
+    <row r="1469"/>
+    <row r="1470"/>
+    <row r="1471"/>
+    <row r="1472"/>
+    <row r="1473"/>
+    <row r="1474"/>
+    <row r="1475"/>
+    <row r="1476"/>
+    <row r="1477"/>
+    <row r="1478"/>
+    <row r="1479"/>
+    <row r="1480"/>
+    <row r="1481"/>
+    <row r="1482"/>
+    <row r="1483"/>
+    <row r="1484"/>
+    <row r="1485"/>
+    <row r="1486"/>
+    <row r="1487"/>
+    <row r="1488"/>
+    <row r="1489"/>
+    <row r="1490"/>
+    <row r="1491"/>
+    <row r="1492"/>
+    <row r="1493"/>
+    <row r="1494"/>
+    <row r="1495"/>
+    <row r="1496"/>
+    <row r="1497"/>
+    <row r="1498"/>
+    <row r="1499"/>
+    <row r="1500"/>
+    <row r="1501"/>
+    <row r="1502"/>
+    <row r="1503"/>
+    <row r="1504"/>
+    <row r="1505"/>
+    <row r="1506"/>
+    <row r="1507"/>
+    <row r="1508"/>
+    <row r="1509"/>
+    <row r="1510"/>
+    <row r="1511"/>
+    <row r="1512"/>
+    <row r="1513"/>
+    <row r="1514"/>
+    <row r="1515"/>
+    <row r="1516"/>
+    <row r="1517"/>
+    <row r="1518"/>
+    <row r="1519"/>
+    <row r="1520"/>
+    <row r="1521"/>
+    <row r="1522"/>
+    <row r="1523"/>
+    <row r="1524"/>
+    <row r="1525"/>
+    <row r="1526"/>
+    <row r="1527"/>
+    <row r="1528"/>
+    <row r="1529"/>
+    <row r="1530"/>
+    <row r="1531"/>
+    <row r="1532"/>
+    <row r="1533"/>
+    <row r="1534"/>
+    <row r="1535"/>
+    <row r="1536"/>
+    <row r="1537"/>
+    <row r="1538"/>
+    <row r="1539"/>
+    <row r="1540"/>
+    <row r="1541"/>
+    <row r="1542"/>
+    <row r="1543"/>
+    <row r="1544"/>
+    <row r="1545"/>
+    <row r="1546"/>
+    <row r="1547"/>
+    <row r="1548"/>
+    <row r="1549"/>
+    <row r="1550"/>
+    <row r="1551"/>
+    <row r="1552"/>
+    <row r="1553"/>
+    <row r="1554"/>
+    <row r="1555"/>
+    <row r="1556"/>
+    <row r="1557"/>
+    <row r="1558"/>
+    <row r="1559"/>
+    <row r="1560"/>
+    <row r="1561"/>
+    <row r="1562"/>
+    <row r="1563"/>
+    <row r="1564"/>
+    <row r="1565"/>
+    <row r="1566"/>
+    <row r="1567"/>
+    <row r="1568"/>
+    <row r="1569"/>
+    <row r="1570"/>
+    <row r="1571"/>
+    <row r="1572"/>
+    <row r="1573"/>
+    <row r="1574"/>
+    <row r="1575"/>
+    <row r="1576"/>
+    <row r="1577"/>
+    <row r="1578"/>
+    <row r="1579"/>
+    <row r="1580"/>
+    <row r="1581"/>
+    <row r="1582"/>
+    <row r="1583"/>
+    <row r="1584"/>
+    <row r="1585"/>
+    <row r="1586"/>
+    <row r="1587"/>
+    <row r="1588"/>
+    <row r="1589"/>
+    <row r="1590"/>
+    <row r="1591"/>
+    <row r="1592"/>
+    <row r="1593"/>
+    <row r="1594"/>
+    <row r="1595"/>
+    <row r="1596"/>
+    <row r="1597"/>
+    <row r="1598"/>
+    <row r="1599"/>
+    <row r="1600"/>
+    <row r="1601"/>
+    <row r="1602"/>
+    <row r="1603"/>
+    <row r="1604"/>
+    <row r="1605"/>
+    <row r="1606"/>
+    <row r="1607"/>
+    <row r="1608"/>
+    <row r="1609"/>
+    <row r="1610"/>
+    <row r="1611"/>
+    <row r="1612"/>
+    <row r="1613"/>
+    <row r="1614"/>
+    <row r="1615"/>
+    <row r="1616"/>
+    <row r="1617"/>
+    <row r="1618"/>
+    <row r="1619"/>
+    <row r="1620"/>
+    <row r="1621"/>
+    <row r="1622"/>
+    <row r="1623"/>
+    <row r="1624"/>
+    <row r="1625"/>
+    <row r="1626"/>
+    <row r="1627"/>
+    <row r="1628"/>
+    <row r="1629"/>
+    <row r="1630"/>
+    <row r="1631"/>
+    <row r="1632"/>
+    <row r="1633"/>
+    <row r="1634"/>
+    <row r="1635"/>
+    <row r="1636"/>
+    <row r="1637"/>
+    <row r="1638"/>
+    <row r="1639"/>
+    <row r="1640"/>
+    <row r="1641"/>
+    <row r="1642"/>
+    <row r="1643"/>
+    <row r="1644"/>
+    <row r="1645"/>
+    <row r="1646"/>
+    <row r="1647"/>
+    <row r="1648"/>
+    <row r="1649"/>
+    <row r="1650"/>
+    <row r="1651"/>
+    <row r="1652"/>
+    <row r="1653"/>
+    <row r="1654"/>
+    <row r="1655"/>
+    <row r="1656"/>
+    <row r="1657"/>
+    <row r="1658"/>
+    <row r="1659"/>
+    <row r="1660"/>
+    <row r="1661"/>
+    <row r="1662"/>
+    <row r="1663"/>
+    <row r="1664"/>
+    <row r="1665"/>
+    <row r="1666"/>
+    <row r="1667"/>
+    <row r="1668"/>
+    <row r="1669"/>
+    <row r="1670"/>
+    <row r="1671"/>
+    <row r="1672"/>
+    <row r="1673"/>
+    <row r="1674"/>
+    <row r="1675"/>
+    <row r="1676"/>
+    <row r="1677"/>
+    <row r="1678"/>
+    <row r="1679"/>
+    <row r="1680"/>
+    <row r="1681"/>
+    <row r="1682"/>
+    <row r="1683"/>
+    <row r="1684"/>
+    <row r="1685"/>
+    <row r="1686"/>
+    <row r="1687"/>
+    <row r="1688"/>
+    <row r="1689"/>
+    <row r="1690"/>
+    <row r="1691"/>
+    <row r="1692"/>
+    <row r="1693"/>
+    <row r="1694"/>
+    <row r="1695"/>
+    <row r="1696"/>
+    <row r="1697"/>
+    <row r="1698"/>
+    <row r="1699"/>
+    <row r="1700"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
@@ -16546,10 +18014,10 @@
   <dimension ref="B2:E110"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.89453125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="19.77" customWidth="1" style="42" min="2" max="2"/>
-    <col width="19.78" customWidth="1" style="42" min="3" max="3"/>
-    <col width="17.16" customWidth="1" style="42" min="4" max="4"/>
-    <col width="29.63" customWidth="1" style="42" min="5" max="5"/>
+    <col width="19.77" customWidth="1" style="75" min="2" max="2"/>
+    <col width="19.78" customWidth="1" style="75" min="3" max="3"/>
+    <col width="17.16" customWidth="1" style="75" min="4" max="4"/>
+    <col width="29.63" customWidth="1" style="75" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="2" ht="12.75" customHeight="1" s="69">
@@ -16582,7 +18050,7 @@
         </is>
       </c>
       <c r="D3" s="77" t="n"/>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="75" t="inlineStr">
         <is>
           <t>2XS</t>
         </is>
@@ -17381,8 +18849,8 @@
   <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.48828125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="54.83" customWidth="1" style="42" min="1" max="1"/>
-    <col width="215.56" customWidth="1" style="42" min="2" max="2"/>
+    <col width="54.83" customWidth="1" style="75" min="1" max="1"/>
+    <col width="215.56" customWidth="1" style="75" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="69">
@@ -17398,7 +18866,7 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="69">
-      <c r="A2" s="80" t="inlineStr">
+      <c r="A2" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000001&gt; АРАФАТКА</t>
         </is>
@@ -17410,7 +18878,7 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="69">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000002&gt; БАБОЧКА</t>
         </is>
@@ -17422,7 +18890,7 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="69">
-      <c r="A4" s="80" t="inlineStr">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000003&gt; БАЛАКЛАВА</t>
         </is>
@@ -17434,7 +18902,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="69">
-      <c r="A5" s="80" t="inlineStr">
+      <c r="A5" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000004&gt; БАНДАНА</t>
         </is>
@@ -17446,7 +18914,7 @@
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="69">
-      <c r="A6" s="80" t="inlineStr">
+      <c r="A6" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000005&gt; БАНТ</t>
         </is>
@@ -17458,7 +18926,7 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="69">
-      <c r="A7" s="80" t="inlineStr">
+      <c r="A7" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000006&gt; БАСКА</t>
         </is>
@@ -17470,7 +18938,7 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="69">
-      <c r="A8" s="80" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000007&gt; БАФФ</t>
         </is>
@@ -17482,7 +18950,7 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="69">
-      <c r="A9" s="80" t="inlineStr">
+      <c r="A9" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000008&gt; ВОРОТНИК</t>
         </is>
@@ -17506,7 +18974,7 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="69">
-      <c r="A11" s="80" t="inlineStr">
+      <c r="A11" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000009&gt; ВУАЛЬ</t>
         </is>
@@ -17518,7 +18986,7 @@
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="69">
-      <c r="A12" s="80" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000010&gt; ГАЛСТУК</t>
         </is>
@@ -17530,7 +18998,7 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="69">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000011&gt; ГАЛСТУК-БАБОЧКА</t>
         </is>
@@ -17542,7 +19010,7 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="69">
-      <c r="A14" s="80" t="inlineStr">
+      <c r="A14" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000012&gt; ГЕЙТОР</t>
         </is>
@@ -17554,7 +19022,7 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="69">
-      <c r="A15" s="80" t="inlineStr">
+      <c r="A15" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000013&gt; ГОРЖЕТКА</t>
         </is>
@@ -17574,7 +19042,7 @@
       <c r="B16" s="84" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="69">
-      <c r="A17" s="80" t="inlineStr">
+      <c r="A17" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000014&gt; ДИАДЕМА</t>
         </is>
@@ -17582,7 +19050,7 @@
       <c r="B17" s="84" t="n"/>
     </row>
     <row r="18" ht="48.75" customHeight="1" s="69">
-      <c r="A18" s="80" t="inlineStr">
+      <c r="A18" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000015&gt; ЖАБО</t>
         </is>
@@ -17590,7 +19058,7 @@
       <c r="B18" s="84" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="69">
-      <c r="A19" s="80" t="inlineStr">
+      <c r="A19" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000016&gt; ЗАКОЛКА</t>
         </is>
@@ -17598,7 +19066,7 @@
       <c r="B19" s="84" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="69">
-      <c r="A20" s="80" t="inlineStr">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000017&gt; КАПЮШОН</t>
         </is>
@@ -17606,7 +19074,7 @@
       <c r="B20" s="84" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="69">
-      <c r="A21" s="80" t="inlineStr">
+      <c r="A21" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000018&gt; КАШНЕ</t>
         </is>
@@ -17614,7 +19082,7 @@
       <c r="B21" s="84" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="69">
-      <c r="A22" s="80" t="inlineStr">
+      <c r="A22" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000019&gt; КОСЫНКА</t>
         </is>
@@ -17622,7 +19090,7 @@
       <c r="B22" s="84" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="69">
-      <c r="A23" s="80" t="inlineStr">
+      <c r="A23" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000020&gt; ЛЕНТА</t>
         </is>
@@ -17638,7 +19106,7 @@
       <c r="B24" s="84" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="69">
-      <c r="A25" s="80" t="inlineStr">
+      <c r="A25" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000021&gt; МАНИШКА</t>
         </is>
@@ -17646,7 +19114,7 @@
       <c r="B25" s="84" t="n"/>
     </row>
     <row r="26" ht="34.5" customHeight="1" s="69">
-      <c r="A26" s="80" t="inlineStr">
+      <c r="A26" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000022&gt; МАНТИЛЬЯ</t>
         </is>
@@ -17654,7 +19122,7 @@
       <c r="B26" s="84" t="n"/>
     </row>
     <row r="27" ht="34.5" customHeight="1" s="69">
-      <c r="A27" s="80" t="inlineStr">
+      <c r="A27" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000023&gt; МАСКА</t>
         </is>
@@ -17662,7 +19130,7 @@
       <c r="B27" s="84" t="n"/>
     </row>
     <row r="28" ht="33" customHeight="1" s="69">
-      <c r="A28" s="80" t="inlineStr">
+      <c r="A28" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000024&gt; НАГРУДНИК</t>
         </is>
@@ -17670,7 +19138,7 @@
       <c r="B28" s="84" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1" s="69">
-      <c r="A29" s="80" t="inlineStr">
+      <c r="A29" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000025&gt; НАМАЗНИК</t>
         </is>
@@ -17686,7 +19154,7 @@
       <c r="B30" s="84" t="n"/>
     </row>
     <row r="31" ht="36.75" customHeight="1" s="69">
-      <c r="A31" s="80" t="inlineStr">
+      <c r="A31" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000026&gt; ПАЛАНТИН</t>
         </is>
@@ -17694,7 +19162,7 @@
       <c r="B31" s="84" t="n"/>
     </row>
     <row r="32" ht="25.5" customHeight="1" s="69">
-      <c r="A32" s="80" t="inlineStr">
+      <c r="A32" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000027&gt; ПАРЕО</t>
         </is>
@@ -17710,7 +19178,7 @@
       <c r="B33" s="84" t="n"/>
     </row>
     <row r="34" ht="39.75" customHeight="1" s="69">
-      <c r="A34" s="80" t="inlineStr">
+      <c r="A34" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000028&gt; ПЕЛЕНКА</t>
         </is>
@@ -17718,7 +19186,7 @@
       <c r="B34" s="84" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="69">
-      <c r="A35" s="80" t="inlineStr">
+      <c r="A35" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000029&gt; ПЕЛЕРИНА</t>
         </is>
@@ -17726,7 +19194,7 @@
       <c r="B35" s="84" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="69">
-      <c r="A36" s="80" t="inlineStr">
+      <c r="A36" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000030&gt; ПЛАТОК</t>
         </is>
@@ -17734,7 +19202,7 @@
       <c r="B36" s="84" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="69">
-      <c r="A37" s="80" t="inlineStr">
+      <c r="A37" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000031&gt; ПЛАТОК ГОЛОВНОЙ</t>
         </is>
@@ -17742,7 +19210,7 @@
       <c r="B37" s="84" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="69">
-      <c r="A38" s="80" t="inlineStr">
+      <c r="A38" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000032&gt; ПЛАТОК НОСОВОЙ</t>
         </is>
@@ -17750,7 +19218,7 @@
       <c r="B38" s="84" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="69">
-      <c r="A39" s="80" t="inlineStr">
+      <c r="A39" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000033&gt; ПЛАТОК ШЕЙНЫЙ</t>
         </is>
@@ -17758,7 +19226,7 @@
       <c r="B39" s="84" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="69">
-      <c r="A40" s="80" t="inlineStr">
+      <c r="A40" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000059&gt; ПОВЯЗКА НА ГОЛОВУ</t>
         </is>
@@ -17766,7 +19234,7 @@
       <c r="B40" s="84" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="69">
-      <c r="A41" s="80" t="inlineStr">
+      <c r="A41" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000034&gt; ПОДТЯЖКИ</t>
         </is>
@@ -17774,7 +19242,7 @@
       <c r="B41" s="84" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="69">
-      <c r="A42" s="80" t="inlineStr">
+      <c r="A42" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000035&gt; ПОДШЛЕМНИК</t>
         </is>
@@ -17782,7 +19250,7 @@
       <c r="B42" s="84" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="69">
-      <c r="A43" s="80" t="inlineStr">
+      <c r="A43" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000036&gt; ПОРТУПЕЯ</t>
         </is>
@@ -17790,7 +19258,7 @@
       <c r="B43" s="84" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="69">
-      <c r="A44" s="80" t="inlineStr">
+      <c r="A44" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000037&gt; ПОЯС</t>
         </is>
@@ -17798,7 +19266,7 @@
       <c r="B44" s="84" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="69">
-      <c r="A45" s="80" t="inlineStr">
+      <c r="A45" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000038&gt; РЕЗИНКА НА ГОЛОВУ</t>
         </is>
@@ -17806,7 +19274,7 @@
       <c r="B45" s="84" t="n"/>
     </row>
     <row r="46" ht="13.5" customHeight="1" s="69">
-      <c r="A46" s="80" t="inlineStr">
+      <c r="A46" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000039&gt; РЕМЕНЬ</t>
         </is>
@@ -17814,7 +19282,7 @@
       <c r="B46" s="84" t="n"/>
     </row>
     <row r="47" ht="13.5" customHeight="1" s="69">
-      <c r="A47" s="80" t="inlineStr">
+      <c r="A47" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000052&gt; РУКАВА</t>
         </is>
@@ -17822,7 +19290,7 @@
       <c r="B47" s="84" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="69">
-      <c r="A48" s="80" t="inlineStr">
+      <c r="A48" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000040&gt; СНУД</t>
         </is>
@@ -17830,7 +19298,7 @@
       <c r="B48" s="84" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="69">
-      <c r="A49" s="80" t="inlineStr">
+      <c r="A49" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000041&gt; ТРЕССЫ</t>
         </is>
@@ -17838,7 +19306,7 @@
       <c r="B49" s="84" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="69">
-      <c r="A50" s="80" t="inlineStr">
+      <c r="A50" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000042&gt; ФАТА</t>
         </is>
@@ -17846,7 +19314,7 @@
       <c r="B50" s="84" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="69">
-      <c r="A51" s="80" t="inlineStr">
+      <c r="A51" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000043&gt; ХИДЖАБ</t>
         </is>
@@ -17854,7 +19322,7 @@
       <c r="B51" s="84" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="69">
-      <c r="A52" s="80" t="inlineStr">
+      <c r="A52" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000044&gt; ХОМУТ</t>
         </is>
@@ -17862,7 +19330,7 @@
       <c r="B52" s="84" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="69">
-      <c r="A53" s="80" t="inlineStr">
+      <c r="A53" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000045&gt; ЧАЛМА</t>
         </is>
@@ -17870,42 +19338,42 @@
       <c r="B53" s="84" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="69">
-      <c r="A54" s="80" t="inlineStr">
+      <c r="A54" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000046&gt; ЧОКЕР</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="69">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000047&gt; ШАЛЬ</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="69">
-      <c r="A56" s="80" t="inlineStr">
+      <c r="A56" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000048&gt; ШАПКА-ШАРФ</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="69">
-      <c r="A57" s="80" t="inlineStr">
+      <c r="A57" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000053&gt; ШАПОЧКА ДЛЯ ПЛАВАНИЯ</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="69">
-      <c r="A58" s="80" t="inlineStr">
+      <c r="A58" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000049&gt; ШАРФ-СНУД</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="69">
-      <c r="A59" s="80" t="inlineStr">
+      <c r="A59" s="85" t="inlineStr">
         <is>
           <t>&lt;4000000050&gt; ШАРФ-КАПЮШОН</t>
         </is>

--- a/app/download_dir/system_files/шали_по каждому размеру.xlsx
+++ b/app/download_dir/system_files/шали_по каждому размеру.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Данные" sheetId="1" state="visible" r:id="rId1"/>
@@ -245,7 +245,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -501,6 +501,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,6 +901,7 @@
     <col width="17.78" customWidth="1" style="75" min="15" max="15"/>
     <col width="16" customWidth="1" style="75" min="16" max="16"/>
     <col width="25.96" customWidth="1" style="75" min="17" max="17"/>
+    <col width="20" customWidth="1" style="69" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="64.5" customFormat="1" customHeight="1" s="44">
@@ -976,6 +984,11 @@
 Действия документа
 Формат dd.mm.yyyy
 ( например 23.10.2023)</t>
+        </is>
+      </c>
+      <c r="R1" s="49" t="inlineStr">
+        <is>
+          <t>Вес в граммах</t>
         </is>
       </c>
       <c r="AME1" s="75" t="n"/>
@@ -1312,6 +1325,11 @@
       </c>
       <c r="P6" s="60" t="n"/>
       <c r="Q6" s="47" t="n"/>
+      <c r="R6" s="87" t="inlineStr">
+        <is>
+          <t>Обязательное поле: общий вес позиции, целое число больше 0. Просьба указать актуальный вес товара в ГРАММАХ для отчетности РОСПРИРОДНАДЗОР.</t>
+        </is>
+      </c>
       <c r="AME6" s="75" t="n"/>
       <c r="AMF6" s="75" t="n"/>
       <c r="AMG6" s="75" t="n"/>
@@ -1404,7 +1422,9 @@
           <t>23.12.2023</t>
         </is>
       </c>
-      <c r="R7" s="50" t="n"/>
+      <c r="R7" s="88" t="n">
+        <v>1000</v>
+      </c>
       <c r="S7" s="50" t="n"/>
       <c r="T7" s="50" t="n"/>
       <c r="U7" s="50" t="n"/>
@@ -1495,7 +1515,9 @@
       <c r="O8" s="66" t="n"/>
       <c r="P8" s="67" t="n"/>
       <c r="Q8" s="67" t="n"/>
-      <c r="R8" s="50" t="n"/>
+      <c r="R8" s="88" t="n">
+        <v>1000</v>
+      </c>
       <c r="S8" s="50" t="n"/>
       <c r="T8" s="50" t="n"/>
       <c r="U8" s="50" t="n"/>
@@ -1532,6 +1554,7 @@
       <c r="O9" s="68" t="n"/>
       <c r="P9" s="61" t="n"/>
       <c r="Q9" s="61" t="n"/>
+      <c r="R9" s="89" t="n"/>
       <c r="AME9" s="75" t="n"/>
       <c r="AMF9" s="75" t="n"/>
       <c r="AMG9" s="75" t="n"/>
@@ -1558,6 +1581,7 @@
       <c r="O10" s="68" t="n"/>
       <c r="P10" s="61" t="n"/>
       <c r="Q10" s="61" t="n"/>
+      <c r="R10" s="89" t="n"/>
       <c r="AME10" s="75" t="n"/>
       <c r="AMF10" s="75" t="n"/>
       <c r="AMG10" s="75" t="n"/>
@@ -1584,6 +1608,7 @@
       <c r="O11" s="68" t="n"/>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="61" t="n"/>
+      <c r="R11" s="89" t="n"/>
       <c r="AME11" s="75" t="n"/>
       <c r="AMF11" s="75" t="n"/>
       <c r="AMG11" s="75" t="n"/>
@@ -1610,6 +1635,7 @@
       <c r="O12" s="68" t="n"/>
       <c r="P12" s="61" t="n"/>
       <c r="Q12" s="61" t="n"/>
+      <c r="R12" s="89" t="n"/>
       <c r="AME12" s="75" t="n"/>
       <c r="AMF12" s="75" t="n"/>
       <c r="AMG12" s="75" t="n"/>
@@ -1636,6 +1662,7 @@
       <c r="O13" s="68" t="n"/>
       <c r="P13" s="61" t="n"/>
       <c r="Q13" s="61" t="n"/>
+      <c r="R13" s="89" t="n"/>
       <c r="AME13" s="75" t="n"/>
       <c r="AMF13" s="75" t="n"/>
       <c r="AMG13" s="75" t="n"/>
@@ -1662,6 +1689,7 @@
       <c r="O14" s="68" t="n"/>
       <c r="P14" s="61" t="n"/>
       <c r="Q14" s="61" t="n"/>
+      <c r="R14" s="89" t="n"/>
       <c r="AME14" s="75" t="n"/>
       <c r="AMF14" s="75" t="n"/>
       <c r="AMG14" s="75" t="n"/>
@@ -1688,6 +1716,7 @@
       <c r="O15" s="68" t="n"/>
       <c r="P15" s="61" t="n"/>
       <c r="Q15" s="61" t="n"/>
+      <c r="R15" s="89" t="n"/>
       <c r="AME15" s="75" t="n"/>
       <c r="AMF15" s="75" t="n"/>
       <c r="AMG15" s="75" t="n"/>
@@ -1714,6 +1743,7 @@
       <c r="O16" s="68" t="n"/>
       <c r="P16" s="61" t="n"/>
       <c r="Q16" s="61" t="n"/>
+      <c r="R16" s="89" t="n"/>
       <c r="AME16" s="75" t="n"/>
       <c r="AMF16" s="75" t="n"/>
       <c r="AMG16" s="75" t="n"/>
@@ -1740,6 +1770,7 @@
       <c r="O17" s="68" t="n"/>
       <c r="P17" s="61" t="n"/>
       <c r="Q17" s="61" t="n"/>
+      <c r="R17" s="89" t="n"/>
       <c r="AME17" s="75" t="n"/>
       <c r="AMF17" s="75" t="n"/>
       <c r="AMG17" s="75" t="n"/>
@@ -1766,6 +1797,7 @@
       <c r="O18" s="68" t="n"/>
       <c r="P18" s="61" t="n"/>
       <c r="Q18" s="61" t="n"/>
+      <c r="R18" s="89" t="n"/>
       <c r="AME18" s="75" t="n"/>
       <c r="AMF18" s="75" t="n"/>
       <c r="AMG18" s="75" t="n"/>
@@ -1792,6 +1824,7 @@
       <c r="O19" s="68" t="n"/>
       <c r="P19" s="61" t="n"/>
       <c r="Q19" s="61" t="n"/>
+      <c r="R19" s="89" t="n"/>
       <c r="AME19" s="75" t="n"/>
       <c r="AMF19" s="75" t="n"/>
       <c r="AMG19" s="75" t="n"/>
@@ -1818,6 +1851,7 @@
       <c r="O20" s="68" t="n"/>
       <c r="P20" s="61" t="n"/>
       <c r="Q20" s="61" t="n"/>
+      <c r="R20" s="89" t="n"/>
       <c r="AME20" s="75" t="n"/>
       <c r="AMF20" s="75" t="n"/>
       <c r="AMG20" s="75" t="n"/>
@@ -1844,6 +1878,7 @@
       <c r="O21" s="68" t="n"/>
       <c r="P21" s="61" t="n"/>
       <c r="Q21" s="61" t="n"/>
+      <c r="R21" s="89" t="n"/>
       <c r="AME21" s="75" t="n"/>
       <c r="AMF21" s="75" t="n"/>
       <c r="AMG21" s="75" t="n"/>
@@ -1870,6 +1905,7 @@
       <c r="O22" s="68" t="n"/>
       <c r="P22" s="61" t="n"/>
       <c r="Q22" s="61" t="n"/>
+      <c r="R22" s="89" t="n"/>
       <c r="AME22" s="75" t="n"/>
       <c r="AMF22" s="75" t="n"/>
       <c r="AMG22" s="75" t="n"/>
@@ -1896,6 +1932,7 @@
       <c r="O23" s="68" t="n"/>
       <c r="P23" s="61" t="n"/>
       <c r="Q23" s="61" t="n"/>
+      <c r="R23" s="89" t="n"/>
       <c r="AME23" s="75" t="n"/>
       <c r="AMF23" s="75" t="n"/>
       <c r="AMG23" s="75" t="n"/>
@@ -1922,6 +1959,7 @@
       <c r="O24" s="68" t="n"/>
       <c r="P24" s="61" t="n"/>
       <c r="Q24" s="61" t="n"/>
+      <c r="R24" s="89" t="n"/>
       <c r="AME24" s="75" t="n"/>
       <c r="AMF24" s="75" t="n"/>
       <c r="AMG24" s="75" t="n"/>
@@ -1948,6 +1986,7 @@
       <c r="O25" s="68" t="n"/>
       <c r="P25" s="61" t="n"/>
       <c r="Q25" s="61" t="n"/>
+      <c r="R25" s="89" t="n"/>
       <c r="AME25" s="75" t="n"/>
       <c r="AMF25" s="75" t="n"/>
       <c r="AMG25" s="75" t="n"/>
@@ -1974,6 +2013,7 @@
       <c r="O26" s="68" t="n"/>
       <c r="P26" s="61" t="n"/>
       <c r="Q26" s="61" t="n"/>
+      <c r="R26" s="89" t="n"/>
       <c r="AME26" s="75" t="n"/>
       <c r="AMF26" s="75" t="n"/>
       <c r="AMG26" s="75" t="n"/>
@@ -2000,6 +2040,7 @@
       <c r="O27" s="68" t="n"/>
       <c r="P27" s="61" t="n"/>
       <c r="Q27" s="61" t="n"/>
+      <c r="R27" s="89" t="n"/>
       <c r="AME27" s="75" t="n"/>
       <c r="AMF27" s="75" t="n"/>
       <c r="AMG27" s="75" t="n"/>
@@ -2026,6 +2067,7 @@
       <c r="O28" s="68" t="n"/>
       <c r="P28" s="61" t="n"/>
       <c r="Q28" s="61" t="n"/>
+      <c r="R28" s="89" t="n"/>
       <c r="AME28" s="75" t="n"/>
       <c r="AMF28" s="75" t="n"/>
       <c r="AMG28" s="75" t="n"/>
@@ -2052,6 +2094,7 @@
       <c r="O29" s="68" t="n"/>
       <c r="P29" s="61" t="n"/>
       <c r="Q29" s="61" t="n"/>
+      <c r="R29" s="89" t="n"/>
       <c r="AME29" s="75" t="n"/>
       <c r="AMF29" s="75" t="n"/>
       <c r="AMG29" s="75" t="n"/>
@@ -2078,6 +2121,7 @@
       <c r="O30" s="68" t="n"/>
       <c r="P30" s="61" t="n"/>
       <c r="Q30" s="61" t="n"/>
+      <c r="R30" s="89" t="n"/>
       <c r="AME30" s="75" t="n"/>
       <c r="AMF30" s="75" t="n"/>
       <c r="AMG30" s="75" t="n"/>
@@ -2104,6 +2148,7 @@
       <c r="O31" s="68" t="n"/>
       <c r="P31" s="61" t="n"/>
       <c r="Q31" s="61" t="n"/>
+      <c r="R31" s="89" t="n"/>
       <c r="AME31" s="75" t="n"/>
       <c r="AMF31" s="75" t="n"/>
       <c r="AMG31" s="75" t="n"/>
@@ -2130,6 +2175,7 @@
       <c r="O32" s="68" t="n"/>
       <c r="P32" s="61" t="n"/>
       <c r="Q32" s="61" t="n"/>
+      <c r="R32" s="89" t="n"/>
       <c r="AME32" s="75" t="n"/>
       <c r="AMF32" s="75" t="n"/>
       <c r="AMG32" s="75" t="n"/>
@@ -2156,6 +2202,7 @@
       <c r="O33" s="68" t="n"/>
       <c r="P33" s="61" t="n"/>
       <c r="Q33" s="61" t="n"/>
+      <c r="R33" s="89" t="n"/>
       <c r="AME33" s="75" t="n"/>
       <c r="AMF33" s="75" t="n"/>
       <c r="AMG33" s="75" t="n"/>
@@ -2182,6 +2229,7 @@
       <c r="O34" s="68" t="n"/>
       <c r="P34" s="61" t="n"/>
       <c r="Q34" s="61" t="n"/>
+      <c r="R34" s="89" t="n"/>
       <c r="AME34" s="75" t="n"/>
       <c r="AMF34" s="75" t="n"/>
       <c r="AMG34" s="75" t="n"/>
@@ -2208,6 +2256,7 @@
       <c r="O35" s="68" t="n"/>
       <c r="P35" s="61" t="n"/>
       <c r="Q35" s="61" t="n"/>
+      <c r="R35" s="89" t="n"/>
       <c r="AME35" s="75" t="n"/>
       <c r="AMF35" s="75" t="n"/>
       <c r="AMG35" s="75" t="n"/>
@@ -2234,6 +2283,7 @@
       <c r="O36" s="68" t="n"/>
       <c r="P36" s="61" t="n"/>
       <c r="Q36" s="61" t="n"/>
+      <c r="R36" s="89" t="n"/>
       <c r="AME36" s="75" t="n"/>
       <c r="AMF36" s="75" t="n"/>
       <c r="AMG36" s="75" t="n"/>
@@ -2260,6 +2310,7 @@
       <c r="O37" s="68" t="n"/>
       <c r="P37" s="61" t="n"/>
       <c r="Q37" s="61" t="n"/>
+      <c r="R37" s="89" t="n"/>
       <c r="AME37" s="75" t="n"/>
       <c r="AMF37" s="75" t="n"/>
       <c r="AMG37" s="75" t="n"/>
@@ -2286,6 +2337,7 @@
       <c r="O38" s="68" t="n"/>
       <c r="P38" s="61" t="n"/>
       <c r="Q38" s="61" t="n"/>
+      <c r="R38" s="89" t="n"/>
       <c r="AME38" s="75" t="n"/>
       <c r="AMF38" s="75" t="n"/>
       <c r="AMG38" s="75" t="n"/>
@@ -2312,6 +2364,7 @@
       <c r="O39" s="68" t="n"/>
       <c r="P39" s="61" t="n"/>
       <c r="Q39" s="61" t="n"/>
+      <c r="R39" s="89" t="n"/>
       <c r="AME39" s="75" t="n"/>
       <c r="AMF39" s="75" t="n"/>
       <c r="AMG39" s="75" t="n"/>
@@ -2338,6 +2391,7 @@
       <c r="O40" s="68" t="n"/>
       <c r="P40" s="61" t="n"/>
       <c r="Q40" s="61" t="n"/>
+      <c r="R40" s="89" t="n"/>
       <c r="AME40" s="75" t="n"/>
       <c r="AMF40" s="75" t="n"/>
       <c r="AMG40" s="75" t="n"/>
@@ -2364,6 +2418,7 @@
       <c r="O41" s="68" t="n"/>
       <c r="P41" s="61" t="n"/>
       <c r="Q41" s="61" t="n"/>
+      <c r="R41" s="89" t="n"/>
       <c r="AME41" s="75" t="n"/>
       <c r="AMF41" s="75" t="n"/>
       <c r="AMG41" s="75" t="n"/>
@@ -2390,6 +2445,7 @@
       <c r="O42" s="68" t="n"/>
       <c r="P42" s="61" t="n"/>
       <c r="Q42" s="61" t="n"/>
+      <c r="R42" s="89" t="n"/>
       <c r="AME42" s="75" t="n"/>
       <c r="AMF42" s="75" t="n"/>
       <c r="AMG42" s="75" t="n"/>
@@ -2416,6 +2472,7 @@
       <c r="O43" s="68" t="n"/>
       <c r="P43" s="61" t="n"/>
       <c r="Q43" s="61" t="n"/>
+      <c r="R43" s="89" t="n"/>
       <c r="AME43" s="75" t="n"/>
       <c r="AMF43" s="75" t="n"/>
       <c r="AMG43" s="75" t="n"/>
@@ -2442,6 +2499,7 @@
       <c r="O44" s="68" t="n"/>
       <c r="P44" s="61" t="n"/>
       <c r="Q44" s="61" t="n"/>
+      <c r="R44" s="89" t="n"/>
       <c r="AME44" s="75" t="n"/>
       <c r="AMF44" s="75" t="n"/>
       <c r="AMG44" s="75" t="n"/>
@@ -2468,6 +2526,7 @@
       <c r="O45" s="68" t="n"/>
       <c r="P45" s="61" t="n"/>
       <c r="Q45" s="61" t="n"/>
+      <c r="R45" s="89" t="n"/>
       <c r="AME45" s="75" t="n"/>
       <c r="AMF45" s="75" t="n"/>
       <c r="AMG45" s="75" t="n"/>
@@ -2488,6 +2547,7 @@
       <c r="O46" s="68" t="n"/>
       <c r="P46" s="61" t="n"/>
       <c r="Q46" s="61" t="n"/>
+      <c r="R46" s="89" t="n"/>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="69">
       <c r="F47" s="65" t="n"/>
@@ -2502,6 +2562,7 @@
       <c r="O47" s="68" t="n"/>
       <c r="P47" s="61" t="n"/>
       <c r="Q47" s="61" t="n"/>
+      <c r="R47" s="89" t="n"/>
     </row>
     <row r="48" ht="12.75" customHeight="1" s="69">
       <c r="F48" s="65" t="n"/>
@@ -2516,6 +2577,7 @@
       <c r="O48" s="68" t="n"/>
       <c r="P48" s="61" t="n"/>
       <c r="Q48" s="61" t="n"/>
+      <c r="R48" s="89" t="n"/>
     </row>
     <row r="49" ht="12.75" customHeight="1" s="69">
       <c r="F49" s="65" t="n"/>
@@ -2530,6 +2592,7 @@
       <c r="O49" s="68" t="n"/>
       <c r="P49" s="61" t="n"/>
       <c r="Q49" s="61" t="n"/>
+      <c r="R49" s="89" t="n"/>
     </row>
     <row r="50" ht="12.75" customHeight="1" s="69">
       <c r="F50" s="65" t="n"/>
@@ -2544,6 +2607,7 @@
       <c r="O50" s="68" t="n"/>
       <c r="P50" s="61" t="n"/>
       <c r="Q50" s="61" t="n"/>
+      <c r="R50" s="89" t="n"/>
     </row>
     <row r="51" ht="12.75" customHeight="1" s="69">
       <c r="F51" s="65" t="n"/>
@@ -2558,6 +2622,7 @@
       <c r="O51" s="68" t="n"/>
       <c r="P51" s="61" t="n"/>
       <c r="Q51" s="61" t="n"/>
+      <c r="R51" s="89" t="n"/>
     </row>
     <row r="52" ht="12.75" customHeight="1" s="69">
       <c r="F52" s="65" t="n"/>
@@ -2572,6 +2637,7 @@
       <c r="O52" s="68" t="n"/>
       <c r="P52" s="61" t="n"/>
       <c r="Q52" s="61" t="n"/>
+      <c r="R52" s="89" t="n"/>
     </row>
     <row r="53" ht="12.75" customHeight="1" s="69">
       <c r="F53" s="65" t="n"/>
@@ -2586,6 +2652,7 @@
       <c r="O53" s="68" t="n"/>
       <c r="P53" s="61" t="n"/>
       <c r="Q53" s="61" t="n"/>
+      <c r="R53" s="89" t="n"/>
     </row>
     <row r="54" ht="12.75" customHeight="1" s="69">
       <c r="F54" s="65" t="n"/>
@@ -2600,6 +2667,7 @@
       <c r="O54" s="68" t="n"/>
       <c r="P54" s="61" t="n"/>
       <c r="Q54" s="61" t="n"/>
+      <c r="R54" s="89" t="n"/>
     </row>
     <row r="55" ht="12.75" customHeight="1" s="69">
       <c r="F55" s="65" t="n"/>
@@ -2614,6 +2682,7 @@
       <c r="O55" s="68" t="n"/>
       <c r="P55" s="61" t="n"/>
       <c r="Q55" s="61" t="n"/>
+      <c r="R55" s="89" t="n"/>
     </row>
     <row r="56" ht="12.75" customHeight="1" s="69">
       <c r="F56" s="65" t="n"/>
@@ -2628,6 +2697,7 @@
       <c r="O56" s="68" t="n"/>
       <c r="P56" s="61" t="n"/>
       <c r="Q56" s="61" t="n"/>
+      <c r="R56" s="89" t="n"/>
     </row>
     <row r="57" ht="12.75" customHeight="1" s="69">
       <c r="F57" s="65" t="n"/>
@@ -2642,6 +2712,7 @@
       <c r="O57" s="68" t="n"/>
       <c r="P57" s="61" t="n"/>
       <c r="Q57" s="61" t="n"/>
+      <c r="R57" s="89" t="n"/>
     </row>
     <row r="58" ht="12.75" customHeight="1" s="69">
       <c r="F58" s="65" t="n"/>
@@ -2656,6 +2727,7 @@
       <c r="O58" s="68" t="n"/>
       <c r="P58" s="61" t="n"/>
       <c r="Q58" s="61" t="n"/>
+      <c r="R58" s="89" t="n"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" s="69">
       <c r="F59" s="65" t="n"/>
@@ -2670,6 +2742,7 @@
       <c r="O59" s="68" t="n"/>
       <c r="P59" s="61" t="n"/>
       <c r="Q59" s="61" t="n"/>
+      <c r="R59" s="89" t="n"/>
     </row>
     <row r="60" ht="12.75" customHeight="1" s="69">
       <c r="F60" s="65" t="n"/>
@@ -2684,6 +2757,7 @@
       <c r="O60" s="68" t="n"/>
       <c r="P60" s="61" t="n"/>
       <c r="Q60" s="61" t="n"/>
+      <c r="R60" s="89" t="n"/>
     </row>
     <row r="61" ht="12.75" customHeight="1" s="69">
       <c r="F61" s="65" t="n"/>
@@ -2698,6 +2772,7 @@
       <c r="O61" s="68" t="n"/>
       <c r="P61" s="61" t="n"/>
       <c r="Q61" s="61" t="n"/>
+      <c r="R61" s="89" t="n"/>
     </row>
     <row r="62" ht="12.75" customHeight="1" s="69">
       <c r="F62" s="65" t="n"/>
@@ -2712,6 +2787,7 @@
       <c r="O62" s="68" t="n"/>
       <c r="P62" s="61" t="n"/>
       <c r="Q62" s="61" t="n"/>
+      <c r="R62" s="89" t="n"/>
     </row>
     <row r="63" ht="12.75" customHeight="1" s="69">
       <c r="F63" s="65" t="n"/>
@@ -2726,6 +2802,7 @@
       <c r="O63" s="68" t="n"/>
       <c r="P63" s="61" t="n"/>
       <c r="Q63" s="61" t="n"/>
+      <c r="R63" s="89" t="n"/>
     </row>
     <row r="64" ht="12.75" customHeight="1" s="69">
       <c r="F64" s="65" t="n"/>
@@ -2740,6 +2817,7 @@
       <c r="O64" s="68" t="n"/>
       <c r="P64" s="61" t="n"/>
       <c r="Q64" s="61" t="n"/>
+      <c r="R64" s="89" t="n"/>
     </row>
     <row r="65" ht="12.75" customHeight="1" s="69">
       <c r="F65" s="65" t="n"/>
@@ -2754,6 +2832,7 @@
       <c r="O65" s="68" t="n"/>
       <c r="P65" s="61" t="n"/>
       <c r="Q65" s="61" t="n"/>
+      <c r="R65" s="89" t="n"/>
     </row>
     <row r="66" ht="12.75" customHeight="1" s="69">
       <c r="F66" s="65" t="n"/>
@@ -2768,6 +2847,7 @@
       <c r="O66" s="68" t="n"/>
       <c r="P66" s="61" t="n"/>
       <c r="Q66" s="61" t="n"/>
+      <c r="R66" s="89" t="n"/>
     </row>
     <row r="67" ht="12.75" customHeight="1" s="69">
       <c r="F67" s="65" t="n"/>
@@ -2782,6 +2862,7 @@
       <c r="O67" s="68" t="n"/>
       <c r="P67" s="61" t="n"/>
       <c r="Q67" s="61" t="n"/>
+      <c r="R67" s="89" t="n"/>
     </row>
     <row r="68" ht="12.75" customHeight="1" s="69">
       <c r="F68" s="65" t="n"/>
@@ -2796,6 +2877,7 @@
       <c r="O68" s="68" t="n"/>
       <c r="P68" s="61" t="n"/>
       <c r="Q68" s="61" t="n"/>
+      <c r="R68" s="89" t="n"/>
     </row>
     <row r="69" ht="12.75" customHeight="1" s="69">
       <c r="F69" s="65" t="n"/>
@@ -2810,6 +2892,7 @@
       <c r="O69" s="68" t="n"/>
       <c r="P69" s="61" t="n"/>
       <c r="Q69" s="61" t="n"/>
+      <c r="R69" s="89" t="n"/>
     </row>
     <row r="70" ht="12.75" customHeight="1" s="69">
       <c r="F70" s="65" t="n"/>
@@ -2824,6 +2907,7 @@
       <c r="O70" s="68" t="n"/>
       <c r="P70" s="61" t="n"/>
       <c r="Q70" s="61" t="n"/>
+      <c r="R70" s="89" t="n"/>
     </row>
     <row r="71" ht="12.75" customHeight="1" s="69">
       <c r="F71" s="65" t="n"/>
@@ -2838,6 +2922,7 @@
       <c r="O71" s="68" t="n"/>
       <c r="P71" s="61" t="n"/>
       <c r="Q71" s="61" t="n"/>
+      <c r="R71" s="89" t="n"/>
     </row>
     <row r="72" ht="12.75" customHeight="1" s="69">
       <c r="F72" s="65" t="n"/>
@@ -2852,6 +2937,7 @@
       <c r="O72" s="68" t="n"/>
       <c r="P72" s="61" t="n"/>
       <c r="Q72" s="61" t="n"/>
+      <c r="R72" s="89" t="n"/>
     </row>
     <row r="73" ht="12.75" customHeight="1" s="69">
       <c r="F73" s="65" t="n"/>
@@ -2866,6 +2952,7 @@
       <c r="O73" s="68" t="n"/>
       <c r="P73" s="61" t="n"/>
       <c r="Q73" s="61" t="n"/>
+      <c r="R73" s="89" t="n"/>
     </row>
     <row r="74" ht="12.75" customHeight="1" s="69">
       <c r="F74" s="65" t="n"/>
@@ -2880,6 +2967,7 @@
       <c r="O74" s="68" t="n"/>
       <c r="P74" s="61" t="n"/>
       <c r="Q74" s="61" t="n"/>
+      <c r="R74" s="89" t="n"/>
     </row>
     <row r="75" ht="12.75" customHeight="1" s="69">
       <c r="F75" s="65" t="n"/>
@@ -2894,6 +2982,7 @@
       <c r="O75" s="68" t="n"/>
       <c r="P75" s="61" t="n"/>
       <c r="Q75" s="61" t="n"/>
+      <c r="R75" s="89" t="n"/>
     </row>
     <row r="76" ht="12.75" customHeight="1" s="69">
       <c r="F76" s="65" t="n"/>
@@ -2908,6 +2997,7 @@
       <c r="O76" s="68" t="n"/>
       <c r="P76" s="61" t="n"/>
       <c r="Q76" s="61" t="n"/>
+      <c r="R76" s="89" t="n"/>
     </row>
     <row r="77" ht="12.75" customHeight="1" s="69">
       <c r="F77" s="65" t="n"/>
@@ -2922,6 +3012,7 @@
       <c r="O77" s="68" t="n"/>
       <c r="P77" s="61" t="n"/>
       <c r="Q77" s="61" t="n"/>
+      <c r="R77" s="89" t="n"/>
     </row>
     <row r="78" ht="12.75" customHeight="1" s="69">
       <c r="F78" s="65" t="n"/>
@@ -2936,6 +3027,7 @@
       <c r="O78" s="68" t="n"/>
       <c r="P78" s="61" t="n"/>
       <c r="Q78" s="61" t="n"/>
+      <c r="R78" s="89" t="n"/>
     </row>
     <row r="79" ht="12.75" customHeight="1" s="69">
       <c r="F79" s="65" t="n"/>
@@ -2950,6 +3042,7 @@
       <c r="O79" s="68" t="n"/>
       <c r="P79" s="61" t="n"/>
       <c r="Q79" s="61" t="n"/>
+      <c r="R79" s="89" t="n"/>
     </row>
     <row r="80" ht="12.75" customHeight="1" s="69">
       <c r="F80" s="65" t="n"/>
@@ -2964,6 +3057,7 @@
       <c r="O80" s="68" t="n"/>
       <c r="P80" s="61" t="n"/>
       <c r="Q80" s="61" t="n"/>
+      <c r="R80" s="89" t="n"/>
     </row>
     <row r="81" ht="12.75" customHeight="1" s="69">
       <c r="F81" s="65" t="n"/>
@@ -2978,6 +3072,7 @@
       <c r="O81" s="68" t="n"/>
       <c r="P81" s="61" t="n"/>
       <c r="Q81" s="61" t="n"/>
+      <c r="R81" s="89" t="n"/>
     </row>
     <row r="82" ht="12.75" customHeight="1" s="69">
       <c r="F82" s="65" t="n"/>
@@ -2992,6 +3087,7 @@
       <c r="O82" s="68" t="n"/>
       <c r="P82" s="61" t="n"/>
       <c r="Q82" s="61" t="n"/>
+      <c r="R82" s="89" t="n"/>
     </row>
     <row r="83" ht="12.75" customHeight="1" s="69">
       <c r="F83" s="65" t="n"/>
@@ -3006,6 +3102,7 @@
       <c r="O83" s="68" t="n"/>
       <c r="P83" s="61" t="n"/>
       <c r="Q83" s="61" t="n"/>
+      <c r="R83" s="89" t="n"/>
     </row>
     <row r="84" ht="12.75" customHeight="1" s="69">
       <c r="F84" s="65" t="n"/>
@@ -3020,6 +3117,7 @@
       <c r="O84" s="68" t="n"/>
       <c r="P84" s="61" t="n"/>
       <c r="Q84" s="61" t="n"/>
+      <c r="R84" s="89" t="n"/>
     </row>
     <row r="85" ht="12.75" customHeight="1" s="69">
       <c r="F85" s="65" t="n"/>
@@ -3034,6 +3132,7 @@
       <c r="O85" s="68" t="n"/>
       <c r="P85" s="61" t="n"/>
       <c r="Q85" s="61" t="n"/>
+      <c r="R85" s="89" t="n"/>
     </row>
     <row r="86" ht="12.75" customHeight="1" s="69">
       <c r="F86" s="65" t="n"/>
@@ -3048,6 +3147,7 @@
       <c r="O86" s="68" t="n"/>
       <c r="P86" s="61" t="n"/>
       <c r="Q86" s="61" t="n"/>
+      <c r="R86" s="89" t="n"/>
     </row>
     <row r="87" ht="12.75" customHeight="1" s="69">
       <c r="F87" s="65" t="n"/>
@@ -3062,6 +3162,7 @@
       <c r="O87" s="68" t="n"/>
       <c r="P87" s="61" t="n"/>
       <c r="Q87" s="61" t="n"/>
+      <c r="R87" s="89" t="n"/>
     </row>
     <row r="88" ht="12.75" customHeight="1" s="69">
       <c r="F88" s="65" t="n"/>
@@ -3076,6 +3177,7 @@
       <c r="O88" s="68" t="n"/>
       <c r="P88" s="61" t="n"/>
       <c r="Q88" s="61" t="n"/>
+      <c r="R88" s="89" t="n"/>
     </row>
     <row r="89" ht="12.75" customHeight="1" s="69">
       <c r="F89" s="65" t="n"/>
@@ -3090,6 +3192,7 @@
       <c r="O89" s="68" t="n"/>
       <c r="P89" s="61" t="n"/>
       <c r="Q89" s="61" t="n"/>
+      <c r="R89" s="89" t="n"/>
     </row>
     <row r="90" ht="12.75" customHeight="1" s="69">
       <c r="F90" s="65" t="n"/>
@@ -3104,6 +3207,7 @@
       <c r="O90" s="68" t="n"/>
       <c r="P90" s="61" t="n"/>
       <c r="Q90" s="61" t="n"/>
+      <c r="R90" s="89" t="n"/>
     </row>
     <row r="91" ht="12.75" customHeight="1" s="69">
       <c r="F91" s="65" t="n"/>
@@ -3118,6 +3222,7 @@
       <c r="O91" s="68" t="n"/>
       <c r="P91" s="61" t="n"/>
       <c r="Q91" s="61" t="n"/>
+      <c r="R91" s="89" t="n"/>
     </row>
     <row r="92" ht="12.75" customHeight="1" s="69">
       <c r="F92" s="65" t="n"/>
@@ -3132,6 +3237,7 @@
       <c r="O92" s="68" t="n"/>
       <c r="P92" s="61" t="n"/>
       <c r="Q92" s="61" t="n"/>
+      <c r="R92" s="89" t="n"/>
     </row>
     <row r="93" ht="12.75" customHeight="1" s="69">
       <c r="F93" s="65" t="n"/>
@@ -3146,6 +3252,7 @@
       <c r="O93" s="68" t="n"/>
       <c r="P93" s="61" t="n"/>
       <c r="Q93" s="61" t="n"/>
+      <c r="R93" s="89" t="n"/>
     </row>
     <row r="94" ht="12.75" customHeight="1" s="69">
       <c r="F94" s="65" t="n"/>
@@ -3160,6 +3267,7 @@
       <c r="O94" s="68" t="n"/>
       <c r="P94" s="61" t="n"/>
       <c r="Q94" s="61" t="n"/>
+      <c r="R94" s="89" t="n"/>
     </row>
     <row r="95" ht="12.75" customHeight="1" s="69">
       <c r="F95" s="65" t="n"/>
@@ -3174,6 +3282,7 @@
       <c r="O95" s="68" t="n"/>
       <c r="P95" s="61" t="n"/>
       <c r="Q95" s="61" t="n"/>
+      <c r="R95" s="89" t="n"/>
     </row>
     <row r="96" ht="12.75" customHeight="1" s="69">
       <c r="F96" s="65" t="n"/>
@@ -3188,6 +3297,7 @@
       <c r="O96" s="68" t="n"/>
       <c r="P96" s="61" t="n"/>
       <c r="Q96" s="61" t="n"/>
+      <c r="R96" s="89" t="n"/>
     </row>
     <row r="97" ht="12.75" customHeight="1" s="69">
       <c r="F97" s="65" t="n"/>
@@ -3202,6 +3312,7 @@
       <c r="O97" s="68" t="n"/>
       <c r="P97" s="61" t="n"/>
       <c r="Q97" s="61" t="n"/>
+      <c r="R97" s="89" t="n"/>
     </row>
     <row r="98" ht="12.75" customHeight="1" s="69">
       <c r="F98" s="65" t="n"/>
@@ -3216,6 +3327,7 @@
       <c r="O98" s="68" t="n"/>
       <c r="P98" s="61" t="n"/>
       <c r="Q98" s="61" t="n"/>
+      <c r="R98" s="89" t="n"/>
     </row>
     <row r="99" ht="12.75" customHeight="1" s="69">
       <c r="F99" s="65" t="n"/>
@@ -3230,6 +3342,7 @@
       <c r="O99" s="68" t="n"/>
       <c r="P99" s="61" t="n"/>
       <c r="Q99" s="61" t="n"/>
+      <c r="R99" s="89" t="n"/>
     </row>
     <row r="100" ht="12.75" customHeight="1" s="69">
       <c r="F100" s="65" t="n"/>
@@ -3244,6 +3357,7 @@
       <c r="O100" s="68" t="n"/>
       <c r="P100" s="61" t="n"/>
       <c r="Q100" s="61" t="n"/>
+      <c r="R100" s="89" t="n"/>
     </row>
     <row r="101" ht="12.75" customHeight="1" s="69">
       <c r="F101" s="65" t="n"/>
@@ -3258,6 +3372,7 @@
       <c r="O101" s="68" t="n"/>
       <c r="P101" s="61" t="n"/>
       <c r="Q101" s="61" t="n"/>
+      <c r="R101" s="89" t="n"/>
     </row>
     <row r="102" ht="12.75" customHeight="1" s="69">
       <c r="F102" s="65" t="n"/>
@@ -3272,6 +3387,7 @@
       <c r="O102" s="68" t="n"/>
       <c r="P102" s="61" t="n"/>
       <c r="Q102" s="61" t="n"/>
+      <c r="R102" s="89" t="n"/>
     </row>
     <row r="103" ht="12.75" customHeight="1" s="69">
       <c r="F103" s="65" t="n"/>
@@ -3286,6 +3402,7 @@
       <c r="O103" s="68" t="n"/>
       <c r="P103" s="61" t="n"/>
       <c r="Q103" s="61" t="n"/>
+      <c r="R103" s="89" t="n"/>
     </row>
     <row r="104" ht="12.75" customHeight="1" s="69">
       <c r="F104" s="65" t="n"/>
@@ -3300,6 +3417,7 @@
       <c r="O104" s="68" t="n"/>
       <c r="P104" s="61" t="n"/>
       <c r="Q104" s="61" t="n"/>
+      <c r="R104" s="89" t="n"/>
     </row>
     <row r="105" ht="12.75" customHeight="1" s="69">
       <c r="F105" s="65" t="n"/>
@@ -3314,6 +3432,7 @@
       <c r="O105" s="68" t="n"/>
       <c r="P105" s="61" t="n"/>
       <c r="Q105" s="61" t="n"/>
+      <c r="R105" s="89" t="n"/>
     </row>
     <row r="106" ht="12.75" customHeight="1" s="69">
       <c r="F106" s="65" t="n"/>
@@ -3328,6 +3447,7 @@
       <c r="O106" s="68" t="n"/>
       <c r="P106" s="61" t="n"/>
       <c r="Q106" s="61" t="n"/>
+      <c r="R106" s="89" t="n"/>
     </row>
     <row r="107" ht="12.75" customHeight="1" s="69">
       <c r="F107" s="65" t="n"/>
@@ -3342,6 +3462,7 @@
       <c r="O107" s="68" t="n"/>
       <c r="P107" s="61" t="n"/>
       <c r="Q107" s="61" t="n"/>
+      <c r="R107" s="89" t="n"/>
     </row>
     <row r="108" ht="12.75" customHeight="1" s="69">
       <c r="F108" s="65" t="n"/>
@@ -3356,6 +3477,7 @@
       <c r="O108" s="68" t="n"/>
       <c r="P108" s="61" t="n"/>
       <c r="Q108" s="61" t="n"/>
+      <c r="R108" s="89" t="n"/>
     </row>
     <row r="109" ht="12.75" customHeight="1" s="69">
       <c r="F109" s="65" t="n"/>
@@ -3370,6 +3492,7 @@
       <c r="O109" s="68" t="n"/>
       <c r="P109" s="61" t="n"/>
       <c r="Q109" s="61" t="n"/>
+      <c r="R109" s="89" t="n"/>
     </row>
     <row r="110" ht="12.75" customHeight="1" s="69">
       <c r="F110" s="65" t="n"/>
@@ -3384,6 +3507,7 @@
       <c r="O110" s="68" t="n"/>
       <c r="P110" s="61" t="n"/>
       <c r="Q110" s="61" t="n"/>
+      <c r="R110" s="89" t="n"/>
     </row>
     <row r="111" ht="12.75" customHeight="1" s="69">
       <c r="F111" s="65" t="n"/>
@@ -3398,6 +3522,7 @@
       <c r="O111" s="68" t="n"/>
       <c r="P111" s="61" t="n"/>
       <c r="Q111" s="61" t="n"/>
+      <c r="R111" s="89" t="n"/>
     </row>
     <row r="112" ht="12.75" customHeight="1" s="69">
       <c r="F112" s="65" t="n"/>
@@ -3412,6 +3537,7 @@
       <c r="O112" s="68" t="n"/>
       <c r="P112" s="61" t="n"/>
       <c r="Q112" s="61" t="n"/>
+      <c r="R112" s="89" t="n"/>
     </row>
     <row r="113" ht="12.75" customHeight="1" s="69">
       <c r="F113" s="65" t="n"/>
@@ -3426,6 +3552,7 @@
       <c r="O113" s="68" t="n"/>
       <c r="P113" s="61" t="n"/>
       <c r="Q113" s="61" t="n"/>
+      <c r="R113" s="89" t="n"/>
     </row>
     <row r="114" ht="12.75" customHeight="1" s="69">
       <c r="F114" s="65" t="n"/>
@@ -3440,6 +3567,7 @@
       <c r="O114" s="68" t="n"/>
       <c r="P114" s="61" t="n"/>
       <c r="Q114" s="61" t="n"/>
+      <c r="R114" s="89" t="n"/>
     </row>
     <row r="115" ht="12.75" customHeight="1" s="69">
       <c r="F115" s="65" t="n"/>
@@ -3454,6 +3582,7 @@
       <c r="O115" s="68" t="n"/>
       <c r="P115" s="61" t="n"/>
       <c r="Q115" s="61" t="n"/>
+      <c r="R115" s="89" t="n"/>
     </row>
     <row r="116" ht="12.75" customHeight="1" s="69">
       <c r="F116" s="65" t="n"/>
@@ -3468,6 +3597,7 @@
       <c r="O116" s="68" t="n"/>
       <c r="P116" s="61" t="n"/>
       <c r="Q116" s="61" t="n"/>
+      <c r="R116" s="89" t="n"/>
     </row>
     <row r="117" ht="12.75" customHeight="1" s="69">
       <c r="F117" s="65" t="n"/>
@@ -3482,6 +3612,7 @@
       <c r="O117" s="68" t="n"/>
       <c r="P117" s="61" t="n"/>
       <c r="Q117" s="61" t="n"/>
+      <c r="R117" s="89" t="n"/>
     </row>
     <row r="118" ht="12.75" customHeight="1" s="69">
       <c r="F118" s="65" t="n"/>
@@ -3496,6 +3627,7 @@
       <c r="O118" s="68" t="n"/>
       <c r="P118" s="61" t="n"/>
       <c r="Q118" s="61" t="n"/>
+      <c r="R118" s="89" t="n"/>
     </row>
     <row r="119" ht="12.75" customHeight="1" s="69">
       <c r="F119" s="65" t="n"/>
@@ -3510,6 +3642,7 @@
       <c r="O119" s="68" t="n"/>
       <c r="P119" s="61" t="n"/>
       <c r="Q119" s="61" t="n"/>
+      <c r="R119" s="89" t="n"/>
     </row>
     <row r="120" ht="12.75" customHeight="1" s="69">
       <c r="F120" s="65" t="n"/>
@@ -3524,6 +3657,7 @@
       <c r="O120" s="68" t="n"/>
       <c r="P120" s="61" t="n"/>
       <c r="Q120" s="61" t="n"/>
+      <c r="R120" s="89" t="n"/>
     </row>
     <row r="121" ht="12.75" customHeight="1" s="69">
       <c r="F121" s="65" t="n"/>
@@ -3538,6 +3672,7 @@
       <c r="O121" s="68" t="n"/>
       <c r="P121" s="61" t="n"/>
       <c r="Q121" s="61" t="n"/>
+      <c r="R121" s="89" t="n"/>
     </row>
     <row r="122" ht="12.75" customHeight="1" s="69">
       <c r="F122" s="65" t="n"/>
@@ -3552,6 +3687,7 @@
       <c r="O122" s="68" t="n"/>
       <c r="P122" s="61" t="n"/>
       <c r="Q122" s="61" t="n"/>
+      <c r="R122" s="89" t="n"/>
     </row>
     <row r="123" ht="12.75" customHeight="1" s="69">
       <c r="F123" s="65" t="n"/>
@@ -3566,6 +3702,7 @@
       <c r="O123" s="68" t="n"/>
       <c r="P123" s="61" t="n"/>
       <c r="Q123" s="61" t="n"/>
+      <c r="R123" s="89" t="n"/>
     </row>
     <row r="124" ht="12.75" customHeight="1" s="69">
       <c r="F124" s="65" t="n"/>
@@ -3580,6 +3717,7 @@
       <c r="O124" s="68" t="n"/>
       <c r="P124" s="61" t="n"/>
       <c r="Q124" s="61" t="n"/>
+      <c r="R124" s="89" t="n"/>
     </row>
     <row r="125" ht="12.75" customHeight="1" s="69">
       <c r="F125" s="65" t="n"/>
@@ -3594,6 +3732,7 @@
       <c r="O125" s="68" t="n"/>
       <c r="P125" s="61" t="n"/>
       <c r="Q125" s="61" t="n"/>
+      <c r="R125" s="89" t="n"/>
     </row>
     <row r="126" ht="12.75" customHeight="1" s="69">
       <c r="F126" s="65" t="n"/>
@@ -3608,6 +3747,7 @@
       <c r="O126" s="68" t="n"/>
       <c r="P126" s="61" t="n"/>
       <c r="Q126" s="61" t="n"/>
+      <c r="R126" s="89" t="n"/>
     </row>
     <row r="127" ht="12.75" customHeight="1" s="69">
       <c r="F127" s="65" t="n"/>
@@ -3622,6 +3762,7 @@
       <c r="O127" s="68" t="n"/>
       <c r="P127" s="61" t="n"/>
       <c r="Q127" s="61" t="n"/>
+      <c r="R127" s="89" t="n"/>
     </row>
     <row r="128" ht="12.75" customHeight="1" s="69">
       <c r="F128" s="65" t="n"/>
@@ -3636,6 +3777,7 @@
       <c r="O128" s="68" t="n"/>
       <c r="P128" s="61" t="n"/>
       <c r="Q128" s="61" t="n"/>
+      <c r="R128" s="89" t="n"/>
     </row>
     <row r="129" ht="12.75" customHeight="1" s="69">
       <c r="F129" s="65" t="n"/>
@@ -3650,6 +3792,7 @@
       <c r="O129" s="68" t="n"/>
       <c r="P129" s="61" t="n"/>
       <c r="Q129" s="61" t="n"/>
+      <c r="R129" s="89" t="n"/>
     </row>
     <row r="130" ht="12.75" customHeight="1" s="69">
       <c r="F130" s="65" t="n"/>
@@ -3664,6 +3807,7 @@
       <c r="O130" s="68" t="n"/>
       <c r="P130" s="61" t="n"/>
       <c r="Q130" s="61" t="n"/>
+      <c r="R130" s="89" t="n"/>
     </row>
     <row r="131" ht="12.75" customHeight="1" s="69">
       <c r="F131" s="65" t="n"/>
@@ -3678,6 +3822,7 @@
       <c r="O131" s="68" t="n"/>
       <c r="P131" s="61" t="n"/>
       <c r="Q131" s="61" t="n"/>
+      <c r="R131" s="89" t="n"/>
     </row>
     <row r="132" ht="12.75" customHeight="1" s="69">
       <c r="F132" s="65" t="n"/>
@@ -3692,6 +3837,7 @@
       <c r="O132" s="68" t="n"/>
       <c r="P132" s="61" t="n"/>
       <c r="Q132" s="61" t="n"/>
+      <c r="R132" s="89" t="n"/>
     </row>
     <row r="133" ht="12.75" customHeight="1" s="69">
       <c r="F133" s="65" t="n"/>
@@ -3706,6 +3852,7 @@
       <c r="O133" s="68" t="n"/>
       <c r="P133" s="61" t="n"/>
       <c r="Q133" s="61" t="n"/>
+      <c r="R133" s="89" t="n"/>
     </row>
     <row r="134" ht="12.75" customHeight="1" s="69">
       <c r="F134" s="65" t="n"/>
@@ -3720,6 +3867,7 @@
       <c r="O134" s="68" t="n"/>
       <c r="P134" s="61" t="n"/>
       <c r="Q134" s="61" t="n"/>
+      <c r="R134" s="89" t="n"/>
     </row>
     <row r="135" ht="12.75" customHeight="1" s="69">
       <c r="F135" s="65" t="n"/>
@@ -3734,6 +3882,7 @@
       <c r="O135" s="68" t="n"/>
       <c r="P135" s="61" t="n"/>
       <c r="Q135" s="61" t="n"/>
+      <c r="R135" s="89" t="n"/>
     </row>
     <row r="136" ht="12.75" customHeight="1" s="69">
       <c r="F136" s="65" t="n"/>
@@ -3748,6 +3897,7 @@
       <c r="O136" s="68" t="n"/>
       <c r="P136" s="61" t="n"/>
       <c r="Q136" s="61" t="n"/>
+      <c r="R136" s="89" t="n"/>
     </row>
     <row r="137" ht="12.75" customHeight="1" s="69">
       <c r="F137" s="65" t="n"/>
@@ -3762,6 +3912,7 @@
       <c r="O137" s="68" t="n"/>
       <c r="P137" s="61" t="n"/>
       <c r="Q137" s="61" t="n"/>
+      <c r="R137" s="89" t="n"/>
     </row>
     <row r="138" ht="12.75" customHeight="1" s="69">
       <c r="F138" s="65" t="n"/>
@@ -3776,6 +3927,7 @@
       <c r="O138" s="68" t="n"/>
       <c r="P138" s="61" t="n"/>
       <c r="Q138" s="61" t="n"/>
+      <c r="R138" s="89" t="n"/>
     </row>
     <row r="139" ht="12.75" customHeight="1" s="69">
       <c r="F139" s="65" t="n"/>
@@ -3790,6 +3942,7 @@
       <c r="O139" s="68" t="n"/>
       <c r="P139" s="61" t="n"/>
       <c r="Q139" s="61" t="n"/>
+      <c r="R139" s="89" t="n"/>
     </row>
     <row r="140" ht="12.75" customHeight="1" s="69">
       <c r="F140" s="65" t="n"/>
@@ -3804,6 +3957,7 @@
       <c r="O140" s="68" t="n"/>
       <c r="P140" s="61" t="n"/>
       <c r="Q140" s="61" t="n"/>
+      <c r="R140" s="89" t="n"/>
     </row>
     <row r="141" ht="12.75" customHeight="1" s="69">
       <c r="F141" s="65" t="n"/>
@@ -3818,6 +3972,7 @@
       <c r="O141" s="68" t="n"/>
       <c r="P141" s="61" t="n"/>
       <c r="Q141" s="61" t="n"/>
+      <c r="R141" s="89" t="n"/>
     </row>
     <row r="142" ht="12.75" customHeight="1" s="69">
       <c r="F142" s="65" t="n"/>
@@ -3832,6 +3987,7 @@
       <c r="O142" s="68" t="n"/>
       <c r="P142" s="61" t="n"/>
       <c r="Q142" s="61" t="n"/>
+      <c r="R142" s="89" t="n"/>
     </row>
     <row r="143" ht="12.75" customHeight="1" s="69">
       <c r="F143" s="65" t="n"/>
@@ -3846,6 +4002,7 @@
       <c r="O143" s="68" t="n"/>
       <c r="P143" s="61" t="n"/>
       <c r="Q143" s="61" t="n"/>
+      <c r="R143" s="89" t="n"/>
     </row>
     <row r="144" ht="12.75" customHeight="1" s="69">
       <c r="F144" s="65" t="n"/>
@@ -3860,6 +4017,7 @@
       <c r="O144" s="68" t="n"/>
       <c r="P144" s="61" t="n"/>
       <c r="Q144" s="61" t="n"/>
+      <c r="R144" s="89" t="n"/>
     </row>
     <row r="145" ht="12.75" customHeight="1" s="69">
       <c r="F145" s="65" t="n"/>
@@ -3874,6 +4032,7 @@
       <c r="O145" s="68" t="n"/>
       <c r="P145" s="61" t="n"/>
       <c r="Q145" s="61" t="n"/>
+      <c r="R145" s="89" t="n"/>
     </row>
     <row r="146" ht="12.75" customHeight="1" s="69">
       <c r="F146" s="65" t="n"/>
@@ -3888,6 +4047,7 @@
       <c r="O146" s="68" t="n"/>
       <c r="P146" s="61" t="n"/>
       <c r="Q146" s="61" t="n"/>
+      <c r="R146" s="89" t="n"/>
     </row>
     <row r="147" ht="12.75" customHeight="1" s="69">
       <c r="F147" s="65" t="n"/>
@@ -3902,6 +4062,7 @@
       <c r="O147" s="68" t="n"/>
       <c r="P147" s="61" t="n"/>
       <c r="Q147" s="61" t="n"/>
+      <c r="R147" s="89" t="n"/>
     </row>
     <row r="148" ht="12.75" customHeight="1" s="69">
       <c r="F148" s="65" t="n"/>
@@ -3916,6 +4077,7 @@
       <c r="O148" s="68" t="n"/>
       <c r="P148" s="61" t="n"/>
       <c r="Q148" s="61" t="n"/>
+      <c r="R148" s="89" t="n"/>
     </row>
     <row r="149" ht="12.75" customHeight="1" s="69">
       <c r="F149" s="65" t="n"/>
@@ -3930,6 +4092,7 @@
       <c r="O149" s="68" t="n"/>
       <c r="P149" s="61" t="n"/>
       <c r="Q149" s="61" t="n"/>
+      <c r="R149" s="89" t="n"/>
     </row>
     <row r="150" ht="12.75" customHeight="1" s="69">
       <c r="F150" s="65" t="n"/>
@@ -3944,6 +4107,7 @@
       <c r="O150" s="68" t="n"/>
       <c r="P150" s="61" t="n"/>
       <c r="Q150" s="61" t="n"/>
+      <c r="R150" s="89" t="n"/>
     </row>
     <row r="151" ht="12.75" customHeight="1" s="69">
       <c r="F151" s="65" t="n"/>
@@ -3958,6 +4122,7 @@
       <c r="O151" s="68" t="n"/>
       <c r="P151" s="61" t="n"/>
       <c r="Q151" s="61" t="n"/>
+      <c r="R151" s="89" t="n"/>
     </row>
     <row r="152" ht="12.75" customHeight="1" s="69">
       <c r="F152" s="65" t="n"/>
@@ -3972,6 +4137,7 @@
       <c r="O152" s="68" t="n"/>
       <c r="P152" s="61" t="n"/>
       <c r="Q152" s="61" t="n"/>
+      <c r="R152" s="89" t="n"/>
     </row>
     <row r="153" ht="12.75" customHeight="1" s="69">
       <c r="F153" s="65" t="n"/>
@@ -3986,6 +4152,7 @@
       <c r="O153" s="68" t="n"/>
       <c r="P153" s="61" t="n"/>
       <c r="Q153" s="61" t="n"/>
+      <c r="R153" s="89" t="n"/>
     </row>
     <row r="154" ht="12.75" customHeight="1" s="69">
       <c r="F154" s="65" t="n"/>
@@ -4000,6 +4167,7 @@
       <c r="O154" s="68" t="n"/>
       <c r="P154" s="61" t="n"/>
       <c r="Q154" s="61" t="n"/>
+      <c r="R154" s="89" t="n"/>
     </row>
     <row r="155" ht="12.75" customHeight="1" s="69">
       <c r="F155" s="65" t="n"/>
@@ -4014,6 +4182,7 @@
       <c r="O155" s="68" t="n"/>
       <c r="P155" s="61" t="n"/>
       <c r="Q155" s="61" t="n"/>
+      <c r="R155" s="89" t="n"/>
     </row>
     <row r="156" ht="12.75" customHeight="1" s="69">
       <c r="F156" s="65" t="n"/>
@@ -4028,6 +4197,7 @@
       <c r="O156" s="68" t="n"/>
       <c r="P156" s="61" t="n"/>
       <c r="Q156" s="61" t="n"/>
+      <c r="R156" s="89" t="n"/>
     </row>
     <row r="157" ht="12.75" customHeight="1" s="69">
       <c r="F157" s="65" t="n"/>
@@ -4042,6 +4212,7 @@
       <c r="O157" s="68" t="n"/>
       <c r="P157" s="61" t="n"/>
       <c r="Q157" s="61" t="n"/>
+      <c r="R157" s="89" t="n"/>
     </row>
     <row r="158" ht="12.75" customHeight="1" s="69">
       <c r="F158" s="65" t="n"/>
@@ -4056,6 +4227,7 @@
       <c r="O158" s="68" t="n"/>
       <c r="P158" s="61" t="n"/>
       <c r="Q158" s="61" t="n"/>
+      <c r="R158" s="89" t="n"/>
     </row>
     <row r="159" ht="12.75" customHeight="1" s="69">
       <c r="F159" s="65" t="n"/>
@@ -4070,6 +4242,7 @@
       <c r="O159" s="68" t="n"/>
       <c r="P159" s="61" t="n"/>
       <c r="Q159" s="61" t="n"/>
+      <c r="R159" s="89" t="n"/>
     </row>
     <row r="160" ht="12.75" customHeight="1" s="69">
       <c r="F160" s="65" t="n"/>
@@ -4084,6 +4257,7 @@
       <c r="O160" s="68" t="n"/>
       <c r="P160" s="61" t="n"/>
       <c r="Q160" s="61" t="n"/>
+      <c r="R160" s="89" t="n"/>
     </row>
     <row r="161" ht="12.75" customHeight="1" s="69">
       <c r="F161" s="65" t="n"/>
@@ -4098,6 +4272,7 @@
       <c r="O161" s="68" t="n"/>
       <c r="P161" s="61" t="n"/>
       <c r="Q161" s="61" t="n"/>
+      <c r="R161" s="89" t="n"/>
     </row>
     <row r="162" ht="12.75" customHeight="1" s="69">
       <c r="F162" s="65" t="n"/>
@@ -4112,6 +4287,7 @@
       <c r="O162" s="68" t="n"/>
       <c r="P162" s="61" t="n"/>
       <c r="Q162" s="61" t="n"/>
+      <c r="R162" s="89" t="n"/>
     </row>
     <row r="163" ht="12.75" customHeight="1" s="69">
       <c r="F163" s="65" t="n"/>
@@ -4126,6 +4302,7 @@
       <c r="O163" s="68" t="n"/>
       <c r="P163" s="61" t="n"/>
       <c r="Q163" s="61" t="n"/>
+      <c r="R163" s="89" t="n"/>
     </row>
     <row r="164" ht="12.75" customHeight="1" s="69">
       <c r="F164" s="65" t="n"/>
@@ -4140,6 +4317,7 @@
       <c r="O164" s="68" t="n"/>
       <c r="P164" s="61" t="n"/>
       <c r="Q164" s="61" t="n"/>
+      <c r="R164" s="89" t="n"/>
     </row>
     <row r="165" ht="12.75" customHeight="1" s="69">
       <c r="F165" s="65" t="n"/>
@@ -4154,6 +4332,7 @@
       <c r="O165" s="68" t="n"/>
       <c r="P165" s="61" t="n"/>
       <c r="Q165" s="61" t="n"/>
+      <c r="R165" s="89" t="n"/>
     </row>
     <row r="166" ht="12.75" customHeight="1" s="69">
       <c r="F166" s="65" t="n"/>
@@ -4168,6 +4347,7 @@
       <c r="O166" s="68" t="n"/>
       <c r="P166" s="61" t="n"/>
       <c r="Q166" s="61" t="n"/>
+      <c r="R166" s="89" t="n"/>
     </row>
     <row r="167" ht="12.75" customHeight="1" s="69">
       <c r="F167" s="65" t="n"/>
@@ -4182,6 +4362,7 @@
       <c r="O167" s="68" t="n"/>
       <c r="P167" s="61" t="n"/>
       <c r="Q167" s="61" t="n"/>
+      <c r="R167" s="89" t="n"/>
     </row>
     <row r="168" ht="12.75" customHeight="1" s="69">
       <c r="F168" s="65" t="n"/>
@@ -4196,6 +4377,7 @@
       <c r="O168" s="68" t="n"/>
       <c r="P168" s="61" t="n"/>
       <c r="Q168" s="61" t="n"/>
+      <c r="R168" s="89" t="n"/>
     </row>
     <row r="169" ht="12.75" customHeight="1" s="69">
       <c r="F169" s="65" t="n"/>
@@ -4210,6 +4392,7 @@
       <c r="O169" s="68" t="n"/>
       <c r="P169" s="61" t="n"/>
       <c r="Q169" s="61" t="n"/>
+      <c r="R169" s="89" t="n"/>
     </row>
     <row r="170" ht="12.75" customHeight="1" s="69">
       <c r="F170" s="65" t="n"/>
@@ -4224,6 +4407,7 @@
       <c r="O170" s="68" t="n"/>
       <c r="P170" s="61" t="n"/>
       <c r="Q170" s="61" t="n"/>
+      <c r="R170" s="89" t="n"/>
     </row>
     <row r="171" ht="12.75" customHeight="1" s="69">
       <c r="F171" s="65" t="n"/>
@@ -4238,6 +4422,7 @@
       <c r="O171" s="68" t="n"/>
       <c r="P171" s="61" t="n"/>
       <c r="Q171" s="61" t="n"/>
+      <c r="R171" s="89" t="n"/>
     </row>
     <row r="172" ht="12.75" customHeight="1" s="69">
       <c r="F172" s="65" t="n"/>
@@ -4252,6 +4437,7 @@
       <c r="O172" s="68" t="n"/>
       <c r="P172" s="61" t="n"/>
       <c r="Q172" s="61" t="n"/>
+      <c r="R172" s="89" t="n"/>
     </row>
     <row r="173" ht="12.75" customHeight="1" s="69">
       <c r="F173" s="65" t="n"/>
@@ -4266,6 +4452,7 @@
       <c r="O173" s="68" t="n"/>
       <c r="P173" s="61" t="n"/>
       <c r="Q173" s="61" t="n"/>
+      <c r="R173" s="89" t="n"/>
     </row>
     <row r="174" ht="12.75" customHeight="1" s="69">
       <c r="F174" s="65" t="n"/>
@@ -4280,6 +4467,7 @@
       <c r="O174" s="68" t="n"/>
       <c r="P174" s="61" t="n"/>
       <c r="Q174" s="61" t="n"/>
+      <c r="R174" s="89" t="n"/>
     </row>
     <row r="175" ht="12.75" customHeight="1" s="69">
       <c r="F175" s="65" t="n"/>
@@ -4294,6 +4482,7 @@
       <c r="O175" s="68" t="n"/>
       <c r="P175" s="61" t="n"/>
       <c r="Q175" s="61" t="n"/>
+      <c r="R175" s="89" t="n"/>
     </row>
     <row r="176" ht="12.75" customHeight="1" s="69">
       <c r="F176" s="65" t="n"/>
@@ -4308,6 +4497,7 @@
       <c r="O176" s="68" t="n"/>
       <c r="P176" s="61" t="n"/>
       <c r="Q176" s="61" t="n"/>
+      <c r="R176" s="89" t="n"/>
     </row>
     <row r="177" ht="12.75" customHeight="1" s="69">
       <c r="F177" s="65" t="n"/>
@@ -4322,6 +4512,7 @@
       <c r="O177" s="68" t="n"/>
       <c r="P177" s="61" t="n"/>
       <c r="Q177" s="61" t="n"/>
+      <c r="R177" s="89" t="n"/>
     </row>
     <row r="178" ht="12.75" customHeight="1" s="69">
       <c r="F178" s="65" t="n"/>
@@ -4336,6 +4527,7 @@
       <c r="O178" s="68" t="n"/>
       <c r="P178" s="61" t="n"/>
       <c r="Q178" s="61" t="n"/>
+      <c r="R178" s="89" t="n"/>
     </row>
     <row r="179" ht="12.75" customHeight="1" s="69">
       <c r="F179" s="65" t="n"/>
@@ -4350,6 +4542,7 @@
       <c r="O179" s="68" t="n"/>
       <c r="P179" s="61" t="n"/>
       <c r="Q179" s="61" t="n"/>
+      <c r="R179" s="89" t="n"/>
     </row>
     <row r="180" ht="12.75" customHeight="1" s="69">
       <c r="F180" s="65" t="n"/>
@@ -4364,6 +4557,7 @@
       <c r="O180" s="68" t="n"/>
       <c r="P180" s="61" t="n"/>
       <c r="Q180" s="61" t="n"/>
+      <c r="R180" s="89" t="n"/>
     </row>
     <row r="181" ht="12.75" customHeight="1" s="69">
       <c r="F181" s="65" t="n"/>
@@ -4378,6 +4572,7 @@
       <c r="O181" s="68" t="n"/>
       <c r="P181" s="61" t="n"/>
       <c r="Q181" s="61" t="n"/>
+      <c r="R181" s="89" t="n"/>
     </row>
     <row r="182" ht="12.75" customHeight="1" s="69">
       <c r="F182" s="65" t="n"/>
@@ -4392,6 +4587,7 @@
       <c r="O182" s="68" t="n"/>
       <c r="P182" s="61" t="n"/>
       <c r="Q182" s="61" t="n"/>
+      <c r="R182" s="89" t="n"/>
     </row>
     <row r="183" ht="12.75" customHeight="1" s="69">
       <c r="F183" s="65" t="n"/>
@@ -4406,6 +4602,7 @@
       <c r="O183" s="68" t="n"/>
       <c r="P183" s="61" t="n"/>
       <c r="Q183" s="61" t="n"/>
+      <c r="R183" s="89" t="n"/>
     </row>
     <row r="184" ht="12.75" customHeight="1" s="69">
       <c r="F184" s="65" t="n"/>
@@ -4420,6 +4617,7 @@
       <c r="O184" s="68" t="n"/>
       <c r="P184" s="61" t="n"/>
       <c r="Q184" s="61" t="n"/>
+      <c r="R184" s="89" t="n"/>
     </row>
     <row r="185" ht="12.75" customHeight="1" s="69">
       <c r="F185" s="65" t="n"/>
@@ -4434,6 +4632,7 @@
       <c r="O185" s="68" t="n"/>
       <c r="P185" s="61" t="n"/>
       <c r="Q185" s="61" t="n"/>
+      <c r="R185" s="89" t="n"/>
     </row>
     <row r="186" ht="12.75" customHeight="1" s="69">
       <c r="F186" s="65" t="n"/>
@@ -4448,6 +4647,7 @@
       <c r="O186" s="68" t="n"/>
       <c r="P186" s="61" t="n"/>
       <c r="Q186" s="61" t="n"/>
+      <c r="R186" s="89" t="n"/>
     </row>
     <row r="187" ht="12.75" customHeight="1" s="69">
       <c r="F187" s="65" t="n"/>
@@ -4462,6 +4662,7 @@
       <c r="O187" s="68" t="n"/>
       <c r="P187" s="61" t="n"/>
       <c r="Q187" s="61" t="n"/>
+      <c r="R187" s="89" t="n"/>
     </row>
     <row r="188" ht="12.75" customHeight="1" s="69">
       <c r="F188" s="65" t="n"/>
@@ -4476,6 +4677,7 @@
       <c r="O188" s="68" t="n"/>
       <c r="P188" s="61" t="n"/>
       <c r="Q188" s="61" t="n"/>
+      <c r="R188" s="89" t="n"/>
     </row>
     <row r="189" ht="12.75" customHeight="1" s="69">
       <c r="F189" s="65" t="n"/>
@@ -4490,6 +4692,7 @@
       <c r="O189" s="68" t="n"/>
       <c r="P189" s="61" t="n"/>
       <c r="Q189" s="61" t="n"/>
+      <c r="R189" s="89" t="n"/>
     </row>
     <row r="190" ht="12.75" customHeight="1" s="69">
       <c r="F190" s="65" t="n"/>
@@ -4504,6 +4707,7 @@
       <c r="O190" s="68" t="n"/>
       <c r="P190" s="61" t="n"/>
       <c r="Q190" s="61" t="n"/>
+      <c r="R190" s="89" t="n"/>
     </row>
     <row r="191" ht="12.75" customHeight="1" s="69">
       <c r="F191" s="65" t="n"/>
@@ -4518,6 +4722,7 @@
       <c r="O191" s="68" t="n"/>
       <c r="P191" s="61" t="n"/>
       <c r="Q191" s="61" t="n"/>
+      <c r="R191" s="89" t="n"/>
     </row>
     <row r="192" ht="12.75" customHeight="1" s="69">
       <c r="F192" s="65" t="n"/>
@@ -4532,6 +4737,7 @@
       <c r="O192" s="68" t="n"/>
       <c r="P192" s="61" t="n"/>
       <c r="Q192" s="61" t="n"/>
+      <c r="R192" s="89" t="n"/>
     </row>
     <row r="193" ht="12.75" customHeight="1" s="69">
       <c r="F193" s="65" t="n"/>
@@ -4546,6 +4752,7 @@
       <c r="O193" s="68" t="n"/>
       <c r="P193" s="61" t="n"/>
       <c r="Q193" s="61" t="n"/>
+      <c r="R193" s="89" t="n"/>
     </row>
     <row r="194" ht="12.75" customHeight="1" s="69">
       <c r="F194" s="65" t="n"/>
@@ -4560,6 +4767,7 @@
       <c r="O194" s="68" t="n"/>
       <c r="P194" s="61" t="n"/>
       <c r="Q194" s="61" t="n"/>
+      <c r="R194" s="89" t="n"/>
     </row>
     <row r="195" ht="12.75" customHeight="1" s="69">
       <c r="F195" s="65" t="n"/>
@@ -4574,6 +4782,7 @@
       <c r="O195" s="68" t="n"/>
       <c r="P195" s="61" t="n"/>
       <c r="Q195" s="61" t="n"/>
+      <c r="R195" s="89" t="n"/>
     </row>
     <row r="196" ht="12.75" customHeight="1" s="69">
       <c r="F196" s="65" t="n"/>
@@ -4588,6 +4797,7 @@
       <c r="O196" s="68" t="n"/>
       <c r="P196" s="61" t="n"/>
       <c r="Q196" s="61" t="n"/>
+      <c r="R196" s="89" t="n"/>
     </row>
     <row r="197" ht="12.75" customHeight="1" s="69">
       <c r="F197" s="65" t="n"/>
@@ -4602,6 +4812,7 @@
       <c r="O197" s="68" t="n"/>
       <c r="P197" s="61" t="n"/>
       <c r="Q197" s="61" t="n"/>
+      <c r="R197" s="89" t="n"/>
     </row>
     <row r="198" ht="12.75" customHeight="1" s="69">
       <c r="F198" s="65" t="n"/>
@@ -4616,6 +4827,7 @@
       <c r="O198" s="68" t="n"/>
       <c r="P198" s="61" t="n"/>
       <c r="Q198" s="61" t="n"/>
+      <c r="R198" s="89" t="n"/>
     </row>
     <row r="199" ht="12.75" customHeight="1" s="69">
       <c r="F199" s="65" t="n"/>
@@ -4630,6 +4842,7 @@
       <c r="O199" s="68" t="n"/>
       <c r="P199" s="61" t="n"/>
       <c r="Q199" s="61" t="n"/>
+      <c r="R199" s="89" t="n"/>
     </row>
     <row r="200" ht="12.75" customHeight="1" s="69">
       <c r="F200" s="65" t="n"/>
@@ -4644,6 +4857,7 @@
       <c r="O200" s="68" t="n"/>
       <c r="P200" s="61" t="n"/>
       <c r="Q200" s="61" t="n"/>
+      <c r="R200" s="89" t="n"/>
     </row>
     <row r="201" ht="12.75" customHeight="1" s="69">
       <c r="F201" s="65" t="n"/>
@@ -4658,6 +4872,7 @@
       <c r="O201" s="68" t="n"/>
       <c r="P201" s="61" t="n"/>
       <c r="Q201" s="61" t="n"/>
+      <c r="R201" s="89" t="n"/>
     </row>
     <row r="202" ht="12.75" customHeight="1" s="69">
       <c r="F202" s="65" t="n"/>
@@ -4672,6 +4887,7 @@
       <c r="O202" s="68" t="n"/>
       <c r="P202" s="61" t="n"/>
       <c r="Q202" s="61" t="n"/>
+      <c r="R202" s="89" t="n"/>
     </row>
     <row r="203" ht="12.75" customHeight="1" s="69">
       <c r="F203" s="65" t="n"/>
@@ -4686,6 +4902,7 @@
       <c r="O203" s="68" t="n"/>
       <c r="P203" s="61" t="n"/>
       <c r="Q203" s="61" t="n"/>
+      <c r="R203" s="89" t="n"/>
     </row>
     <row r="204" ht="12.75" customHeight="1" s="69">
       <c r="F204" s="65" t="n"/>
@@ -4700,6 +4917,7 @@
       <c r="O204" s="68" t="n"/>
       <c r="P204" s="61" t="n"/>
       <c r="Q204" s="61" t="n"/>
+      <c r="R204" s="89" t="n"/>
     </row>
     <row r="205" ht="12.75" customHeight="1" s="69">
       <c r="F205" s="65" t="n"/>
@@ -4714,6 +4932,7 @@
       <c r="O205" s="68" t="n"/>
       <c r="P205" s="61" t="n"/>
       <c r="Q205" s="61" t="n"/>
+      <c r="R205" s="89" t="n"/>
     </row>
     <row r="206" ht="12.75" customHeight="1" s="69">
       <c r="F206" s="65" t="n"/>
@@ -4728,6 +4947,7 @@
       <c r="O206" s="68" t="n"/>
       <c r="P206" s="61" t="n"/>
       <c r="Q206" s="61" t="n"/>
+      <c r="R206" s="89" t="n"/>
     </row>
     <row r="207" ht="12.75" customHeight="1" s="69">
       <c r="F207" s="65" t="n"/>
@@ -4742,6 +4962,7 @@
       <c r="O207" s="68" t="n"/>
       <c r="P207" s="61" t="n"/>
       <c r="Q207" s="61" t="n"/>
+      <c r="R207" s="89" t="n"/>
     </row>
     <row r="208" ht="12.75" customHeight="1" s="69">
       <c r="F208" s="65" t="n"/>
@@ -4756,6 +4977,7 @@
       <c r="O208" s="68" t="n"/>
       <c r="P208" s="61" t="n"/>
       <c r="Q208" s="61" t="n"/>
+      <c r="R208" s="89" t="n"/>
     </row>
     <row r="209" ht="12.75" customHeight="1" s="69">
       <c r="F209" s="65" t="n"/>
@@ -4770,6 +4992,7 @@
       <c r="O209" s="68" t="n"/>
       <c r="P209" s="61" t="n"/>
       <c r="Q209" s="61" t="n"/>
+      <c r="R209" s="89" t="n"/>
     </row>
     <row r="210" ht="12.75" customHeight="1" s="69">
       <c r="F210" s="65" t="n"/>
@@ -4784,6 +5007,7 @@
       <c r="O210" s="68" t="n"/>
       <c r="P210" s="61" t="n"/>
       <c r="Q210" s="61" t="n"/>
+      <c r="R210" s="89" t="n"/>
     </row>
     <row r="211" ht="12.75" customHeight="1" s="69">
       <c r="F211" s="65" t="n"/>
@@ -4798,6 +5022,7 @@
       <c r="O211" s="68" t="n"/>
       <c r="P211" s="61" t="n"/>
       <c r="Q211" s="61" t="n"/>
+      <c r="R211" s="89" t="n"/>
     </row>
     <row r="212" ht="12.75" customHeight="1" s="69">
       <c r="F212" s="65" t="n"/>
@@ -4812,6 +5037,7 @@
       <c r="O212" s="68" t="n"/>
       <c r="P212" s="61" t="n"/>
       <c r="Q212" s="61" t="n"/>
+      <c r="R212" s="89" t="n"/>
     </row>
     <row r="213" ht="12.75" customHeight="1" s="69">
       <c r="F213" s="65" t="n"/>
@@ -4826,6 +5052,7 @@
       <c r="O213" s="68" t="n"/>
       <c r="P213" s="61" t="n"/>
       <c r="Q213" s="61" t="n"/>
+      <c r="R213" s="89" t="n"/>
     </row>
     <row r="214" ht="12.75" customHeight="1" s="69">
       <c r="F214" s="65" t="n"/>
@@ -4840,6 +5067,7 @@
       <c r="O214" s="68" t="n"/>
       <c r="P214" s="61" t="n"/>
       <c r="Q214" s="61" t="n"/>
+      <c r="R214" s="89" t="n"/>
     </row>
     <row r="215" ht="12.75" customHeight="1" s="69">
       <c r="F215" s="65" t="n"/>
@@ -4854,6 +5082,7 @@
       <c r="O215" s="68" t="n"/>
       <c r="P215" s="61" t="n"/>
       <c r="Q215" s="61" t="n"/>
+      <c r="R215" s="89" t="n"/>
     </row>
     <row r="216" ht="12.75" customHeight="1" s="69">
       <c r="F216" s="65" t="n"/>
@@ -4868,6 +5097,7 @@
       <c r="O216" s="68" t="n"/>
       <c r="P216" s="61" t="n"/>
       <c r="Q216" s="61" t="n"/>
+      <c r="R216" s="89" t="n"/>
     </row>
     <row r="217" ht="12.75" customHeight="1" s="69">
       <c r="F217" s="65" t="n"/>
@@ -4882,6 +5112,7 @@
       <c r="O217" s="68" t="n"/>
       <c r="P217" s="61" t="n"/>
       <c r="Q217" s="61" t="n"/>
+      <c r="R217" s="89" t="n"/>
     </row>
     <row r="218" ht="12.75" customHeight="1" s="69">
       <c r="F218" s="65" t="n"/>
@@ -4896,6 +5127,7 @@
       <c r="O218" s="68" t="n"/>
       <c r="P218" s="61" t="n"/>
       <c r="Q218" s="61" t="n"/>
+      <c r="R218" s="89" t="n"/>
     </row>
     <row r="219" ht="12.75" customHeight="1" s="69">
       <c r="F219" s="65" t="n"/>
@@ -4910,6 +5142,7 @@
       <c r="O219" s="68" t="n"/>
       <c r="P219" s="61" t="n"/>
       <c r="Q219" s="61" t="n"/>
+      <c r="R219" s="89" t="n"/>
     </row>
     <row r="220" ht="12.75" customHeight="1" s="69">
       <c r="F220" s="65" t="n"/>
@@ -4924,6 +5157,7 @@
       <c r="O220" s="68" t="n"/>
       <c r="P220" s="61" t="n"/>
       <c r="Q220" s="61" t="n"/>
+      <c r="R220" s="89" t="n"/>
     </row>
     <row r="221" ht="12.75" customHeight="1" s="69">
       <c r="F221" s="65" t="n"/>
@@ -4938,6 +5172,7 @@
       <c r="O221" s="68" t="n"/>
       <c r="P221" s="61" t="n"/>
       <c r="Q221" s="61" t="n"/>
+      <c r="R221" s="89" t="n"/>
     </row>
     <row r="222" ht="12.75" customHeight="1" s="69">
       <c r="F222" s="65" t="n"/>
@@ -4952,6 +5187,7 @@
       <c r="O222" s="68" t="n"/>
       <c r="P222" s="61" t="n"/>
       <c r="Q222" s="61" t="n"/>
+      <c r="R222" s="89" t="n"/>
     </row>
     <row r="223" ht="12.75" customHeight="1" s="69">
       <c r="F223" s="65" t="n"/>
@@ -4966,6 +5202,7 @@
       <c r="O223" s="68" t="n"/>
       <c r="P223" s="61" t="n"/>
       <c r="Q223" s="61" t="n"/>
+      <c r="R223" s="89" t="n"/>
     </row>
     <row r="224" ht="12.75" customHeight="1" s="69">
       <c r="F224" s="65" t="n"/>
@@ -4980,6 +5217,7 @@
       <c r="O224" s="68" t="n"/>
       <c r="P224" s="61" t="n"/>
       <c r="Q224" s="61" t="n"/>
+      <c r="R224" s="89" t="n"/>
     </row>
     <row r="225" ht="12.75" customHeight="1" s="69">
       <c r="F225" s="65" t="n"/>
@@ -4994,6 +5232,7 @@
       <c r="O225" s="68" t="n"/>
       <c r="P225" s="61" t="n"/>
       <c r="Q225" s="61" t="n"/>
+      <c r="R225" s="89" t="n"/>
     </row>
     <row r="226" ht="12.75" customHeight="1" s="69">
       <c r="F226" s="65" t="n"/>
@@ -5008,6 +5247,7 @@
       <c r="O226" s="68" t="n"/>
       <c r="P226" s="61" t="n"/>
       <c r="Q226" s="61" t="n"/>
+      <c r="R226" s="89" t="n"/>
     </row>
     <row r="227" ht="12.75" customHeight="1" s="69">
       <c r="F227" s="65" t="n"/>
@@ -5022,6 +5262,7 @@
       <c r="O227" s="68" t="n"/>
       <c r="P227" s="61" t="n"/>
       <c r="Q227" s="61" t="n"/>
+      <c r="R227" s="89" t="n"/>
     </row>
     <row r="228" ht="12.75" customHeight="1" s="69">
       <c r="F228" s="65" t="n"/>
@@ -5036,6 +5277,7 @@
       <c r="O228" s="68" t="n"/>
       <c r="P228" s="61" t="n"/>
       <c r="Q228" s="61" t="n"/>
+      <c r="R228" s="89" t="n"/>
     </row>
     <row r="229" ht="12.75" customHeight="1" s="69">
       <c r="F229" s="65" t="n"/>
@@ -5050,6 +5292,7 @@
       <c r="O229" s="68" t="n"/>
       <c r="P229" s="61" t="n"/>
       <c r="Q229" s="61" t="n"/>
+      <c r="R229" s="89" t="n"/>
     </row>
     <row r="230" ht="12.75" customHeight="1" s="69">
       <c r="F230" s="65" t="n"/>
@@ -5064,6 +5307,7 @@
       <c r="O230" s="68" t="n"/>
       <c r="P230" s="61" t="n"/>
       <c r="Q230" s="61" t="n"/>
+      <c r="R230" s="89" t="n"/>
     </row>
     <row r="231" ht="12.75" customHeight="1" s="69">
       <c r="F231" s="65" t="n"/>
@@ -5078,6 +5322,7 @@
       <c r="O231" s="68" t="n"/>
       <c r="P231" s="61" t="n"/>
       <c r="Q231" s="61" t="n"/>
+      <c r="R231" s="89" t="n"/>
     </row>
     <row r="232" ht="12.75" customHeight="1" s="69">
       <c r="F232" s="65" t="n"/>
@@ -5092,6 +5337,7 @@
       <c r="O232" s="68" t="n"/>
       <c r="P232" s="61" t="n"/>
       <c r="Q232" s="61" t="n"/>
+      <c r="R232" s="89" t="n"/>
     </row>
     <row r="233" ht="12.75" customHeight="1" s="69">
       <c r="F233" s="65" t="n"/>
@@ -5106,6 +5352,7 @@
       <c r="O233" s="68" t="n"/>
       <c r="P233" s="61" t="n"/>
       <c r="Q233" s="61" t="n"/>
+      <c r="R233" s="89" t="n"/>
     </row>
     <row r="234" ht="12.75" customHeight="1" s="69">
       <c r="F234" s="65" t="n"/>
@@ -5120,6 +5367,7 @@
       <c r="O234" s="68" t="n"/>
       <c r="P234" s="61" t="n"/>
       <c r="Q234" s="61" t="n"/>
+      <c r="R234" s="89" t="n"/>
     </row>
     <row r="235" ht="12.75" customHeight="1" s="69">
       <c r="F235" s="65" t="n"/>
@@ -5134,6 +5382,7 @@
       <c r="O235" s="68" t="n"/>
       <c r="P235" s="61" t="n"/>
       <c r="Q235" s="61" t="n"/>
+      <c r="R235" s="89" t="n"/>
     </row>
     <row r="236" ht="12.75" customHeight="1" s="69">
       <c r="F236" s="65" t="n"/>
@@ -5148,6 +5397,7 @@
       <c r="O236" s="68" t="n"/>
       <c r="P236" s="61" t="n"/>
       <c r="Q236" s="61" t="n"/>
+      <c r="R236" s="89" t="n"/>
     </row>
     <row r="237" ht="12.75" customHeight="1" s="69">
       <c r="F237" s="65" t="n"/>
@@ -5162,6 +5412,7 @@
       <c r="O237" s="68" t="n"/>
       <c r="P237" s="61" t="n"/>
       <c r="Q237" s="61" t="n"/>
+      <c r="R237" s="89" t="n"/>
     </row>
     <row r="238" ht="12.75" customHeight="1" s="69">
       <c r="F238" s="65" t="n"/>
@@ -5176,6 +5427,7 @@
       <c r="O238" s="68" t="n"/>
       <c r="P238" s="61" t="n"/>
       <c r="Q238" s="61" t="n"/>
+      <c r="R238" s="89" t="n"/>
     </row>
     <row r="239" ht="12.75" customHeight="1" s="69">
       <c r="F239" s="65" t="n"/>
@@ -5190,6 +5442,7 @@
       <c r="O239" s="68" t="n"/>
       <c r="P239" s="61" t="n"/>
       <c r="Q239" s="61" t="n"/>
+      <c r="R239" s="89" t="n"/>
     </row>
     <row r="240" ht="12.75" customHeight="1" s="69">
       <c r="F240" s="65" t="n"/>
@@ -5204,6 +5457,7 @@
       <c r="O240" s="68" t="n"/>
       <c r="P240" s="61" t="n"/>
       <c r="Q240" s="61" t="n"/>
+      <c r="R240" s="89" t="n"/>
     </row>
     <row r="241" ht="12.75" customHeight="1" s="69">
       <c r="F241" s="65" t="n"/>
@@ -5218,6 +5472,7 @@
       <c r="O241" s="68" t="n"/>
       <c r="P241" s="61" t="n"/>
       <c r="Q241" s="61" t="n"/>
+      <c r="R241" s="89" t="n"/>
     </row>
     <row r="242" ht="12.75" customHeight="1" s="69">
       <c r="F242" s="65" t="n"/>
@@ -5232,6 +5487,7 @@
       <c r="O242" s="68" t="n"/>
       <c r="P242" s="61" t="n"/>
       <c r="Q242" s="61" t="n"/>
+      <c r="R242" s="89" t="n"/>
     </row>
     <row r="243" ht="12.75" customHeight="1" s="69">
       <c r="F243" s="65" t="n"/>
@@ -5246,6 +5502,7 @@
       <c r="O243" s="68" t="n"/>
       <c r="P243" s="61" t="n"/>
       <c r="Q243" s="61" t="n"/>
+      <c r="R243" s="89" t="n"/>
     </row>
     <row r="244" ht="12.75" customHeight="1" s="69">
       <c r="F244" s="65" t="n"/>
@@ -5260,6 +5517,7 @@
       <c r="O244" s="68" t="n"/>
       <c r="P244" s="61" t="n"/>
       <c r="Q244" s="61" t="n"/>
+      <c r="R244" s="89" t="n"/>
     </row>
     <row r="245" ht="12.75" customHeight="1" s="69">
       <c r="F245" s="65" t="n"/>
@@ -5274,6 +5532,7 @@
       <c r="O245" s="68" t="n"/>
       <c r="P245" s="61" t="n"/>
       <c r="Q245" s="61" t="n"/>
+      <c r="R245" s="89" t="n"/>
     </row>
     <row r="246" ht="12.75" customHeight="1" s="69">
       <c r="F246" s="65" t="n"/>
@@ -5288,6 +5547,7 @@
       <c r="O246" s="68" t="n"/>
       <c r="P246" s="61" t="n"/>
       <c r="Q246" s="61" t="n"/>
+      <c r="R246" s="89" t="n"/>
     </row>
     <row r="247" ht="12.75" customHeight="1" s="69">
       <c r="F247" s="65" t="n"/>
@@ -5302,6 +5562,7 @@
       <c r="O247" s="68" t="n"/>
       <c r="P247" s="61" t="n"/>
       <c r="Q247" s="61" t="n"/>
+      <c r="R247" s="89" t="n"/>
     </row>
     <row r="248" ht="12.75" customHeight="1" s="69">
       <c r="F248" s="65" t="n"/>
@@ -5316,6 +5577,7 @@
       <c r="O248" s="68" t="n"/>
       <c r="P248" s="61" t="n"/>
       <c r="Q248" s="61" t="n"/>
+      <c r="R248" s="89" t="n"/>
     </row>
     <row r="249" ht="12.75" customHeight="1" s="69">
       <c r="F249" s="65" t="n"/>
@@ -5330,6 +5592,7 @@
       <c r="O249" s="68" t="n"/>
       <c r="P249" s="61" t="n"/>
       <c r="Q249" s="61" t="n"/>
+      <c r="R249" s="89" t="n"/>
     </row>
     <row r="250" ht="12.75" customHeight="1" s="69">
       <c r="F250" s="65" t="n"/>
@@ -5344,6 +5607,7 @@
       <c r="O250" s="68" t="n"/>
       <c r="P250" s="61" t="n"/>
       <c r="Q250" s="61" t="n"/>
+      <c r="R250" s="89" t="n"/>
     </row>
     <row r="251" ht="12.75" customHeight="1" s="69">
       <c r="F251" s="65" t="n"/>
@@ -5358,6 +5622,7 @@
       <c r="O251" s="68" t="n"/>
       <c r="P251" s="61" t="n"/>
       <c r="Q251" s="61" t="n"/>
+      <c r="R251" s="89" t="n"/>
     </row>
     <row r="252" ht="12.75" customHeight="1" s="69">
       <c r="F252" s="65" t="n"/>
@@ -5372,6 +5637,7 @@
       <c r="O252" s="68" t="n"/>
       <c r="P252" s="61" t="n"/>
       <c r="Q252" s="61" t="n"/>
+      <c r="R252" s="89" t="n"/>
     </row>
     <row r="253" ht="12.75" customHeight="1" s="69">
       <c r="F253" s="65" t="n"/>
@@ -5386,6 +5652,7 @@
       <c r="O253" s="68" t="n"/>
       <c r="P253" s="61" t="n"/>
       <c r="Q253" s="61" t="n"/>
+      <c r="R253" s="89" t="n"/>
     </row>
     <row r="254" ht="12.75" customHeight="1" s="69">
       <c r="F254" s="65" t="n"/>
@@ -5400,6 +5667,7 @@
       <c r="O254" s="68" t="n"/>
       <c r="P254" s="61" t="n"/>
       <c r="Q254" s="61" t="n"/>
+      <c r="R254" s="89" t="n"/>
     </row>
     <row r="255" ht="12.75" customHeight="1" s="69">
       <c r="F255" s="65" t="n"/>
@@ -5414,6 +5682,7 @@
       <c r="O255" s="68" t="n"/>
       <c r="P255" s="61" t="n"/>
       <c r="Q255" s="61" t="n"/>
+      <c r="R255" s="89" t="n"/>
     </row>
     <row r="256" ht="12.75" customHeight="1" s="69">
       <c r="F256" s="65" t="n"/>
@@ -5428,6 +5697,7 @@
       <c r="O256" s="68" t="n"/>
       <c r="P256" s="61" t="n"/>
       <c r="Q256" s="61" t="n"/>
+      <c r="R256" s="89" t="n"/>
     </row>
     <row r="257" ht="12.75" customHeight="1" s="69">
       <c r="F257" s="65" t="n"/>
@@ -5442,6 +5712,7 @@
       <c r="O257" s="68" t="n"/>
       <c r="P257" s="61" t="n"/>
       <c r="Q257" s="61" t="n"/>
+      <c r="R257" s="89" t="n"/>
     </row>
     <row r="258" ht="12.75" customHeight="1" s="69">
       <c r="F258" s="65" t="n"/>
@@ -5456,6 +5727,7 @@
       <c r="O258" s="68" t="n"/>
       <c r="P258" s="61" t="n"/>
       <c r="Q258" s="61" t="n"/>
+      <c r="R258" s="89" t="n"/>
     </row>
     <row r="259" ht="12.75" customHeight="1" s="69">
       <c r="F259" s="65" t="n"/>
@@ -5470,6 +5742,7 @@
       <c r="O259" s="68" t="n"/>
       <c r="P259" s="61" t="n"/>
       <c r="Q259" s="61" t="n"/>
+      <c r="R259" s="89" t="n"/>
     </row>
     <row r="260" ht="12.75" customHeight="1" s="69">
       <c r="F260" s="65" t="n"/>
@@ -5484,6 +5757,7 @@
       <c r="O260" s="68" t="n"/>
       <c r="P260" s="61" t="n"/>
       <c r="Q260" s="61" t="n"/>
+      <c r="R260" s="89" t="n"/>
     </row>
     <row r="261" ht="12.75" customHeight="1" s="69">
       <c r="F261" s="65" t="n"/>
@@ -5498,6 +5772,7 @@
       <c r="O261" s="68" t="n"/>
       <c r="P261" s="61" t="n"/>
       <c r="Q261" s="61" t="n"/>
+      <c r="R261" s="89" t="n"/>
     </row>
     <row r="262" ht="12.75" customHeight="1" s="69">
       <c r="F262" s="65" t="n"/>
@@ -5512,6 +5787,7 @@
       <c r="O262" s="68" t="n"/>
       <c r="P262" s="61" t="n"/>
       <c r="Q262" s="61" t="n"/>
+      <c r="R262" s="89" t="n"/>
     </row>
     <row r="263" ht="12.75" customHeight="1" s="69">
       <c r="F263" s="65" t="n"/>
@@ -5526,6 +5802,7 @@
       <c r="O263" s="68" t="n"/>
       <c r="P263" s="61" t="n"/>
       <c r="Q263" s="61" t="n"/>
+      <c r="R263" s="89" t="n"/>
     </row>
     <row r="264" ht="12.75" customHeight="1" s="69">
       <c r="F264" s="65" t="n"/>
@@ -5540,6 +5817,7 @@
       <c r="O264" s="68" t="n"/>
       <c r="P264" s="61" t="n"/>
       <c r="Q264" s="61" t="n"/>
+      <c r="R264" s="89" t="n"/>
     </row>
     <row r="265" ht="12.75" customHeight="1" s="69">
       <c r="F265" s="65" t="n"/>
@@ -5554,6 +5832,7 @@
       <c r="O265" s="68" t="n"/>
       <c r="P265" s="61" t="n"/>
       <c r="Q265" s="61" t="n"/>
+      <c r="R265" s="89" t="n"/>
     </row>
     <row r="266" ht="12.75" customHeight="1" s="69">
       <c r="F266" s="65" t="n"/>
@@ -5568,6 +5847,7 @@
       <c r="O266" s="68" t="n"/>
       <c r="P266" s="61" t="n"/>
       <c r="Q266" s="61" t="n"/>
+      <c r="R266" s="89" t="n"/>
     </row>
     <row r="267" ht="12.75" customHeight="1" s="69">
       <c r="F267" s="65" t="n"/>
@@ -5582,6 +5862,7 @@
       <c r="O267" s="68" t="n"/>
       <c r="P267" s="61" t="n"/>
       <c r="Q267" s="61" t="n"/>
+      <c r="R267" s="89" t="n"/>
     </row>
     <row r="268" ht="12.75" customHeight="1" s="69">
       <c r="F268" s="65" t="n"/>
@@ -5596,6 +5877,7 @@
       <c r="O268" s="68" t="n"/>
       <c r="P268" s="61" t="n"/>
       <c r="Q268" s="61" t="n"/>
+      <c r="R268" s="89" t="n"/>
     </row>
     <row r="269" ht="12.75" customHeight="1" s="69">
       <c r="F269" s="65" t="n"/>
@@ -5610,6 +5892,7 @@
       <c r="O269" s="68" t="n"/>
       <c r="P269" s="61" t="n"/>
       <c r="Q269" s="61" t="n"/>
+      <c r="R269" s="89" t="n"/>
     </row>
     <row r="270" ht="12.75" customHeight="1" s="69">
       <c r="F270" s="65" t="n"/>
@@ -5624,6 +5907,7 @@
       <c r="O270" s="68" t="n"/>
       <c r="P270" s="61" t="n"/>
       <c r="Q270" s="61" t="n"/>
+      <c r="R270" s="89" t="n"/>
     </row>
     <row r="271" ht="12.75" customHeight="1" s="69">
       <c r="F271" s="65" t="n"/>
@@ -5638,6 +5922,7 @@
       <c r="O271" s="68" t="n"/>
       <c r="P271" s="61" t="n"/>
       <c r="Q271" s="61" t="n"/>
+      <c r="R271" s="89" t="n"/>
     </row>
     <row r="272" ht="12.75" customHeight="1" s="69">
       <c r="F272" s="65" t="n"/>
@@ -5652,6 +5937,7 @@
       <c r="O272" s="68" t="n"/>
       <c r="P272" s="61" t="n"/>
       <c r="Q272" s="61" t="n"/>
+      <c r="R272" s="89" t="n"/>
     </row>
     <row r="273" ht="12.75" customHeight="1" s="69">
       <c r="F273" s="65" t="n"/>
@@ -5666,6 +5952,7 @@
       <c r="O273" s="68" t="n"/>
       <c r="P273" s="61" t="n"/>
       <c r="Q273" s="61" t="n"/>
+      <c r="R273" s="89" t="n"/>
     </row>
     <row r="274" ht="12.75" customHeight="1" s="69">
       <c r="F274" s="65" t="n"/>
@@ -5680,6 +5967,7 @@
       <c r="O274" s="68" t="n"/>
       <c r="P274" s="61" t="n"/>
       <c r="Q274" s="61" t="n"/>
+      <c r="R274" s="89" t="n"/>
     </row>
     <row r="275" ht="12.75" customHeight="1" s="69">
       <c r="F275" s="65" t="n"/>
@@ -5694,6 +5982,7 @@
       <c r="O275" s="68" t="n"/>
       <c r="P275" s="61" t="n"/>
       <c r="Q275" s="61" t="n"/>
+      <c r="R275" s="89" t="n"/>
     </row>
     <row r="276" ht="12.75" customHeight="1" s="69">
       <c r="F276" s="65" t="n"/>
@@ -5708,6 +5997,7 @@
       <c r="O276" s="68" t="n"/>
       <c r="P276" s="61" t="n"/>
       <c r="Q276" s="61" t="n"/>
+      <c r="R276" s="89" t="n"/>
     </row>
     <row r="277" ht="12.75" customHeight="1" s="69">
       <c r="F277" s="65" t="n"/>
@@ -5722,6 +6012,7 @@
       <c r="O277" s="68" t="n"/>
       <c r="P277" s="61" t="n"/>
       <c r="Q277" s="61" t="n"/>
+      <c r="R277" s="89" t="n"/>
     </row>
     <row r="278" ht="12.75" customHeight="1" s="69">
       <c r="F278" s="65" t="n"/>
@@ -5736,6 +6027,7 @@
       <c r="O278" s="68" t="n"/>
       <c r="P278" s="61" t="n"/>
       <c r="Q278" s="61" t="n"/>
+      <c r="R278" s="89" t="n"/>
     </row>
     <row r="279" ht="12.75" customHeight="1" s="69">
       <c r="F279" s="65" t="n"/>
@@ -5750,6 +6042,7 @@
       <c r="O279" s="68" t="n"/>
       <c r="P279" s="61" t="n"/>
       <c r="Q279" s="61" t="n"/>
+      <c r="R279" s="89" t="n"/>
     </row>
     <row r="280" ht="12.75" customHeight="1" s="69">
       <c r="F280" s="65" t="n"/>
@@ -5764,6 +6057,7 @@
       <c r="O280" s="68" t="n"/>
       <c r="P280" s="61" t="n"/>
       <c r="Q280" s="61" t="n"/>
+      <c r="R280" s="89" t="n"/>
     </row>
     <row r="281" ht="12.75" customHeight="1" s="69">
       <c r="F281" s="65" t="n"/>
@@ -5778,6 +6072,7 @@
       <c r="O281" s="68" t="n"/>
       <c r="P281" s="61" t="n"/>
       <c r="Q281" s="61" t="n"/>
+      <c r="R281" s="89" t="n"/>
     </row>
     <row r="282" ht="12.75" customHeight="1" s="69">
       <c r="F282" s="65" t="n"/>
@@ -5792,6 +6087,7 @@
       <c r="O282" s="68" t="n"/>
       <c r="P282" s="61" t="n"/>
       <c r="Q282" s="61" t="n"/>
+      <c r="R282" s="89" t="n"/>
     </row>
     <row r="283" ht="12.75" customHeight="1" s="69">
       <c r="F283" s="65" t="n"/>
@@ -5806,6 +6102,7 @@
       <c r="O283" s="68" t="n"/>
       <c r="P283" s="61" t="n"/>
       <c r="Q283" s="61" t="n"/>
+      <c r="R283" s="89" t="n"/>
     </row>
     <row r="284" ht="12.75" customHeight="1" s="69">
       <c r="F284" s="65" t="n"/>
@@ -5820,6 +6117,7 @@
       <c r="O284" s="68" t="n"/>
       <c r="P284" s="61" t="n"/>
       <c r="Q284" s="61" t="n"/>
+      <c r="R284" s="89" t="n"/>
     </row>
     <row r="285" ht="12.75" customHeight="1" s="69">
       <c r="F285" s="65" t="n"/>
@@ -5834,6 +6132,7 @@
       <c r="O285" s="68" t="n"/>
       <c r="P285" s="61" t="n"/>
       <c r="Q285" s="61" t="n"/>
+      <c r="R285" s="89" t="n"/>
     </row>
     <row r="286" ht="12.75" customHeight="1" s="69">
       <c r="F286" s="65" t="n"/>
@@ -5848,6 +6147,7 @@
       <c r="O286" s="68" t="n"/>
       <c r="P286" s="61" t="n"/>
       <c r="Q286" s="61" t="n"/>
+      <c r="R286" s="89" t="n"/>
     </row>
     <row r="287" ht="12.75" customHeight="1" s="69">
       <c r="F287" s="65" t="n"/>
@@ -5862,6 +6162,7 @@
       <c r="O287" s="68" t="n"/>
       <c r="P287" s="61" t="n"/>
       <c r="Q287" s="61" t="n"/>
+      <c r="R287" s="89" t="n"/>
     </row>
     <row r="288" ht="12.75" customHeight="1" s="69">
       <c r="F288" s="65" t="n"/>
@@ -5876,6 +6177,7 @@
       <c r="O288" s="68" t="n"/>
       <c r="P288" s="61" t="n"/>
       <c r="Q288" s="61" t="n"/>
+      <c r="R288" s="89" t="n"/>
     </row>
     <row r="289" ht="12.75" customHeight="1" s="69">
       <c r="F289" s="65" t="n"/>
@@ -5890,6 +6192,7 @@
       <c r="O289" s="68" t="n"/>
       <c r="P289" s="61" t="n"/>
       <c r="Q289" s="61" t="n"/>
+      <c r="R289" s="89" t="n"/>
     </row>
     <row r="290" ht="12.75" customHeight="1" s="69">
       <c r="F290" s="65" t="n"/>
@@ -5904,6 +6207,7 @@
       <c r="O290" s="68" t="n"/>
       <c r="P290" s="61" t="n"/>
       <c r="Q290" s="61" t="n"/>
+      <c r="R290" s="89" t="n"/>
     </row>
     <row r="291" ht="12.75" customHeight="1" s="69">
       <c r="F291" s="65" t="n"/>
@@ -5918,6 +6222,7 @@
       <c r="O291" s="68" t="n"/>
       <c r="P291" s="61" t="n"/>
       <c r="Q291" s="61" t="n"/>
+      <c r="R291" s="89" t="n"/>
     </row>
     <row r="292" ht="12.75" customHeight="1" s="69">
       <c r="F292" s="65" t="n"/>
@@ -5932,6 +6237,7 @@
       <c r="O292" s="68" t="n"/>
       <c r="P292" s="61" t="n"/>
       <c r="Q292" s="61" t="n"/>
+      <c r="R292" s="89" t="n"/>
     </row>
     <row r="293" ht="12.75" customHeight="1" s="69">
       <c r="F293" s="65" t="n"/>
@@ -5946,6 +6252,7 @@
       <c r="O293" s="68" t="n"/>
       <c r="P293" s="61" t="n"/>
       <c r="Q293" s="61" t="n"/>
+      <c r="R293" s="89" t="n"/>
     </row>
     <row r="294" ht="12.75" customHeight="1" s="69">
       <c r="F294" s="65" t="n"/>
@@ -5960,6 +6267,7 @@
       <c r="O294" s="68" t="n"/>
       <c r="P294" s="61" t="n"/>
       <c r="Q294" s="61" t="n"/>
+      <c r="R294" s="89" t="n"/>
     </row>
     <row r="295" ht="12.75" customHeight="1" s="69">
       <c r="F295" s="65" t="n"/>
@@ -5974,6 +6282,7 @@
       <c r="O295" s="68" t="n"/>
       <c r="P295" s="61" t="n"/>
       <c r="Q295" s="61" t="n"/>
+      <c r="R295" s="89" t="n"/>
     </row>
     <row r="296" ht="12.75" customHeight="1" s="69">
       <c r="F296" s="65" t="n"/>
@@ -5988,6 +6297,7 @@
       <c r="O296" s="68" t="n"/>
       <c r="P296" s="61" t="n"/>
       <c r="Q296" s="61" t="n"/>
+      <c r="R296" s="89" t="n"/>
     </row>
     <row r="297" ht="12.75" customHeight="1" s="69">
       <c r="F297" s="65" t="n"/>
@@ -6002,6 +6312,7 @@
       <c r="O297" s="68" t="n"/>
       <c r="P297" s="61" t="n"/>
       <c r="Q297" s="61" t="n"/>
+      <c r="R297" s="89" t="n"/>
     </row>
     <row r="298" ht="12.75" customHeight="1" s="69">
       <c r="F298" s="65" t="n"/>
@@ -6016,6 +6327,7 @@
       <c r="O298" s="68" t="n"/>
       <c r="P298" s="61" t="n"/>
       <c r="Q298" s="61" t="n"/>
+      <c r="R298" s="89" t="n"/>
     </row>
     <row r="299" ht="12.75" customHeight="1" s="69">
       <c r="F299" s="65" t="n"/>
@@ -6030,6 +6342,7 @@
       <c r="O299" s="68" t="n"/>
       <c r="P299" s="61" t="n"/>
       <c r="Q299" s="61" t="n"/>
+      <c r="R299" s="89" t="n"/>
     </row>
     <row r="300" ht="12.75" customHeight="1" s="69">
       <c r="F300" s="65" t="n"/>
@@ -6044,6 +6357,7 @@
       <c r="O300" s="68" t="n"/>
       <c r="P300" s="61" t="n"/>
       <c r="Q300" s="61" t="n"/>
+      <c r="R300" s="89" t="n"/>
     </row>
     <row r="301" ht="12.75" customHeight="1" s="69">
       <c r="F301" s="65" t="n"/>
@@ -6058,6 +6372,7 @@
       <c r="O301" s="68" t="n"/>
       <c r="P301" s="61" t="n"/>
       <c r="Q301" s="61" t="n"/>
+      <c r="R301" s="89" t="n"/>
     </row>
     <row r="302" ht="12.75" customHeight="1" s="69">
       <c r="F302" s="65" t="n"/>
@@ -6072,6 +6387,7 @@
       <c r="O302" s="68" t="n"/>
       <c r="P302" s="61" t="n"/>
       <c r="Q302" s="61" t="n"/>
+      <c r="R302" s="89" t="n"/>
     </row>
     <row r="303" ht="12.75" customHeight="1" s="69">
       <c r="F303" s="65" t="n"/>
@@ -6086,6 +6402,7 @@
       <c r="O303" s="68" t="n"/>
       <c r="P303" s="61" t="n"/>
       <c r="Q303" s="61" t="n"/>
+      <c r="R303" s="89" t="n"/>
     </row>
     <row r="304" ht="12.75" customHeight="1" s="69">
       <c r="F304" s="65" t="n"/>
@@ -6100,6 +6417,7 @@
       <c r="O304" s="68" t="n"/>
       <c r="P304" s="61" t="n"/>
       <c r="Q304" s="61" t="n"/>
+      <c r="R304" s="89" t="n"/>
     </row>
     <row r="305" ht="12.75" customHeight="1" s="69">
       <c r="F305" s="65" t="n"/>
@@ -6114,6 +6432,7 @@
       <c r="O305" s="68" t="n"/>
       <c r="P305" s="61" t="n"/>
       <c r="Q305" s="61" t="n"/>
+      <c r="R305" s="89" t="n"/>
     </row>
     <row r="306" ht="12.75" customHeight="1" s="69">
       <c r="F306" s="65" t="n"/>
@@ -6128,6 +6447,7 @@
       <c r="O306" s="68" t="n"/>
       <c r="P306" s="61" t="n"/>
       <c r="Q306" s="61" t="n"/>
+      <c r="R306" s="89" t="n"/>
     </row>
     <row r="307" ht="12.75" customHeight="1" s="69">
       <c r="F307" s="65" t="n"/>
@@ -6142,6 +6462,7 @@
       <c r="O307" s="68" t="n"/>
       <c r="P307" s="61" t="n"/>
       <c r="Q307" s="61" t="n"/>
+      <c r="R307" s="89" t="n"/>
     </row>
     <row r="308" ht="12.75" customHeight="1" s="69">
       <c r="F308" s="65" t="n"/>
@@ -6156,6 +6477,7 @@
       <c r="O308" s="68" t="n"/>
       <c r="P308" s="61" t="n"/>
       <c r="Q308" s="61" t="n"/>
+      <c r="R308" s="89" t="n"/>
     </row>
     <row r="309" ht="12.75" customHeight="1" s="69">
       <c r="F309" s="65" t="n"/>
@@ -6170,6 +6492,7 @@
       <c r="O309" s="68" t="n"/>
       <c r="P309" s="61" t="n"/>
       <c r="Q309" s="61" t="n"/>
+      <c r="R309" s="89" t="n"/>
     </row>
     <row r="310" ht="12.75" customHeight="1" s="69">
       <c r="F310" s="65" t="n"/>
@@ -6184,6 +6507,7 @@
       <c r="O310" s="68" t="n"/>
       <c r="P310" s="61" t="n"/>
       <c r="Q310" s="61" t="n"/>
+      <c r="R310" s="89" t="n"/>
     </row>
     <row r="311" ht="12.75" customHeight="1" s="69">
       <c r="F311" s="65" t="n"/>
@@ -6198,6 +6522,7 @@
       <c r="O311" s="68" t="n"/>
       <c r="P311" s="61" t="n"/>
       <c r="Q311" s="61" t="n"/>
+      <c r="R311" s="89" t="n"/>
     </row>
     <row r="312" ht="12.75" customHeight="1" s="69">
       <c r="F312" s="65" t="n"/>
@@ -6212,6 +6537,7 @@
       <c r="O312" s="68" t="n"/>
       <c r="P312" s="61" t="n"/>
       <c r="Q312" s="61" t="n"/>
+      <c r="R312" s="89" t="n"/>
     </row>
     <row r="313" ht="12.75" customHeight="1" s="69">
       <c r="F313" s="65" t="n"/>
@@ -6226,6 +6552,7 @@
       <c r="O313" s="68" t="n"/>
       <c r="P313" s="61" t="n"/>
       <c r="Q313" s="61" t="n"/>
+      <c r="R313" s="89" t="n"/>
     </row>
     <row r="314" ht="12.75" customHeight="1" s="69">
       <c r="F314" s="65" t="n"/>
@@ -6240,6 +6567,7 @@
       <c r="O314" s="68" t="n"/>
       <c r="P314" s="61" t="n"/>
       <c r="Q314" s="61" t="n"/>
+      <c r="R314" s="89" t="n"/>
     </row>
     <row r="315" ht="12.75" customHeight="1" s="69">
       <c r="F315" s="65" t="n"/>
@@ -6254,6 +6582,7 @@
       <c r="O315" s="68" t="n"/>
       <c r="P315" s="61" t="n"/>
       <c r="Q315" s="61" t="n"/>
+      <c r="R315" s="89" t="n"/>
     </row>
     <row r="316" ht="12.75" customHeight="1" s="69">
       <c r="F316" s="65" t="n"/>
@@ -6268,6 +6597,7 @@
       <c r="O316" s="68" t="n"/>
       <c r="P316" s="61" t="n"/>
       <c r="Q316" s="61" t="n"/>
+      <c r="R316" s="89" t="n"/>
     </row>
     <row r="317" ht="12.75" customHeight="1" s="69">
       <c r="F317" s="65" t="n"/>
@@ -6282,6 +6612,7 @@
       <c r="O317" s="68" t="n"/>
       <c r="P317" s="61" t="n"/>
       <c r="Q317" s="61" t="n"/>
+      <c r="R317" s="89" t="n"/>
     </row>
     <row r="318" ht="12.75" customHeight="1" s="69">
       <c r="F318" s="65" t="n"/>
@@ -6296,6 +6627,7 @@
       <c r="O318" s="68" t="n"/>
       <c r="P318" s="61" t="n"/>
       <c r="Q318" s="61" t="n"/>
+      <c r="R318" s="89" t="n"/>
     </row>
     <row r="319" ht="12.75" customHeight="1" s="69">
       <c r="F319" s="65" t="n"/>
@@ -6310,6 +6642,7 @@
       <c r="O319" s="68" t="n"/>
       <c r="P319" s="61" t="n"/>
       <c r="Q319" s="61" t="n"/>
+      <c r="R319" s="89" t="n"/>
     </row>
     <row r="320" ht="12.75" customHeight="1" s="69">
       <c r="F320" s="65" t="n"/>
@@ -6324,6 +6657,7 @@
       <c r="O320" s="68" t="n"/>
       <c r="P320" s="61" t="n"/>
       <c r="Q320" s="61" t="n"/>
+      <c r="R320" s="89" t="n"/>
     </row>
     <row r="321" ht="12.75" customHeight="1" s="69">
       <c r="F321" s="65" t="n"/>
@@ -6338,6 +6672,7 @@
       <c r="O321" s="68" t="n"/>
       <c r="P321" s="61" t="n"/>
       <c r="Q321" s="61" t="n"/>
+      <c r="R321" s="89" t="n"/>
     </row>
     <row r="322" ht="12.75" customHeight="1" s="69">
       <c r="F322" s="65" t="n"/>
@@ -6352,6 +6687,7 @@
       <c r="O322" s="68" t="n"/>
       <c r="P322" s="61" t="n"/>
       <c r="Q322" s="61" t="n"/>
+      <c r="R322" s="89" t="n"/>
     </row>
     <row r="323" ht="12.75" customHeight="1" s="69">
       <c r="F323" s="65" t="n"/>
@@ -6366,6 +6702,7 @@
       <c r="O323" s="68" t="n"/>
       <c r="P323" s="61" t="n"/>
       <c r="Q323" s="61" t="n"/>
+      <c r="R323" s="89" t="n"/>
     </row>
     <row r="324" ht="12.75" customHeight="1" s="69">
       <c r="F324" s="65" t="n"/>
@@ -6380,6 +6717,7 @@
       <c r="O324" s="68" t="n"/>
       <c r="P324" s="61" t="n"/>
       <c r="Q324" s="61" t="n"/>
+      <c r="R324" s="89" t="n"/>
     </row>
     <row r="325" ht="12.75" customHeight="1" s="69">
       <c r="F325" s="65" t="n"/>
@@ -6394,6 +6732,7 @@
       <c r="O325" s="68" t="n"/>
       <c r="P325" s="61" t="n"/>
       <c r="Q325" s="61" t="n"/>
+      <c r="R325" s="89" t="n"/>
     </row>
     <row r="326" ht="12.75" customHeight="1" s="69">
       <c r="F326" s="65" t="n"/>
@@ -6408,6 +6747,7 @@
       <c r="O326" s="68" t="n"/>
       <c r="P326" s="61" t="n"/>
       <c r="Q326" s="61" t="n"/>
+      <c r="R326" s="89" t="n"/>
     </row>
     <row r="327" ht="12.75" customHeight="1" s="69">
       <c r="F327" s="65" t="n"/>
@@ -6422,6 +6762,7 @@
       <c r="O327" s="68" t="n"/>
       <c r="P327" s="61" t="n"/>
       <c r="Q327" s="61" t="n"/>
+      <c r="R327" s="89" t="n"/>
     </row>
     <row r="328" ht="12.75" customHeight="1" s="69">
       <c r="F328" s="65" t="n"/>
@@ -6436,6 +6777,7 @@
       <c r="O328" s="68" t="n"/>
       <c r="P328" s="61" t="n"/>
       <c r="Q328" s="61" t="n"/>
+      <c r="R328" s="89" t="n"/>
     </row>
     <row r="329" ht="12.75" customHeight="1" s="69">
       <c r="F329" s="65" t="n"/>
@@ -6450,6 +6792,7 @@
       <c r="O329" s="68" t="n"/>
       <c r="P329" s="61" t="n"/>
       <c r="Q329" s="61" t="n"/>
+      <c r="R329" s="89" t="n"/>
     </row>
     <row r="330" ht="12.75" customHeight="1" s="69">
       <c r="F330" s="65" t="n"/>
@@ -6464,6 +6807,7 @@
       <c r="O330" s="68" t="n"/>
       <c r="P330" s="61" t="n"/>
       <c r="Q330" s="61" t="n"/>
+      <c r="R330" s="89" t="n"/>
     </row>
     <row r="331" ht="12.75" customHeight="1" s="69">
       <c r="F331" s="65" t="n"/>
@@ -6478,6 +6822,7 @@
       <c r="O331" s="68" t="n"/>
       <c r="P331" s="61" t="n"/>
       <c r="Q331" s="61" t="n"/>
+      <c r="R331" s="89" t="n"/>
     </row>
     <row r="332" ht="12.75" customHeight="1" s="69">
       <c r="F332" s="65" t="n"/>
@@ -6492,6 +6837,7 @@
       <c r="O332" s="68" t="n"/>
       <c r="P332" s="61" t="n"/>
       <c r="Q332" s="61" t="n"/>
+      <c r="R332" s="89" t="n"/>
     </row>
     <row r="333" ht="12.75" customHeight="1" s="69">
       <c r="F333" s="65" t="n"/>
@@ -6506,6 +6852,7 @@
       <c r="O333" s="68" t="n"/>
       <c r="P333" s="61" t="n"/>
       <c r="Q333" s="61" t="n"/>
+      <c r="R333" s="89" t="n"/>
     </row>
     <row r="334" ht="12.75" customHeight="1" s="69">
       <c r="F334" s="65" t="n"/>
@@ -6520,6 +6867,7 @@
       <c r="O334" s="68" t="n"/>
       <c r="P334" s="61" t="n"/>
       <c r="Q334" s="61" t="n"/>
+      <c r="R334" s="89" t="n"/>
     </row>
     <row r="335" ht="12.75" customHeight="1" s="69">
       <c r="F335" s="65" t="n"/>
@@ -6534,6 +6882,7 @@
       <c r="O335" s="68" t="n"/>
       <c r="P335" s="61" t="n"/>
       <c r="Q335" s="61" t="n"/>
+      <c r="R335" s="89" t="n"/>
     </row>
     <row r="336" ht="12.75" customHeight="1" s="69">
       <c r="F336" s="65" t="n"/>
@@ -6548,6 +6897,7 @@
       <c r="O336" s="68" t="n"/>
       <c r="P336" s="61" t="n"/>
       <c r="Q336" s="61" t="n"/>
+      <c r="R336" s="89" t="n"/>
     </row>
     <row r="337" ht="12.75" customHeight="1" s="69">
       <c r="F337" s="65" t="n"/>
@@ -6562,6 +6912,7 @@
       <c r="O337" s="68" t="n"/>
       <c r="P337" s="61" t="n"/>
       <c r="Q337" s="61" t="n"/>
+      <c r="R337" s="89" t="n"/>
     </row>
     <row r="338" ht="12.75" customHeight="1" s="69">
       <c r="F338" s="65" t="n"/>
@@ -6576,6 +6927,7 @@
       <c r="O338" s="68" t="n"/>
       <c r="P338" s="61" t="n"/>
       <c r="Q338" s="61" t="n"/>
+      <c r="R338" s="89" t="n"/>
     </row>
     <row r="339" ht="12.75" customHeight="1" s="69">
       <c r="F339" s="65" t="n"/>
@@ -6590,6 +6942,7 @@
       <c r="O339" s="68" t="n"/>
       <c r="P339" s="61" t="n"/>
       <c r="Q339" s="61" t="n"/>
+      <c r="R339" s="89" t="n"/>
     </row>
     <row r="340" ht="12.75" customHeight="1" s="69">
       <c r="F340" s="65" t="n"/>
@@ -6604,6 +6957,7 @@
       <c r="O340" s="68" t="n"/>
       <c r="P340" s="61" t="n"/>
       <c r="Q340" s="61" t="n"/>
+      <c r="R340" s="89" t="n"/>
     </row>
     <row r="341" ht="12.75" customHeight="1" s="69">
       <c r="F341" s="65" t="n"/>
@@ -6618,6 +6972,7 @@
       <c r="O341" s="68" t="n"/>
       <c r="P341" s="61" t="n"/>
       <c r="Q341" s="61" t="n"/>
+      <c r="R341" s="89" t="n"/>
     </row>
     <row r="342" ht="12.75" customHeight="1" s="69">
       <c r="F342" s="65" t="n"/>
@@ -6632,6 +6987,7 @@
       <c r="O342" s="68" t="n"/>
       <c r="P342" s="61" t="n"/>
       <c r="Q342" s="61" t="n"/>
+      <c r="R342" s="89" t="n"/>
     </row>
     <row r="343" ht="12.75" customHeight="1" s="69">
       <c r="F343" s="65" t="n"/>
@@ -6646,6 +7002,7 @@
       <c r="O343" s="68" t="n"/>
       <c r="P343" s="61" t="n"/>
       <c r="Q343" s="61" t="n"/>
+      <c r="R343" s="89" t="n"/>
     </row>
     <row r="344" ht="12.75" customHeight="1" s="69">
       <c r="F344" s="65" t="n"/>
@@ -6660,6 +7017,7 @@
       <c r="O344" s="68" t="n"/>
       <c r="P344" s="61" t="n"/>
       <c r="Q344" s="61" t="n"/>
+      <c r="R344" s="89" t="n"/>
     </row>
     <row r="345" ht="12.75" customHeight="1" s="69">
       <c r="F345" s="65" t="n"/>
@@ -6674,6 +7032,7 @@
       <c r="O345" s="68" t="n"/>
       <c r="P345" s="61" t="n"/>
       <c r="Q345" s="61" t="n"/>
+      <c r="R345" s="89" t="n"/>
     </row>
     <row r="346" ht="12.75" customHeight="1" s="69">
       <c r="F346" s="65" t="n"/>
@@ -6688,6 +7047,7 @@
       <c r="O346" s="68" t="n"/>
       <c r="P346" s="61" t="n"/>
       <c r="Q346" s="61" t="n"/>
+      <c r="R346" s="89" t="n"/>
     </row>
     <row r="347" ht="12.75" customHeight="1" s="69">
       <c r="F347" s="65" t="n"/>
@@ -6702,6 +7062,7 @@
       <c r="O347" s="68" t="n"/>
       <c r="P347" s="61" t="n"/>
       <c r="Q347" s="61" t="n"/>
+      <c r="R347" s="89" t="n"/>
     </row>
     <row r="348" ht="12.75" customHeight="1" s="69">
       <c r="F348" s="65" t="n"/>
@@ -6716,6 +7077,7 @@
       <c r="O348" s="68" t="n"/>
       <c r="P348" s="61" t="n"/>
       <c r="Q348" s="61" t="n"/>
+      <c r="R348" s="89" t="n"/>
     </row>
     <row r="349" ht="12.75" customHeight="1" s="69">
       <c r="F349" s="65" t="n"/>
@@ -6730,6 +7092,7 @@
       <c r="O349" s="68" t="n"/>
       <c r="P349" s="61" t="n"/>
       <c r="Q349" s="61" t="n"/>
+      <c r="R349" s="89" t="n"/>
     </row>
     <row r="350" ht="12.75" customHeight="1" s="69">
       <c r="F350" s="65" t="n"/>
@@ -6744,6 +7107,7 @@
       <c r="O350" s="68" t="n"/>
       <c r="P350" s="61" t="n"/>
       <c r="Q350" s="61" t="n"/>
+      <c r="R350" s="89" t="n"/>
     </row>
     <row r="351" ht="12.75" customHeight="1" s="69">
       <c r="F351" s="65" t="n"/>
@@ -6758,6 +7122,7 @@
       <c r="O351" s="68" t="n"/>
       <c r="P351" s="61" t="n"/>
       <c r="Q351" s="61" t="n"/>
+      <c r="R351" s="89" t="n"/>
     </row>
     <row r="352" ht="12.75" customHeight="1" s="69">
       <c r="F352" s="65" t="n"/>
@@ -6772,6 +7137,7 @@
       <c r="O352" s="68" t="n"/>
       <c r="P352" s="61" t="n"/>
       <c r="Q352" s="61" t="n"/>
+      <c r="R352" s="89" t="n"/>
     </row>
     <row r="353" ht="12.75" customHeight="1" s="69">
       <c r="F353" s="65" t="n"/>
@@ -6786,6 +7152,7 @@
       <c r="O353" s="68" t="n"/>
       <c r="P353" s="61" t="n"/>
       <c r="Q353" s="61" t="n"/>
+      <c r="R353" s="89" t="n"/>
     </row>
     <row r="354" ht="12.75" customHeight="1" s="69">
       <c r="F354" s="65" t="n"/>
@@ -6800,6 +7167,7 @@
       <c r="O354" s="68" t="n"/>
       <c r="P354" s="61" t="n"/>
       <c r="Q354" s="61" t="n"/>
+      <c r="R354" s="89" t="n"/>
     </row>
     <row r="355" ht="12.75" customHeight="1" s="69">
       <c r="F355" s="65" t="n"/>
@@ -6814,6 +7182,7 @@
       <c r="O355" s="68" t="n"/>
       <c r="P355" s="61" t="n"/>
       <c r="Q355" s="61" t="n"/>
+      <c r="R355" s="89" t="n"/>
     </row>
     <row r="356" ht="12.75" customHeight="1" s="69">
       <c r="F356" s="65" t="n"/>
@@ -6828,6 +7197,7 @@
       <c r="O356" s="68" t="n"/>
       <c r="P356" s="61" t="n"/>
       <c r="Q356" s="61" t="n"/>
+      <c r="R356" s="89" t="n"/>
     </row>
     <row r="357" ht="12.75" customHeight="1" s="69">
       <c r="F357" s="65" t="n"/>
@@ -6842,6 +7212,7 @@
       <c r="O357" s="68" t="n"/>
       <c r="P357" s="61" t="n"/>
       <c r="Q357" s="61" t="n"/>
+      <c r="R357" s="89" t="n"/>
     </row>
     <row r="358" ht="12.75" customHeight="1" s="69">
       <c r="F358" s="65" t="n"/>
@@ -6856,6 +7227,7 @@
       <c r="O358" s="68" t="n"/>
       <c r="P358" s="61" t="n"/>
       <c r="Q358" s="61" t="n"/>
+      <c r="R358" s="89" t="n"/>
     </row>
     <row r="359" ht="12.75" customHeight="1" s="69">
       <c r="F359" s="65" t="n"/>
@@ -6870,6 +7242,7 @@
       <c r="O359" s="68" t="n"/>
       <c r="P359" s="61" t="n"/>
       <c r="Q359" s="61" t="n"/>
+      <c r="R359" s="89" t="n"/>
     </row>
     <row r="360" ht="12.75" customHeight="1" s="69">
       <c r="F360" s="65" t="n"/>
@@ -6884,6 +7257,7 @@
       <c r="O360" s="68" t="n"/>
       <c r="P360" s="61" t="n"/>
       <c r="Q360" s="61" t="n"/>
+      <c r="R360" s="89" t="n"/>
     </row>
     <row r="361" ht="12.75" customHeight="1" s="69">
       <c r="F361" s="65" t="n"/>
@@ -6898,6 +7272,7 @@
       <c r="O361" s="68" t="n"/>
       <c r="P361" s="61" t="n"/>
       <c r="Q361" s="61" t="n"/>
+      <c r="R361" s="89" t="n"/>
     </row>
     <row r="362" ht="12.75" customHeight="1" s="69">
       <c r="F362" s="65" t="n"/>
@@ -6912,6 +7287,7 @@
       <c r="O362" s="68" t="n"/>
       <c r="P362" s="61" t="n"/>
       <c r="Q362" s="61" t="n"/>
+      <c r="R362" s="89" t="n"/>
     </row>
     <row r="363" ht="12.75" customHeight="1" s="69">
       <c r="F363" s="65" t="n"/>
@@ -6926,6 +7302,7 @@
       <c r="O363" s="68" t="n"/>
       <c r="P363" s="61" t="n"/>
       <c r="Q363" s="61" t="n"/>
+      <c r="R363" s="89" t="n"/>
     </row>
     <row r="364" ht="12.75" customHeight="1" s="69">
       <c r="F364" s="65" t="n"/>
@@ -6940,6 +7317,7 @@
       <c r="O364" s="68" t="n"/>
       <c r="P364" s="61" t="n"/>
       <c r="Q364" s="61" t="n"/>
+      <c r="R364" s="89" t="n"/>
     </row>
     <row r="365" ht="12.75" customHeight="1" s="69">
       <c r="F365" s="65" t="n"/>
@@ -6954,6 +7332,7 @@
       <c r="O365" s="68" t="n"/>
       <c r="P365" s="61" t="n"/>
       <c r="Q365" s="61" t="n"/>
+      <c r="R365" s="89" t="n"/>
     </row>
     <row r="366" ht="12.75" customHeight="1" s="69">
       <c r="F366" s="65" t="n"/>
@@ -6968,6 +7347,7 @@
       <c r="O366" s="68" t="n"/>
       <c r="P366" s="61" t="n"/>
       <c r="Q366" s="61" t="n"/>
+      <c r="R366" s="89" t="n"/>
     </row>
     <row r="367" ht="12.75" customHeight="1" s="69">
       <c r="F367" s="65" t="n"/>
@@ -6982,6 +7362,7 @@
       <c r="O367" s="68" t="n"/>
       <c r="P367" s="61" t="n"/>
       <c r="Q367" s="61" t="n"/>
+      <c r="R367" s="89" t="n"/>
     </row>
     <row r="368" ht="12.75" customHeight="1" s="69">
       <c r="F368" s="65" t="n"/>
@@ -6996,6 +7377,7 @@
       <c r="O368" s="68" t="n"/>
       <c r="P368" s="61" t="n"/>
       <c r="Q368" s="61" t="n"/>
+      <c r="R368" s="89" t="n"/>
     </row>
     <row r="369" ht="12.75" customHeight="1" s="69">
       <c r="F369" s="65" t="n"/>
@@ -7010,6 +7392,7 @@
       <c r="O369" s="68" t="n"/>
       <c r="P369" s="61" t="n"/>
       <c r="Q369" s="61" t="n"/>
+      <c r="R369" s="89" t="n"/>
     </row>
     <row r="370" ht="12.75" customHeight="1" s="69">
       <c r="F370" s="65" t="n"/>
@@ -7024,6 +7407,7 @@
       <c r="O370" s="68" t="n"/>
       <c r="P370" s="61" t="n"/>
       <c r="Q370" s="61" t="n"/>
+      <c r="R370" s="89" t="n"/>
     </row>
     <row r="371" ht="12.75" customHeight="1" s="69">
       <c r="F371" s="65" t="n"/>
@@ -7038,6 +7422,7 @@
       <c r="O371" s="68" t="n"/>
       <c r="P371" s="61" t="n"/>
       <c r="Q371" s="61" t="n"/>
+      <c r="R371" s="89" t="n"/>
     </row>
     <row r="372" ht="12.75" customHeight="1" s="69">
       <c r="F372" s="65" t="n"/>
@@ -7052,6 +7437,7 @@
       <c r="O372" s="68" t="n"/>
       <c r="P372" s="61" t="n"/>
       <c r="Q372" s="61" t="n"/>
+      <c r="R372" s="89" t="n"/>
     </row>
     <row r="373" ht="12.75" customHeight="1" s="69">
       <c r="F373" s="65" t="n"/>
@@ -7066,6 +7452,7 @@
       <c r="O373" s="68" t="n"/>
       <c r="P373" s="61" t="n"/>
       <c r="Q373" s="61" t="n"/>
+      <c r="R373" s="89" t="n"/>
     </row>
     <row r="374" ht="12.75" customHeight="1" s="69">
       <c r="F374" s="65" t="n"/>
@@ -7080,6 +7467,7 @@
       <c r="O374" s="68" t="n"/>
       <c r="P374" s="61" t="n"/>
       <c r="Q374" s="61" t="n"/>
+      <c r="R374" s="89" t="n"/>
     </row>
     <row r="375" ht="12.75" customHeight="1" s="69">
       <c r="F375" s="65" t="n"/>
@@ -7094,6 +7482,7 @@
       <c r="O375" s="68" t="n"/>
       <c r="P375" s="61" t="n"/>
       <c r="Q375" s="61" t="n"/>
+      <c r="R375" s="89" t="n"/>
     </row>
     <row r="376" ht="12.75" customHeight="1" s="69">
       <c r="F376" s="65" t="n"/>
@@ -7108,6 +7497,7 @@
       <c r="O376" s="68" t="n"/>
       <c r="P376" s="61" t="n"/>
       <c r="Q376" s="61" t="n"/>
+      <c r="R376" s="89" t="n"/>
     </row>
     <row r="377" ht="12.75" customHeight="1" s="69">
       <c r="F377" s="65" t="n"/>
@@ -7122,6 +7512,7 @@
       <c r="O377" s="68" t="n"/>
       <c r="P377" s="61" t="n"/>
       <c r="Q377" s="61" t="n"/>
+      <c r="R377" s="89" t="n"/>
     </row>
     <row r="378" ht="12.75" customHeight="1" s="69">
       <c r="F378" s="65" t="n"/>
@@ -7136,6 +7527,7 @@
       <c r="O378" s="68" t="n"/>
       <c r="P378" s="61" t="n"/>
       <c r="Q378" s="61" t="n"/>
+      <c r="R378" s="89" t="n"/>
     </row>
     <row r="379" ht="12.75" customHeight="1" s="69">
       <c r="F379" s="65" t="n"/>
@@ -7150,6 +7542,7 @@
       <c r="O379" s="68" t="n"/>
       <c r="P379" s="61" t="n"/>
       <c r="Q379" s="61" t="n"/>
+      <c r="R379" s="89" t="n"/>
     </row>
     <row r="380" ht="12.75" customHeight="1" s="69">
       <c r="F380" s="65" t="n"/>
@@ -7164,6 +7557,7 @@
       <c r="O380" s="68" t="n"/>
       <c r="P380" s="61" t="n"/>
       <c r="Q380" s="61" t="n"/>
+      <c r="R380" s="89" t="n"/>
     </row>
     <row r="381" ht="12.75" customHeight="1" s="69">
       <c r="F381" s="65" t="n"/>
@@ -7178,6 +7572,7 @@
       <c r="O381" s="68" t="n"/>
       <c r="P381" s="61" t="n"/>
       <c r="Q381" s="61" t="n"/>
+      <c r="R381" s="89" t="n"/>
     </row>
     <row r="382" ht="12.75" customHeight="1" s="69">
       <c r="F382" s="65" t="n"/>
@@ -7192,6 +7587,7 @@
       <c r="O382" s="68" t="n"/>
       <c r="P382" s="61" t="n"/>
       <c r="Q382" s="61" t="n"/>
+      <c r="R382" s="89" t="n"/>
     </row>
     <row r="383" ht="12.75" customHeight="1" s="69">
       <c r="F383" s="65" t="n"/>
@@ -7206,6 +7602,7 @@
       <c r="O383" s="68" t="n"/>
       <c r="P383" s="61" t="n"/>
       <c r="Q383" s="61" t="n"/>
+      <c r="R383" s="89" t="n"/>
     </row>
     <row r="384" ht="12.75" customHeight="1" s="69">
       <c r="F384" s="65" t="n"/>
@@ -7220,6 +7617,7 @@
       <c r="O384" s="68" t="n"/>
       <c r="P384" s="61" t="n"/>
       <c r="Q384" s="61" t="n"/>
+      <c r="R384" s="89" t="n"/>
     </row>
     <row r="385" ht="12.75" customHeight="1" s="69">
       <c r="F385" s="65" t="n"/>
@@ -7234,6 +7632,7 @@
       <c r="O385" s="68" t="n"/>
       <c r="P385" s="61" t="n"/>
       <c r="Q385" s="61" t="n"/>
+      <c r="R385" s="89" t="n"/>
     </row>
     <row r="386" ht="12.75" customHeight="1" s="69">
       <c r="F386" s="65" t="n"/>
@@ -7248,6 +7647,7 @@
       <c r="O386" s="68" t="n"/>
       <c r="P386" s="61" t="n"/>
       <c r="Q386" s="61" t="n"/>
+      <c r="R386" s="89" t="n"/>
     </row>
     <row r="387" ht="12.75" customHeight="1" s="69">
       <c r="F387" s="65" t="n"/>
@@ -7262,6 +7662,7 @@
       <c r="O387" s="68" t="n"/>
       <c r="P387" s="61" t="n"/>
       <c r="Q387" s="61" t="n"/>
+      <c r="R387" s="89" t="n"/>
     </row>
     <row r="388" ht="12.75" customHeight="1" s="69">
       <c r="F388" s="65" t="n"/>
@@ -7276,6 +7677,7 @@
       <c r="O388" s="68" t="n"/>
       <c r="P388" s="61" t="n"/>
       <c r="Q388" s="61" t="n"/>
+      <c r="R388" s="89" t="n"/>
     </row>
     <row r="389" ht="12.75" customHeight="1" s="69">
       <c r="F389" s="65" t="n"/>
@@ -7290,6 +7692,7 @@
       <c r="O389" s="68" t="n"/>
       <c r="P389" s="61" t="n"/>
       <c r="Q389" s="61" t="n"/>
+      <c r="R389" s="89" t="n"/>
     </row>
     <row r="390" ht="12.75" customHeight="1" s="69">
       <c r="F390" s="65" t="n"/>
@@ -7304,6 +7707,7 @@
       <c r="O390" s="68" t="n"/>
       <c r="P390" s="61" t="n"/>
       <c r="Q390" s="61" t="n"/>
+      <c r="R390" s="89" t="n"/>
     </row>
     <row r="391" ht="12.75" customHeight="1" s="69">
       <c r="F391" s="65" t="n"/>
@@ -7318,6 +7722,7 @@
       <c r="O391" s="68" t="n"/>
       <c r="P391" s="61" t="n"/>
       <c r="Q391" s="61" t="n"/>
+      <c r="R391" s="89" t="n"/>
     </row>
     <row r="392" ht="12.75" customHeight="1" s="69">
       <c r="F392" s="65" t="n"/>
@@ -7332,6 +7737,7 @@
       <c r="O392" s="68" t="n"/>
       <c r="P392" s="61" t="n"/>
       <c r="Q392" s="61" t="n"/>
+      <c r="R392" s="89" t="n"/>
     </row>
     <row r="393" ht="12.75" customHeight="1" s="69">
       <c r="F393" s="65" t="n"/>
@@ -7346,6 +7752,7 @@
       <c r="O393" s="68" t="n"/>
       <c r="P393" s="61" t="n"/>
       <c r="Q393" s="61" t="n"/>
+      <c r="R393" s="89" t="n"/>
     </row>
     <row r="394" ht="12.75" customHeight="1" s="69">
       <c r="F394" s="65" t="n"/>
@@ -7360,6 +7767,7 @@
       <c r="O394" s="68" t="n"/>
       <c r="P394" s="61" t="n"/>
       <c r="Q394" s="61" t="n"/>
+      <c r="R394" s="89" t="n"/>
     </row>
     <row r="395" ht="12.75" customHeight="1" s="69">
       <c r="F395" s="65" t="n"/>
@@ -7374,6 +7782,7 @@
       <c r="O395" s="68" t="n"/>
       <c r="P395" s="61" t="n"/>
       <c r="Q395" s="61" t="n"/>
+      <c r="R395" s="89" t="n"/>
     </row>
     <row r="396" ht="12.75" customHeight="1" s="69">
       <c r="F396" s="65" t="n"/>
@@ -7388,6 +7797,7 @@
       <c r="O396" s="68" t="n"/>
       <c r="P396" s="61" t="n"/>
       <c r="Q396" s="61" t="n"/>
+      <c r="R396" s="89" t="n"/>
     </row>
     <row r="397" ht="12.75" customHeight="1" s="69">
       <c r="F397" s="65" t="n"/>
@@ -7402,6 +7812,7 @@
       <c r="O397" s="68" t="n"/>
       <c r="P397" s="61" t="n"/>
       <c r="Q397" s="61" t="n"/>
+      <c r="R397" s="89" t="n"/>
     </row>
     <row r="398" ht="12.75" customHeight="1" s="69">
       <c r="F398" s="65" t="n"/>
@@ -7416,6 +7827,7 @@
       <c r="O398" s="68" t="n"/>
       <c r="P398" s="61" t="n"/>
       <c r="Q398" s="61" t="n"/>
+      <c r="R398" s="89" t="n"/>
     </row>
     <row r="399" ht="12.75" customHeight="1" s="69">
       <c r="F399" s="65" t="n"/>
@@ -7430,6 +7842,7 @@
       <c r="O399" s="68" t="n"/>
       <c r="P399" s="61" t="n"/>
       <c r="Q399" s="61" t="n"/>
+      <c r="R399" s="89" t="n"/>
     </row>
     <row r="400" ht="12.75" customHeight="1" s="69">
       <c r="F400" s="65" t="n"/>
@@ -7444,6 +7857,7 @@
       <c r="O400" s="68" t="n"/>
       <c r="P400" s="61" t="n"/>
       <c r="Q400" s="61" t="n"/>
+      <c r="R400" s="89" t="n"/>
     </row>
     <row r="401" ht="12.75" customHeight="1" s="69">
       <c r="F401" s="65" t="n"/>
@@ -7454,6 +7868,7 @@
       <c r="O401" s="68" t="n"/>
       <c r="P401" s="61" t="n"/>
       <c r="Q401" s="61" t="n"/>
+      <c r="R401" s="89" t="n"/>
     </row>
     <row r="402" ht="12.75" customHeight="1" s="69">
       <c r="F402" s="65" t="n"/>
@@ -7464,6 +7879,7 @@
       <c r="O402" s="68" t="n"/>
       <c r="P402" s="61" t="n"/>
       <c r="Q402" s="61" t="n"/>
+      <c r="R402" s="89" t="n"/>
     </row>
     <row r="403" ht="12.75" customHeight="1" s="69">
       <c r="F403" s="65" t="n"/>
@@ -7474,6 +7890,7 @@
       <c r="O403" s="68" t="n"/>
       <c r="P403" s="61" t="n"/>
       <c r="Q403" s="61" t="n"/>
+      <c r="R403" s="89" t="n"/>
     </row>
     <row r="404" ht="12.75" customHeight="1" s="69">
       <c r="F404" s="65" t="n"/>
@@ -7484,6 +7901,7 @@
       <c r="O404" s="68" t="n"/>
       <c r="P404" s="61" t="n"/>
       <c r="Q404" s="61" t="n"/>
+      <c r="R404" s="89" t="n"/>
     </row>
     <row r="405" ht="12.75" customHeight="1" s="69">
       <c r="F405" s="65" t="n"/>
@@ -7494,6 +7912,7 @@
       <c r="O405" s="68" t="n"/>
       <c r="P405" s="61" t="n"/>
       <c r="Q405" s="61" t="n"/>
+      <c r="R405" s="89" t="n"/>
     </row>
     <row r="406" ht="12.75" customHeight="1" s="69">
       <c r="F406" s="65" t="n"/>
@@ -7504,6 +7923,7 @@
       <c r="O406" s="68" t="n"/>
       <c r="P406" s="61" t="n"/>
       <c r="Q406" s="61" t="n"/>
+      <c r="R406" s="89" t="n"/>
     </row>
     <row r="407" ht="12.75" customHeight="1" s="69">
       <c r="F407" s="65" t="n"/>
@@ -7514,6 +7934,7 @@
       <c r="O407" s="68" t="n"/>
       <c r="P407" s="61" t="n"/>
       <c r="Q407" s="61" t="n"/>
+      <c r="R407" s="89" t="n"/>
     </row>
     <row r="408" ht="12.75" customHeight="1" s="69">
       <c r="F408" s="65" t="n"/>
@@ -7524,6 +7945,7 @@
       <c r="O408" s="68" t="n"/>
       <c r="P408" s="61" t="n"/>
       <c r="Q408" s="61" t="n"/>
+      <c r="R408" s="89" t="n"/>
     </row>
     <row r="409" ht="12.75" customHeight="1" s="69">
       <c r="F409" s="65" t="n"/>
@@ -7534,6 +7956,7 @@
       <c r="O409" s="68" t="n"/>
       <c r="P409" s="61" t="n"/>
       <c r="Q409" s="61" t="n"/>
+      <c r="R409" s="89" t="n"/>
     </row>
     <row r="410" ht="12.75" customHeight="1" s="69">
       <c r="F410" s="65" t="n"/>
@@ -7544,6 +7967,7 @@
       <c r="O410" s="68" t="n"/>
       <c r="P410" s="61" t="n"/>
       <c r="Q410" s="61" t="n"/>
+      <c r="R410" s="89" t="n"/>
     </row>
     <row r="411" ht="12.75" customHeight="1" s="69">
       <c r="F411" s="65" t="n"/>
@@ -7554,6 +7978,7 @@
       <c r="O411" s="68" t="n"/>
       <c r="P411" s="61" t="n"/>
       <c r="Q411" s="61" t="n"/>
+      <c r="R411" s="89" t="n"/>
     </row>
     <row r="412" ht="12.75" customHeight="1" s="69">
       <c r="F412" s="65" t="n"/>
@@ -7564,6 +7989,7 @@
       <c r="O412" s="68" t="n"/>
       <c r="P412" s="61" t="n"/>
       <c r="Q412" s="61" t="n"/>
+      <c r="R412" s="89" t="n"/>
     </row>
     <row r="413" ht="12.75" customHeight="1" s="69">
       <c r="F413" s="65" t="n"/>
@@ -7574,6 +8000,7 @@
       <c r="O413" s="68" t="n"/>
       <c r="P413" s="61" t="n"/>
       <c r="Q413" s="61" t="n"/>
+      <c r="R413" s="89" t="n"/>
     </row>
     <row r="414" ht="12.75" customHeight="1" s="69">
       <c r="F414" s="65" t="n"/>
@@ -7584,6 +8011,7 @@
       <c r="O414" s="68" t="n"/>
       <c r="P414" s="61" t="n"/>
       <c r="Q414" s="61" t="n"/>
+      <c r="R414" s="89" t="n"/>
     </row>
     <row r="415" ht="12.75" customHeight="1" s="69">
       <c r="F415" s="65" t="n"/>
@@ -7594,6 +8022,7 @@
       <c r="O415" s="68" t="n"/>
       <c r="P415" s="61" t="n"/>
       <c r="Q415" s="61" t="n"/>
+      <c r="R415" s="89" t="n"/>
     </row>
     <row r="416" ht="12.75" customHeight="1" s="69">
       <c r="F416" s="65" t="n"/>
@@ -7604,6 +8033,7 @@
       <c r="O416" s="68" t="n"/>
       <c r="P416" s="61" t="n"/>
       <c r="Q416" s="61" t="n"/>
+      <c r="R416" s="89" t="n"/>
     </row>
     <row r="417" ht="12.75" customHeight="1" s="69">
       <c r="F417" s="65" t="n"/>
@@ -7614,6 +8044,7 @@
       <c r="O417" s="68" t="n"/>
       <c r="P417" s="61" t="n"/>
       <c r="Q417" s="61" t="n"/>
+      <c r="R417" s="89" t="n"/>
     </row>
     <row r="418" ht="12.75" customHeight="1" s="69">
       <c r="F418" s="65" t="n"/>
@@ -7624,6 +8055,7 @@
       <c r="O418" s="68" t="n"/>
       <c r="P418" s="61" t="n"/>
       <c r="Q418" s="61" t="n"/>
+      <c r="R418" s="89" t="n"/>
     </row>
     <row r="419" ht="12.75" customHeight="1" s="69">
       <c r="F419" s="65" t="n"/>
@@ -7634,6 +8066,7 @@
       <c r="O419" s="68" t="n"/>
       <c r="P419" s="61" t="n"/>
       <c r="Q419" s="61" t="n"/>
+      <c r="R419" s="89" t="n"/>
     </row>
     <row r="420" ht="12.75" customHeight="1" s="69">
       <c r="F420" s="65" t="n"/>
@@ -7644,6 +8077,7 @@
       <c r="O420" s="68" t="n"/>
       <c r="P420" s="61" t="n"/>
       <c r="Q420" s="61" t="n"/>
+      <c r="R420" s="89" t="n"/>
     </row>
     <row r="421" ht="12.75" customHeight="1" s="69">
       <c r="F421" s="65" t="n"/>
@@ -7654,6 +8088,7 @@
       <c r="O421" s="68" t="n"/>
       <c r="P421" s="61" t="n"/>
       <c r="Q421" s="61" t="n"/>
+      <c r="R421" s="89" t="n"/>
     </row>
     <row r="422" ht="12.75" customHeight="1" s="69">
       <c r="F422" s="65" t="n"/>
@@ -7664,6 +8099,7 @@
       <c r="O422" s="68" t="n"/>
       <c r="P422" s="61" t="n"/>
       <c r="Q422" s="61" t="n"/>
+      <c r="R422" s="89" t="n"/>
     </row>
     <row r="423" ht="12.75" customHeight="1" s="69">
       <c r="F423" s="65" t="n"/>
@@ -7674,6 +8110,7 @@
       <c r="O423" s="68" t="n"/>
       <c r="P423" s="61" t="n"/>
       <c r="Q423" s="61" t="n"/>
+      <c r="R423" s="89" t="n"/>
     </row>
     <row r="424" ht="12.75" customHeight="1" s="69">
       <c r="F424" s="65" t="n"/>
@@ -7684,6 +8121,7 @@
       <c r="O424" s="68" t="n"/>
       <c r="P424" s="61" t="n"/>
       <c r="Q424" s="61" t="n"/>
+      <c r="R424" s="89" t="n"/>
     </row>
     <row r="425" ht="12.75" customHeight="1" s="69">
       <c r="F425" s="65" t="n"/>
@@ -7694,6 +8132,7 @@
       <c r="O425" s="68" t="n"/>
       <c r="P425" s="61" t="n"/>
       <c r="Q425" s="61" t="n"/>
+      <c r="R425" s="89" t="n"/>
     </row>
     <row r="426" ht="12.75" customHeight="1" s="69">
       <c r="F426" s="65" t="n"/>
@@ -7704,6 +8143,7 @@
       <c r="O426" s="68" t="n"/>
       <c r="P426" s="61" t="n"/>
       <c r="Q426" s="61" t="n"/>
+      <c r="R426" s="89" t="n"/>
     </row>
     <row r="427" ht="12.75" customHeight="1" s="69">
       <c r="F427" s="65" t="n"/>
@@ -7714,6 +8154,7 @@
       <c r="O427" s="68" t="n"/>
       <c r="P427" s="61" t="n"/>
       <c r="Q427" s="61" t="n"/>
+      <c r="R427" s="89" t="n"/>
     </row>
     <row r="428" ht="12.75" customHeight="1" s="69">
       <c r="F428" s="65" t="n"/>
@@ -7724,6 +8165,7 @@
       <c r="O428" s="68" t="n"/>
       <c r="P428" s="61" t="n"/>
       <c r="Q428" s="61" t="n"/>
+      <c r="R428" s="89" t="n"/>
     </row>
     <row r="429" ht="12.75" customHeight="1" s="69">
       <c r="F429" s="65" t="n"/>
@@ -7734,6 +8176,7 @@
       <c r="O429" s="68" t="n"/>
       <c r="P429" s="61" t="n"/>
       <c r="Q429" s="61" t="n"/>
+      <c r="R429" s="89" t="n"/>
     </row>
     <row r="430" ht="12.75" customHeight="1" s="69">
       <c r="F430" s="65" t="n"/>
@@ -7744,6 +8187,7 @@
       <c r="O430" s="68" t="n"/>
       <c r="P430" s="61" t="n"/>
       <c r="Q430" s="61" t="n"/>
+      <c r="R430" s="89" t="n"/>
     </row>
     <row r="431" ht="12.75" customHeight="1" s="69">
       <c r="F431" s="65" t="n"/>
@@ -7754,6 +8198,7 @@
       <c r="O431" s="68" t="n"/>
       <c r="P431" s="61" t="n"/>
       <c r="Q431" s="61" t="n"/>
+      <c r="R431" s="89" t="n"/>
     </row>
     <row r="432" ht="12.75" customHeight="1" s="69">
       <c r="F432" s="65" t="n"/>
@@ -7764,6 +8209,7 @@
       <c r="O432" s="68" t="n"/>
       <c r="P432" s="61" t="n"/>
       <c r="Q432" s="61" t="n"/>
+      <c r="R432" s="89" t="n"/>
     </row>
     <row r="433" ht="12.75" customHeight="1" s="69">
       <c r="F433" s="65" t="n"/>
@@ -7774,6 +8220,7 @@
       <c r="O433" s="68" t="n"/>
       <c r="P433" s="61" t="n"/>
       <c r="Q433" s="61" t="n"/>
+      <c r="R433" s="89" t="n"/>
     </row>
     <row r="434" ht="12.75" customHeight="1" s="69">
       <c r="F434" s="65" t="n"/>
@@ -7784,6 +8231,7 @@
       <c r="O434" s="68" t="n"/>
       <c r="P434" s="61" t="n"/>
       <c r="Q434" s="61" t="n"/>
+      <c r="R434" s="89" t="n"/>
     </row>
     <row r="435" ht="12.75" customHeight="1" s="69">
       <c r="F435" s="65" t="n"/>
@@ -7794,6 +8242,7 @@
       <c r="O435" s="68" t="n"/>
       <c r="P435" s="61" t="n"/>
       <c r="Q435" s="61" t="n"/>
+      <c r="R435" s="89" t="n"/>
     </row>
     <row r="436" ht="12.75" customHeight="1" s="69">
       <c r="F436" s="65" t="n"/>
@@ -7804,6 +8253,7 @@
       <c r="O436" s="68" t="n"/>
       <c r="P436" s="61" t="n"/>
       <c r="Q436" s="61" t="n"/>
+      <c r="R436" s="89" t="n"/>
     </row>
     <row r="437" ht="12.75" customHeight="1" s="69">
       <c r="F437" s="65" t="n"/>
@@ -7814,6 +8264,7 @@
       <c r="O437" s="68" t="n"/>
       <c r="P437" s="61" t="n"/>
       <c r="Q437" s="61" t="n"/>
+      <c r="R437" s="89" t="n"/>
     </row>
     <row r="438" ht="12.75" customHeight="1" s="69">
       <c r="F438" s="65" t="n"/>
@@ -7824,6 +8275,7 @@
       <c r="O438" s="68" t="n"/>
       <c r="P438" s="61" t="n"/>
       <c r="Q438" s="61" t="n"/>
+      <c r="R438" s="89" t="n"/>
     </row>
     <row r="439" ht="12.75" customHeight="1" s="69">
       <c r="F439" s="65" t="n"/>
@@ -7834,6 +8286,7 @@
       <c r="O439" s="68" t="n"/>
       <c r="P439" s="61" t="n"/>
       <c r="Q439" s="61" t="n"/>
+      <c r="R439" s="89" t="n"/>
     </row>
     <row r="440" ht="12.75" customHeight="1" s="69">
       <c r="F440" s="65" t="n"/>
@@ -7844,6 +8297,7 @@
       <c r="O440" s="68" t="n"/>
       <c r="P440" s="61" t="n"/>
       <c r="Q440" s="61" t="n"/>
+      <c r="R440" s="89" t="n"/>
     </row>
     <row r="441" ht="12.75" customHeight="1" s="69">
       <c r="F441" s="65" t="n"/>
@@ -7854,6 +8308,7 @@
       <c r="O441" s="68" t="n"/>
       <c r="P441" s="61" t="n"/>
       <c r="Q441" s="61" t="n"/>
+      <c r="R441" s="89" t="n"/>
     </row>
     <row r="442" ht="12.75" customHeight="1" s="69">
       <c r="F442" s="65" t="n"/>
@@ -7864,6 +8319,7 @@
       <c r="O442" s="68" t="n"/>
       <c r="P442" s="61" t="n"/>
       <c r="Q442" s="61" t="n"/>
+      <c r="R442" s="89" t="n"/>
     </row>
     <row r="443" ht="12.75" customHeight="1" s="69">
       <c r="F443" s="65" t="n"/>
@@ -7874,6 +8330,7 @@
       <c r="O443" s="68" t="n"/>
       <c r="P443" s="61" t="n"/>
       <c r="Q443" s="61" t="n"/>
+      <c r="R443" s="89" t="n"/>
     </row>
     <row r="444" ht="12.75" customHeight="1" s="69">
       <c r="F444" s="65" t="n"/>
@@ -7884,6 +8341,7 @@
       <c r="O444" s="68" t="n"/>
       <c r="P444" s="61" t="n"/>
       <c r="Q444" s="61" t="n"/>
+      <c r="R444" s="89" t="n"/>
     </row>
     <row r="445" ht="12.75" customHeight="1" s="69">
       <c r="F445" s="65" t="n"/>
@@ -7894,6 +8352,7 @@
       <c r="O445" s="68" t="n"/>
       <c r="P445" s="61" t="n"/>
       <c r="Q445" s="61" t="n"/>
+      <c r="R445" s="89" t="n"/>
     </row>
     <row r="446" ht="12.75" customHeight="1" s="69">
       <c r="F446" s="65" t="n"/>
@@ -7904,6 +8363,7 @@
       <c r="O446" s="68" t="n"/>
       <c r="P446" s="61" t="n"/>
       <c r="Q446" s="61" t="n"/>
+      <c r="R446" s="89" t="n"/>
     </row>
     <row r="447" ht="12.75" customHeight="1" s="69">
       <c r="F447" s="65" t="n"/>
@@ -7914,6 +8374,7 @@
       <c r="O447" s="68" t="n"/>
       <c r="P447" s="61" t="n"/>
       <c r="Q447" s="61" t="n"/>
+      <c r="R447" s="89" t="n"/>
     </row>
     <row r="448" ht="12.75" customHeight="1" s="69">
       <c r="F448" s="65" t="n"/>
@@ -7924,6 +8385,7 @@
       <c r="O448" s="68" t="n"/>
       <c r="P448" s="61" t="n"/>
       <c r="Q448" s="61" t="n"/>
+      <c r="R448" s="89" t="n"/>
     </row>
     <row r="449" ht="12.75" customHeight="1" s="69">
       <c r="F449" s="65" t="n"/>
@@ -7934,6 +8396,7 @@
       <c r="O449" s="68" t="n"/>
       <c r="P449" s="61" t="n"/>
       <c r="Q449" s="61" t="n"/>
+      <c r="R449" s="89" t="n"/>
     </row>
     <row r="450" ht="12.75" customHeight="1" s="69">
       <c r="F450" s="65" t="n"/>
@@ -7944,6 +8407,7 @@
       <c r="O450" s="68" t="n"/>
       <c r="P450" s="61" t="n"/>
       <c r="Q450" s="61" t="n"/>
+      <c r="R450" s="89" t="n"/>
     </row>
     <row r="451" ht="12.75" customHeight="1" s="69">
       <c r="F451" s="65" t="n"/>
@@ -7954,6 +8418,7 @@
       <c r="O451" s="68" t="n"/>
       <c r="P451" s="61" t="n"/>
       <c r="Q451" s="61" t="n"/>
+      <c r="R451" s="89" t="n"/>
     </row>
     <row r="452" ht="12.75" customHeight="1" s="69">
       <c r="F452" s="65" t="n"/>
@@ -7964,6 +8429,7 @@
       <c r="O452" s="68" t="n"/>
       <c r="P452" s="61" t="n"/>
       <c r="Q452" s="61" t="n"/>
+      <c r="R452" s="89" t="n"/>
     </row>
     <row r="453" ht="12.75" customHeight="1" s="69">
       <c r="F453" s="65" t="n"/>
@@ -7974,6 +8440,7 @@
       <c r="O453" s="68" t="n"/>
       <c r="P453" s="61" t="n"/>
       <c r="Q453" s="61" t="n"/>
+      <c r="R453" s="89" t="n"/>
     </row>
     <row r="454" ht="12.75" customHeight="1" s="69">
       <c r="F454" s="65" t="n"/>
@@ -7984,6 +8451,7 @@
       <c r="O454" s="68" t="n"/>
       <c r="P454" s="61" t="n"/>
       <c r="Q454" s="61" t="n"/>
+      <c r="R454" s="89" t="n"/>
     </row>
     <row r="455" ht="12.75" customHeight="1" s="69">
       <c r="F455" s="65" t="n"/>
@@ -7994,6 +8462,7 @@
       <c r="O455" s="68" t="n"/>
       <c r="P455" s="61" t="n"/>
       <c r="Q455" s="61" t="n"/>
+      <c r="R455" s="89" t="n"/>
     </row>
     <row r="456" ht="12.75" customHeight="1" s="69">
       <c r="F456" s="65" t="n"/>
@@ -8004,6 +8473,7 @@
       <c r="O456" s="68" t="n"/>
       <c r="P456" s="61" t="n"/>
       <c r="Q456" s="61" t="n"/>
+      <c r="R456" s="89" t="n"/>
     </row>
     <row r="457" ht="12.75" customHeight="1" s="69">
       <c r="F457" s="65" t="n"/>
@@ -8014,6 +8484,7 @@
       <c r="O457" s="68" t="n"/>
       <c r="P457" s="61" t="n"/>
       <c r="Q457" s="61" t="n"/>
+      <c r="R457" s="89" t="n"/>
     </row>
     <row r="458" ht="12.75" customHeight="1" s="69">
       <c r="F458" s="65" t="n"/>
@@ -8024,6 +8495,7 @@
       <c r="O458" s="68" t="n"/>
       <c r="P458" s="61" t="n"/>
       <c r="Q458" s="61" t="n"/>
+      <c r="R458" s="89" t="n"/>
     </row>
     <row r="459" ht="12.75" customHeight="1" s="69">
       <c r="F459" s="65" t="n"/>
@@ -8034,6 +8506,7 @@
       <c r="O459" s="68" t="n"/>
       <c r="P459" s="61" t="n"/>
       <c r="Q459" s="61" t="n"/>
+      <c r="R459" s="89" t="n"/>
     </row>
     <row r="460" ht="12.75" customHeight="1" s="69">
       <c r="F460" s="65" t="n"/>
@@ -8044,6 +8517,7 @@
       <c r="O460" s="68" t="n"/>
       <c r="P460" s="61" t="n"/>
       <c r="Q460" s="61" t="n"/>
+      <c r="R460" s="89" t="n"/>
     </row>
     <row r="461" ht="12.75" customHeight="1" s="69">
       <c r="F461" s="65" t="n"/>
@@ -8054,6 +8528,7 @@
       <c r="O461" s="68" t="n"/>
       <c r="P461" s="61" t="n"/>
       <c r="Q461" s="61" t="n"/>
+      <c r="R461" s="89" t="n"/>
     </row>
     <row r="462" ht="12.75" customHeight="1" s="69">
       <c r="F462" s="65" t="n"/>
@@ -8064,6 +8539,7 @@
       <c r="O462" s="68" t="n"/>
       <c r="P462" s="61" t="n"/>
       <c r="Q462" s="61" t="n"/>
+      <c r="R462" s="89" t="n"/>
     </row>
     <row r="463" ht="12.75" customHeight="1" s="69">
       <c r="F463" s="65" t="n"/>
@@ -8074,6 +8550,7 @@
       <c r="O463" s="68" t="n"/>
       <c r="P463" s="61" t="n"/>
       <c r="Q463" s="61" t="n"/>
+      <c r="R463" s="89" t="n"/>
     </row>
     <row r="464" ht="12.75" customHeight="1" s="69">
       <c r="F464" s="65" t="n"/>
@@ -8084,6 +8561,7 @@
       <c r="O464" s="68" t="n"/>
       <c r="P464" s="61" t="n"/>
       <c r="Q464" s="61" t="n"/>
+      <c r="R464" s="89" t="n"/>
     </row>
     <row r="465" ht="12.75" customHeight="1" s="69">
       <c r="F465" s="65" t="n"/>
@@ -8094,6 +8572,7 @@
       <c r="O465" s="68" t="n"/>
       <c r="P465" s="61" t="n"/>
       <c r="Q465" s="61" t="n"/>
+      <c r="R465" s="89" t="n"/>
     </row>
     <row r="466" ht="12.75" customHeight="1" s="69">
       <c r="F466" s="65" t="n"/>
@@ -8104,6 +8583,7 @@
       <c r="O466" s="68" t="n"/>
       <c r="P466" s="61" t="n"/>
       <c r="Q466" s="61" t="n"/>
+      <c r="R466" s="89" t="n"/>
     </row>
     <row r="467" ht="12.75" customHeight="1" s="69">
       <c r="F467" s="65" t="n"/>
@@ -8114,6 +8594,7 @@
       <c r="O467" s="68" t="n"/>
       <c r="P467" s="61" t="n"/>
       <c r="Q467" s="61" t="n"/>
+      <c r="R467" s="89" t="n"/>
     </row>
     <row r="468" ht="12.75" customHeight="1" s="69">
       <c r="F468" s="65" t="n"/>
@@ -8124,6 +8605,7 @@
       <c r="O468" s="68" t="n"/>
       <c r="P468" s="61" t="n"/>
       <c r="Q468" s="61" t="n"/>
+      <c r="R468" s="89" t="n"/>
     </row>
     <row r="469" ht="12.75" customHeight="1" s="69">
       <c r="F469" s="65" t="n"/>
@@ -8134,6 +8616,7 @@
       <c r="O469" s="68" t="n"/>
       <c r="P469" s="61" t="n"/>
       <c r="Q469" s="61" t="n"/>
+      <c r="R469" s="89" t="n"/>
     </row>
     <row r="470" ht="12.75" customHeight="1" s="69">
       <c r="F470" s="65" t="n"/>
@@ -8144,6 +8627,7 @@
       <c r="O470" s="68" t="n"/>
       <c r="P470" s="61" t="n"/>
       <c r="Q470" s="61" t="n"/>
+      <c r="R470" s="89" t="n"/>
     </row>
     <row r="471" ht="12.75" customHeight="1" s="69">
       <c r="F471" s="65" t="n"/>
@@ -8154,6 +8638,7 @@
       <c r="O471" s="68" t="n"/>
       <c r="P471" s="61" t="n"/>
       <c r="Q471" s="61" t="n"/>
+      <c r="R471" s="89" t="n"/>
     </row>
     <row r="472" ht="12.75" customHeight="1" s="69">
       <c r="F472" s="65" t="n"/>
@@ -8164,6 +8649,7 @@
       <c r="O472" s="68" t="n"/>
       <c r="P472" s="61" t="n"/>
       <c r="Q472" s="61" t="n"/>
+      <c r="R472" s="89" t="n"/>
     </row>
     <row r="473" ht="12.75" customHeight="1" s="69">
       <c r="F473" s="65" t="n"/>
@@ -8174,6 +8660,7 @@
       <c r="O473" s="68" t="n"/>
       <c r="P473" s="61" t="n"/>
       <c r="Q473" s="61" t="n"/>
+      <c r="R473" s="89" t="n"/>
     </row>
     <row r="474" ht="12.75" customHeight="1" s="69">
       <c r="F474" s="65" t="n"/>
@@ -8184,6 +8671,7 @@
       <c r="O474" s="68" t="n"/>
       <c r="P474" s="61" t="n"/>
       <c r="Q474" s="61" t="n"/>
+      <c r="R474" s="89" t="n"/>
     </row>
     <row r="475" ht="12.75" customHeight="1" s="69">
       <c r="F475" s="65" t="n"/>
@@ -8194,6 +8682,7 @@
       <c r="O475" s="68" t="n"/>
       <c r="P475" s="61" t="n"/>
       <c r="Q475" s="61" t="n"/>
+      <c r="R475" s="89" t="n"/>
     </row>
     <row r="476" ht="12.75" customHeight="1" s="69">
       <c r="F476" s="65" t="n"/>
@@ -8204,6 +8693,7 @@
       <c r="O476" s="68" t="n"/>
       <c r="P476" s="61" t="n"/>
       <c r="Q476" s="61" t="n"/>
+      <c r="R476" s="89" t="n"/>
     </row>
     <row r="477" ht="12.75" customHeight="1" s="69">
       <c r="F477" s="65" t="n"/>
@@ -8214,6 +8704,7 @@
       <c r="O477" s="68" t="n"/>
       <c r="P477" s="61" t="n"/>
       <c r="Q477" s="61" t="n"/>
+      <c r="R477" s="89" t="n"/>
     </row>
     <row r="478" ht="12.75" customHeight="1" s="69">
       <c r="F478" s="65" t="n"/>
@@ -8224,6 +8715,7 @@
       <c r="O478" s="68" t="n"/>
       <c r="P478" s="61" t="n"/>
       <c r="Q478" s="61" t="n"/>
+      <c r="R478" s="89" t="n"/>
     </row>
     <row r="479" ht="12.75" customHeight="1" s="69">
       <c r="F479" s="65" t="n"/>
@@ -8234,6 +8726,7 @@
       <c r="O479" s="68" t="n"/>
       <c r="P479" s="61" t="n"/>
       <c r="Q479" s="61" t="n"/>
+      <c r="R479" s="89" t="n"/>
     </row>
     <row r="480" ht="12.75" customHeight="1" s="69">
       <c r="F480" s="65" t="n"/>
@@ -8244,6 +8737,7 @@
       <c r="O480" s="68" t="n"/>
       <c r="P480" s="61" t="n"/>
       <c r="Q480" s="61" t="n"/>
+      <c r="R480" s="89" t="n"/>
     </row>
     <row r="481" ht="12.75" customHeight="1" s="69">
       <c r="F481" s="65" t="n"/>
@@ -8254,6 +8748,7 @@
       <c r="O481" s="68" t="n"/>
       <c r="P481" s="61" t="n"/>
       <c r="Q481" s="61" t="n"/>
+      <c r="R481" s="89" t="n"/>
     </row>
     <row r="482" ht="12.75" customHeight="1" s="69">
       <c r="F482" s="65" t="n"/>
@@ -8264,6 +8759,7 @@
       <c r="O482" s="68" t="n"/>
       <c r="P482" s="61" t="n"/>
       <c r="Q482" s="61" t="n"/>
+      <c r="R482" s="89" t="n"/>
     </row>
     <row r="483" ht="12.75" customHeight="1" s="69">
       <c r="F483" s="65" t="n"/>
@@ -8274,6 +8770,7 @@
       <c r="O483" s="68" t="n"/>
       <c r="P483" s="61" t="n"/>
       <c r="Q483" s="61" t="n"/>
+      <c r="R483" s="89" t="n"/>
     </row>
     <row r="484" ht="12.75" customHeight="1" s="69">
       <c r="F484" s="65" t="n"/>
@@ -8284,6 +8781,7 @@
       <c r="O484" s="68" t="n"/>
       <c r="P484" s="61" t="n"/>
       <c r="Q484" s="61" t="n"/>
+      <c r="R484" s="89" t="n"/>
     </row>
     <row r="485" ht="12.75" customHeight="1" s="69">
       <c r="F485" s="65" t="n"/>
@@ -8294,6 +8792,7 @@
       <c r="O485" s="68" t="n"/>
       <c r="P485" s="61" t="n"/>
       <c r="Q485" s="61" t="n"/>
+      <c r="R485" s="89" t="n"/>
     </row>
     <row r="486" ht="12.75" customHeight="1" s="69">
       <c r="F486" s="65" t="n"/>
@@ -8304,6 +8803,7 @@
       <c r="O486" s="68" t="n"/>
       <c r="P486" s="61" t="n"/>
       <c r="Q486" s="61" t="n"/>
+      <c r="R486" s="89" t="n"/>
     </row>
     <row r="487" ht="12.75" customHeight="1" s="69">
       <c r="F487" s="65" t="n"/>
@@ -8314,6 +8814,7 @@
       <c r="O487" s="68" t="n"/>
       <c r="P487" s="61" t="n"/>
       <c r="Q487" s="61" t="n"/>
+      <c r="R487" s="89" t="n"/>
     </row>
     <row r="488" ht="12.75" customHeight="1" s="69">
       <c r="F488" s="65" t="n"/>
@@ -8324,6 +8825,7 @@
       <c r="O488" s="68" t="n"/>
       <c r="P488" s="61" t="n"/>
       <c r="Q488" s="61" t="n"/>
+      <c r="R488" s="89" t="n"/>
     </row>
     <row r="489" ht="12.75" customHeight="1" s="69">
       <c r="F489" s="65" t="n"/>
@@ -8334,6 +8836,7 @@
       <c r="O489" s="68" t="n"/>
       <c r="P489" s="61" t="n"/>
       <c r="Q489" s="61" t="n"/>
+      <c r="R489" s="89" t="n"/>
     </row>
     <row r="490" ht="12.75" customHeight="1" s="69">
       <c r="F490" s="65" t="n"/>
@@ -8344,6 +8847,7 @@
       <c r="O490" s="68" t="n"/>
       <c r="P490" s="61" t="n"/>
       <c r="Q490" s="61" t="n"/>
+      <c r="R490" s="89" t="n"/>
     </row>
     <row r="491" ht="12.75" customHeight="1" s="69">
       <c r="F491" s="65" t="n"/>
@@ -8354,6 +8858,7 @@
       <c r="O491" s="68" t="n"/>
       <c r="P491" s="61" t="n"/>
       <c r="Q491" s="61" t="n"/>
+      <c r="R491" s="89" t="n"/>
     </row>
     <row r="492" ht="12.75" customHeight="1" s="69">
       <c r="F492" s="65" t="n"/>
@@ -8364,6 +8869,7 @@
       <c r="O492" s="68" t="n"/>
       <c r="P492" s="61" t="n"/>
       <c r="Q492" s="61" t="n"/>
+      <c r="R492" s="89" t="n"/>
     </row>
     <row r="493" ht="12.75" customHeight="1" s="69">
       <c r="F493" s="65" t="n"/>
@@ -8374,6 +8880,7 @@
       <c r="O493" s="68" t="n"/>
       <c r="P493" s="61" t="n"/>
       <c r="Q493" s="61" t="n"/>
+      <c r="R493" s="89" t="n"/>
     </row>
     <row r="494" ht="12.75" customHeight="1" s="69">
       <c r="F494" s="65" t="n"/>
@@ -8384,6 +8891,7 @@
       <c r="O494" s="68" t="n"/>
       <c r="P494" s="61" t="n"/>
       <c r="Q494" s="61" t="n"/>
+      <c r="R494" s="89" t="n"/>
     </row>
     <row r="495" ht="12.75" customHeight="1" s="69">
       <c r="F495" s="65" t="n"/>
@@ -8394,6 +8902,7 @@
       <c r="O495" s="68" t="n"/>
       <c r="P495" s="61" t="n"/>
       <c r="Q495" s="61" t="n"/>
+      <c r="R495" s="89" t="n"/>
     </row>
     <row r="496" ht="12.75" customHeight="1" s="69">
       <c r="F496" s="65" t="n"/>
@@ -8404,6 +8913,7 @@
       <c r="O496" s="68" t="n"/>
       <c r="P496" s="61" t="n"/>
       <c r="Q496" s="61" t="n"/>
+      <c r="R496" s="89" t="n"/>
     </row>
     <row r="497" ht="12.75" customHeight="1" s="69">
       <c r="F497" s="65" t="n"/>
@@ -8414,6 +8924,7 @@
       <c r="O497" s="68" t="n"/>
       <c r="P497" s="61" t="n"/>
       <c r="Q497" s="61" t="n"/>
+      <c r="R497" s="89" t="n"/>
     </row>
     <row r="498" ht="12.75" customHeight="1" s="69">
       <c r="F498" s="65" t="n"/>
@@ -8424,6 +8935,7 @@
       <c r="O498" s="68" t="n"/>
       <c r="P498" s="61" t="n"/>
       <c r="Q498" s="61" t="n"/>
+      <c r="R498" s="89" t="n"/>
     </row>
     <row r="499" ht="12.75" customHeight="1" s="69">
       <c r="F499" s="65" t="n"/>
@@ -8434,6 +8946,7 @@
       <c r="O499" s="68" t="n"/>
       <c r="P499" s="61" t="n"/>
       <c r="Q499" s="61" t="n"/>
+      <c r="R499" s="89" t="n"/>
     </row>
     <row r="500" ht="12.75" customHeight="1" s="69">
       <c r="F500" s="65" t="n"/>
@@ -8444,6 +8957,7 @@
       <c r="O500" s="68" t="n"/>
       <c r="P500" s="61" t="n"/>
       <c r="Q500" s="61" t="n"/>
+      <c r="R500" s="89" t="n"/>
     </row>
     <row r="501" ht="12.75" customHeight="1" s="69">
       <c r="F501" s="65" t="n"/>
@@ -8454,6 +8968,7 @@
       <c r="O501" s="68" t="n"/>
       <c r="P501" s="61" t="n"/>
       <c r="Q501" s="61" t="n"/>
+      <c r="R501" s="89" t="n"/>
     </row>
     <row r="502" ht="12.75" customHeight="1" s="69">
       <c r="F502" s="65" t="n"/>
@@ -8464,6 +8979,7 @@
       <c r="O502" s="68" t="n"/>
       <c r="P502" s="61" t="n"/>
       <c r="Q502" s="61" t="n"/>
+      <c r="R502" s="89" t="n"/>
     </row>
     <row r="503" ht="12.75" customHeight="1" s="69">
       <c r="F503" s="65" t="n"/>
@@ -8474,6 +8990,7 @@
       <c r="O503" s="68" t="n"/>
       <c r="P503" s="61" t="n"/>
       <c r="Q503" s="61" t="n"/>
+      <c r="R503" s="89" t="n"/>
     </row>
     <row r="504" ht="12.75" customHeight="1" s="69">
       <c r="F504" s="65" t="n"/>
@@ -8484,6 +9001,7 @@
       <c r="O504" s="68" t="n"/>
       <c r="P504" s="61" t="n"/>
       <c r="Q504" s="61" t="n"/>
+      <c r="R504" s="89" t="n"/>
     </row>
     <row r="505" ht="12.75" customHeight="1" s="69">
       <c r="F505" s="65" t="n"/>
@@ -8494,6 +9012,7 @@
       <c r="O505" s="68" t="n"/>
       <c r="P505" s="61" t="n"/>
       <c r="Q505" s="61" t="n"/>
+      <c r="R505" s="89" t="n"/>
     </row>
     <row r="506" ht="12.75" customHeight="1" s="69">
       <c r="F506" s="65" t="n"/>
@@ -8504,6 +9023,7 @@
       <c r="O506" s="68" t="n"/>
       <c r="P506" s="61" t="n"/>
       <c r="Q506" s="61" t="n"/>
+      <c r="R506" s="89" t="n"/>
     </row>
     <row r="507" ht="12.75" customHeight="1" s="69">
       <c r="F507" s="65" t="n"/>
@@ -8514,6 +9034,7 @@
       <c r="O507" s="68" t="n"/>
       <c r="P507" s="61" t="n"/>
       <c r="Q507" s="61" t="n"/>
+      <c r="R507" s="89" t="n"/>
     </row>
     <row r="508" ht="12.75" customHeight="1" s="69">
       <c r="F508" s="65" t="n"/>
@@ -8524,6 +9045,7 @@
       <c r="O508" s="68" t="n"/>
       <c r="P508" s="61" t="n"/>
       <c r="Q508" s="61" t="n"/>
+      <c r="R508" s="89" t="n"/>
     </row>
     <row r="509" ht="12.75" customHeight="1" s="69">
       <c r="F509" s="65" t="n"/>
@@ -8534,6 +9056,7 @@
       <c r="O509" s="68" t="n"/>
       <c r="P509" s="61" t="n"/>
       <c r="Q509" s="61" t="n"/>
+      <c r="R509" s="89" t="n"/>
     </row>
     <row r="510" ht="12.75" customHeight="1" s="69">
       <c r="F510" s="65" t="n"/>
@@ -8544,6 +9067,7 @@
       <c r="O510" s="68" t="n"/>
       <c r="P510" s="61" t="n"/>
       <c r="Q510" s="61" t="n"/>
+      <c r="R510" s="89" t="n"/>
     </row>
     <row r="511" ht="12.75" customHeight="1" s="69">
       <c r="F511" s="65" t="n"/>
@@ -8554,6 +9078,7 @@
       <c r="O511" s="68" t="n"/>
       <c r="P511" s="61" t="n"/>
       <c r="Q511" s="61" t="n"/>
+      <c r="R511" s="89" t="n"/>
     </row>
     <row r="512" ht="12.75" customHeight="1" s="69">
       <c r="F512" s="65" t="n"/>
@@ -8564,6 +9089,7 @@
       <c r="O512" s="68" t="n"/>
       <c r="P512" s="61" t="n"/>
       <c r="Q512" s="61" t="n"/>
+      <c r="R512" s="89" t="n"/>
     </row>
     <row r="513" ht="12.75" customHeight="1" s="69">
       <c r="F513" s="65" t="n"/>
@@ -8574,6 +9100,7 @@
       <c r="O513" s="68" t="n"/>
       <c r="P513" s="61" t="n"/>
       <c r="Q513" s="61" t="n"/>
+      <c r="R513" s="89" t="n"/>
     </row>
     <row r="514" ht="12.75" customHeight="1" s="69">
       <c r="F514" s="65" t="n"/>
@@ -8584,6 +9111,7 @@
       <c r="O514" s="68" t="n"/>
       <c r="P514" s="61" t="n"/>
       <c r="Q514" s="61" t="n"/>
+      <c r="R514" s="89" t="n"/>
     </row>
     <row r="515" ht="12.75" customHeight="1" s="69">
       <c r="F515" s="65" t="n"/>
@@ -8594,6 +9122,7 @@
       <c r="O515" s="68" t="n"/>
       <c r="P515" s="61" t="n"/>
       <c r="Q515" s="61" t="n"/>
+      <c r="R515" s="89" t="n"/>
     </row>
     <row r="516" ht="12.75" customHeight="1" s="69">
       <c r="F516" s="65" t="n"/>
@@ -8604,6 +9133,7 @@
       <c r="O516" s="68" t="n"/>
       <c r="P516" s="61" t="n"/>
       <c r="Q516" s="61" t="n"/>
+      <c r="R516" s="89" t="n"/>
     </row>
     <row r="517" ht="12.75" customHeight="1" s="69">
       <c r="F517" s="65" t="n"/>
@@ -8614,6 +9144,7 @@
       <c r="O517" s="68" t="n"/>
       <c r="P517" s="61" t="n"/>
       <c r="Q517" s="61" t="n"/>
+      <c r="R517" s="89" t="n"/>
     </row>
     <row r="518" ht="12.75" customHeight="1" s="69">
       <c r="F518" s="65" t="n"/>
@@ -8624,6 +9155,7 @@
       <c r="O518" s="68" t="n"/>
       <c r="P518" s="61" t="n"/>
       <c r="Q518" s="61" t="n"/>
+      <c r="R518" s="89" t="n"/>
     </row>
     <row r="519" ht="12.75" customHeight="1" s="69">
       <c r="F519" s="65" t="n"/>
@@ -8634,6 +9166,7 @@
       <c r="O519" s="68" t="n"/>
       <c r="P519" s="61" t="n"/>
       <c r="Q519" s="61" t="n"/>
+      <c r="R519" s="89" t="n"/>
     </row>
     <row r="520" ht="12.75" customHeight="1" s="69">
       <c r="F520" s="65" t="n"/>
@@ -8644,6 +9177,7 @@
       <c r="O520" s="68" t="n"/>
       <c r="P520" s="61" t="n"/>
       <c r="Q520" s="61" t="n"/>
+      <c r="R520" s="89" t="n"/>
     </row>
     <row r="521" ht="12.75" customHeight="1" s="69">
       <c r="F521" s="65" t="n"/>
@@ -8654,6 +9188,7 @@
       <c r="O521" s="68" t="n"/>
       <c r="P521" s="61" t="n"/>
       <c r="Q521" s="61" t="n"/>
+      <c r="R521" s="89" t="n"/>
     </row>
     <row r="522" ht="12.75" customHeight="1" s="69">
       <c r="F522" s="65" t="n"/>
@@ -8664,6 +9199,7 @@
       <c r="O522" s="68" t="n"/>
       <c r="P522" s="61" t="n"/>
       <c r="Q522" s="61" t="n"/>
+      <c r="R522" s="89" t="n"/>
     </row>
     <row r="523" ht="12.75" customHeight="1" s="69">
       <c r="F523" s="65" t="n"/>
@@ -8674,6 +9210,7 @@
       <c r="O523" s="68" t="n"/>
       <c r="P523" s="61" t="n"/>
       <c r="Q523" s="61" t="n"/>
+      <c r="R523" s="89" t="n"/>
     </row>
     <row r="524" ht="12.75" customHeight="1" s="69">
       <c r="F524" s="65" t="n"/>
@@ -8684,6 +9221,7 @@
       <c r="O524" s="68" t="n"/>
       <c r="P524" s="61" t="n"/>
       <c r="Q524" s="61" t="n"/>
+      <c r="R524" s="89" t="n"/>
     </row>
     <row r="525" ht="12.75" customHeight="1" s="69">
       <c r="F525" s="65" t="n"/>
@@ -8694,6 +9232,7 @@
       <c r="O525" s="68" t="n"/>
       <c r="P525" s="61" t="n"/>
       <c r="Q525" s="61" t="n"/>
+      <c r="R525" s="89" t="n"/>
     </row>
     <row r="526" ht="12.75" customHeight="1" s="69">
       <c r="F526" s="65" t="n"/>
@@ -8704,6 +9243,7 @@
       <c r="O526" s="68" t="n"/>
       <c r="P526" s="61" t="n"/>
       <c r="Q526" s="61" t="n"/>
+      <c r="R526" s="89" t="n"/>
     </row>
     <row r="527" ht="12.75" customHeight="1" s="69">
       <c r="F527" s="65" t="n"/>
@@ -8714,6 +9254,7 @@
       <c r="O527" s="68" t="n"/>
       <c r="P527" s="61" t="n"/>
       <c r="Q527" s="61" t="n"/>
+      <c r="R527" s="89" t="n"/>
     </row>
     <row r="528" ht="12.75" customHeight="1" s="69">
       <c r="F528" s="65" t="n"/>
@@ -8724,6 +9265,7 @@
       <c r="O528" s="68" t="n"/>
       <c r="P528" s="61" t="n"/>
       <c r="Q528" s="61" t="n"/>
+      <c r="R528" s="89" t="n"/>
     </row>
     <row r="529" ht="12.75" customHeight="1" s="69">
       <c r="F529" s="65" t="n"/>
@@ -8734,6 +9276,7 @@
       <c r="O529" s="68" t="n"/>
       <c r="P529" s="61" t="n"/>
       <c r="Q529" s="61" t="n"/>
+      <c r="R529" s="89" t="n"/>
     </row>
     <row r="530" ht="12.75" customHeight="1" s="69">
       <c r="F530" s="65" t="n"/>
@@ -8744,6 +9287,7 @@
       <c r="O530" s="68" t="n"/>
       <c r="P530" s="61" t="n"/>
       <c r="Q530" s="61" t="n"/>
+      <c r="R530" s="89" t="n"/>
     </row>
     <row r="531" ht="12.75" customHeight="1" s="69">
       <c r="F531" s="65" t="n"/>
@@ -8754,6 +9298,7 @@
       <c r="O531" s="68" t="n"/>
       <c r="P531" s="61" t="n"/>
       <c r="Q531" s="61" t="n"/>
+      <c r="R531" s="89" t="n"/>
     </row>
     <row r="532" ht="12.75" customHeight="1" s="69">
       <c r="F532" s="65" t="n"/>
@@ -8764,6 +9309,7 @@
       <c r="O532" s="68" t="n"/>
       <c r="P532" s="61" t="n"/>
       <c r="Q532" s="61" t="n"/>
+      <c r="R532" s="89" t="n"/>
     </row>
     <row r="533" ht="12.75" customHeight="1" s="69">
       <c r="F533" s="65" t="n"/>
@@ -8774,6 +9320,7 @@
       <c r="O533" s="68" t="n"/>
       <c r="P533" s="61" t="n"/>
       <c r="Q533" s="61" t="n"/>
+      <c r="R533" s="89" t="n"/>
     </row>
     <row r="534" ht="12.75" customHeight="1" s="69">
       <c r="F534" s="65" t="n"/>
@@ -8784,6 +9331,7 @@
       <c r="O534" s="68" t="n"/>
       <c r="P534" s="61" t="n"/>
       <c r="Q534" s="61" t="n"/>
+      <c r="R534" s="89" t="n"/>
     </row>
     <row r="535" ht="12.75" customHeight="1" s="69">
       <c r="F535" s="65" t="n"/>
@@ -8794,6 +9342,7 @@
       <c r="O535" s="68" t="n"/>
       <c r="P535" s="61" t="n"/>
       <c r="Q535" s="61" t="n"/>
+      <c r="R535" s="89" t="n"/>
     </row>
     <row r="536" ht="12.75" customHeight="1" s="69">
       <c r="F536" s="65" t="n"/>
@@ -8804,6 +9353,7 @@
       <c r="O536" s="68" t="n"/>
       <c r="P536" s="61" t="n"/>
       <c r="Q536" s="61" t="n"/>
+      <c r="R536" s="89" t="n"/>
     </row>
     <row r="537" ht="12.75" customHeight="1" s="69">
       <c r="F537" s="65" t="n"/>
@@ -8814,6 +9364,7 @@
       <c r="O537" s="68" t="n"/>
       <c r="P537" s="61" t="n"/>
       <c r="Q537" s="61" t="n"/>
+      <c r="R537" s="89" t="n"/>
     </row>
     <row r="538" ht="12.75" customHeight="1" s="69">
       <c r="F538" s="65" t="n"/>
@@ -8824,6 +9375,7 @@
       <c r="O538" s="68" t="n"/>
       <c r="P538" s="61" t="n"/>
       <c r="Q538" s="61" t="n"/>
+      <c r="R538" s="89" t="n"/>
     </row>
     <row r="539" ht="12.75" customHeight="1" s="69">
       <c r="F539" s="65" t="n"/>
@@ -8834,6 +9386,7 @@
       <c r="O539" s="68" t="n"/>
       <c r="P539" s="61" t="n"/>
       <c r="Q539" s="61" t="n"/>
+      <c r="R539" s="89" t="n"/>
     </row>
     <row r="540" ht="12.75" customHeight="1" s="69">
       <c r="F540" s="65" t="n"/>
@@ -8844,6 +9397,7 @@
       <c r="O540" s="68" t="n"/>
       <c r="P540" s="61" t="n"/>
       <c r="Q540" s="61" t="n"/>
+      <c r="R540" s="89" t="n"/>
     </row>
     <row r="541" ht="12.75" customHeight="1" s="69">
       <c r="F541" s="65" t="n"/>
@@ -8854,6 +9408,7 @@
       <c r="O541" s="68" t="n"/>
       <c r="P541" s="61" t="n"/>
       <c r="Q541" s="61" t="n"/>
+      <c r="R541" s="89" t="n"/>
     </row>
     <row r="542" ht="12.75" customHeight="1" s="69">
       <c r="F542" s="65" t="n"/>
@@ -8864,6 +9419,7 @@
       <c r="O542" s="68" t="n"/>
       <c r="P542" s="61" t="n"/>
       <c r="Q542" s="61" t="n"/>
+      <c r="R542" s="89" t="n"/>
     </row>
     <row r="543" ht="12.75" customHeight="1" s="69">
       <c r="F543" s="65" t="n"/>
@@ -8874,6 +9430,7 @@
       <c r="O543" s="68" t="n"/>
       <c r="P543" s="61" t="n"/>
       <c r="Q543" s="61" t="n"/>
+      <c r="R543" s="89" t="n"/>
     </row>
     <row r="544" ht="12.75" customHeight="1" s="69">
       <c r="F544" s="65" t="n"/>
@@ -8884,6 +9441,7 @@
       <c r="O544" s="68" t="n"/>
       <c r="P544" s="61" t="n"/>
       <c r="Q544" s="61" t="n"/>
+      <c r="R544" s="89" t="n"/>
     </row>
     <row r="545" ht="12.75" customHeight="1" s="69">
       <c r="F545" s="65" t="n"/>
@@ -8894,6 +9452,7 @@
       <c r="O545" s="68" t="n"/>
       <c r="P545" s="61" t="n"/>
       <c r="Q545" s="61" t="n"/>
+      <c r="R545" s="89" t="n"/>
     </row>
     <row r="546" ht="12.75" customHeight="1" s="69">
       <c r="F546" s="65" t="n"/>
@@ -8904,6 +9463,7 @@
       <c r="O546" s="68" t="n"/>
       <c r="P546" s="61" t="n"/>
       <c r="Q546" s="61" t="n"/>
+      <c r="R546" s="89" t="n"/>
     </row>
     <row r="547" ht="12.75" customHeight="1" s="69">
       <c r="F547" s="65" t="n"/>
@@ -8914,6 +9474,7 @@
       <c r="O547" s="68" t="n"/>
       <c r="P547" s="61" t="n"/>
       <c r="Q547" s="61" t="n"/>
+      <c r="R547" s="89" t="n"/>
     </row>
     <row r="548" ht="12.75" customHeight="1" s="69">
       <c r="F548" s="65" t="n"/>
@@ -8924,6 +9485,7 @@
       <c r="O548" s="68" t="n"/>
       <c r="P548" s="61" t="n"/>
       <c r="Q548" s="61" t="n"/>
+      <c r="R548" s="89" t="n"/>
     </row>
     <row r="549" ht="12.75" customHeight="1" s="69">
       <c r="F549" s="65" t="n"/>
@@ -8934,6 +9496,7 @@
       <c r="O549" s="68" t="n"/>
       <c r="P549" s="61" t="n"/>
       <c r="Q549" s="61" t="n"/>
+      <c r="R549" s="89" t="n"/>
     </row>
     <row r="550" ht="12.75" customHeight="1" s="69">
       <c r="F550" s="65" t="n"/>
@@ -8944,6 +9507,7 @@
       <c r="O550" s="68" t="n"/>
       <c r="P550" s="61" t="n"/>
       <c r="Q550" s="61" t="n"/>
+      <c r="R550" s="89" t="n"/>
     </row>
     <row r="551" ht="12.75" customHeight="1" s="69">
       <c r="F551" s="65" t="n"/>
@@ -8954,6 +9518,7 @@
       <c r="O551" s="68" t="n"/>
       <c r="P551" s="61" t="n"/>
       <c r="Q551" s="61" t="n"/>
+      <c r="R551" s="89" t="n"/>
     </row>
     <row r="552" ht="12.75" customHeight="1" s="69">
       <c r="F552" s="65" t="n"/>
@@ -8964,6 +9529,7 @@
       <c r="O552" s="68" t="n"/>
       <c r="P552" s="61" t="n"/>
       <c r="Q552" s="61" t="n"/>
+      <c r="R552" s="89" t="n"/>
     </row>
     <row r="553" ht="12.75" customHeight="1" s="69">
       <c r="F553" s="65" t="n"/>
@@ -8974,6 +9540,7 @@
       <c r="O553" s="68" t="n"/>
       <c r="P553" s="61" t="n"/>
       <c r="Q553" s="61" t="n"/>
+      <c r="R553" s="89" t="n"/>
     </row>
     <row r="554" ht="12.75" customHeight="1" s="69">
       <c r="F554" s="65" t="n"/>
@@ -8984,6 +9551,7 @@
       <c r="O554" s="68" t="n"/>
       <c r="P554" s="61" t="n"/>
       <c r="Q554" s="61" t="n"/>
+      <c r="R554" s="89" t="n"/>
     </row>
     <row r="555" ht="12.75" customHeight="1" s="69">
       <c r="F555" s="65" t="n"/>
@@ -8994,6 +9562,7 @@
       <c r="O555" s="68" t="n"/>
       <c r="P555" s="61" t="n"/>
       <c r="Q555" s="61" t="n"/>
+      <c r="R555" s="89" t="n"/>
     </row>
     <row r="556" ht="12.75" customHeight="1" s="69">
       <c r="F556" s="65" t="n"/>
@@ -9004,6 +9573,7 @@
       <c r="O556" s="68" t="n"/>
       <c r="P556" s="61" t="n"/>
       <c r="Q556" s="61" t="n"/>
+      <c r="R556" s="89" t="n"/>
     </row>
     <row r="557" ht="12.75" customHeight="1" s="69">
       <c r="F557" s="65" t="n"/>
@@ -9014,6 +9584,7 @@
       <c r="O557" s="68" t="n"/>
       <c r="P557" s="61" t="n"/>
       <c r="Q557" s="61" t="n"/>
+      <c r="R557" s="89" t="n"/>
     </row>
     <row r="558" ht="12.75" customHeight="1" s="69">
       <c r="F558" s="65" t="n"/>
@@ -9024,6 +9595,7 @@
       <c r="O558" s="68" t="n"/>
       <c r="P558" s="61" t="n"/>
       <c r="Q558" s="61" t="n"/>
+      <c r="R558" s="89" t="n"/>
     </row>
     <row r="559" ht="12.75" customHeight="1" s="69">
       <c r="F559" s="65" t="n"/>
@@ -9034,6 +9606,7 @@
       <c r="O559" s="68" t="n"/>
       <c r="P559" s="61" t="n"/>
       <c r="Q559" s="61" t="n"/>
+      <c r="R559" s="89" t="n"/>
     </row>
     <row r="560" ht="12.75" customHeight="1" s="69">
       <c r="F560" s="65" t="n"/>
@@ -9044,6 +9617,7 @@
       <c r="O560" s="68" t="n"/>
       <c r="P560" s="61" t="n"/>
       <c r="Q560" s="61" t="n"/>
+      <c r="R560" s="89" t="n"/>
     </row>
     <row r="561" ht="12.75" customHeight="1" s="69">
       <c r="F561" s="65" t="n"/>
@@ -9054,6 +9628,7 @@
       <c r="O561" s="68" t="n"/>
       <c r="P561" s="61" t="n"/>
       <c r="Q561" s="61" t="n"/>
+      <c r="R561" s="89" t="n"/>
     </row>
     <row r="562" ht="12.75" customHeight="1" s="69">
       <c r="F562" s="65" t="n"/>
@@ -9064,6 +9639,7 @@
       <c r="O562" s="68" t="n"/>
       <c r="P562" s="61" t="n"/>
       <c r="Q562" s="61" t="n"/>
+      <c r="R562" s="89" t="n"/>
     </row>
     <row r="563" ht="12.75" customHeight="1" s="69">
       <c r="F563" s="65" t="n"/>
@@ -9074,6 +9650,7 @@
       <c r="O563" s="68" t="n"/>
       <c r="P563" s="61" t="n"/>
       <c r="Q563" s="61" t="n"/>
+      <c r="R563" s="89" t="n"/>
     </row>
     <row r="564" ht="12.75" customHeight="1" s="69">
       <c r="F564" s="65" t="n"/>
@@ -9084,6 +9661,7 @@
       <c r="O564" s="68" t="n"/>
       <c r="P564" s="61" t="n"/>
       <c r="Q564" s="61" t="n"/>
+      <c r="R564" s="89" t="n"/>
     </row>
     <row r="565" ht="12.75" customHeight="1" s="69">
       <c r="F565" s="65" t="n"/>
@@ -9094,6 +9672,7 @@
       <c r="O565" s="68" t="n"/>
       <c r="P565" s="61" t="n"/>
       <c r="Q565" s="61" t="n"/>
+      <c r="R565" s="89" t="n"/>
     </row>
     <row r="566" ht="12.75" customHeight="1" s="69">
       <c r="F566" s="65" t="n"/>
@@ -9104,6 +9683,7 @@
       <c r="O566" s="68" t="n"/>
       <c r="P566" s="61" t="n"/>
       <c r="Q566" s="61" t="n"/>
+      <c r="R566" s="89" t="n"/>
     </row>
     <row r="567" ht="12.75" customHeight="1" s="69">
       <c r="F567" s="65" t="n"/>
@@ -9114,6 +9694,7 @@
       <c r="O567" s="68" t="n"/>
       <c r="P567" s="61" t="n"/>
       <c r="Q567" s="61" t="n"/>
+      <c r="R567" s="89" t="n"/>
     </row>
     <row r="568" ht="12.75" customHeight="1" s="69">
       <c r="F568" s="65" t="n"/>
@@ -9124,6 +9705,7 @@
       <c r="O568" s="68" t="n"/>
       <c r="P568" s="61" t="n"/>
       <c r="Q568" s="61" t="n"/>
+      <c r="R568" s="89" t="n"/>
     </row>
     <row r="569" ht="12.75" customHeight="1" s="69">
       <c r="F569" s="65" t="n"/>
@@ -9134,6 +9716,7 @@
       <c r="O569" s="68" t="n"/>
       <c r="P569" s="61" t="n"/>
       <c r="Q569" s="61" t="n"/>
+      <c r="R569" s="89" t="n"/>
     </row>
     <row r="570" ht="12.75" customHeight="1" s="69">
       <c r="F570" s="65" t="n"/>
@@ -9144,6 +9727,7 @@
       <c r="O570" s="68" t="n"/>
       <c r="P570" s="61" t="n"/>
       <c r="Q570" s="61" t="n"/>
+      <c r="R570" s="89" t="n"/>
     </row>
     <row r="571" ht="12.75" customHeight="1" s="69">
       <c r="F571" s="65" t="n"/>
@@ -9154,6 +9738,7 @@
       <c r="O571" s="68" t="n"/>
       <c r="P571" s="61" t="n"/>
       <c r="Q571" s="61" t="n"/>
+      <c r="R571" s="89" t="n"/>
     </row>
     <row r="572" ht="12.75" customHeight="1" s="69">
       <c r="F572" s="65" t="n"/>
@@ -9164,6 +9749,7 @@
       <c r="O572" s="68" t="n"/>
       <c r="P572" s="61" t="n"/>
       <c r="Q572" s="61" t="n"/>
+      <c r="R572" s="89" t="n"/>
     </row>
     <row r="573" ht="12.75" customHeight="1" s="69">
       <c r="F573" s="65" t="n"/>
@@ -9174,6 +9760,7 @@
       <c r="O573" s="68" t="n"/>
       <c r="P573" s="61" t="n"/>
       <c r="Q573" s="61" t="n"/>
+      <c r="R573" s="89" t="n"/>
     </row>
     <row r="574" ht="12.75" customHeight="1" s="69">
       <c r="F574" s="65" t="n"/>
@@ -9184,6 +9771,7 @@
       <c r="O574" s="68" t="n"/>
       <c r="P574" s="61" t="n"/>
       <c r="Q574" s="61" t="n"/>
+      <c r="R574" s="89" t="n"/>
     </row>
     <row r="575" ht="12.75" customHeight="1" s="69">
       <c r="F575" s="65" t="n"/>
@@ -9194,6 +9782,7 @@
       <c r="O575" s="68" t="n"/>
       <c r="P575" s="61" t="n"/>
       <c r="Q575" s="61" t="n"/>
+      <c r="R575" s="89" t="n"/>
     </row>
     <row r="576" ht="12.75" customHeight="1" s="69">
       <c r="F576" s="65" t="n"/>
@@ -9204,6 +9793,7 @@
       <c r="O576" s="68" t="n"/>
       <c r="P576" s="61" t="n"/>
       <c r="Q576" s="61" t="n"/>
+      <c r="R576" s="89" t="n"/>
     </row>
     <row r="577" ht="12.75" customHeight="1" s="69">
       <c r="F577" s="65" t="n"/>
@@ -9214,6 +9804,7 @@
       <c r="O577" s="68" t="n"/>
       <c r="P577" s="61" t="n"/>
       <c r="Q577" s="61" t="n"/>
+      <c r="R577" s="89" t="n"/>
     </row>
     <row r="578" ht="12.75" customHeight="1" s="69">
       <c r="F578" s="65" t="n"/>
@@ -9224,6 +9815,7 @@
       <c r="O578" s="68" t="n"/>
       <c r="P578" s="61" t="n"/>
       <c r="Q578" s="61" t="n"/>
+      <c r="R578" s="89" t="n"/>
     </row>
     <row r="579" ht="12.75" customHeight="1" s="69">
       <c r="F579" s="65" t="n"/>
@@ -9234,6 +9826,7 @@
       <c r="O579" s="68" t="n"/>
       <c r="P579" s="61" t="n"/>
       <c r="Q579" s="61" t="n"/>
+      <c r="R579" s="89" t="n"/>
     </row>
     <row r="580" ht="12.75" customHeight="1" s="69">
       <c r="F580" s="65" t="n"/>
@@ -9244,6 +9837,7 @@
       <c r="O580" s="68" t="n"/>
       <c r="P580" s="61" t="n"/>
       <c r="Q580" s="61" t="n"/>
+      <c r="R580" s="89" t="n"/>
     </row>
     <row r="581" ht="12.75" customHeight="1" s="69">
       <c r="F581" s="65" t="n"/>
@@ -9254,6 +9848,7 @@
       <c r="O581" s="68" t="n"/>
       <c r="P581" s="61" t="n"/>
       <c r="Q581" s="61" t="n"/>
+      <c r="R581" s="89" t="n"/>
     </row>
     <row r="582" ht="12.75" customHeight="1" s="69">
       <c r="F582" s="65" t="n"/>
@@ -9264,6 +9859,7 @@
       <c r="O582" s="68" t="n"/>
       <c r="P582" s="61" t="n"/>
       <c r="Q582" s="61" t="n"/>
+      <c r="R582" s="89" t="n"/>
     </row>
     <row r="583" ht="12.75" customHeight="1" s="69">
       <c r="F583" s="65" t="n"/>
@@ -9274,6 +9870,7 @@
       <c r="O583" s="68" t="n"/>
       <c r="P583" s="61" t="n"/>
       <c r="Q583" s="61" t="n"/>
+      <c r="R583" s="89" t="n"/>
     </row>
     <row r="584" ht="12.75" customHeight="1" s="69">
       <c r="F584" s="65" t="n"/>
@@ -9284,6 +9881,7 @@
       <c r="O584" s="68" t="n"/>
       <c r="P584" s="61" t="n"/>
       <c r="Q584" s="61" t="n"/>
+      <c r="R584" s="89" t="n"/>
     </row>
     <row r="585" ht="12.75" customHeight="1" s="69">
       <c r="F585" s="65" t="n"/>
@@ -9294,6 +9892,7 @@
       <c r="O585" s="68" t="n"/>
       <c r="P585" s="61" t="n"/>
       <c r="Q585" s="61" t="n"/>
+      <c r="R585" s="89" t="n"/>
     </row>
     <row r="586" ht="12.75" customHeight="1" s="69">
       <c r="F586" s="65" t="n"/>
@@ -9304,6 +9903,7 @@
       <c r="O586" s="68" t="n"/>
       <c r="P586" s="61" t="n"/>
       <c r="Q586" s="61" t="n"/>
+      <c r="R586" s="89" t="n"/>
     </row>
     <row r="587" ht="12.75" customHeight="1" s="69">
       <c r="F587" s="65" t="n"/>
@@ -9314,6 +9914,7 @@
       <c r="O587" s="68" t="n"/>
       <c r="P587" s="61" t="n"/>
       <c r="Q587" s="61" t="n"/>
+      <c r="R587" s="89" t="n"/>
     </row>
     <row r="588" ht="12.75" customHeight="1" s="69">
       <c r="F588" s="65" t="n"/>
@@ -9324,6 +9925,7 @@
       <c r="O588" s="68" t="n"/>
       <c r="P588" s="61" t="n"/>
       <c r="Q588" s="61" t="n"/>
+      <c r="R588" s="89" t="n"/>
     </row>
     <row r="589" ht="12.75" customHeight="1" s="69">
       <c r="F589" s="65" t="n"/>
@@ -9334,6 +9936,7 @@
       <c r="O589" s="68" t="n"/>
       <c r="P589" s="61" t="n"/>
       <c r="Q589" s="61" t="n"/>
+      <c r="R589" s="89" t="n"/>
     </row>
     <row r="590" ht="12.75" customHeight="1" s="69">
       <c r="F590" s="65" t="n"/>
@@ -9344,6 +9947,7 @@
       <c r="O590" s="68" t="n"/>
       <c r="P590" s="61" t="n"/>
       <c r="Q590" s="61" t="n"/>
+      <c r="R590" s="89" t="n"/>
     </row>
     <row r="591" ht="12.75" customHeight="1" s="69">
       <c r="F591" s="65" t="n"/>
@@ -9354,6 +9958,7 @@
       <c r="O591" s="68" t="n"/>
       <c r="P591" s="61" t="n"/>
       <c r="Q591" s="61" t="n"/>
+      <c r="R591" s="89" t="n"/>
     </row>
     <row r="592" ht="12.75" customHeight="1" s="69">
       <c r="F592" s="65" t="n"/>
@@ -9364,6 +9969,7 @@
       <c r="O592" s="68" t="n"/>
       <c r="P592" s="61" t="n"/>
       <c r="Q592" s="61" t="n"/>
+      <c r="R592" s="89" t="n"/>
     </row>
     <row r="593" ht="12.75" customHeight="1" s="69">
       <c r="F593" s="65" t="n"/>
@@ -9374,6 +9980,7 @@
       <c r="O593" s="68" t="n"/>
       <c r="P593" s="61" t="n"/>
       <c r="Q593" s="61" t="n"/>
+      <c r="R593" s="89" t="n"/>
     </row>
     <row r="594" ht="12.75" customHeight="1" s="69">
       <c r="F594" s="65" t="n"/>
@@ -9384,6 +9991,7 @@
       <c r="O594" s="68" t="n"/>
       <c r="P594" s="61" t="n"/>
       <c r="Q594" s="61" t="n"/>
+      <c r="R594" s="89" t="n"/>
     </row>
     <row r="595" ht="12.75" customHeight="1" s="69">
       <c r="F595" s="65" t="n"/>
@@ -9394,6 +10002,7 @@
       <c r="O595" s="68" t="n"/>
       <c r="P595" s="61" t="n"/>
       <c r="Q595" s="61" t="n"/>
+      <c r="R595" s="89" t="n"/>
     </row>
     <row r="596" ht="12.75" customHeight="1" s="69">
       <c r="F596" s="65" t="n"/>
@@ -9404,6 +10013,7 @@
       <c r="O596" s="68" t="n"/>
       <c r="P596" s="61" t="n"/>
       <c r="Q596" s="61" t="n"/>
+      <c r="R596" s="89" t="n"/>
     </row>
     <row r="597" ht="12.75" customHeight="1" s="69">
       <c r="F597" s="65" t="n"/>
@@ -9414,6 +10024,7 @@
       <c r="O597" s="68" t="n"/>
       <c r="P597" s="61" t="n"/>
       <c r="Q597" s="61" t="n"/>
+      <c r="R597" s="89" t="n"/>
     </row>
     <row r="598" ht="12.75" customHeight="1" s="69">
       <c r="F598" s="65" t="n"/>
@@ -9424,6 +10035,7 @@
       <c r="O598" s="68" t="n"/>
       <c r="P598" s="61" t="n"/>
       <c r="Q598" s="61" t="n"/>
+      <c r="R598" s="89" t="n"/>
     </row>
     <row r="599" ht="12.75" customHeight="1" s="69">
       <c r="F599" s="65" t="n"/>
@@ -9434,6 +10046,7 @@
       <c r="O599" s="68" t="n"/>
       <c r="P599" s="61" t="n"/>
       <c r="Q599" s="61" t="n"/>
+      <c r="R599" s="89" t="n"/>
     </row>
     <row r="600" ht="12.75" customHeight="1" s="69">
       <c r="F600" s="65" t="n"/>
@@ -9444,6 +10057,7 @@
       <c r="O600" s="68" t="n"/>
       <c r="P600" s="61" t="n"/>
       <c r="Q600" s="61" t="n"/>
+      <c r="R600" s="89" t="n"/>
     </row>
     <row r="601" ht="12.75" customHeight="1" s="69">
       <c r="F601" s="65" t="n"/>
@@ -9454,6 +10068,7 @@
       <c r="O601" s="68" t="n"/>
       <c r="P601" s="61" t="n"/>
       <c r="Q601" s="61" t="n"/>
+      <c r="R601" s="89" t="n"/>
     </row>
     <row r="602" ht="12.75" customHeight="1" s="69">
       <c r="F602" s="65" t="n"/>
@@ -9464,6 +10079,7 @@
       <c r="O602" s="68" t="n"/>
       <c r="P602" s="61" t="n"/>
       <c r="Q602" s="61" t="n"/>
+      <c r="R602" s="89" t="n"/>
     </row>
     <row r="603" ht="12.75" customHeight="1" s="69">
       <c r="F603" s="65" t="n"/>
@@ -9474,6 +10090,7 @@
       <c r="O603" s="68" t="n"/>
       <c r="P603" s="61" t="n"/>
       <c r="Q603" s="61" t="n"/>
+      <c r="R603" s="89" t="n"/>
     </row>
     <row r="604" ht="12.75" customHeight="1" s="69">
       <c r="F604" s="65" t="n"/>
@@ -9484,6 +10101,7 @@
       <c r="O604" s="68" t="n"/>
       <c r="P604" s="61" t="n"/>
       <c r="Q604" s="61" t="n"/>
+      <c r="R604" s="89" t="n"/>
     </row>
     <row r="605" ht="12.75" customHeight="1" s="69">
       <c r="F605" s="65" t="n"/>
@@ -9494,6 +10112,7 @@
       <c r="O605" s="68" t="n"/>
       <c r="P605" s="61" t="n"/>
       <c r="Q605" s="61" t="n"/>
+      <c r="R605" s="89" t="n"/>
     </row>
     <row r="606" ht="12.75" customHeight="1" s="69">
       <c r="F606" s="65" t="n"/>
@@ -9504,6 +10123,7 @@
       <c r="O606" s="68" t="n"/>
       <c r="P606" s="61" t="n"/>
       <c r="Q606" s="61" t="n"/>
+      <c r="R606" s="89" t="n"/>
     </row>
     <row r="607" ht="12.75" customHeight="1" s="69">
       <c r="F607" s="65" t="n"/>
@@ -9514,6 +10134,7 @@
       <c r="O607" s="68" t="n"/>
       <c r="P607" s="61" t="n"/>
       <c r="Q607" s="61" t="n"/>
+      <c r="R607" s="89" t="n"/>
     </row>
     <row r="608" ht="12.75" customHeight="1" s="69">
       <c r="F608" s="65" t="n"/>
@@ -9524,6 +10145,7 @@
       <c r="O608" s="68" t="n"/>
       <c r="P608" s="61" t="n"/>
       <c r="Q608" s="61" t="n"/>
+      <c r="R608" s="89" t="n"/>
     </row>
     <row r="609" ht="12.75" customHeight="1" s="69">
       <c r="F609" s="65" t="n"/>
@@ -9534,6 +10156,7 @@
       <c r="O609" s="68" t="n"/>
       <c r="P609" s="61" t="n"/>
       <c r="Q609" s="61" t="n"/>
+      <c r="R609" s="89" t="n"/>
     </row>
     <row r="610" ht="12.75" customHeight="1" s="69">
       <c r="F610" s="65" t="n"/>
@@ -9544,6 +10167,7 @@
       <c r="O610" s="68" t="n"/>
       <c r="P610" s="61" t="n"/>
       <c r="Q610" s="61" t="n"/>
+      <c r="R610" s="89" t="n"/>
     </row>
     <row r="611" ht="12.75" customHeight="1" s="69">
       <c r="F611" s="65" t="n"/>
@@ -9554,6 +10178,7 @@
       <c r="O611" s="68" t="n"/>
       <c r="P611" s="61" t="n"/>
       <c r="Q611" s="61" t="n"/>
+      <c r="R611" s="89" t="n"/>
     </row>
     <row r="612" ht="12.75" customHeight="1" s="69">
       <c r="F612" s="65" t="n"/>
@@ -9564,6 +10189,7 @@
       <c r="O612" s="68" t="n"/>
       <c r="P612" s="61" t="n"/>
       <c r="Q612" s="61" t="n"/>
+      <c r="R612" s="89" t="n"/>
     </row>
     <row r="613" ht="12.75" customHeight="1" s="69">
       <c r="F613" s="65" t="n"/>
@@ -9574,6 +10200,7 @@
       <c r="O613" s="68" t="n"/>
       <c r="P613" s="61" t="n"/>
       <c r="Q613" s="61" t="n"/>
+      <c r="R613" s="89" t="n"/>
     </row>
     <row r="614" ht="12.75" customHeight="1" s="69">
       <c r="F614" s="65" t="n"/>
@@ -9584,6 +10211,7 @@
       <c r="O614" s="68" t="n"/>
       <c r="P614" s="61" t="n"/>
       <c r="Q614" s="61" t="n"/>
+      <c r="R614" s="89" t="n"/>
     </row>
     <row r="615" ht="12.75" customHeight="1" s="69">
       <c r="F615" s="65" t="n"/>
@@ -9594,6 +10222,7 @@
       <c r="O615" s="68" t="n"/>
       <c r="P615" s="61" t="n"/>
       <c r="Q615" s="61" t="n"/>
+      <c r="R615" s="89" t="n"/>
     </row>
     <row r="616" ht="12.75" customHeight="1" s="69">
       <c r="F616" s="65" t="n"/>
@@ -9604,6 +10233,7 @@
       <c r="O616" s="68" t="n"/>
       <c r="P616" s="61" t="n"/>
       <c r="Q616" s="61" t="n"/>
+      <c r="R616" s="89" t="n"/>
     </row>
     <row r="617" ht="12.75" customHeight="1" s="69">
       <c r="F617" s="65" t="n"/>
@@ -9614,6 +10244,7 @@
       <c r="O617" s="68" t="n"/>
       <c r="P617" s="61" t="n"/>
       <c r="Q617" s="61" t="n"/>
+      <c r="R617" s="89" t="n"/>
     </row>
     <row r="618" ht="12.75" customHeight="1" s="69">
       <c r="F618" s="65" t="n"/>
@@ -9624,6 +10255,7 @@
       <c r="O618" s="68" t="n"/>
       <c r="P618" s="61" t="n"/>
       <c r="Q618" s="61" t="n"/>
+      <c r="R618" s="89" t="n"/>
     </row>
     <row r="619" ht="12.75" customHeight="1" s="69">
       <c r="F619" s="65" t="n"/>
@@ -9634,6 +10266,7 @@
       <c r="O619" s="68" t="n"/>
       <c r="P619" s="61" t="n"/>
       <c r="Q619" s="61" t="n"/>
+      <c r="R619" s="89" t="n"/>
     </row>
     <row r="620" ht="12.75" customHeight="1" s="69">
       <c r="F620" s="65" t="n"/>
@@ -9644,6 +10277,7 @@
       <c r="O620" s="68" t="n"/>
       <c r="P620" s="61" t="n"/>
       <c r="Q620" s="61" t="n"/>
+      <c r="R620" s="89" t="n"/>
     </row>
     <row r="621" ht="12.75" customHeight="1" s="69">
       <c r="F621" s="65" t="n"/>
@@ -9654,6 +10288,7 @@
       <c r="O621" s="68" t="n"/>
       <c r="P621" s="61" t="n"/>
       <c r="Q621" s="61" t="n"/>
+      <c r="R621" s="89" t="n"/>
     </row>
     <row r="622" ht="12.75" customHeight="1" s="69">
       <c r="F622" s="65" t="n"/>
@@ -9664,6 +10299,7 @@
       <c r="O622" s="68" t="n"/>
       <c r="P622" s="61" t="n"/>
       <c r="Q622" s="61" t="n"/>
+      <c r="R622" s="89" t="n"/>
     </row>
     <row r="623" ht="12.75" customHeight="1" s="69">
       <c r="F623" s="65" t="n"/>
@@ -9674,6 +10310,7 @@
       <c r="O623" s="68" t="n"/>
       <c r="P623" s="61" t="n"/>
       <c r="Q623" s="61" t="n"/>
+      <c r="R623" s="89" t="n"/>
     </row>
     <row r="624" ht="12.75" customHeight="1" s="69">
       <c r="F624" s="65" t="n"/>
@@ -9684,6 +10321,7 @@
       <c r="O624" s="68" t="n"/>
       <c r="P624" s="61" t="n"/>
       <c r="Q624" s="61" t="n"/>
+      <c r="R624" s="89" t="n"/>
     </row>
     <row r="625" ht="12.75" customHeight="1" s="69">
       <c r="F625" s="65" t="n"/>
@@ -9694,6 +10332,7 @@
       <c r="O625" s="68" t="n"/>
       <c r="P625" s="61" t="n"/>
       <c r="Q625" s="61" t="n"/>
+      <c r="R625" s="89" t="n"/>
     </row>
     <row r="626" ht="12.75" customHeight="1" s="69">
       <c r="F626" s="65" t="n"/>
@@ -9704,6 +10343,7 @@
       <c r="O626" s="68" t="n"/>
       <c r="P626" s="61" t="n"/>
       <c r="Q626" s="61" t="n"/>
+      <c r="R626" s="89" t="n"/>
     </row>
     <row r="627" ht="12.75" customHeight="1" s="69">
       <c r="F627" s="65" t="n"/>
@@ -9714,6 +10354,7 @@
       <c r="O627" s="68" t="n"/>
       <c r="P627" s="61" t="n"/>
       <c r="Q627" s="61" t="n"/>
+      <c r="R627" s="89" t="n"/>
     </row>
     <row r="628" ht="12.75" customHeight="1" s="69">
       <c r="F628" s="65" t="n"/>
@@ -9724,6 +10365,7 @@
       <c r="O628" s="68" t="n"/>
       <c r="P628" s="61" t="n"/>
       <c r="Q628" s="61" t="n"/>
+      <c r="R628" s="89" t="n"/>
     </row>
     <row r="629" ht="12.75" customHeight="1" s="69">
       <c r="F629" s="65" t="n"/>
@@ -9734,6 +10376,7 @@
       <c r="O629" s="68" t="n"/>
       <c r="P629" s="61" t="n"/>
       <c r="Q629" s="61" t="n"/>
+      <c r="R629" s="89" t="n"/>
     </row>
     <row r="630" ht="12.75" customHeight="1" s="69">
       <c r="F630" s="65" t="n"/>
@@ -9744,6 +10387,7 @@
       <c r="O630" s="68" t="n"/>
       <c r="P630" s="61" t="n"/>
       <c r="Q630" s="61" t="n"/>
+      <c r="R630" s="89" t="n"/>
     </row>
     <row r="631" ht="12.75" customHeight="1" s="69">
       <c r="F631" s="65" t="n"/>
@@ -9754,6 +10398,7 @@
       <c r="O631" s="68" t="n"/>
       <c r="P631" s="61" t="n"/>
       <c r="Q631" s="61" t="n"/>
+      <c r="R631" s="89" t="n"/>
     </row>
     <row r="632" ht="12.75" customHeight="1" s="69">
       <c r="F632" s="65" t="n"/>
@@ -9764,6 +10409,7 @@
       <c r="O632" s="68" t="n"/>
       <c r="P632" s="61" t="n"/>
       <c r="Q632" s="61" t="n"/>
+      <c r="R632" s="89" t="n"/>
     </row>
     <row r="633" ht="12.75" customHeight="1" s="69">
       <c r="F633" s="65" t="n"/>
@@ -9774,6 +10420,7 @@
       <c r="O633" s="68" t="n"/>
       <c r="P633" s="61" t="n"/>
       <c r="Q633" s="61" t="n"/>
+      <c r="R633" s="89" t="n"/>
     </row>
     <row r="634" ht="12.75" customHeight="1" s="69">
       <c r="F634" s="65" t="n"/>
@@ -9784,6 +10431,7 @@
       <c r="O634" s="68" t="n"/>
       <c r="P634" s="61" t="n"/>
       <c r="Q634" s="61" t="n"/>
+      <c r="R634" s="89" t="n"/>
     </row>
     <row r="635" ht="12.75" customHeight="1" s="69">
       <c r="F635" s="65" t="n"/>
@@ -9794,6 +10442,7 @@
       <c r="O635" s="68" t="n"/>
       <c r="P635" s="61" t="n"/>
       <c r="Q635" s="61" t="n"/>
+      <c r="R635" s="89" t="n"/>
     </row>
     <row r="636" ht="12.75" customHeight="1" s="69">
       <c r="F636" s="65" t="n"/>
@@ -9804,6 +10453,7 @@
       <c r="O636" s="68" t="n"/>
       <c r="P636" s="61" t="n"/>
       <c r="Q636" s="61" t="n"/>
+      <c r="R636" s="89" t="n"/>
     </row>
     <row r="637" ht="12.75" customHeight="1" s="69">
       <c r="F637" s="65" t="n"/>
@@ -9814,6 +10464,7 @@
       <c r="O637" s="68" t="n"/>
       <c r="P637" s="61" t="n"/>
       <c r="Q637" s="61" t="n"/>
+      <c r="R637" s="89" t="n"/>
     </row>
     <row r="638" ht="12.75" customHeight="1" s="69">
       <c r="F638" s="65" t="n"/>
@@ -9824,6 +10475,7 @@
       <c r="O638" s="68" t="n"/>
       <c r="P638" s="61" t="n"/>
       <c r="Q638" s="61" t="n"/>
+      <c r="R638" s="89" t="n"/>
     </row>
     <row r="639" ht="12.75" customHeight="1" s="69">
       <c r="F639" s="65" t="n"/>
@@ -9834,6 +10486,7 @@
       <c r="O639" s="68" t="n"/>
       <c r="P639" s="61" t="n"/>
       <c r="Q639" s="61" t="n"/>
+      <c r="R639" s="89" t="n"/>
     </row>
     <row r="640" ht="12.75" customHeight="1" s="69">
       <c r="F640" s="65" t="n"/>
@@ -9844,6 +10497,7 @@
       <c r="O640" s="68" t="n"/>
       <c r="P640" s="61" t="n"/>
       <c r="Q640" s="61" t="n"/>
+      <c r="R640" s="89" t="n"/>
     </row>
     <row r="641" ht="12.75" customHeight="1" s="69">
       <c r="F641" s="65" t="n"/>
@@ -9854,6 +10508,7 @@
       <c r="O641" s="68" t="n"/>
       <c r="P641" s="61" t="n"/>
       <c r="Q641" s="61" t="n"/>
+      <c r="R641" s="89" t="n"/>
     </row>
     <row r="642" ht="12.75" customHeight="1" s="69">
       <c r="F642" s="65" t="n"/>
@@ -9864,6 +10519,7 @@
       <c r="O642" s="68" t="n"/>
       <c r="P642" s="61" t="n"/>
       <c r="Q642" s="61" t="n"/>
+      <c r="R642" s="89" t="n"/>
     </row>
     <row r="643" ht="12.75" customHeight="1" s="69">
       <c r="F643" s="65" t="n"/>
@@ -9874,6 +10530,7 @@
       <c r="O643" s="68" t="n"/>
       <c r="P643" s="61" t="n"/>
       <c r="Q643" s="61" t="n"/>
+      <c r="R643" s="89" t="n"/>
     </row>
     <row r="644" ht="12.75" customHeight="1" s="69">
       <c r="F644" s="65" t="n"/>
@@ -9884,6 +10541,7 @@
       <c r="O644" s="68" t="n"/>
       <c r="P644" s="61" t="n"/>
       <c r="Q644" s="61" t="n"/>
+      <c r="R644" s="89" t="n"/>
     </row>
     <row r="645" ht="12.75" customHeight="1" s="69">
       <c r="F645" s="65" t="n"/>
@@ -9894,6 +10552,7 @@
       <c r="O645" s="68" t="n"/>
       <c r="P645" s="61" t="n"/>
       <c r="Q645" s="61" t="n"/>
+      <c r="R645" s="89" t="n"/>
     </row>
     <row r="646" ht="12.75" customHeight="1" s="69">
       <c r="F646" s="65" t="n"/>
@@ -9904,6 +10563,7 @@
       <c r="O646" s="68" t="n"/>
       <c r="P646" s="61" t="n"/>
       <c r="Q646" s="61" t="n"/>
+      <c r="R646" s="89" t="n"/>
     </row>
     <row r="647" ht="12.75" customHeight="1" s="69">
       <c r="F647" s="65" t="n"/>
@@ -9914,6 +10574,7 @@
       <c r="O647" s="68" t="n"/>
       <c r="P647" s="61" t="n"/>
       <c r="Q647" s="61" t="n"/>
+      <c r="R647" s="89" t="n"/>
     </row>
     <row r="648" ht="12.75" customHeight="1" s="69">
       <c r="F648" s="65" t="n"/>
@@ -9924,6 +10585,7 @@
       <c r="O648" s="68" t="n"/>
       <c r="P648" s="61" t="n"/>
       <c r="Q648" s="61" t="n"/>
+      <c r="R648" s="89" t="n"/>
     </row>
     <row r="649" ht="12.75" customHeight="1" s="69">
       <c r="F649" s="65" t="n"/>
@@ -9934,6 +10596,7 @@
       <c r="O649" s="68" t="n"/>
       <c r="P649" s="61" t="n"/>
       <c r="Q649" s="61" t="n"/>
+      <c r="R649" s="89" t="n"/>
     </row>
     <row r="650" ht="12.75" customHeight="1" s="69">
       <c r="F650" s="65" t="n"/>
@@ -9944,6 +10607,7 @@
       <c r="O650" s="68" t="n"/>
       <c r="P650" s="61" t="n"/>
       <c r="Q650" s="61" t="n"/>
+      <c r="R650" s="89" t="n"/>
     </row>
     <row r="651" ht="12.75" customHeight="1" s="69">
       <c r="F651" s="65" t="n"/>
@@ -9954,6 +10618,7 @@
       <c r="O651" s="68" t="n"/>
       <c r="P651" s="61" t="n"/>
       <c r="Q651" s="61" t="n"/>
+      <c r="R651" s="89" t="n"/>
     </row>
     <row r="652" ht="12.75" customHeight="1" s="69">
       <c r="F652" s="65" t="n"/>
@@ -9964,6 +10629,7 @@
       <c r="O652" s="68" t="n"/>
       <c r="P652" s="61" t="n"/>
       <c r="Q652" s="61" t="n"/>
+      <c r="R652" s="89" t="n"/>
     </row>
     <row r="653" ht="12.75" customHeight="1" s="69">
       <c r="F653" s="65" t="n"/>
@@ -9974,6 +10640,7 @@
       <c r="O653" s="68" t="n"/>
       <c r="P653" s="61" t="n"/>
       <c r="Q653" s="61" t="n"/>
+      <c r="R653" s="89" t="n"/>
     </row>
     <row r="654" ht="12.75" customHeight="1" s="69">
       <c r="F654" s="65" t="n"/>
@@ -9984,6 +10651,7 @@
       <c r="O654" s="68" t="n"/>
       <c r="P654" s="61" t="n"/>
       <c r="Q654" s="61" t="n"/>
+      <c r="R654" s="89" t="n"/>
     </row>
     <row r="655" ht="12.75" customHeight="1" s="69">
       <c r="F655" s="65" t="n"/>
@@ -9994,6 +10662,7 @@
       <c r="O655" s="68" t="n"/>
       <c r="P655" s="61" t="n"/>
       <c r="Q655" s="61" t="n"/>
+      <c r="R655" s="89" t="n"/>
     </row>
     <row r="656" ht="12.75" customHeight="1" s="69">
       <c r="F656" s="65" t="n"/>
@@ -10004,6 +10673,7 @@
       <c r="O656" s="68" t="n"/>
       <c r="P656" s="61" t="n"/>
       <c r="Q656" s="61" t="n"/>
+      <c r="R656" s="89" t="n"/>
     </row>
     <row r="657" ht="12.75" customHeight="1" s="69">
       <c r="F657" s="65" t="n"/>
@@ -10014,6 +10684,7 @@
       <c r="O657" s="68" t="n"/>
       <c r="P657" s="61" t="n"/>
       <c r="Q657" s="61" t="n"/>
+      <c r="R657" s="89" t="n"/>
     </row>
     <row r="658" ht="12.75" customHeight="1" s="69">
       <c r="F658" s="65" t="n"/>
@@ -10024,6 +10695,7 @@
       <c r="O658" s="68" t="n"/>
       <c r="P658" s="61" t="n"/>
       <c r="Q658" s="61" t="n"/>
+      <c r="R658" s="89" t="n"/>
     </row>
     <row r="659" ht="12.75" customHeight="1" s="69">
       <c r="F659" s="65" t="n"/>
@@ -10034,6 +10706,7 @@
       <c r="O659" s="68" t="n"/>
       <c r="P659" s="61" t="n"/>
       <c r="Q659" s="61" t="n"/>
+      <c r="R659" s="89" t="n"/>
     </row>
     <row r="660" ht="12.75" customHeight="1" s="69">
       <c r="F660" s="65" t="n"/>
@@ -10044,6 +10717,7 @@
       <c r="O660" s="68" t="n"/>
       <c r="P660" s="61" t="n"/>
       <c r="Q660" s="61" t="n"/>
+      <c r="R660" s="89" t="n"/>
     </row>
     <row r="661" ht="12.75" customHeight="1" s="69">
       <c r="F661" s="65" t="n"/>
@@ -10054,6 +10728,7 @@
       <c r="O661" s="68" t="n"/>
       <c r="P661" s="61" t="n"/>
       <c r="Q661" s="61" t="n"/>
+      <c r="R661" s="89" t="n"/>
     </row>
     <row r="662" ht="12.75" customHeight="1" s="69">
       <c r="F662" s="65" t="n"/>
@@ -10064,6 +10739,7 @@
       <c r="O662" s="68" t="n"/>
       <c r="P662" s="61" t="n"/>
       <c r="Q662" s="61" t="n"/>
+      <c r="R662" s="89" t="n"/>
     </row>
     <row r="663" ht="12.75" customHeight="1" s="69">
       <c r="F663" s="65" t="n"/>
@@ -10074,6 +10750,7 @@
       <c r="O663" s="68" t="n"/>
       <c r="P663" s="61" t="n"/>
       <c r="Q663" s="61" t="n"/>
+      <c r="R663" s="89" t="n"/>
     </row>
     <row r="664" ht="12.75" customHeight="1" s="69">
       <c r="F664" s="65" t="n"/>
@@ -10084,6 +10761,7 @@
       <c r="O664" s="68" t="n"/>
       <c r="P664" s="61" t="n"/>
       <c r="Q664" s="61" t="n"/>
+      <c r="R664" s="89" t="n"/>
     </row>
     <row r="665" ht="12.75" customHeight="1" s="69">
       <c r="F665" s="65" t="n"/>
@@ -10094,6 +10772,7 @@
       <c r="O665" s="68" t="n"/>
       <c r="P665" s="61" t="n"/>
       <c r="Q665" s="61" t="n"/>
+      <c r="R665" s="89" t="n"/>
     </row>
     <row r="666" ht="12.75" customHeight="1" s="69">
       <c r="F666" s="65" t="n"/>
@@ -10104,6 +10783,7 @@
       <c r="O666" s="68" t="n"/>
       <c r="P666" s="61" t="n"/>
       <c r="Q666" s="61" t="n"/>
+      <c r="R666" s="89" t="n"/>
     </row>
     <row r="667" ht="12.75" customHeight="1" s="69">
       <c r="F667" s="65" t="n"/>
@@ -10114,6 +10794,7 @@
       <c r="O667" s="68" t="n"/>
       <c r="P667" s="61" t="n"/>
       <c r="Q667" s="61" t="n"/>
+      <c r="R667" s="89" t="n"/>
     </row>
     <row r="668" ht="12.75" customHeight="1" s="69">
       <c r="F668" s="65" t="n"/>
@@ -10124,6 +10805,7 @@
       <c r="O668" s="68" t="n"/>
       <c r="P668" s="61" t="n"/>
       <c r="Q668" s="61" t="n"/>
+      <c r="R668" s="89" t="n"/>
     </row>
     <row r="669" ht="12.75" customHeight="1" s="69">
       <c r="F669" s="65" t="n"/>
@@ -10134,6 +10816,7 @@
       <c r="O669" s="68" t="n"/>
       <c r="P669" s="61" t="n"/>
       <c r="Q669" s="61" t="n"/>
+      <c r="R669" s="89" t="n"/>
     </row>
     <row r="670" ht="12.75" customHeight="1" s="69">
       <c r="F670" s="65" t="n"/>
@@ -10144,6 +10827,7 @@
       <c r="O670" s="68" t="n"/>
       <c r="P670" s="61" t="n"/>
       <c r="Q670" s="61" t="n"/>
+      <c r="R670" s="89" t="n"/>
     </row>
     <row r="671" ht="12.75" customHeight="1" s="69">
       <c r="F671" s="65" t="n"/>
@@ -10154,6 +10838,7 @@
       <c r="O671" s="68" t="n"/>
       <c r="P671" s="61" t="n"/>
       <c r="Q671" s="61" t="n"/>
+      <c r="R671" s="89" t="n"/>
     </row>
     <row r="672" ht="12.75" customHeight="1" s="69">
       <c r="F672" s="65" t="n"/>
@@ -10164,6 +10849,7 @@
       <c r="O672" s="68" t="n"/>
       <c r="P672" s="61" t="n"/>
       <c r="Q672" s="61" t="n"/>
+      <c r="R672" s="89" t="n"/>
     </row>
     <row r="673" ht="12.75" customHeight="1" s="69">
       <c r="F673" s="65" t="n"/>
@@ -10174,6 +10860,7 @@
       <c r="O673" s="68" t="n"/>
       <c r="P673" s="61" t="n"/>
       <c r="Q673" s="61" t="n"/>
+      <c r="R673" s="89" t="n"/>
     </row>
     <row r="674" ht="12.75" customHeight="1" s="69">
       <c r="F674" s="65" t="n"/>
@@ -10184,6 +10871,7 @@
       <c r="O674" s="68" t="n"/>
       <c r="P674" s="61" t="n"/>
       <c r="Q674" s="61" t="n"/>
+      <c r="R674" s="89" t="n"/>
     </row>
     <row r="675" ht="12.75" customHeight="1" s="69">
       <c r="F675" s="65" t="n"/>
@@ -10194,6 +10882,7 @@
       <c r="O675" s="68" t="n"/>
       <c r="P675" s="61" t="n"/>
       <c r="Q675" s="61" t="n"/>
+      <c r="R675" s="89" t="n"/>
     </row>
     <row r="676" ht="12.75" customHeight="1" s="69">
       <c r="F676" s="65" t="n"/>
@@ -10204,6 +10893,7 @@
       <c r="O676" s="68" t="n"/>
       <c r="P676" s="61" t="n"/>
       <c r="Q676" s="61" t="n"/>
+      <c r="R676" s="89" t="n"/>
     </row>
     <row r="677" ht="12.75" customHeight="1" s="69">
       <c r="F677" s="65" t="n"/>
@@ -10214,6 +10904,7 @@
       <c r="O677" s="68" t="n"/>
       <c r="P677" s="61" t="n"/>
       <c r="Q677" s="61" t="n"/>
+      <c r="R677" s="89" t="n"/>
     </row>
     <row r="678" ht="12.75" customHeight="1" s="69">
       <c r="F678" s="65" t="n"/>
@@ -10224,6 +10915,7 @@
       <c r="O678" s="68" t="n"/>
       <c r="P678" s="61" t="n"/>
       <c r="Q678" s="61" t="n"/>
+      <c r="R678" s="89" t="n"/>
     </row>
     <row r="679" ht="12.75" customHeight="1" s="69">
       <c r="F679" s="65" t="n"/>
@@ -10234,6 +10926,7 @@
       <c r="O679" s="68" t="n"/>
       <c r="P679" s="61" t="n"/>
       <c r="Q679" s="61" t="n"/>
+      <c r="R679" s="89" t="n"/>
     </row>
     <row r="680" ht="12.75" customHeight="1" s="69">
       <c r="F680" s="65" t="n"/>
@@ -10244,6 +10937,7 @@
       <c r="O680" s="68" t="n"/>
       <c r="P680" s="61" t="n"/>
       <c r="Q680" s="61" t="n"/>
+      <c r="R680" s="89" t="n"/>
     </row>
     <row r="681" ht="12.75" customHeight="1" s="69">
       <c r="F681" s="65" t="n"/>
@@ -10254,6 +10948,7 @@
       <c r="O681" s="68" t="n"/>
       <c r="P681" s="61" t="n"/>
       <c r="Q681" s="61" t="n"/>
+      <c r="R681" s="89" t="n"/>
     </row>
     <row r="682" ht="12.75" customHeight="1" s="69">
       <c r="F682" s="65" t="n"/>
@@ -10264,6 +10959,7 @@
       <c r="O682" s="68" t="n"/>
       <c r="P682" s="61" t="n"/>
       <c r="Q682" s="61" t="n"/>
+      <c r="R682" s="89" t="n"/>
     </row>
     <row r="683" ht="12.75" customHeight="1" s="69">
       <c r="F683" s="65" t="n"/>
@@ -10274,6 +10970,7 @@
       <c r="O683" s="68" t="n"/>
       <c r="P683" s="61" t="n"/>
       <c r="Q683" s="61" t="n"/>
+      <c r="R683" s="89" t="n"/>
     </row>
     <row r="684" ht="12.75" customHeight="1" s="69">
       <c r="F684" s="65" t="n"/>
@@ -10284,6 +10981,7 @@
       <c r="O684" s="68" t="n"/>
       <c r="P684" s="61" t="n"/>
       <c r="Q684" s="61" t="n"/>
+      <c r="R684" s="89" t="n"/>
     </row>
     <row r="685" ht="12.75" customHeight="1" s="69">
       <c r="F685" s="65" t="n"/>
@@ -10294,6 +10992,7 @@
       <c r="O685" s="68" t="n"/>
       <c r="P685" s="61" t="n"/>
       <c r="Q685" s="61" t="n"/>
+      <c r="R685" s="89" t="n"/>
     </row>
     <row r="686" ht="12.75" customHeight="1" s="69">
       <c r="F686" s="65" t="n"/>
@@ -10304,6 +11003,7 @@
       <c r="O686" s="68" t="n"/>
       <c r="P686" s="61" t="n"/>
       <c r="Q686" s="61" t="n"/>
+      <c r="R686" s="89" t="n"/>
     </row>
     <row r="687" ht="12.75" customHeight="1" s="69">
       <c r="F687" s="65" t="n"/>
@@ -10314,6 +11014,7 @@
       <c r="O687" s="68" t="n"/>
       <c r="P687" s="61" t="n"/>
       <c r="Q687" s="61" t="n"/>
+      <c r="R687" s="89" t="n"/>
     </row>
     <row r="688" ht="12.75" customHeight="1" s="69">
       <c r="F688" s="65" t="n"/>
@@ -10324,6 +11025,7 @@
       <c r="O688" s="68" t="n"/>
       <c r="P688" s="61" t="n"/>
       <c r="Q688" s="61" t="n"/>
+      <c r="R688" s="89" t="n"/>
     </row>
     <row r="689" ht="12.75" customHeight="1" s="69">
       <c r="F689" s="65" t="n"/>
@@ -10334,6 +11036,7 @@
       <c r="O689" s="68" t="n"/>
       <c r="P689" s="61" t="n"/>
       <c r="Q689" s="61" t="n"/>
+      <c r="R689" s="89" t="n"/>
     </row>
     <row r="690" ht="12.75" customHeight="1" s="69">
       <c r="F690" s="65" t="n"/>
@@ -10344,6 +11047,7 @@
       <c r="O690" s="68" t="n"/>
       <c r="P690" s="61" t="n"/>
       <c r="Q690" s="61" t="n"/>
+      <c r="R690" s="89" t="n"/>
     </row>
     <row r="691" ht="12.75" customHeight="1" s="69">
       <c r="F691" s="65" t="n"/>
@@ -10354,6 +11058,7 @@
       <c r="O691" s="68" t="n"/>
       <c r="P691" s="61" t="n"/>
       <c r="Q691" s="61" t="n"/>
+      <c r="R691" s="89" t="n"/>
     </row>
     <row r="692" ht="12.75" customHeight="1" s="69">
       <c r="F692" s="65" t="n"/>
@@ -10364,6 +11069,7 @@
       <c r="O692" s="68" t="n"/>
       <c r="P692" s="61" t="n"/>
       <c r="Q692" s="61" t="n"/>
+      <c r="R692" s="89" t="n"/>
     </row>
     <row r="693" ht="12.75" customHeight="1" s="69">
       <c r="F693" s="65" t="n"/>
@@ -10374,6 +11080,7 @@
       <c r="O693" s="68" t="n"/>
       <c r="P693" s="61" t="n"/>
       <c r="Q693" s="61" t="n"/>
+      <c r="R693" s="89" t="n"/>
     </row>
     <row r="694" ht="12.75" customHeight="1" s="69">
       <c r="F694" s="65" t="n"/>
@@ -10384,6 +11091,7 @@
       <c r="O694" s="68" t="n"/>
       <c r="P694" s="61" t="n"/>
       <c r="Q694" s="61" t="n"/>
+      <c r="R694" s="89" t="n"/>
     </row>
     <row r="695" ht="12.75" customHeight="1" s="69">
       <c r="F695" s="65" t="n"/>
@@ -10394,6 +11102,7 @@
       <c r="O695" s="68" t="n"/>
       <c r="P695" s="61" t="n"/>
       <c r="Q695" s="61" t="n"/>
+      <c r="R695" s="89" t="n"/>
     </row>
     <row r="696" ht="12.75" customHeight="1" s="69">
       <c r="F696" s="65" t="n"/>
@@ -10404,6 +11113,7 @@
       <c r="O696" s="68" t="n"/>
       <c r="P696" s="61" t="n"/>
       <c r="Q696" s="61" t="n"/>
+      <c r="R696" s="89" t="n"/>
     </row>
     <row r="697" ht="12.75" customHeight="1" s="69">
       <c r="F697" s="65" t="n"/>
@@ -10414,6 +11124,7 @@
       <c r="O697" s="68" t="n"/>
       <c r="P697" s="61" t="n"/>
       <c r="Q697" s="61" t="n"/>
+      <c r="R697" s="89" t="n"/>
     </row>
     <row r="698" ht="12.75" customHeight="1" s="69">
       <c r="F698" s="65" t="n"/>
@@ -10424,6 +11135,7 @@
       <c r="O698" s="68" t="n"/>
       <c r="P698" s="61" t="n"/>
       <c r="Q698" s="61" t="n"/>
+      <c r="R698" s="89" t="n"/>
     </row>
     <row r="699" ht="12.75" customHeight="1" s="69">
       <c r="F699" s="65" t="n"/>
@@ -10434,6 +11146,7 @@
       <c r="O699" s="68" t="n"/>
       <c r="P699" s="61" t="n"/>
       <c r="Q699" s="61" t="n"/>
+      <c r="R699" s="89" t="n"/>
     </row>
     <row r="700" ht="12.75" customHeight="1" s="69">
       <c r="F700" s="65" t="n"/>
@@ -10444,6 +11157,7 @@
       <c r="O700" s="68" t="n"/>
       <c r="P700" s="61" t="n"/>
       <c r="Q700" s="61" t="n"/>
+      <c r="R700" s="89" t="n"/>
     </row>
     <row r="701" ht="12.75" customHeight="1" s="69">
       <c r="F701" s="65" t="n"/>
@@ -10454,6 +11168,7 @@
       <c r="O701" s="68" t="n"/>
       <c r="P701" s="61" t="n"/>
       <c r="Q701" s="61" t="n"/>
+      <c r="R701" s="89" t="n"/>
     </row>
     <row r="702" ht="12.75" customHeight="1" s="69">
       <c r="F702" s="65" t="n"/>
@@ -10464,6 +11179,7 @@
       <c r="O702" s="68" t="n"/>
       <c r="P702" s="61" t="n"/>
       <c r="Q702" s="61" t="n"/>
+      <c r="R702" s="89" t="n"/>
     </row>
     <row r="703" ht="12.75" customHeight="1" s="69">
       <c r="F703" s="65" t="n"/>
@@ -10474,6 +11190,7 @@
       <c r="O703" s="68" t="n"/>
       <c r="P703" s="61" t="n"/>
       <c r="Q703" s="61" t="n"/>
+      <c r="R703" s="89" t="n"/>
     </row>
     <row r="704" ht="12.75" customHeight="1" s="69">
       <c r="F704" s="65" t="n"/>
@@ -10484,6 +11201,7 @@
       <c r="O704" s="68" t="n"/>
       <c r="P704" s="61" t="n"/>
       <c r="Q704" s="61" t="n"/>
+      <c r="R704" s="89" t="n"/>
     </row>
     <row r="705" ht="12.75" customHeight="1" s="69">
       <c r="F705" s="65" t="n"/>
@@ -10494,6 +11212,7 @@
       <c r="O705" s="68" t="n"/>
       <c r="P705" s="61" t="n"/>
       <c r="Q705" s="61" t="n"/>
+      <c r="R705" s="89" t="n"/>
     </row>
     <row r="706" ht="12.75" customHeight="1" s="69">
       <c r="F706" s="65" t="n"/>
@@ -10504,6 +11223,7 @@
       <c r="O706" s="68" t="n"/>
       <c r="P706" s="61" t="n"/>
       <c r="Q706" s="61" t="n"/>
+      <c r="R706" s="89" t="n"/>
     </row>
     <row r="707" ht="12.75" customHeight="1" s="69">
       <c r="F707" s="65" t="n"/>
@@ -10514,6 +11234,7 @@
       <c r="O707" s="68" t="n"/>
       <c r="P707" s="61" t="n"/>
       <c r="Q707" s="61" t="n"/>
+      <c r="R707" s="89" t="n"/>
     </row>
     <row r="708" ht="12.75" customHeight="1" s="69">
       <c r="F708" s="65" t="n"/>
@@ -10524,6 +11245,7 @@
       <c r="O708" s="68" t="n"/>
       <c r="P708" s="61" t="n"/>
       <c r="Q708" s="61" t="n"/>
+      <c r="R708" s="89" t="n"/>
     </row>
     <row r="709" ht="12.75" customHeight="1" s="69">
       <c r="F709" s="65" t="n"/>
@@ -10534,6 +11256,7 @@
       <c r="O709" s="68" t="n"/>
       <c r="P709" s="61" t="n"/>
       <c r="Q709" s="61" t="n"/>
+      <c r="R709" s="89" t="n"/>
     </row>
     <row r="710" ht="12.75" customHeight="1" s="69">
       <c r="F710" s="65" t="n"/>
@@ -10544,6 +11267,7 @@
       <c r="O710" s="68" t="n"/>
       <c r="P710" s="61" t="n"/>
       <c r="Q710" s="61" t="n"/>
+      <c r="R710" s="89" t="n"/>
     </row>
     <row r="711" ht="12.75" customHeight="1" s="69">
       <c r="F711" s="65" t="n"/>
@@ -10554,6 +11278,7 @@
       <c r="O711" s="68" t="n"/>
       <c r="P711" s="61" t="n"/>
       <c r="Q711" s="61" t="n"/>
+      <c r="R711" s="89" t="n"/>
     </row>
     <row r="712" ht="12.75" customHeight="1" s="69">
       <c r="F712" s="65" t="n"/>
@@ -10564,6 +11289,7 @@
       <c r="O712" s="68" t="n"/>
       <c r="P712" s="61" t="n"/>
       <c r="Q712" s="61" t="n"/>
+      <c r="R712" s="89" t="n"/>
     </row>
     <row r="713" ht="12.75" customHeight="1" s="69">
       <c r="F713" s="65" t="n"/>
@@ -10574,6 +11300,7 @@
       <c r="O713" s="68" t="n"/>
       <c r="P713" s="61" t="n"/>
       <c r="Q713" s="61" t="n"/>
+      <c r="R713" s="89" t="n"/>
     </row>
     <row r="714" ht="12.75" customHeight="1" s="69">
       <c r="F714" s="65" t="n"/>
@@ -10584,6 +11311,7 @@
       <c r="O714" s="68" t="n"/>
       <c r="P714" s="61" t="n"/>
       <c r="Q714" s="61" t="n"/>
+      <c r="R714" s="89" t="n"/>
     </row>
     <row r="715" ht="12.75" customHeight="1" s="69">
       <c r="F715" s="65" t="n"/>
@@ -10594,6 +11322,7 @@
       <c r="O715" s="68" t="n"/>
       <c r="P715" s="61" t="n"/>
       <c r="Q715" s="61" t="n"/>
+      <c r="R715" s="89" t="n"/>
     </row>
     <row r="716" ht="12.75" customHeight="1" s="69">
       <c r="F716" s="65" t="n"/>
@@ -10604,6 +11333,7 @@
       <c r="O716" s="68" t="n"/>
       <c r="P716" s="61" t="n"/>
       <c r="Q716" s="61" t="n"/>
+      <c r="R716" s="89" t="n"/>
     </row>
     <row r="717" ht="12.75" customHeight="1" s="69">
       <c r="F717" s="65" t="n"/>
@@ -10614,6 +11344,7 @@
       <c r="O717" s="68" t="n"/>
       <c r="P717" s="61" t="n"/>
       <c r="Q717" s="61" t="n"/>
+      <c r="R717" s="89" t="n"/>
     </row>
     <row r="718" ht="12.75" customHeight="1" s="69">
       <c r="F718" s="65" t="n"/>
@@ -10624,6 +11355,7 @@
       <c r="O718" s="68" t="n"/>
       <c r="P718" s="61" t="n"/>
       <c r="Q718" s="61" t="n"/>
+      <c r="R718" s="89" t="n"/>
     </row>
     <row r="719" ht="12.75" customHeight="1" s="69">
       <c r="F719" s="65" t="n"/>
@@ -10634,6 +11366,7 @@
       <c r="O719" s="68" t="n"/>
       <c r="P719" s="61" t="n"/>
       <c r="Q719" s="61" t="n"/>
+      <c r="R719" s="89" t="n"/>
     </row>
     <row r="720" ht="12.75" customHeight="1" s="69">
       <c r="F720" s="65" t="n"/>
@@ -10644,6 +11377,7 @@
       <c r="O720" s="68" t="n"/>
       <c r="P720" s="61" t="n"/>
       <c r="Q720" s="61" t="n"/>
+      <c r="R720" s="89" t="n"/>
     </row>
     <row r="721" ht="12.75" customHeight="1" s="69">
       <c r="F721" s="65" t="n"/>
@@ -10654,6 +11388,7 @@
       <c r="O721" s="68" t="n"/>
       <c r="P721" s="61" t="n"/>
       <c r="Q721" s="61" t="n"/>
+      <c r="R721" s="89" t="n"/>
     </row>
     <row r="722" ht="12.75" customHeight="1" s="69">
       <c r="F722" s="65" t="n"/>
@@ -10664,6 +11399,7 @@
       <c r="O722" s="68" t="n"/>
       <c r="P722" s="61" t="n"/>
       <c r="Q722" s="61" t="n"/>
+      <c r="R722" s="89" t="n"/>
     </row>
     <row r="723" ht="12.75" customHeight="1" s="69">
       <c r="F723" s="65" t="n"/>
@@ -10674,6 +11410,7 @@
       <c r="O723" s="68" t="n"/>
       <c r="P723" s="61" t="n"/>
       <c r="Q723" s="61" t="n"/>
+      <c r="R723" s="89" t="n"/>
     </row>
     <row r="724" ht="12.75" customHeight="1" s="69">
       <c r="F724" s="65" t="n"/>
@@ -10684,6 +11421,7 @@
       <c r="O724" s="68" t="n"/>
       <c r="P724" s="61" t="n"/>
       <c r="Q724" s="61" t="n"/>
+      <c r="R724" s="89" t="n"/>
     </row>
     <row r="725" ht="12.75" customHeight="1" s="69">
       <c r="F725" s="65" t="n"/>
@@ -10694,6 +11432,7 @@
       <c r="O725" s="68" t="n"/>
       <c r="P725" s="61" t="n"/>
       <c r="Q725" s="61" t="n"/>
+      <c r="R725" s="89" t="n"/>
     </row>
     <row r="726" ht="12.75" customHeight="1" s="69">
       <c r="F726" s="65" t="n"/>
@@ -10704,6 +11443,7 @@
       <c r="O726" s="68" t="n"/>
       <c r="P726" s="61" t="n"/>
       <c r="Q726" s="61" t="n"/>
+      <c r="R726" s="89" t="n"/>
     </row>
     <row r="727" ht="12.75" customHeight="1" s="69">
       <c r="F727" s="65" t="n"/>
@@ -10714,6 +11454,7 @@
       <c r="O727" s="68" t="n"/>
       <c r="P727" s="61" t="n"/>
       <c r="Q727" s="61" t="n"/>
+      <c r="R727" s="89" t="n"/>
     </row>
     <row r="728" ht="12.75" customHeight="1" s="69">
       <c r="F728" s="65" t="n"/>
@@ -10724,6 +11465,7 @@
       <c r="O728" s="68" t="n"/>
       <c r="P728" s="61" t="n"/>
       <c r="Q728" s="61" t="n"/>
+      <c r="R728" s="89" t="n"/>
     </row>
     <row r="729" ht="12.75" customHeight="1" s="69">
       <c r="F729" s="65" t="n"/>
@@ -10734,6 +11476,7 @@
       <c r="O729" s="68" t="n"/>
       <c r="P729" s="61" t="n"/>
       <c r="Q729" s="61" t="n"/>
+      <c r="R729" s="89" t="n"/>
     </row>
     <row r="730" ht="12.75" customHeight="1" s="69">
       <c r="F730" s="65" t="n"/>
@@ -10744,6 +11487,7 @@
       <c r="O730" s="68" t="n"/>
       <c r="P730" s="61" t="n"/>
       <c r="Q730" s="61" t="n"/>
+      <c r="R730" s="89" t="n"/>
     </row>
     <row r="731" ht="12.75" customHeight="1" s="69">
       <c r="F731" s="65" t="n"/>
@@ -10754,6 +11498,7 @@
       <c r="O731" s="68" t="n"/>
       <c r="P731" s="61" t="n"/>
       <c r="Q731" s="61" t="n"/>
+      <c r="R731" s="89" t="n"/>
     </row>
     <row r="732" ht="12.75" customHeight="1" s="69">
       <c r="F732" s="65" t="n"/>
@@ -10764,6 +11509,7 @@
       <c r="O732" s="68" t="n"/>
       <c r="P732" s="61" t="n"/>
       <c r="Q732" s="61" t="n"/>
+      <c r="R732" s="89" t="n"/>
     </row>
     <row r="733" ht="12.75" customHeight="1" s="69">
       <c r="F733" s="65" t="n"/>
@@ -10774,6 +11520,7 @@
       <c r="O733" s="68" t="n"/>
       <c r="P733" s="61" t="n"/>
       <c r="Q733" s="61" t="n"/>
+      <c r="R733" s="89" t="n"/>
     </row>
     <row r="734" ht="12.75" customHeight="1" s="69">
       <c r="F734" s="65" t="n"/>
@@ -10784,6 +11531,7 @@
       <c r="O734" s="68" t="n"/>
       <c r="P734" s="61" t="n"/>
       <c r="Q734" s="61" t="n"/>
+      <c r="R734" s="89" t="n"/>
     </row>
     <row r="735" ht="12.75" customHeight="1" s="69">
       <c r="F735" s="65" t="n"/>
@@ -10794,6 +11542,7 @@
       <c r="O735" s="68" t="n"/>
       <c r="P735" s="61" t="n"/>
       <c r="Q735" s="61" t="n"/>
+      <c r="R735" s="89" t="n"/>
     </row>
     <row r="736" ht="12.75" customHeight="1" s="69">
       <c r="F736" s="65" t="n"/>
@@ -10804,6 +11553,7 @@
       <c r="O736" s="68" t="n"/>
       <c r="P736" s="61" t="n"/>
       <c r="Q736" s="61" t="n"/>
+      <c r="R736" s="89" t="n"/>
     </row>
     <row r="737" ht="12.75" customHeight="1" s="69">
       <c r="F737" s="65" t="n"/>
@@ -10814,6 +11564,7 @@
       <c r="O737" s="68" t="n"/>
       <c r="P737" s="61" t="n"/>
       <c r="Q737" s="61" t="n"/>
+      <c r="R737" s="89" t="n"/>
     </row>
     <row r="738" ht="12.75" customHeight="1" s="69">
       <c r="F738" s="65" t="n"/>
@@ -10824,6 +11575,7 @@
       <c r="O738" s="68" t="n"/>
       <c r="P738" s="61" t="n"/>
       <c r="Q738" s="61" t="n"/>
+      <c r="R738" s="89" t="n"/>
     </row>
     <row r="739" ht="12.75" customHeight="1" s="69">
       <c r="F739" s="65" t="n"/>
@@ -10834,6 +11586,7 @@
       <c r="O739" s="68" t="n"/>
       <c r="P739" s="61" t="n"/>
       <c r="Q739" s="61" t="n"/>
+      <c r="R739" s="89" t="n"/>
     </row>
     <row r="740" ht="12.75" customHeight="1" s="69">
       <c r="F740" s="65" t="n"/>
@@ -10844,6 +11597,7 @@
       <c r="O740" s="68" t="n"/>
       <c r="P740" s="61" t="n"/>
       <c r="Q740" s="61" t="n"/>
+      <c r="R740" s="89" t="n"/>
     </row>
     <row r="741" ht="12.75" customHeight="1" s="69">
       <c r="F741" s="65" t="n"/>
@@ -10854,6 +11608,7 @@
       <c r="O741" s="68" t="n"/>
       <c r="P741" s="61" t="n"/>
       <c r="Q741" s="61" t="n"/>
+      <c r="R741" s="89" t="n"/>
     </row>
     <row r="742" ht="12.75" customHeight="1" s="69">
       <c r="F742" s="65" t="n"/>
@@ -10864,6 +11619,7 @@
       <c r="O742" s="68" t="n"/>
       <c r="P742" s="61" t="n"/>
       <c r="Q742" s="61" t="n"/>
+      <c r="R742" s="89" t="n"/>
     </row>
     <row r="743" ht="12.75" customHeight="1" s="69">
       <c r="F743" s="65" t="n"/>
@@ -10874,6 +11630,7 @@
       <c r="O743" s="68" t="n"/>
       <c r="P743" s="61" t="n"/>
       <c r="Q743" s="61" t="n"/>
+      <c r="R743" s="89" t="n"/>
     </row>
     <row r="744" ht="12.75" customHeight="1" s="69">
       <c r="F744" s="65" t="n"/>
@@ -10884,6 +11641,7 @@
       <c r="O744" s="68" t="n"/>
       <c r="P744" s="61" t="n"/>
       <c r="Q744" s="61" t="n"/>
+      <c r="R744" s="89" t="n"/>
     </row>
     <row r="745" ht="12.75" customHeight="1" s="69">
       <c r="F745" s="65" t="n"/>
@@ -10894,6 +11652,7 @@
       <c r="O745" s="68" t="n"/>
       <c r="P745" s="61" t="n"/>
       <c r="Q745" s="61" t="n"/>
+      <c r="R745" s="89" t="n"/>
     </row>
     <row r="746" ht="12.75" customHeight="1" s="69">
       <c r="F746" s="65" t="n"/>
@@ -10904,6 +11663,7 @@
       <c r="O746" s="68" t="n"/>
       <c r="P746" s="61" t="n"/>
       <c r="Q746" s="61" t="n"/>
+      <c r="R746" s="89" t="n"/>
     </row>
     <row r="747" ht="12.75" customHeight="1" s="69">
       <c r="F747" s="65" t="n"/>
@@ -10914,6 +11674,7 @@
       <c r="O747" s="68" t="n"/>
       <c r="P747" s="61" t="n"/>
       <c r="Q747" s="61" t="n"/>
+      <c r="R747" s="89" t="n"/>
     </row>
     <row r="748" ht="12.75" customHeight="1" s="69">
       <c r="F748" s="65" t="n"/>
@@ -10924,6 +11685,7 @@
       <c r="O748" s="68" t="n"/>
       <c r="P748" s="61" t="n"/>
       <c r="Q748" s="61" t="n"/>
+      <c r="R748" s="89" t="n"/>
     </row>
     <row r="749" ht="12.75" customHeight="1" s="69">
       <c r="F749" s="65" t="n"/>
@@ -10934,6 +11696,7 @@
       <c r="O749" s="68" t="n"/>
       <c r="P749" s="61" t="n"/>
       <c r="Q749" s="61" t="n"/>
+      <c r="R749" s="89" t="n"/>
     </row>
     <row r="750" ht="12.75" customHeight="1" s="69">
       <c r="F750" s="65" t="n"/>
@@ -10944,6 +11707,7 @@
       <c r="O750" s="68" t="n"/>
       <c r="P750" s="61" t="n"/>
       <c r="Q750" s="61" t="n"/>
+      <c r="R750" s="89" t="n"/>
     </row>
     <row r="751" ht="12.75" customHeight="1" s="69">
       <c r="F751" s="65" t="n"/>
@@ -10954,6 +11718,7 @@
       <c r="O751" s="68" t="n"/>
       <c r="P751" s="61" t="n"/>
       <c r="Q751" s="61" t="n"/>
+      <c r="R751" s="89" t="n"/>
     </row>
     <row r="752" ht="12.75" customHeight="1" s="69">
       <c r="F752" s="65" t="n"/>
@@ -10964,6 +11729,7 @@
       <c r="O752" s="68" t="n"/>
       <c r="P752" s="61" t="n"/>
       <c r="Q752" s="61" t="n"/>
+      <c r="R752" s="89" t="n"/>
     </row>
     <row r="753" ht="12.75" customHeight="1" s="69">
       <c r="F753" s="65" t="n"/>
@@ -10974,6 +11740,7 @@
       <c r="O753" s="68" t="n"/>
       <c r="P753" s="61" t="n"/>
       <c r="Q753" s="61" t="n"/>
+      <c r="R753" s="89" t="n"/>
     </row>
     <row r="754" ht="12.75" customHeight="1" s="69">
       <c r="F754" s="65" t="n"/>
@@ -10984,6 +11751,7 @@
       <c r="O754" s="68" t="n"/>
       <c r="P754" s="61" t="n"/>
       <c r="Q754" s="61" t="n"/>
+      <c r="R754" s="89" t="n"/>
     </row>
     <row r="755" ht="12.75" customHeight="1" s="69">
       <c r="F755" s="65" t="n"/>
@@ -10994,6 +11762,7 @@
       <c r="O755" s="68" t="n"/>
       <c r="P755" s="61" t="n"/>
       <c r="Q755" s="61" t="n"/>
+      <c r="R755" s="89" t="n"/>
     </row>
     <row r="756" ht="12.75" customHeight="1" s="69">
       <c r="F756" s="65" t="n"/>
@@ -11004,6 +11773,7 @@
       <c r="O756" s="68" t="n"/>
       <c r="P756" s="61" t="n"/>
       <c r="Q756" s="61" t="n"/>
+      <c r="R756" s="89" t="n"/>
     </row>
     <row r="757" ht="12.75" customHeight="1" s="69">
       <c r="F757" s="65" t="n"/>
@@ -11014,6 +11784,7 @@
       <c r="O757" s="68" t="n"/>
       <c r="P757" s="61" t="n"/>
       <c r="Q757" s="61" t="n"/>
+      <c r="R757" s="89" t="n"/>
     </row>
     <row r="758" ht="12.75" customHeight="1" s="69">
       <c r="F758" s="65" t="n"/>
@@ -11024,6 +11795,7 @@
       <c r="O758" s="68" t="n"/>
       <c r="P758" s="61" t="n"/>
       <c r="Q758" s="61" t="n"/>
+      <c r="R758" s="89" t="n"/>
     </row>
     <row r="759" ht="12.75" customHeight="1" s="69">
       <c r="F759" s="65" t="n"/>
@@ -11034,6 +11806,7 @@
       <c r="O759" s="68" t="n"/>
       <c r="P759" s="61" t="n"/>
       <c r="Q759" s="61" t="n"/>
+      <c r="R759" s="89" t="n"/>
     </row>
     <row r="760" ht="12.75" customHeight="1" s="69">
       <c r="F760" s="65" t="n"/>
@@ -11044,6 +11817,7 @@
       <c r="O760" s="68" t="n"/>
       <c r="P760" s="61" t="n"/>
       <c r="Q760" s="61" t="n"/>
+      <c r="R760" s="89" t="n"/>
     </row>
     <row r="761" ht="12.75" customHeight="1" s="69">
       <c r="F761" s="65" t="n"/>
@@ -11054,6 +11828,7 @@
       <c r="O761" s="68" t="n"/>
       <c r="P761" s="61" t="n"/>
       <c r="Q761" s="61" t="n"/>
+      <c r="R761" s="89" t="n"/>
     </row>
     <row r="762" ht="12.75" customHeight="1" s="69">
       <c r="F762" s="65" t="n"/>
@@ -11064,6 +11839,7 @@
       <c r="O762" s="68" t="n"/>
       <c r="P762" s="61" t="n"/>
       <c r="Q762" s="61" t="n"/>
+      <c r="R762" s="89" t="n"/>
     </row>
     <row r="763" ht="12.75" customHeight="1" s="69">
       <c r="F763" s="65" t="n"/>
@@ -11074,6 +11850,7 @@
       <c r="O763" s="68" t="n"/>
       <c r="P763" s="61" t="n"/>
       <c r="Q763" s="61" t="n"/>
+      <c r="R763" s="89" t="n"/>
     </row>
     <row r="764" ht="12.75" customHeight="1" s="69">
       <c r="F764" s="65" t="n"/>
@@ -11084,6 +11861,7 @@
       <c r="O764" s="68" t="n"/>
       <c r="P764" s="61" t="n"/>
       <c r="Q764" s="61" t="n"/>
+      <c r="R764" s="89" t="n"/>
     </row>
     <row r="765" ht="12.75" customHeight="1" s="69">
       <c r="F765" s="65" t="n"/>
@@ -11094,6 +11872,7 @@
       <c r="O765" s="68" t="n"/>
       <c r="P765" s="61" t="n"/>
       <c r="Q765" s="61" t="n"/>
+      <c r="R765" s="89" t="n"/>
     </row>
     <row r="766" ht="12.75" customHeight="1" s="69">
       <c r="F766" s="65" t="n"/>
@@ -11104,6 +11883,7 @@
       <c r="O766" s="68" t="n"/>
       <c r="P766" s="61" t="n"/>
       <c r="Q766" s="61" t="n"/>
+      <c r="R766" s="89" t="n"/>
     </row>
     <row r="767" ht="12.75" customHeight="1" s="69">
       <c r="F767" s="65" t="n"/>
@@ -11114,6 +11894,7 @@
       <c r="O767" s="68" t="n"/>
       <c r="P767" s="61" t="n"/>
       <c r="Q767" s="61" t="n"/>
+      <c r="R767" s="89" t="n"/>
     </row>
     <row r="768" ht="12.75" customHeight="1" s="69">
       <c r="F768" s="65" t="n"/>
@@ -11124,6 +11905,7 @@
       <c r="O768" s="68" t="n"/>
       <c r="P768" s="61" t="n"/>
       <c r="Q768" s="61" t="n"/>
+      <c r="R768" s="89" t="n"/>
     </row>
     <row r="769" ht="12.75" customHeight="1" s="69">
       <c r="F769" s="65" t="n"/>
@@ -11134,6 +11916,7 @@
       <c r="O769" s="68" t="n"/>
       <c r="P769" s="61" t="n"/>
       <c r="Q769" s="61" t="n"/>
+      <c r="R769" s="89" t="n"/>
     </row>
     <row r="770" ht="12.75" customHeight="1" s="69">
       <c r="F770" s="65" t="n"/>
@@ -11144,6 +11927,7 @@
       <c r="O770" s="68" t="n"/>
       <c r="P770" s="61" t="n"/>
       <c r="Q770" s="61" t="n"/>
+      <c r="R770" s="89" t="n"/>
     </row>
     <row r="771" ht="12.75" customHeight="1" s="69">
       <c r="F771" s="65" t="n"/>
@@ -11154,6 +11938,7 @@
       <c r="O771" s="68" t="n"/>
       <c r="P771" s="61" t="n"/>
       <c r="Q771" s="61" t="n"/>
+      <c r="R771" s="89" t="n"/>
     </row>
     <row r="772" ht="12.75" customHeight="1" s="69">
       <c r="F772" s="65" t="n"/>
@@ -11164,6 +11949,7 @@
       <c r="O772" s="68" t="n"/>
       <c r="P772" s="61" t="n"/>
       <c r="Q772" s="61" t="n"/>
+      <c r="R772" s="89" t="n"/>
     </row>
     <row r="773" ht="12.75" customHeight="1" s="69">
       <c r="F773" s="65" t="n"/>
@@ -11174,6 +11960,7 @@
       <c r="O773" s="68" t="n"/>
       <c r="P773" s="61" t="n"/>
       <c r="Q773" s="61" t="n"/>
+      <c r="R773" s="89" t="n"/>
     </row>
     <row r="774" ht="12.75" customHeight="1" s="69">
       <c r="F774" s="65" t="n"/>
@@ -11184,6 +11971,7 @@
       <c r="O774" s="68" t="n"/>
       <c r="P774" s="61" t="n"/>
       <c r="Q774" s="61" t="n"/>
+      <c r="R774" s="89" t="n"/>
     </row>
     <row r="775" ht="12.75" customHeight="1" s="69">
       <c r="F775" s="65" t="n"/>
@@ -11194,6 +11982,7 @@
       <c r="O775" s="68" t="n"/>
       <c r="P775" s="61" t="n"/>
       <c r="Q775" s="61" t="n"/>
+      <c r="R775" s="89" t="n"/>
     </row>
     <row r="776" ht="12.75" customHeight="1" s="69">
       <c r="F776" s="65" t="n"/>
@@ -11204,6 +11993,7 @@
       <c r="O776" s="68" t="n"/>
       <c r="P776" s="61" t="n"/>
       <c r="Q776" s="61" t="n"/>
+      <c r="R776" s="89" t="n"/>
     </row>
     <row r="777" ht="12.75" customHeight="1" s="69">
       <c r="F777" s="65" t="n"/>
@@ -11214,6 +12004,7 @@
       <c r="O777" s="68" t="n"/>
       <c r="P777" s="61" t="n"/>
       <c r="Q777" s="61" t="n"/>
+      <c r="R777" s="89" t="n"/>
     </row>
     <row r="778" ht="12.75" customHeight="1" s="69">
       <c r="F778" s="65" t="n"/>
@@ -11224,6 +12015,7 @@
       <c r="O778" s="68" t="n"/>
       <c r="P778" s="61" t="n"/>
       <c r="Q778" s="61" t="n"/>
+      <c r="R778" s="89" t="n"/>
     </row>
     <row r="779" ht="12.75" customHeight="1" s="69">
       <c r="F779" s="65" t="n"/>
@@ -11234,6 +12026,7 @@
       <c r="O779" s="68" t="n"/>
       <c r="P779" s="61" t="n"/>
       <c r="Q779" s="61" t="n"/>
+      <c r="R779" s="89" t="n"/>
     </row>
     <row r="780" ht="12.75" customHeight="1" s="69">
       <c r="F780" s="65" t="n"/>
@@ -11244,6 +12037,7 @@
       <c r="O780" s="68" t="n"/>
       <c r="P780" s="61" t="n"/>
       <c r="Q780" s="61" t="n"/>
+      <c r="R780" s="89" t="n"/>
     </row>
     <row r="781" ht="12.75" customHeight="1" s="69">
       <c r="F781" s="65" t="n"/>
@@ -11254,6 +12048,7 @@
       <c r="O781" s="68" t="n"/>
       <c r="P781" s="61" t="n"/>
       <c r="Q781" s="61" t="n"/>
+      <c r="R781" s="89" t="n"/>
     </row>
     <row r="782" ht="12.75" customHeight="1" s="69">
       <c r="F782" s="65" t="n"/>
@@ -11264,6 +12059,7 @@
       <c r="O782" s="68" t="n"/>
       <c r="P782" s="61" t="n"/>
       <c r="Q782" s="61" t="n"/>
+      <c r="R782" s="89" t="n"/>
     </row>
     <row r="783" ht="12.75" customHeight="1" s="69">
       <c r="F783" s="65" t="n"/>
@@ -11274,6 +12070,7 @@
       <c r="O783" s="68" t="n"/>
       <c r="P783" s="61" t="n"/>
       <c r="Q783" s="61" t="n"/>
+      <c r="R783" s="89" t="n"/>
     </row>
     <row r="784" ht="12.75" customHeight="1" s="69">
       <c r="F784" s="65" t="n"/>
@@ -11284,6 +12081,7 @@
       <c r="O784" s="68" t="n"/>
       <c r="P784" s="61" t="n"/>
       <c r="Q784" s="61" t="n"/>
+      <c r="R784" s="89" t="n"/>
     </row>
     <row r="785" ht="12.75" customHeight="1" s="69">
       <c r="F785" s="65" t="n"/>
@@ -11294,6 +12092,7 @@
       <c r="O785" s="68" t="n"/>
       <c r="P785" s="61" t="n"/>
       <c r="Q785" s="61" t="n"/>
+      <c r="R785" s="89" t="n"/>
     </row>
     <row r="786" ht="12.75" customHeight="1" s="69">
       <c r="F786" s="65" t="n"/>
@@ -11304,6 +12103,7 @@
       <c r="O786" s="68" t="n"/>
       <c r="P786" s="61" t="n"/>
       <c r="Q786" s="61" t="n"/>
+      <c r="R786" s="89" t="n"/>
     </row>
     <row r="787" ht="12.75" customHeight="1" s="69">
       <c r="F787" s="65" t="n"/>
@@ -11314,6 +12114,7 @@
       <c r="O787" s="68" t="n"/>
       <c r="P787" s="61" t="n"/>
       <c r="Q787" s="61" t="n"/>
+      <c r="R787" s="89" t="n"/>
     </row>
     <row r="788" ht="12.75" customHeight="1" s="69">
       <c r="F788" s="65" t="n"/>
@@ -11324,6 +12125,7 @@
       <c r="O788" s="68" t="n"/>
       <c r="P788" s="61" t="n"/>
       <c r="Q788" s="61" t="n"/>
+      <c r="R788" s="89" t="n"/>
     </row>
     <row r="789" ht="12.75" customHeight="1" s="69">
       <c r="F789" s="65" t="n"/>
@@ -11334,6 +12136,7 @@
       <c r="O789" s="68" t="n"/>
       <c r="P789" s="61" t="n"/>
       <c r="Q789" s="61" t="n"/>
+      <c r="R789" s="89" t="n"/>
     </row>
     <row r="790" ht="12.75" customHeight="1" s="69">
       <c r="F790" s="65" t="n"/>
@@ -11344,6 +12147,7 @@
       <c r="O790" s="68" t="n"/>
       <c r="P790" s="61" t="n"/>
       <c r="Q790" s="61" t="n"/>
+      <c r="R790" s="89" t="n"/>
     </row>
     <row r="791" ht="12.75" customHeight="1" s="69">
       <c r="F791" s="65" t="n"/>
@@ -11354,6 +12158,7 @@
       <c r="O791" s="68" t="n"/>
       <c r="P791" s="61" t="n"/>
       <c r="Q791" s="61" t="n"/>
+      <c r="R791" s="89" t="n"/>
     </row>
     <row r="792" ht="12.75" customHeight="1" s="69">
       <c r="F792" s="65" t="n"/>
@@ -11364,6 +12169,7 @@
       <c r="O792" s="68" t="n"/>
       <c r="P792" s="61" t="n"/>
       <c r="Q792" s="61" t="n"/>
+      <c r="R792" s="89" t="n"/>
     </row>
     <row r="793" ht="12.75" customHeight="1" s="69">
       <c r="F793" s="65" t="n"/>
@@ -11374,6 +12180,7 @@
       <c r="O793" s="68" t="n"/>
       <c r="P793" s="61" t="n"/>
       <c r="Q793" s="61" t="n"/>
+      <c r="R793" s="89" t="n"/>
     </row>
     <row r="794" ht="12.75" customHeight="1" s="69">
       <c r="F794" s="65" t="n"/>
@@ -11384,6 +12191,7 @@
       <c r="O794" s="68" t="n"/>
       <c r="P794" s="61" t="n"/>
       <c r="Q794" s="61" t="n"/>
+      <c r="R794" s="89" t="n"/>
     </row>
     <row r="795" ht="12.75" customHeight="1" s="69">
       <c r="F795" s="65" t="n"/>
@@ -11394,6 +12202,7 @@
       <c r="O795" s="68" t="n"/>
       <c r="P795" s="61" t="n"/>
       <c r="Q795" s="61" t="n"/>
+      <c r="R795" s="89" t="n"/>
     </row>
     <row r="796" ht="12.75" customHeight="1" s="69">
       <c r="F796" s="65" t="n"/>
@@ -11404,6 +12213,7 @@
       <c r="O796" s="68" t="n"/>
       <c r="P796" s="61" t="n"/>
       <c r="Q796" s="61" t="n"/>
+      <c r="R796" s="89" t="n"/>
     </row>
     <row r="797" ht="12.75" customHeight="1" s="69">
       <c r="F797" s="65" t="n"/>
@@ -11414,6 +12224,7 @@
       <c r="O797" s="68" t="n"/>
       <c r="P797" s="61" t="n"/>
       <c r="Q797" s="61" t="n"/>
+      <c r="R797" s="89" t="n"/>
     </row>
     <row r="798" ht="12.75" customHeight="1" s="69">
       <c r="F798" s="65" t="n"/>
@@ -11424,6 +12235,7 @@
       <c r="O798" s="68" t="n"/>
       <c r="P798" s="61" t="n"/>
       <c r="Q798" s="61" t="n"/>
+      <c r="R798" s="89" t="n"/>
     </row>
     <row r="799" ht="12.75" customHeight="1" s="69">
       <c r="F799" s="65" t="n"/>
@@ -11434,6 +12246,7 @@
       <c r="O799" s="68" t="n"/>
       <c r="P799" s="61" t="n"/>
       <c r="Q799" s="61" t="n"/>
+      <c r="R799" s="89" t="n"/>
     </row>
     <row r="800" ht="12.75" customHeight="1" s="69">
       <c r="F800" s="65" t="n"/>
@@ -11444,6 +12257,7 @@
       <c r="O800" s="68" t="n"/>
       <c r="P800" s="61" t="n"/>
       <c r="Q800" s="61" t="n"/>
+      <c r="R800" s="89" t="n"/>
     </row>
     <row r="801" ht="12.75" customHeight="1" s="69">
       <c r="F801" s="65" t="n"/>
@@ -11454,6 +12268,7 @@
       <c r="O801" s="68" t="n"/>
       <c r="P801" s="61" t="n"/>
       <c r="Q801" s="61" t="n"/>
+      <c r="R801" s="89" t="n"/>
     </row>
     <row r="802" ht="12.75" customHeight="1" s="69">
       <c r="F802" s="65" t="n"/>
@@ -11464,6 +12279,7 @@
       <c r="O802" s="68" t="n"/>
       <c r="P802" s="61" t="n"/>
       <c r="Q802" s="61" t="n"/>
+      <c r="R802" s="89" t="n"/>
     </row>
     <row r="803" ht="12.75" customHeight="1" s="69">
       <c r="F803" s="65" t="n"/>
@@ -11474,6 +12290,7 @@
       <c r="O803" s="68" t="n"/>
       <c r="P803" s="61" t="n"/>
       <c r="Q803" s="61" t="n"/>
+      <c r="R803" s="89" t="n"/>
     </row>
     <row r="804" ht="12.75" customHeight="1" s="69">
       <c r="F804" s="65" t="n"/>
@@ -11484,6 +12301,7 @@
       <c r="O804" s="68" t="n"/>
       <c r="P804" s="61" t="n"/>
       <c r="Q804" s="61" t="n"/>
+      <c r="R804" s="89" t="n"/>
     </row>
     <row r="805" ht="12.75" customHeight="1" s="69">
       <c r="F805" s="65" t="n"/>
@@ -11494,6 +12312,7 @@
       <c r="O805" s="68" t="n"/>
       <c r="P805" s="61" t="n"/>
       <c r="Q805" s="61" t="n"/>
+      <c r="R805" s="89" t="n"/>
     </row>
     <row r="806" ht="12.75" customHeight="1" s="69">
       <c r="F806" s="65" t="n"/>
@@ -11504,6 +12323,7 @@
       <c r="O806" s="68" t="n"/>
       <c r="P806" s="61" t="n"/>
       <c r="Q806" s="61" t="n"/>
+      <c r="R806" s="89" t="n"/>
     </row>
     <row r="807" ht="12.75" customHeight="1" s="69">
       <c r="F807" s="65" t="n"/>
@@ -11514,6 +12334,7 @@
       <c r="O807" s="68" t="n"/>
       <c r="P807" s="61" t="n"/>
       <c r="Q807" s="61" t="n"/>
+      <c r="R807" s="89" t="n"/>
     </row>
     <row r="808" ht="12.75" customHeight="1" s="69">
       <c r="F808" s="65" t="n"/>
@@ -11524,6 +12345,7 @@
       <c r="O808" s="68" t="n"/>
       <c r="P808" s="61" t="n"/>
       <c r="Q808" s="61" t="n"/>
+      <c r="R808" s="89" t="n"/>
     </row>
     <row r="809" ht="12.75" customHeight="1" s="69">
       <c r="F809" s="65" t="n"/>
@@ -11534,6 +12356,7 @@
       <c r="O809" s="68" t="n"/>
       <c r="P809" s="61" t="n"/>
       <c r="Q809" s="61" t="n"/>
+      <c r="R809" s="89" t="n"/>
     </row>
     <row r="810" ht="12.75" customHeight="1" s="69">
       <c r="F810" s="65" t="n"/>
@@ -11544,6 +12367,7 @@
       <c r="O810" s="68" t="n"/>
       <c r="P810" s="61" t="n"/>
       <c r="Q810" s="61" t="n"/>
+      <c r="R810" s="89" t="n"/>
     </row>
     <row r="811" ht="12.75" customHeight="1" s="69">
       <c r="F811" s="65" t="n"/>
@@ -11554,6 +12378,7 @@
       <c r="O811" s="68" t="n"/>
       <c r="P811" s="61" t="n"/>
       <c r="Q811" s="61" t="n"/>
+      <c r="R811" s="89" t="n"/>
     </row>
     <row r="812" ht="12.75" customHeight="1" s="69">
       <c r="F812" s="65" t="n"/>
@@ -11564,6 +12389,7 @@
       <c r="O812" s="68" t="n"/>
       <c r="P812" s="61" t="n"/>
       <c r="Q812" s="61" t="n"/>
+      <c r="R812" s="89" t="n"/>
     </row>
     <row r="813" ht="12.75" customHeight="1" s="69">
       <c r="F813" s="65" t="n"/>
@@ -11574,6 +12400,7 @@
       <c r="O813" s="68" t="n"/>
       <c r="P813" s="61" t="n"/>
       <c r="Q813" s="61" t="n"/>
+      <c r="R813" s="89" t="n"/>
     </row>
     <row r="814" ht="12.75" customHeight="1" s="69">
       <c r="F814" s="65" t="n"/>
@@ -11584,6 +12411,7 @@
       <c r="O814" s="68" t="n"/>
       <c r="P814" s="61" t="n"/>
       <c r="Q814" s="61" t="n"/>
+      <c r="R814" s="89" t="n"/>
     </row>
     <row r="815" ht="12.75" customHeight="1" s="69">
       <c r="F815" s="65" t="n"/>
@@ -11594,6 +12422,7 @@
       <c r="O815" s="68" t="n"/>
       <c r="P815" s="61" t="n"/>
       <c r="Q815" s="61" t="n"/>
+      <c r="R815" s="89" t="n"/>
     </row>
     <row r="816" ht="12.75" customHeight="1" s="69">
       <c r="F816" s="65" t="n"/>
@@ -11604,6 +12433,7 @@
       <c r="O816" s="68" t="n"/>
       <c r="P816" s="61" t="n"/>
       <c r="Q816" s="61" t="n"/>
+      <c r="R816" s="89" t="n"/>
     </row>
     <row r="817" ht="12.75" customHeight="1" s="69">
       <c r="F817" s="65" t="n"/>
@@ -11614,6 +12444,7 @@
       <c r="O817" s="68" t="n"/>
       <c r="P817" s="61" t="n"/>
       <c r="Q817" s="61" t="n"/>
+      <c r="R817" s="89" t="n"/>
     </row>
     <row r="818" ht="12.75" customHeight="1" s="69">
       <c r="F818" s="65" t="n"/>
@@ -11624,6 +12455,7 @@
       <c r="O818" s="68" t="n"/>
       <c r="P818" s="61" t="n"/>
       <c r="Q818" s="61" t="n"/>
+      <c r="R818" s="89" t="n"/>
     </row>
     <row r="819" ht="12.75" customHeight="1" s="69">
       <c r="F819" s="65" t="n"/>
@@ -11634,6 +12466,7 @@
       <c r="O819" s="68" t="n"/>
       <c r="P819" s="61" t="n"/>
       <c r="Q819" s="61" t="n"/>
+      <c r="R819" s="89" t="n"/>
     </row>
     <row r="820" ht="12.75" customHeight="1" s="69">
       <c r="F820" s="65" t="n"/>
@@ -11644,6 +12477,7 @@
       <c r="O820" s="68" t="n"/>
       <c r="P820" s="61" t="n"/>
       <c r="Q820" s="61" t="n"/>
+      <c r="R820" s="89" t="n"/>
     </row>
     <row r="821" ht="12.75" customHeight="1" s="69">
       <c r="F821" s="65" t="n"/>
@@ -11654,6 +12488,7 @@
       <c r="O821" s="68" t="n"/>
       <c r="P821" s="61" t="n"/>
       <c r="Q821" s="61" t="n"/>
+      <c r="R821" s="89" t="n"/>
     </row>
     <row r="822" ht="12.75" customHeight="1" s="69">
       <c r="F822" s="65" t="n"/>
@@ -11664,6 +12499,7 @@
       <c r="O822" s="68" t="n"/>
       <c r="P822" s="61" t="n"/>
       <c r="Q822" s="61" t="n"/>
+      <c r="R822" s="89" t="n"/>
     </row>
     <row r="823" ht="12.75" customHeight="1" s="69">
       <c r="F823" s="65" t="n"/>
@@ -11674,6 +12510,7 @@
       <c r="O823" s="68" t="n"/>
       <c r="P823" s="61" t="n"/>
       <c r="Q823" s="61" t="n"/>
+      <c r="R823" s="89" t="n"/>
     </row>
     <row r="824" ht="12.75" customHeight="1" s="69">
       <c r="F824" s="65" t="n"/>
@@ -11684,6 +12521,7 @@
       <c r="O824" s="68" t="n"/>
       <c r="P824" s="61" t="n"/>
       <c r="Q824" s="61" t="n"/>
+      <c r="R824" s="89" t="n"/>
     </row>
     <row r="825" ht="12.75" customHeight="1" s="69">
       <c r="F825" s="65" t="n"/>
@@ -11694,6 +12532,7 @@
       <c r="O825" s="68" t="n"/>
       <c r="P825" s="61" t="n"/>
       <c r="Q825" s="61" t="n"/>
+      <c r="R825" s="89" t="n"/>
     </row>
     <row r="826" ht="12.75" customHeight="1" s="69">
       <c r="F826" s="65" t="n"/>
@@ -11704,6 +12543,7 @@
       <c r="O826" s="68" t="n"/>
       <c r="P826" s="61" t="n"/>
       <c r="Q826" s="61" t="n"/>
+      <c r="R826" s="89" t="n"/>
     </row>
     <row r="827" ht="12.75" customHeight="1" s="69">
       <c r="F827" s="65" t="n"/>
@@ -11714,6 +12554,7 @@
       <c r="O827" s="68" t="n"/>
       <c r="P827" s="61" t="n"/>
       <c r="Q827" s="61" t="n"/>
+      <c r="R827" s="89" t="n"/>
     </row>
     <row r="828" ht="12.75" customHeight="1" s="69">
       <c r="F828" s="65" t="n"/>
@@ -11724,6 +12565,7 @@
       <c r="O828" s="68" t="n"/>
       <c r="P828" s="61" t="n"/>
       <c r="Q828" s="61" t="n"/>
+      <c r="R828" s="89" t="n"/>
     </row>
     <row r="829" ht="12.75" customHeight="1" s="69">
       <c r="F829" s="65" t="n"/>
@@ -11734,6 +12576,7 @@
       <c r="O829" s="68" t="n"/>
       <c r="P829" s="61" t="n"/>
       <c r="Q829" s="61" t="n"/>
+      <c r="R829" s="89" t="n"/>
     </row>
     <row r="830" ht="12.75" customHeight="1" s="69">
       <c r="F830" s="65" t="n"/>
@@ -11744,6 +12587,7 @@
       <c r="O830" s="68" t="n"/>
       <c r="P830" s="61" t="n"/>
       <c r="Q830" s="61" t="n"/>
+      <c r="R830" s="89" t="n"/>
     </row>
     <row r="831" ht="12.75" customHeight="1" s="69">
       <c r="F831" s="65" t="n"/>
@@ -11754,6 +12598,7 @@
       <c r="O831" s="68" t="n"/>
       <c r="P831" s="61" t="n"/>
       <c r="Q831" s="61" t="n"/>
+      <c r="R831" s="89" t="n"/>
     </row>
     <row r="832" ht="12.75" customHeight="1" s="69">
       <c r="F832" s="65" t="n"/>
@@ -11764,6 +12609,7 @@
       <c r="O832" s="68" t="n"/>
       <c r="P832" s="61" t="n"/>
       <c r="Q832" s="61" t="n"/>
+      <c r="R832" s="89" t="n"/>
     </row>
     <row r="833" ht="12.75" customHeight="1" s="69">
       <c r="F833" s="65" t="n"/>
@@ -11774,6 +12620,7 @@
       <c r="O833" s="68" t="n"/>
       <c r="P833" s="61" t="n"/>
       <c r="Q833" s="61" t="n"/>
+      <c r="R833" s="89" t="n"/>
     </row>
     <row r="834" ht="12.75" customHeight="1" s="69">
       <c r="F834" s="65" t="n"/>
@@ -11784,6 +12631,7 @@
       <c r="O834" s="68" t="n"/>
       <c r="P834" s="61" t="n"/>
       <c r="Q834" s="61" t="n"/>
+      <c r="R834" s="89" t="n"/>
     </row>
     <row r="835" ht="12.75" customHeight="1" s="69">
       <c r="F835" s="65" t="n"/>
@@ -11794,6 +12642,7 @@
       <c r="O835" s="68" t="n"/>
       <c r="P835" s="61" t="n"/>
       <c r="Q835" s="61" t="n"/>
+      <c r="R835" s="89" t="n"/>
     </row>
     <row r="836" ht="12.75" customHeight="1" s="69">
       <c r="F836" s="65" t="n"/>
@@ -11804,6 +12653,7 @@
       <c r="O836" s="68" t="n"/>
       <c r="P836" s="61" t="n"/>
       <c r="Q836" s="61" t="n"/>
+      <c r="R836" s="89" t="n"/>
     </row>
     <row r="837" ht="12.75" customHeight="1" s="69">
       <c r="F837" s="65" t="n"/>
@@ -11814,6 +12664,7 @@
       <c r="O837" s="68" t="n"/>
       <c r="P837" s="61" t="n"/>
       <c r="Q837" s="61" t="n"/>
+      <c r="R837" s="89" t="n"/>
     </row>
     <row r="838" ht="12.75" customHeight="1" s="69">
       <c r="F838" s="65" t="n"/>
@@ -11824,6 +12675,7 @@
       <c r="O838" s="68" t="n"/>
       <c r="P838" s="61" t="n"/>
       <c r="Q838" s="61" t="n"/>
+      <c r="R838" s="89" t="n"/>
     </row>
     <row r="839" ht="12.75" customHeight="1" s="69">
       <c r="F839" s="65" t="n"/>
@@ -11834,6 +12686,7 @@
       <c r="O839" s="68" t="n"/>
       <c r="P839" s="61" t="n"/>
       <c r="Q839" s="61" t="n"/>
+      <c r="R839" s="89" t="n"/>
     </row>
     <row r="840" ht="12.75" customHeight="1" s="69">
       <c r="F840" s="65" t="n"/>
@@ -11844,6 +12697,7 @@
       <c r="O840" s="68" t="n"/>
       <c r="P840" s="61" t="n"/>
       <c r="Q840" s="61" t="n"/>
+      <c r="R840" s="89" t="n"/>
     </row>
     <row r="841" ht="12.75" customHeight="1" s="69">
       <c r="F841" s="65" t="n"/>
@@ -11854,6 +12708,7 @@
       <c r="O841" s="68" t="n"/>
       <c r="P841" s="61" t="n"/>
       <c r="Q841" s="61" t="n"/>
+      <c r="R841" s="89" t="n"/>
     </row>
     <row r="842" ht="12.75" customHeight="1" s="69">
       <c r="F842" s="65" t="n"/>
@@ -11864,6 +12719,7 @@
       <c r="O842" s="68" t="n"/>
       <c r="P842" s="61" t="n"/>
       <c r="Q842" s="61" t="n"/>
+      <c r="R842" s="89" t="n"/>
     </row>
     <row r="843" ht="12.75" customHeight="1" s="69">
       <c r="F843" s="65" t="n"/>
@@ -11874,6 +12730,7 @@
       <c r="O843" s="68" t="n"/>
       <c r="P843" s="61" t="n"/>
       <c r="Q843" s="61" t="n"/>
+      <c r="R843" s="89" t="n"/>
     </row>
     <row r="844" ht="12.75" customHeight="1" s="69">
       <c r="F844" s="65" t="n"/>
@@ -11884,6 +12741,7 @@
       <c r="O844" s="68" t="n"/>
       <c r="P844" s="61" t="n"/>
       <c r="Q844" s="61" t="n"/>
+      <c r="R844" s="89" t="n"/>
     </row>
     <row r="845" ht="12.75" customHeight="1" s="69">
       <c r="F845" s="65" t="n"/>
@@ -11894,6 +12752,7 @@
       <c r="O845" s="68" t="n"/>
       <c r="P845" s="61" t="n"/>
       <c r="Q845" s="61" t="n"/>
+      <c r="R845" s="89" t="n"/>
     </row>
     <row r="846" ht="12.75" customHeight="1" s="69">
       <c r="F846" s="65" t="n"/>
@@ -11904,6 +12763,7 @@
       <c r="O846" s="68" t="n"/>
       <c r="P846" s="61" t="n"/>
       <c r="Q846" s="61" t="n"/>
+      <c r="R846" s="89" t="n"/>
     </row>
     <row r="847" ht="12.75" customHeight="1" s="69">
       <c r="F847" s="65" t="n"/>
@@ -11914,6 +12774,7 @@
       <c r="O847" s="68" t="n"/>
       <c r="P847" s="61" t="n"/>
       <c r="Q847" s="61" t="n"/>
+      <c r="R847" s="89" t="n"/>
     </row>
     <row r="848" ht="12.75" customHeight="1" s="69">
       <c r="F848" s="65" t="n"/>
@@ -11924,6 +12785,7 @@
       <c r="O848" s="68" t="n"/>
       <c r="P848" s="61" t="n"/>
       <c r="Q848" s="61" t="n"/>
+      <c r="R848" s="89" t="n"/>
     </row>
     <row r="849" ht="12.75" customHeight="1" s="69">
       <c r="F849" s="65" t="n"/>
@@ -11934,6 +12796,7 @@
       <c r="O849" s="68" t="n"/>
       <c r="P849" s="61" t="n"/>
       <c r="Q849" s="61" t="n"/>
+      <c r="R849" s="89" t="n"/>
     </row>
     <row r="850" ht="12.75" customHeight="1" s="69">
       <c r="F850" s="65" t="n"/>
@@ -11944,6 +12807,7 @@
       <c r="O850" s="68" t="n"/>
       <c r="P850" s="61" t="n"/>
       <c r="Q850" s="61" t="n"/>
+      <c r="R850" s="89" t="n"/>
     </row>
     <row r="851" ht="12.75" customHeight="1" s="69">
       <c r="F851" s="65" t="n"/>
@@ -11954,6 +12818,7 @@
       <c r="O851" s="68" t="n"/>
       <c r="P851" s="61" t="n"/>
       <c r="Q851" s="61" t="n"/>
+      <c r="R851" s="89" t="n"/>
     </row>
     <row r="852" ht="12.75" customHeight="1" s="69">
       <c r="F852" s="65" t="n"/>
@@ -11964,6 +12829,7 @@
       <c r="O852" s="68" t="n"/>
       <c r="P852" s="61" t="n"/>
       <c r="Q852" s="61" t="n"/>
+      <c r="R852" s="89" t="n"/>
     </row>
     <row r="853" ht="12.75" customHeight="1" s="69">
       <c r="F853" s="65" t="n"/>
@@ -11974,6 +12840,7 @@
       <c r="O853" s="68" t="n"/>
       <c r="P853" s="61" t="n"/>
       <c r="Q853" s="61" t="n"/>
+      <c r="R853" s="89" t="n"/>
     </row>
     <row r="854" ht="12.75" customHeight="1" s="69">
       <c r="F854" s="65" t="n"/>
@@ -11984,6 +12851,7 @@
       <c r="O854" s="68" t="n"/>
       <c r="P854" s="61" t="n"/>
       <c r="Q854" s="61" t="n"/>
+      <c r="R854" s="89" t="n"/>
     </row>
     <row r="855" ht="12.75" customHeight="1" s="69">
       <c r="F855" s="65" t="n"/>
@@ -11994,6 +12862,7 @@
       <c r="O855" s="68" t="n"/>
       <c r="P855" s="61" t="n"/>
       <c r="Q855" s="61" t="n"/>
+      <c r="R855" s="89" t="n"/>
     </row>
     <row r="856" ht="12.75" customHeight="1" s="69">
       <c r="F856" s="65" t="n"/>
@@ -12004,6 +12873,7 @@
       <c r="O856" s="68" t="n"/>
       <c r="P856" s="61" t="n"/>
       <c r="Q856" s="61" t="n"/>
+      <c r="R856" s="89" t="n"/>
     </row>
     <row r="857" ht="12.75" customHeight="1" s="69">
       <c r="F857" s="65" t="n"/>
@@ -12014,6 +12884,7 @@
       <c r="O857" s="68" t="n"/>
       <c r="P857" s="61" t="n"/>
       <c r="Q857" s="61" t="n"/>
+      <c r="R857" s="89" t="n"/>
     </row>
     <row r="858" ht="12.75" customHeight="1" s="69">
       <c r="F858" s="65" t="n"/>
@@ -12024,6 +12895,7 @@
       <c r="O858" s="68" t="n"/>
       <c r="P858" s="61" t="n"/>
       <c r="Q858" s="61" t="n"/>
+      <c r="R858" s="89" t="n"/>
     </row>
     <row r="859" ht="12.75" customHeight="1" s="69">
       <c r="F859" s="65" t="n"/>
@@ -12034,6 +12906,7 @@
       <c r="O859" s="68" t="n"/>
       <c r="P859" s="61" t="n"/>
       <c r="Q859" s="61" t="n"/>
+      <c r="R859" s="89" t="n"/>
     </row>
     <row r="860" ht="12.75" customHeight="1" s="69">
       <c r="F860" s="65" t="n"/>
@@ -12044,6 +12917,7 @@
       <c r="O860" s="68" t="n"/>
       <c r="P860" s="61" t="n"/>
       <c r="Q860" s="61" t="n"/>
+      <c r="R860" s="89" t="n"/>
     </row>
     <row r="861" ht="12.75" customHeight="1" s="69">
       <c r="F861" s="65" t="n"/>
@@ -12054,6 +12928,7 @@
       <c r="O861" s="68" t="n"/>
       <c r="P861" s="61" t="n"/>
       <c r="Q861" s="61" t="n"/>
+      <c r="R861" s="89" t="n"/>
     </row>
     <row r="862" ht="12.75" customHeight="1" s="69">
       <c r="F862" s="65" t="n"/>
@@ -12064,6 +12939,7 @@
       <c r="O862" s="68" t="n"/>
       <c r="P862" s="61" t="n"/>
       <c r="Q862" s="61" t="n"/>
+      <c r="R862" s="89" t="n"/>
     </row>
     <row r="863" ht="12.75" customHeight="1" s="69">
       <c r="F863" s="65" t="n"/>
@@ -12074,6 +12950,7 @@
       <c r="O863" s="68" t="n"/>
       <c r="P863" s="61" t="n"/>
       <c r="Q863" s="61" t="n"/>
+      <c r="R863" s="89" t="n"/>
     </row>
     <row r="864" ht="12.75" customHeight="1" s="69">
       <c r="F864" s="65" t="n"/>
@@ -12084,6 +12961,7 @@
       <c r="O864" s="68" t="n"/>
       <c r="P864" s="61" t="n"/>
       <c r="Q864" s="61" t="n"/>
+      <c r="R864" s="89" t="n"/>
     </row>
     <row r="865" ht="12.75" customHeight="1" s="69">
       <c r="F865" s="65" t="n"/>
@@ -12094,6 +12972,7 @@
       <c r="O865" s="68" t="n"/>
       <c r="P865" s="61" t="n"/>
       <c r="Q865" s="61" t="n"/>
+      <c r="R865" s="89" t="n"/>
     </row>
     <row r="866" ht="12.75" customHeight="1" s="69">
       <c r="F866" s="65" t="n"/>
@@ -12104,6 +12983,7 @@
       <c r="O866" s="68" t="n"/>
       <c r="P866" s="61" t="n"/>
       <c r="Q866" s="61" t="n"/>
+      <c r="R866" s="89" t="n"/>
     </row>
     <row r="867" ht="12.75" customHeight="1" s="69">
       <c r="F867" s="65" t="n"/>
@@ -12114,6 +12994,7 @@
       <c r="O867" s="68" t="n"/>
       <c r="P867" s="61" t="n"/>
       <c r="Q867" s="61" t="n"/>
+      <c r="R867" s="89" t="n"/>
     </row>
     <row r="868" ht="12.75" customHeight="1" s="69">
       <c r="F868" s="65" t="n"/>
@@ -12124,6 +13005,7 @@
       <c r="O868" s="68" t="n"/>
       <c r="P868" s="61" t="n"/>
       <c r="Q868" s="61" t="n"/>
+      <c r="R868" s="89" t="n"/>
     </row>
     <row r="869" ht="12.75" customHeight="1" s="69">
       <c r="F869" s="65" t="n"/>
@@ -12134,6 +13016,7 @@
       <c r="O869" s="68" t="n"/>
       <c r="P869" s="61" t="n"/>
       <c r="Q869" s="61" t="n"/>
+      <c r="R869" s="89" t="n"/>
     </row>
     <row r="870" ht="12.75" customHeight="1" s="69">
       <c r="F870" s="65" t="n"/>
@@ -12144,6 +13027,7 @@
       <c r="O870" s="68" t="n"/>
       <c r="P870" s="61" t="n"/>
       <c r="Q870" s="61" t="n"/>
+      <c r="R870" s="89" t="n"/>
     </row>
     <row r="871" ht="12.75" customHeight="1" s="69">
       <c r="F871" s="65" t="n"/>
@@ -12154,6 +13038,7 @@
       <c r="O871" s="68" t="n"/>
       <c r="P871" s="61" t="n"/>
       <c r="Q871" s="61" t="n"/>
+      <c r="R871" s="89" t="n"/>
     </row>
     <row r="872" ht="12.75" customHeight="1" s="69">
       <c r="F872" s="65" t="n"/>
@@ -12164,6 +13049,7 @@
       <c r="O872" s="68" t="n"/>
       <c r="P872" s="61" t="n"/>
       <c r="Q872" s="61" t="n"/>
+      <c r="R872" s="89" t="n"/>
     </row>
     <row r="873" ht="12.75" customHeight="1" s="69">
       <c r="F873" s="65" t="n"/>
@@ -12174,6 +13060,7 @@
       <c r="O873" s="68" t="n"/>
       <c r="P873" s="61" t="n"/>
       <c r="Q873" s="61" t="n"/>
+      <c r="R873" s="89" t="n"/>
     </row>
     <row r="874" ht="12.75" customHeight="1" s="69">
       <c r="F874" s="65" t="n"/>
@@ -12184,6 +13071,7 @@
       <c r="O874" s="68" t="n"/>
       <c r="P874" s="61" t="n"/>
       <c r="Q874" s="61" t="n"/>
+      <c r="R874" s="89" t="n"/>
     </row>
     <row r="875" ht="12.75" customHeight="1" s="69">
       <c r="F875" s="65" t="n"/>
@@ -12194,6 +13082,7 @@
       <c r="O875" s="68" t="n"/>
       <c r="P875" s="61" t="n"/>
       <c r="Q875" s="61" t="n"/>
+      <c r="R875" s="89" t="n"/>
     </row>
     <row r="876" ht="12.75" customHeight="1" s="69">
       <c r="F876" s="65" t="n"/>
@@ -12204,6 +13093,7 @@
       <c r="O876" s="68" t="n"/>
       <c r="P876" s="61" t="n"/>
       <c r="Q876" s="61" t="n"/>
+      <c r="R876" s="89" t="n"/>
     </row>
     <row r="877" ht="12.75" customHeight="1" s="69">
       <c r="F877" s="65" t="n"/>
@@ -12214,6 +13104,7 @@
       <c r="O877" s="68" t="n"/>
       <c r="P877" s="61" t="n"/>
       <c r="Q877" s="61" t="n"/>
+      <c r="R877" s="89" t="n"/>
     </row>
     <row r="878" ht="12.75" customHeight="1" s="69">
       <c r="F878" s="65" t="n"/>
@@ -12224,6 +13115,7 @@
       <c r="O878" s="68" t="n"/>
       <c r="P878" s="61" t="n"/>
       <c r="Q878" s="61" t="n"/>
+      <c r="R878" s="89" t="n"/>
     </row>
     <row r="879" ht="12.75" customHeight="1" s="69">
       <c r="F879" s="65" t="n"/>
@@ -12234,6 +13126,7 @@
       <c r="O879" s="68" t="n"/>
       <c r="P879" s="61" t="n"/>
       <c r="Q879" s="61" t="n"/>
+      <c r="R879" s="89" t="n"/>
     </row>
     <row r="880" ht="12.75" customHeight="1" s="69">
       <c r="F880" s="65" t="n"/>
@@ -12244,6 +13137,7 @@
       <c r="O880" s="68" t="n"/>
       <c r="P880" s="61" t="n"/>
       <c r="Q880" s="61" t="n"/>
+      <c r="R880" s="89" t="n"/>
     </row>
     <row r="881" ht="12.75" customHeight="1" s="69">
       <c r="F881" s="65" t="n"/>
@@ -12254,6 +13148,7 @@
       <c r="O881" s="68" t="n"/>
       <c r="P881" s="61" t="n"/>
       <c r="Q881" s="61" t="n"/>
+      <c r="R881" s="89" t="n"/>
     </row>
     <row r="882" ht="12.75" customHeight="1" s="69">
       <c r="F882" s="65" t="n"/>
@@ -12264,6 +13159,7 @@
       <c r="O882" s="68" t="n"/>
       <c r="P882" s="61" t="n"/>
       <c r="Q882" s="61" t="n"/>
+      <c r="R882" s="89" t="n"/>
     </row>
     <row r="883" ht="12.75" customHeight="1" s="69">
       <c r="F883" s="65" t="n"/>
@@ -12274,6 +13170,7 @@
       <c r="O883" s="68" t="n"/>
       <c r="P883" s="61" t="n"/>
       <c r="Q883" s="61" t="n"/>
+      <c r="R883" s="89" t="n"/>
     </row>
     <row r="884" ht="12.75" customHeight="1" s="69">
       <c r="F884" s="65" t="n"/>
@@ -12284,6 +13181,7 @@
       <c r="O884" s="68" t="n"/>
       <c r="P884" s="61" t="n"/>
       <c r="Q884" s="61" t="n"/>
+      <c r="R884" s="89" t="n"/>
     </row>
     <row r="885" ht="12.75" customHeight="1" s="69">
       <c r="F885" s="65" t="n"/>
@@ -12294,6 +13192,7 @@
       <c r="O885" s="68" t="n"/>
       <c r="P885" s="61" t="n"/>
       <c r="Q885" s="61" t="n"/>
+      <c r="R885" s="89" t="n"/>
     </row>
     <row r="886" ht="12.75" customHeight="1" s="69">
       <c r="F886" s="65" t="n"/>
@@ -12304,6 +13203,7 @@
       <c r="O886" s="68" t="n"/>
       <c r="P886" s="61" t="n"/>
       <c r="Q886" s="61" t="n"/>
+      <c r="R886" s="89" t="n"/>
     </row>
     <row r="887" ht="12.75" customHeight="1" s="69">
       <c r="F887" s="65" t="n"/>
@@ -12314,6 +13214,7 @@
       <c r="O887" s="68" t="n"/>
       <c r="P887" s="61" t="n"/>
       <c r="Q887" s="61" t="n"/>
+      <c r="R887" s="89" t="n"/>
     </row>
     <row r="888" ht="12.75" customHeight="1" s="69">
       <c r="F888" s="65" t="n"/>
@@ -12324,6 +13225,7 @@
       <c r="O888" s="68" t="n"/>
       <c r="P888" s="61" t="n"/>
       <c r="Q888" s="61" t="n"/>
+      <c r="R888" s="89" t="n"/>
     </row>
     <row r="889" ht="12.75" customHeight="1" s="69">
       <c r="F889" s="65" t="n"/>
@@ -12334,6 +13236,7 @@
       <c r="O889" s="68" t="n"/>
       <c r="P889" s="61" t="n"/>
       <c r="Q889" s="61" t="n"/>
+      <c r="R889" s="89" t="n"/>
     </row>
     <row r="890" ht="12.75" customHeight="1" s="69">
       <c r="F890" s="65" t="n"/>
@@ -12344,6 +13247,7 @@
       <c r="O890" s="68" t="n"/>
       <c r="P890" s="61" t="n"/>
       <c r="Q890" s="61" t="n"/>
+      <c r="R890" s="89" t="n"/>
     </row>
     <row r="891" ht="12.75" customHeight="1" s="69">
       <c r="F891" s="65" t="n"/>
@@ -12354,6 +13258,7 @@
       <c r="O891" s="68" t="n"/>
       <c r="P891" s="61" t="n"/>
       <c r="Q891" s="61" t="n"/>
+      <c r="R891" s="89" t="n"/>
     </row>
     <row r="892" ht="12.75" customHeight="1" s="69">
       <c r="F892" s="65" t="n"/>
@@ -12364,6 +13269,7 @@
       <c r="O892" s="68" t="n"/>
       <c r="P892" s="61" t="n"/>
       <c r="Q892" s="61" t="n"/>
+      <c r="R892" s="89" t="n"/>
     </row>
     <row r="893" ht="12.75" customHeight="1" s="69">
       <c r="F893" s="65" t="n"/>
@@ -12374,6 +13280,7 @@
       <c r="O893" s="68" t="n"/>
       <c r="P893" s="61" t="n"/>
       <c r="Q893" s="61" t="n"/>
+      <c r="R893" s="89" t="n"/>
     </row>
     <row r="894" ht="12.75" customHeight="1" s="69">
       <c r="F894" s="65" t="n"/>
@@ -12384,6 +13291,7 @@
       <c r="O894" s="68" t="n"/>
       <c r="P894" s="61" t="n"/>
       <c r="Q894" s="61" t="n"/>
+      <c r="R894" s="89" t="n"/>
     </row>
     <row r="895" ht="12.75" customHeight="1" s="69">
       <c r="F895" s="65" t="n"/>
@@ -12394,6 +13302,7 @@
       <c r="O895" s="68" t="n"/>
       <c r="P895" s="61" t="n"/>
       <c r="Q895" s="61" t="n"/>
+      <c r="R895" s="89" t="n"/>
     </row>
     <row r="896" ht="12.75" customHeight="1" s="69">
       <c r="F896" s="65" t="n"/>
@@ -12404,6 +13313,7 @@
       <c r="O896" s="68" t="n"/>
       <c r="P896" s="61" t="n"/>
       <c r="Q896" s="61" t="n"/>
+      <c r="R896" s="89" t="n"/>
     </row>
     <row r="897" ht="12.75" customHeight="1" s="69">
       <c r="F897" s="65" t="n"/>
@@ -12414,6 +13324,7 @@
       <c r="O897" s="68" t="n"/>
       <c r="P897" s="61" t="n"/>
       <c r="Q897" s="61" t="n"/>
+      <c r="R897" s="89" t="n"/>
     </row>
     <row r="898" ht="12.75" customHeight="1" s="69">
       <c r="F898" s="65" t="n"/>
@@ -12424,6 +13335,7 @@
       <c r="O898" s="68" t="n"/>
       <c r="P898" s="61" t="n"/>
       <c r="Q898" s="61" t="n"/>
+      <c r="R898" s="89" t="n"/>
     </row>
     <row r="899" ht="12.75" customHeight="1" s="69">
       <c r="F899" s="65" t="n"/>
@@ -12434,6 +13346,7 @@
       <c r="O899" s="68" t="n"/>
       <c r="P899" s="61" t="n"/>
       <c r="Q899" s="61" t="n"/>
+      <c r="R899" s="89" t="n"/>
     </row>
     <row r="900" ht="12.75" customHeight="1" s="69">
       <c r="F900" s="65" t="n"/>
@@ -12444,6 +13357,7 @@
       <c r="O900" s="68" t="n"/>
       <c r="P900" s="61" t="n"/>
       <c r="Q900" s="61" t="n"/>
+      <c r="R900" s="89" t="n"/>
     </row>
     <row r="901" ht="12.75" customHeight="1" s="69">
       <c r="F901" s="65" t="n"/>
@@ -12454,6 +13368,7 @@
       <c r="O901" s="68" t="n"/>
       <c r="P901" s="61" t="n"/>
       <c r="Q901" s="61" t="n"/>
+      <c r="R901" s="89" t="n"/>
     </row>
     <row r="902" ht="12.75" customHeight="1" s="69">
       <c r="F902" s="65" t="n"/>
@@ -12464,6 +13379,7 @@
       <c r="O902" s="68" t="n"/>
       <c r="P902" s="61" t="n"/>
       <c r="Q902" s="61" t="n"/>
+      <c r="R902" s="89" t="n"/>
     </row>
     <row r="903" ht="12.75" customHeight="1" s="69">
       <c r="F903" s="65" t="n"/>
@@ -12474,6 +13390,7 @@
       <c r="O903" s="68" t="n"/>
       <c r="P903" s="61" t="n"/>
       <c r="Q903" s="61" t="n"/>
+      <c r="R903" s="89" t="n"/>
     </row>
     <row r="904" ht="12.75" customHeight="1" s="69">
       <c r="F904" s="65" t="n"/>
@@ -12484,6 +13401,7 @@
       <c r="O904" s="68" t="n"/>
       <c r="P904" s="61" t="n"/>
       <c r="Q904" s="61" t="n"/>
+      <c r="R904" s="89" t="n"/>
     </row>
     <row r="905" ht="12.75" customHeight="1" s="69">
       <c r="F905" s="65" t="n"/>
@@ -12494,6 +13412,7 @@
       <c r="O905" s="68" t="n"/>
       <c r="P905" s="61" t="n"/>
       <c r="Q905" s="61" t="n"/>
+      <c r="R905" s="89" t="n"/>
     </row>
     <row r="906" ht="12.75" customHeight="1" s="69">
       <c r="F906" s="65" t="n"/>
@@ -12504,6 +13423,7 @@
       <c r="O906" s="68" t="n"/>
       <c r="P906" s="61" t="n"/>
       <c r="Q906" s="61" t="n"/>
+      <c r="R906" s="89" t="n"/>
     </row>
     <row r="907" ht="12.75" customHeight="1" s="69">
       <c r="F907" s="65" t="n"/>
@@ -12514,6 +13434,7 @@
       <c r="O907" s="68" t="n"/>
       <c r="P907" s="61" t="n"/>
       <c r="Q907" s="61" t="n"/>
+      <c r="R907" s="89" t="n"/>
     </row>
     <row r="908" ht="12.75" customHeight="1" s="69">
       <c r="F908" s="65" t="n"/>
@@ -12524,6 +13445,7 @@
       <c r="O908" s="68" t="n"/>
       <c r="P908" s="61" t="n"/>
       <c r="Q908" s="61" t="n"/>
+      <c r="R908" s="89" t="n"/>
     </row>
     <row r="909" ht="12.75" customHeight="1" s="69">
       <c r="F909" s="65" t="n"/>
@@ -12534,6 +13456,7 @@
       <c r="O909" s="68" t="n"/>
       <c r="P909" s="61" t="n"/>
       <c r="Q909" s="61" t="n"/>
+      <c r="R909" s="89" t="n"/>
     </row>
     <row r="910" ht="12.75" customHeight="1" s="69">
       <c r="F910" s="65" t="n"/>
@@ -12544,6 +13467,7 @@
       <c r="O910" s="68" t="n"/>
       <c r="P910" s="61" t="n"/>
       <c r="Q910" s="61" t="n"/>
+      <c r="R910" s="89" t="n"/>
     </row>
     <row r="911" ht="12.75" customHeight="1" s="69">
       <c r="F911" s="65" t="n"/>
@@ -12554,6 +13478,7 @@
       <c r="O911" s="68" t="n"/>
       <c r="P911" s="61" t="n"/>
       <c r="Q911" s="61" t="n"/>
+      <c r="R911" s="89" t="n"/>
     </row>
     <row r="912" ht="12.75" customHeight="1" s="69">
       <c r="F912" s="65" t="n"/>
@@ -12564,6 +13489,7 @@
       <c r="O912" s="68" t="n"/>
       <c r="P912" s="61" t="n"/>
       <c r="Q912" s="61" t="n"/>
+      <c r="R912" s="89" t="n"/>
     </row>
     <row r="913" ht="12.75" customHeight="1" s="69">
       <c r="F913" s="65" t="n"/>
@@ -12574,6 +13500,7 @@
       <c r="O913" s="68" t="n"/>
       <c r="P913" s="61" t="n"/>
       <c r="Q913" s="61" t="n"/>
+      <c r="R913" s="89" t="n"/>
     </row>
     <row r="914" ht="12.75" customHeight="1" s="69">
       <c r="F914" s="65" t="n"/>
@@ -12584,6 +13511,7 @@
       <c r="O914" s="68" t="n"/>
       <c r="P914" s="61" t="n"/>
       <c r="Q914" s="61" t="n"/>
+      <c r="R914" s="89" t="n"/>
     </row>
     <row r="915" ht="12.75" customHeight="1" s="69">
       <c r="F915" s="65" t="n"/>
@@ -12594,6 +13522,7 @@
       <c r="O915" s="68" t="n"/>
       <c r="P915" s="61" t="n"/>
       <c r="Q915" s="61" t="n"/>
+      <c r="R915" s="89" t="n"/>
     </row>
     <row r="916" ht="12.75" customHeight="1" s="69">
       <c r="F916" s="65" t="n"/>
@@ -12604,6 +13533,7 @@
       <c r="O916" s="68" t="n"/>
       <c r="P916" s="61" t="n"/>
       <c r="Q916" s="61" t="n"/>
+      <c r="R916" s="89" t="n"/>
     </row>
     <row r="917" ht="12.75" customHeight="1" s="69">
       <c r="F917" s="65" t="n"/>
@@ -12614,6 +13544,7 @@
       <c r="O917" s="68" t="n"/>
       <c r="P917" s="61" t="n"/>
       <c r="Q917" s="61" t="n"/>
+      <c r="R917" s="89" t="n"/>
     </row>
     <row r="918" ht="12.75" customHeight="1" s="69">
       <c r="F918" s="65" t="n"/>
@@ -12624,6 +13555,7 @@
       <c r="O918" s="68" t="n"/>
       <c r="P918" s="61" t="n"/>
       <c r="Q918" s="61" t="n"/>
+      <c r="R918" s="89" t="n"/>
     </row>
     <row r="919" ht="12.75" customHeight="1" s="69">
       <c r="F919" s="65" t="n"/>
@@ -12634,6 +13566,7 @@
       <c r="O919" s="68" t="n"/>
       <c r="P919" s="61" t="n"/>
       <c r="Q919" s="61" t="n"/>
+      <c r="R919" s="89" t="n"/>
     </row>
     <row r="920" ht="12.75" customHeight="1" s="69">
       <c r="F920" s="65" t="n"/>
@@ -12644,6 +13577,7 @@
       <c r="O920" s="68" t="n"/>
       <c r="P920" s="61" t="n"/>
       <c r="Q920" s="61" t="n"/>
+      <c r="R920" s="89" t="n"/>
     </row>
     <row r="921" ht="12.75" customHeight="1" s="69">
       <c r="F921" s="65" t="n"/>
@@ -12654,6 +13588,7 @@
       <c r="O921" s="68" t="n"/>
       <c r="P921" s="61" t="n"/>
       <c r="Q921" s="61" t="n"/>
+      <c r="R921" s="89" t="n"/>
     </row>
     <row r="922" ht="12.75" customHeight="1" s="69">
       <c r="F922" s="65" t="n"/>
@@ -12664,6 +13599,7 @@
       <c r="O922" s="68" t="n"/>
       <c r="P922" s="61" t="n"/>
       <c r="Q922" s="61" t="n"/>
+      <c r="R922" s="89" t="n"/>
     </row>
     <row r="923" ht="12.75" customHeight="1" s="69">
       <c r="F923" s="65" t="n"/>
@@ -12674,6 +13610,7 @@
       <c r="O923" s="68" t="n"/>
       <c r="P923" s="61" t="n"/>
       <c r="Q923" s="61" t="n"/>
+      <c r="R923" s="89" t="n"/>
     </row>
     <row r="924" ht="12.75" customHeight="1" s="69">
       <c r="F924" s="65" t="n"/>
@@ -12684,6 +13621,7 @@
       <c r="O924" s="68" t="n"/>
       <c r="P924" s="61" t="n"/>
       <c r="Q924" s="61" t="n"/>
+      <c r="R924" s="89" t="n"/>
     </row>
     <row r="925" ht="12.75" customHeight="1" s="69">
       <c r="F925" s="65" t="n"/>
@@ -12694,6 +13632,7 @@
       <c r="O925" s="68" t="n"/>
       <c r="P925" s="61" t="n"/>
       <c r="Q925" s="61" t="n"/>
+      <c r="R925" s="89" t="n"/>
     </row>
     <row r="926" ht="12.75" customHeight="1" s="69">
       <c r="F926" s="65" t="n"/>
@@ -12704,6 +13643,7 @@
       <c r="O926" s="68" t="n"/>
       <c r="P926" s="61" t="n"/>
       <c r="Q926" s="61" t="n"/>
+      <c r="R926" s="89" t="n"/>
     </row>
     <row r="927" ht="12.75" customHeight="1" s="69">
       <c r="F927" s="65" t="n"/>
@@ -12714,6 +13654,7 @@
       <c r="O927" s="68" t="n"/>
       <c r="P927" s="61" t="n"/>
       <c r="Q927" s="61" t="n"/>
+      <c r="R927" s="89" t="n"/>
     </row>
     <row r="928" ht="12.75" customHeight="1" s="69">
       <c r="F928" s="65" t="n"/>
@@ -12724,6 +13665,7 @@
       <c r="O928" s="68" t="n"/>
       <c r="P928" s="61" t="n"/>
       <c r="Q928" s="61" t="n"/>
+      <c r="R928" s="89" t="n"/>
     </row>
     <row r="929" ht="12.75" customHeight="1" s="69">
       <c r="F929" s="65" t="n"/>
@@ -12734,6 +13676,7 @@
       <c r="O929" s="68" t="n"/>
       <c r="P929" s="61" t="n"/>
       <c r="Q929" s="61" t="n"/>
+      <c r="R929" s="89" t="n"/>
     </row>
     <row r="930" ht="12.75" customHeight="1" s="69">
       <c r="F930" s="65" t="n"/>
@@ -12744,6 +13687,7 @@
       <c r="O930" s="68" t="n"/>
       <c r="P930" s="61" t="n"/>
       <c r="Q930" s="61" t="n"/>
+      <c r="R930" s="89" t="n"/>
     </row>
     <row r="931" ht="12.75" customHeight="1" s="69">
       <c r="F931" s="65" t="n"/>
@@ -12754,6 +13698,7 @@
       <c r="O931" s="68" t="n"/>
       <c r="P931" s="61" t="n"/>
       <c r="Q931" s="61" t="n"/>
+      <c r="R931" s="89" t="n"/>
     </row>
     <row r="932" ht="12.75" customHeight="1" s="69">
       <c r="F932" s="65" t="n"/>
@@ -12764,6 +13709,7 @@
       <c r="O932" s="68" t="n"/>
       <c r="P932" s="61" t="n"/>
       <c r="Q932" s="61" t="n"/>
+      <c r="R932" s="89" t="n"/>
     </row>
     <row r="933" ht="12.75" customHeight="1" s="69">
       <c r="F933" s="65" t="n"/>
@@ -12774,6 +13720,7 @@
       <c r="O933" s="68" t="n"/>
       <c r="P933" s="61" t="n"/>
       <c r="Q933" s="61" t="n"/>
+      <c r="R933" s="89" t="n"/>
     </row>
     <row r="934" ht="12.75" customHeight="1" s="69">
       <c r="F934" s="65" t="n"/>
@@ -12784,6 +13731,7 @@
       <c r="O934" s="68" t="n"/>
       <c r="P934" s="61" t="n"/>
       <c r="Q934" s="61" t="n"/>
+      <c r="R934" s="89" t="n"/>
     </row>
     <row r="935" ht="12.75" customHeight="1" s="69">
       <c r="F935" s="65" t="n"/>
@@ -12794,6 +13742,7 @@
       <c r="O935" s="68" t="n"/>
       <c r="P935" s="61" t="n"/>
       <c r="Q935" s="61" t="n"/>
+      <c r="R935" s="89" t="n"/>
     </row>
     <row r="936" ht="12.75" customHeight="1" s="69">
       <c r="F936" s="65" t="n"/>
@@ -12804,6 +13753,7 @@
       <c r="O936" s="68" t="n"/>
       <c r="P936" s="61" t="n"/>
       <c r="Q936" s="61" t="n"/>
+      <c r="R936" s="89" t="n"/>
     </row>
     <row r="937" ht="12.75" customHeight="1" s="69">
       <c r="F937" s="65" t="n"/>
@@ -12814,6 +13764,7 @@
       <c r="O937" s="68" t="n"/>
       <c r="P937" s="61" t="n"/>
       <c r="Q937" s="61" t="n"/>
+      <c r="R937" s="89" t="n"/>
     </row>
     <row r="938" ht="12.75" customHeight="1" s="69">
       <c r="F938" s="65" t="n"/>
@@ -12824,6 +13775,7 @@
       <c r="O938" s="68" t="n"/>
       <c r="P938" s="61" t="n"/>
       <c r="Q938" s="61" t="n"/>
+      <c r="R938" s="89" t="n"/>
     </row>
     <row r="939" ht="12.75" customHeight="1" s="69">
       <c r="F939" s="65" t="n"/>
@@ -12834,6 +13786,7 @@
       <c r="O939" s="68" t="n"/>
       <c r="P939" s="61" t="n"/>
       <c r="Q939" s="61" t="n"/>
+      <c r="R939" s="89" t="n"/>
     </row>
     <row r="940" ht="12.75" customHeight="1" s="69">
       <c r="F940" s="65" t="n"/>
@@ -12844,6 +13797,7 @@
       <c r="O940" s="68" t="n"/>
       <c r="P940" s="61" t="n"/>
       <c r="Q940" s="61" t="n"/>
+      <c r="R940" s="89" t="n"/>
     </row>
     <row r="941" ht="12.75" customHeight="1" s="69">
       <c r="F941" s="65" t="n"/>
@@ -12854,6 +13808,7 @@
       <c r="O941" s="68" t="n"/>
       <c r="P941" s="61" t="n"/>
       <c r="Q941" s="61" t="n"/>
+      <c r="R941" s="89" t="n"/>
     </row>
     <row r="942" ht="12.75" customHeight="1" s="69">
       <c r="F942" s="65" t="n"/>
@@ -12864,6 +13819,7 @@
       <c r="O942" s="68" t="n"/>
       <c r="P942" s="61" t="n"/>
       <c r="Q942" s="61" t="n"/>
+      <c r="R942" s="89" t="n"/>
     </row>
     <row r="943" ht="12.75" customHeight="1" s="69">
       <c r="F943" s="65" t="n"/>
@@ -12874,6 +13830,7 @@
       <c r="O943" s="68" t="n"/>
       <c r="P943" s="61" t="n"/>
       <c r="Q943" s="61" t="n"/>
+      <c r="R943" s="89" t="n"/>
     </row>
     <row r="944" ht="12.75" customHeight="1" s="69">
       <c r="F944" s="65" t="n"/>
@@ -12884,6 +13841,7 @@
       <c r="O944" s="68" t="n"/>
       <c r="P944" s="61" t="n"/>
       <c r="Q944" s="61" t="n"/>
+      <c r="R944" s="89" t="n"/>
     </row>
     <row r="945" ht="12.75" customHeight="1" s="69">
       <c r="F945" s="65" t="n"/>
@@ -12894,6 +13852,7 @@
       <c r="O945" s="68" t="n"/>
       <c r="P945" s="61" t="n"/>
       <c r="Q945" s="61" t="n"/>
+      <c r="R945" s="89" t="n"/>
     </row>
     <row r="946" ht="12.75" customHeight="1" s="69">
       <c r="F946" s="65" t="n"/>
@@ -12904,6 +13863,7 @@
       <c r="O946" s="68" t="n"/>
       <c r="P946" s="61" t="n"/>
       <c r="Q946" s="61" t="n"/>
+      <c r="R946" s="89" t="n"/>
     </row>
     <row r="947" ht="12.75" customHeight="1" s="69">
       <c r="F947" s="65" t="n"/>
@@ -12914,6 +13874,7 @@
       <c r="O947" s="68" t="n"/>
       <c r="P947" s="61" t="n"/>
       <c r="Q947" s="61" t="n"/>
+      <c r="R947" s="89" t="n"/>
     </row>
     <row r="948" ht="12.75" customHeight="1" s="69">
       <c r="F948" s="65" t="n"/>
@@ -12924,6 +13885,7 @@
       <c r="O948" s="68" t="n"/>
       <c r="P948" s="61" t="n"/>
       <c r="Q948" s="61" t="n"/>
+      <c r="R948" s="89" t="n"/>
     </row>
     <row r="949" ht="12.75" customHeight="1" s="69">
       <c r="F949" s="65" t="n"/>
@@ -12934,6 +13896,7 @@
       <c r="O949" s="68" t="n"/>
       <c r="P949" s="61" t="n"/>
       <c r="Q949" s="61" t="n"/>
+      <c r="R949" s="89" t="n"/>
     </row>
     <row r="950" ht="12.75" customHeight="1" s="69">
       <c r="F950" s="65" t="n"/>
@@ -12944,6 +13907,7 @@
       <c r="O950" s="68" t="n"/>
       <c r="P950" s="61" t="n"/>
       <c r="Q950" s="61" t="n"/>
+      <c r="R950" s="89" t="n"/>
     </row>
     <row r="951" ht="12.75" customHeight="1" s="69">
       <c r="F951" s="65" t="n"/>
@@ -12954,6 +13918,7 @@
       <c r="O951" s="68" t="n"/>
       <c r="P951" s="61" t="n"/>
       <c r="Q951" s="61" t="n"/>
+      <c r="R951" s="89" t="n"/>
     </row>
     <row r="952" ht="12.75" customHeight="1" s="69">
       <c r="F952" s="65" t="n"/>
@@ -12964,6 +13929,7 @@
       <c r="O952" s="68" t="n"/>
       <c r="P952" s="61" t="n"/>
       <c r="Q952" s="61" t="n"/>
+      <c r="R952" s="89" t="n"/>
     </row>
     <row r="953" ht="12.75" customHeight="1" s="69">
       <c r="F953" s="65" t="n"/>
@@ -12974,6 +13940,7 @@
       <c r="O953" s="68" t="n"/>
       <c r="P953" s="61" t="n"/>
       <c r="Q953" s="61" t="n"/>
+      <c r="R953" s="89" t="n"/>
     </row>
     <row r="954" ht="12.75" customHeight="1" s="69">
       <c r="F954" s="65" t="n"/>
@@ -12984,6 +13951,7 @@
       <c r="O954" s="68" t="n"/>
       <c r="P954" s="61" t="n"/>
       <c r="Q954" s="61" t="n"/>
+      <c r="R954" s="89" t="n"/>
     </row>
     <row r="955" ht="12.75" customHeight="1" s="69">
       <c r="F955" s="65" t="n"/>
@@ -12994,6 +13962,7 @@
       <c r="O955" s="68" t="n"/>
       <c r="P955" s="61" t="n"/>
       <c r="Q955" s="61" t="n"/>
+      <c r="R955" s="89" t="n"/>
     </row>
     <row r="956" ht="12.75" customHeight="1" s="69">
       <c r="F956" s="65" t="n"/>
@@ -13004,6 +13973,7 @@
       <c r="O956" s="68" t="n"/>
       <c r="P956" s="61" t="n"/>
       <c r="Q956" s="61" t="n"/>
+      <c r="R956" s="89" t="n"/>
     </row>
     <row r="957" ht="12.75" customHeight="1" s="69">
       <c r="F957" s="65" t="n"/>
@@ -13014,6 +13984,7 @@
       <c r="O957" s="68" t="n"/>
       <c r="P957" s="61" t="n"/>
       <c r="Q957" s="61" t="n"/>
+      <c r="R957" s="89" t="n"/>
     </row>
     <row r="958" ht="12.75" customHeight="1" s="69">
       <c r="F958" s="65" t="n"/>
@@ -13024,6 +13995,7 @@
       <c r="O958" s="68" t="n"/>
       <c r="P958" s="61" t="n"/>
       <c r="Q958" s="61" t="n"/>
+      <c r="R958" s="89" t="n"/>
     </row>
     <row r="959" ht="12.75" customHeight="1" s="69">
       <c r="F959" s="65" t="n"/>
@@ -13034,6 +14006,7 @@
       <c r="O959" s="68" t="n"/>
       <c r="P959" s="61" t="n"/>
       <c r="Q959" s="61" t="n"/>
+      <c r="R959" s="89" t="n"/>
     </row>
     <row r="960" ht="12.75" customHeight="1" s="69">
       <c r="F960" s="65" t="n"/>
@@ -13044,6 +14017,7 @@
       <c r="O960" s="68" t="n"/>
       <c r="P960" s="61" t="n"/>
       <c r="Q960" s="61" t="n"/>
+      <c r="R960" s="89" t="n"/>
     </row>
     <row r="961" ht="12.75" customHeight="1" s="69">
       <c r="F961" s="65" t="n"/>
@@ -13054,6 +14028,7 @@
       <c r="O961" s="68" t="n"/>
       <c r="P961" s="61" t="n"/>
       <c r="Q961" s="61" t="n"/>
+      <c r="R961" s="89" t="n"/>
     </row>
     <row r="962" ht="12.75" customHeight="1" s="69">
       <c r="F962" s="65" t="n"/>
@@ -13064,6 +14039,7 @@
       <c r="O962" s="68" t="n"/>
       <c r="P962" s="61" t="n"/>
       <c r="Q962" s="61" t="n"/>
+      <c r="R962" s="89" t="n"/>
     </row>
     <row r="963" ht="12.75" customHeight="1" s="69">
       <c r="F963" s="65" t="n"/>
@@ -13074,6 +14050,7 @@
       <c r="O963" s="68" t="n"/>
       <c r="P963" s="61" t="n"/>
       <c r="Q963" s="61" t="n"/>
+      <c r="R963" s="89" t="n"/>
     </row>
     <row r="964" ht="12.75" customHeight="1" s="69">
       <c r="F964" s="65" t="n"/>
@@ -13084,6 +14061,7 @@
       <c r="O964" s="68" t="n"/>
       <c r="P964" s="61" t="n"/>
       <c r="Q964" s="61" t="n"/>
+      <c r="R964" s="89" t="n"/>
     </row>
     <row r="965" ht="12.75" customHeight="1" s="69">
       <c r="F965" s="65" t="n"/>
@@ -13094,6 +14072,7 @@
       <c r="O965" s="68" t="n"/>
       <c r="P965" s="61" t="n"/>
       <c r="Q965" s="61" t="n"/>
+      <c r="R965" s="89" t="n"/>
     </row>
     <row r="966" ht="12.75" customHeight="1" s="69">
       <c r="F966" s="65" t="n"/>
@@ -13104,6 +14083,7 @@
       <c r="O966" s="68" t="n"/>
       <c r="P966" s="61" t="n"/>
       <c r="Q966" s="61" t="n"/>
+      <c r="R966" s="89" t="n"/>
     </row>
     <row r="967" ht="12.75" customHeight="1" s="69">
       <c r="F967" s="65" t="n"/>
@@ -13114,6 +14094,7 @@
       <c r="O967" s="68" t="n"/>
       <c r="P967" s="61" t="n"/>
       <c r="Q967" s="61" t="n"/>
+      <c r="R967" s="89" t="n"/>
     </row>
     <row r="968" ht="12.75" customHeight="1" s="69">
       <c r="F968" s="65" t="n"/>
@@ -13124,6 +14105,7 @@
       <c r="O968" s="68" t="n"/>
       <c r="P968" s="61" t="n"/>
       <c r="Q968" s="61" t="n"/>
+      <c r="R968" s="89" t="n"/>
     </row>
     <row r="969" ht="12.75" customHeight="1" s="69">
       <c r="F969" s="65" t="n"/>
@@ -13134,6 +14116,7 @@
       <c r="O969" s="68" t="n"/>
       <c r="P969" s="61" t="n"/>
       <c r="Q969" s="61" t="n"/>
+      <c r="R969" s="89" t="n"/>
     </row>
     <row r="970" ht="12.75" customHeight="1" s="69">
       <c r="F970" s="65" t="n"/>
@@ -13144,6 +14127,7 @@
       <c r="O970" s="68" t="n"/>
       <c r="P970" s="61" t="n"/>
       <c r="Q970" s="61" t="n"/>
+      <c r="R970" s="89" t="n"/>
     </row>
     <row r="971" ht="12.75" customHeight="1" s="69">
       <c r="F971" s="65" t="n"/>
@@ -13154,6 +14138,7 @@
       <c r="O971" s="68" t="n"/>
       <c r="P971" s="61" t="n"/>
       <c r="Q971" s="61" t="n"/>
+      <c r="R971" s="89" t="n"/>
     </row>
     <row r="972" ht="12.75" customHeight="1" s="69">
       <c r="F972" s="65" t="n"/>
@@ -13164,6 +14149,7 @@
       <c r="O972" s="68" t="n"/>
       <c r="P972" s="61" t="n"/>
       <c r="Q972" s="61" t="n"/>
+      <c r="R972" s="89" t="n"/>
     </row>
     <row r="973" ht="12.75" customHeight="1" s="69">
       <c r="F973" s="65" t="n"/>
@@ -13174,6 +14160,7 @@
       <c r="O973" s="68" t="n"/>
       <c r="P973" s="61" t="n"/>
       <c r="Q973" s="61" t="n"/>
+      <c r="R973" s="89" t="n"/>
     </row>
     <row r="974" ht="12.75" customHeight="1" s="69">
       <c r="F974" s="65" t="n"/>
@@ -13184,6 +14171,7 @@
       <c r="O974" s="68" t="n"/>
       <c r="P974" s="61" t="n"/>
       <c r="Q974" s="61" t="n"/>
+      <c r="R974" s="89" t="n"/>
     </row>
     <row r="975" ht="12.75" customHeight="1" s="69">
       <c r="F975" s="65" t="n"/>
@@ -13194,6 +14182,7 @@
       <c r="O975" s="68" t="n"/>
       <c r="P975" s="61" t="n"/>
       <c r="Q975" s="61" t="n"/>
+      <c r="R975" s="89" t="n"/>
     </row>
     <row r="976" ht="12.75" customHeight="1" s="69">
       <c r="F976" s="65" t="n"/>
@@ -13204,6 +14193,7 @@
       <c r="O976" s="68" t="n"/>
       <c r="P976" s="61" t="n"/>
       <c r="Q976" s="61" t="n"/>
+      <c r="R976" s="89" t="n"/>
     </row>
     <row r="977" ht="12.75" customHeight="1" s="69">
       <c r="F977" s="65" t="n"/>
@@ -13214,6 +14204,7 @@
       <c r="O977" s="68" t="n"/>
       <c r="P977" s="61" t="n"/>
       <c r="Q977" s="61" t="n"/>
+      <c r="R977" s="89" t="n"/>
     </row>
     <row r="978" ht="12.75" customHeight="1" s="69">
       <c r="F978" s="65" t="n"/>
@@ -13224,6 +14215,7 @@
       <c r="O978" s="68" t="n"/>
       <c r="P978" s="61" t="n"/>
       <c r="Q978" s="61" t="n"/>
+      <c r="R978" s="89" t="n"/>
     </row>
     <row r="979" ht="12.75" customHeight="1" s="69">
       <c r="F979" s="65" t="n"/>
@@ -13234,6 +14226,7 @@
       <c r="O979" s="68" t="n"/>
       <c r="P979" s="61" t="n"/>
       <c r="Q979" s="61" t="n"/>
+      <c r="R979" s="89" t="n"/>
     </row>
     <row r="980" ht="12.75" customHeight="1" s="69">
       <c r="F980" s="65" t="n"/>
@@ -13244,6 +14237,7 @@
       <c r="O980" s="68" t="n"/>
       <c r="P980" s="61" t="n"/>
       <c r="Q980" s="61" t="n"/>
+      <c r="R980" s="89" t="n"/>
     </row>
     <row r="981" ht="12.75" customHeight="1" s="69">
       <c r="F981" s="65" t="n"/>
@@ -13254,6 +14248,7 @@
       <c r="O981" s="68" t="n"/>
       <c r="P981" s="61" t="n"/>
       <c r="Q981" s="61" t="n"/>
+      <c r="R981" s="89" t="n"/>
     </row>
     <row r="982" ht="12.75" customHeight="1" s="69">
       <c r="F982" s="65" t="n"/>
@@ -13264,6 +14259,7 @@
       <c r="O982" s="68" t="n"/>
       <c r="P982" s="61" t="n"/>
       <c r="Q982" s="61" t="n"/>
+      <c r="R982" s="89" t="n"/>
     </row>
     <row r="983" ht="12.75" customHeight="1" s="69">
       <c r="F983" s="65" t="n"/>
@@ -13274,6 +14270,7 @@
       <c r="O983" s="68" t="n"/>
       <c r="P983" s="61" t="n"/>
       <c r="Q983" s="61" t="n"/>
+      <c r="R983" s="89" t="n"/>
     </row>
     <row r="984" ht="12.75" customHeight="1" s="69">
       <c r="F984" s="65" t="n"/>
@@ -13284,6 +14281,7 @@
       <c r="O984" s="68" t="n"/>
       <c r="P984" s="61" t="n"/>
       <c r="Q984" s="61" t="n"/>
+      <c r="R984" s="89" t="n"/>
     </row>
     <row r="985" ht="12.75" customHeight="1" s="69">
       <c r="F985" s="65" t="n"/>
@@ -13294,6 +14292,7 @@
       <c r="O985" s="68" t="n"/>
       <c r="P985" s="61" t="n"/>
       <c r="Q985" s="61" t="n"/>
+      <c r="R985" s="89" t="n"/>
     </row>
     <row r="986" ht="12.75" customHeight="1" s="69">
       <c r="F986" s="65" t="n"/>
@@ -13304,6 +14303,7 @@
       <c r="O986" s="68" t="n"/>
       <c r="P986" s="61" t="n"/>
       <c r="Q986" s="61" t="n"/>
+      <c r="R986" s="89" t="n"/>
     </row>
     <row r="987" ht="12.75" customHeight="1" s="69">
       <c r="F987" s="65" t="n"/>
@@ -13314,6 +14314,7 @@
       <c r="O987" s="68" t="n"/>
       <c r="P987" s="61" t="n"/>
       <c r="Q987" s="61" t="n"/>
+      <c r="R987" s="89" t="n"/>
     </row>
     <row r="988" ht="12.75" customHeight="1" s="69">
       <c r="F988" s="65" t="n"/>
@@ -13324,6 +14325,7 @@
       <c r="O988" s="68" t="n"/>
       <c r="P988" s="61" t="n"/>
       <c r="Q988" s="61" t="n"/>
+      <c r="R988" s="89" t="n"/>
     </row>
     <row r="989" ht="12.75" customHeight="1" s="69">
       <c r="F989" s="65" t="n"/>
@@ -13334,6 +14336,7 @@
       <c r="O989" s="68" t="n"/>
       <c r="P989" s="61" t="n"/>
       <c r="Q989" s="61" t="n"/>
+      <c r="R989" s="89" t="n"/>
     </row>
     <row r="990" ht="12.75" customHeight="1" s="69">
       <c r="F990" s="65" t="n"/>
@@ -13344,6 +14347,7 @@
       <c r="O990" s="68" t="n"/>
       <c r="P990" s="61" t="n"/>
       <c r="Q990" s="61" t="n"/>
+      <c r="R990" s="89" t="n"/>
     </row>
     <row r="991" ht="12.75" customHeight="1" s="69">
       <c r="F991" s="65" t="n"/>
@@ -13354,6 +14358,7 @@
       <c r="O991" s="68" t="n"/>
       <c r="P991" s="61" t="n"/>
       <c r="Q991" s="61" t="n"/>
+      <c r="R991" s="89" t="n"/>
     </row>
     <row r="992" ht="12.75" customHeight="1" s="69">
       <c r="F992" s="65" t="n"/>
@@ -13364,6 +14369,7 @@
       <c r="O992" s="68" t="n"/>
       <c r="P992" s="61" t="n"/>
       <c r="Q992" s="61" t="n"/>
+      <c r="R992" s="89" t="n"/>
     </row>
     <row r="993" ht="12.75" customHeight="1" s="69">
       <c r="F993" s="65" t="n"/>
@@ -13374,6 +14380,7 @@
       <c r="O993" s="68" t="n"/>
       <c r="P993" s="61" t="n"/>
       <c r="Q993" s="61" t="n"/>
+      <c r="R993" s="89" t="n"/>
     </row>
     <row r="994" ht="12.75" customHeight="1" s="69">
       <c r="F994" s="65" t="n"/>
@@ -13384,6 +14391,7 @@
       <c r="O994" s="68" t="n"/>
       <c r="P994" s="61" t="n"/>
       <c r="Q994" s="61" t="n"/>
+      <c r="R994" s="89" t="n"/>
     </row>
     <row r="995" ht="12.75" customHeight="1" s="69">
       <c r="F995" s="65" t="n"/>
@@ -13394,6 +14402,7 @@
       <c r="O995" s="68" t="n"/>
       <c r="P995" s="61" t="n"/>
       <c r="Q995" s="61" t="n"/>
+      <c r="R995" s="89" t="n"/>
     </row>
     <row r="996" ht="12.75" customHeight="1" s="69">
       <c r="F996" s="65" t="n"/>
@@ -13404,6 +14413,7 @@
       <c r="O996" s="68" t="n"/>
       <c r="P996" s="61" t="n"/>
       <c r="Q996" s="61" t="n"/>
+      <c r="R996" s="89" t="n"/>
     </row>
     <row r="997" ht="12.75" customHeight="1" s="69">
       <c r="F997" s="65" t="n"/>
@@ -13414,6 +14424,7 @@
       <c r="O997" s="68" t="n"/>
       <c r="P997" s="61" t="n"/>
       <c r="Q997" s="61" t="n"/>
+      <c r="R997" s="89" t="n"/>
     </row>
     <row r="998" ht="12.75" customHeight="1" s="69">
       <c r="F998" s="65" t="n"/>
@@ -13424,6 +14435,7 @@
       <c r="O998" s="68" t="n"/>
       <c r="P998" s="61" t="n"/>
       <c r="Q998" s="61" t="n"/>
+      <c r="R998" s="89" t="n"/>
     </row>
     <row r="999" ht="12.75" customHeight="1" s="69">
       <c r="F999" s="65" t="n"/>
@@ -13434,6 +14446,7 @@
       <c r="O999" s="68" t="n"/>
       <c r="P999" s="61" t="n"/>
       <c r="Q999" s="61" t="n"/>
+      <c r="R999" s="89" t="n"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1" s="69">
       <c r="F1000" s="65" t="n"/>
@@ -13444,6 +14457,7 @@
       <c r="O1000" s="68" t="n"/>
       <c r="P1000" s="61" t="n"/>
       <c r="Q1000" s="61" t="n"/>
+      <c r="R1000" s="89" t="n"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1" s="69">
       <c r="F1001" s="65" t="n"/>
@@ -13454,6 +14468,7 @@
       <c r="O1001" s="68" t="n"/>
       <c r="P1001" s="61" t="n"/>
       <c r="Q1001" s="61" t="n"/>
+      <c r="R1001" s="89" t="n"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1" s="69">
       <c r="F1002" s="65" t="n"/>
@@ -13464,6 +14479,7 @@
       <c r="O1002" s="68" t="n"/>
       <c r="P1002" s="61" t="n"/>
       <c r="Q1002" s="61" t="n"/>
+      <c r="R1002" s="89" t="n"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1" s="69">
       <c r="F1003" s="65" t="n"/>
@@ -13474,6 +14490,7 @@
       <c r="O1003" s="68" t="n"/>
       <c r="P1003" s="61" t="n"/>
       <c r="Q1003" s="61" t="n"/>
+      <c r="R1003" s="89" t="n"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1" s="69">
       <c r="F1004" s="65" t="n"/>
@@ -13484,6 +14501,7 @@
       <c r="O1004" s="68" t="n"/>
       <c r="P1004" s="61" t="n"/>
       <c r="Q1004" s="61" t="n"/>
+      <c r="R1004" s="89" t="n"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1" s="69">
       <c r="F1005" s="65" t="n"/>
@@ -13494,6 +14512,7 @@
       <c r="O1005" s="68" t="n"/>
       <c r="P1005" s="61" t="n"/>
       <c r="Q1005" s="61" t="n"/>
+      <c r="R1005" s="89" t="n"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1" s="69">
       <c r="F1006" s="65" t="n"/>
@@ -13504,6 +14523,7 @@
       <c r="O1006" s="68" t="n"/>
       <c r="P1006" s="61" t="n"/>
       <c r="Q1006" s="61" t="n"/>
+      <c r="R1006" s="89" t="n"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1" s="69">
       <c r="F1007" s="65" t="n"/>
@@ -13514,6 +14534,7 @@
       <c r="O1007" s="68" t="n"/>
       <c r="P1007" s="61" t="n"/>
       <c r="Q1007" s="61" t="n"/>
+      <c r="R1007" s="89" t="n"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1" s="69">
       <c r="F1008" s="65" t="n"/>
@@ -13524,6 +14545,7 @@
       <c r="O1008" s="68" t="n"/>
       <c r="P1008" s="61" t="n"/>
       <c r="Q1008" s="61" t="n"/>
+      <c r="R1008" s="89" t="n"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1" s="69">
       <c r="F1009" s="65" t="n"/>
@@ -13534,6 +14556,7 @@
       <c r="O1009" s="68" t="n"/>
       <c r="P1009" s="61" t="n"/>
       <c r="Q1009" s="61" t="n"/>
+      <c r="R1009" s="89" t="n"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1" s="69">
       <c r="F1010" s="65" t="n"/>
@@ -13544,6 +14567,7 @@
       <c r="O1010" s="68" t="n"/>
       <c r="P1010" s="61" t="n"/>
       <c r="Q1010" s="61" t="n"/>
+      <c r="R1010" s="89" t="n"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1" s="69">
       <c r="F1011" s="65" t="n"/>
@@ -13554,6 +14578,7 @@
       <c r="O1011" s="68" t="n"/>
       <c r="P1011" s="61" t="n"/>
       <c r="Q1011" s="61" t="n"/>
+      <c r="R1011" s="89" t="n"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1" s="69">
       <c r="F1012" s="65" t="n"/>
@@ -13564,6 +14589,7 @@
       <c r="O1012" s="68" t="n"/>
       <c r="P1012" s="61" t="n"/>
       <c r="Q1012" s="61" t="n"/>
+      <c r="R1012" s="89" t="n"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1" s="69">
       <c r="F1013" s="65" t="n"/>
@@ -13574,6 +14600,7 @@
       <c r="O1013" s="68" t="n"/>
       <c r="P1013" s="61" t="n"/>
       <c r="Q1013" s="61" t="n"/>
+      <c r="R1013" s="89" t="n"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1" s="69">
       <c r="F1014" s="65" t="n"/>
@@ -13584,6 +14611,7 @@
       <c r="O1014" s="68" t="n"/>
       <c r="P1014" s="61" t="n"/>
       <c r="Q1014" s="61" t="n"/>
+      <c r="R1014" s="89" t="n"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1" s="69">
       <c r="F1015" s="65" t="n"/>
@@ -13594,6 +14622,7 @@
       <c r="O1015" s="68" t="n"/>
       <c r="P1015" s="61" t="n"/>
       <c r="Q1015" s="61" t="n"/>
+      <c r="R1015" s="89" t="n"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1" s="69">
       <c r="F1016" s="65" t="n"/>
@@ -13604,6 +14633,7 @@
       <c r="O1016" s="68" t="n"/>
       <c r="P1016" s="61" t="n"/>
       <c r="Q1016" s="61" t="n"/>
+      <c r="R1016" s="89" t="n"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1" s="69">
       <c r="F1017" s="65" t="n"/>
@@ -13614,6 +14644,7 @@
       <c r="O1017" s="68" t="n"/>
       <c r="P1017" s="61" t="n"/>
       <c r="Q1017" s="61" t="n"/>
+      <c r="R1017" s="89" t="n"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1" s="69">
       <c r="F1018" s="65" t="n"/>
@@ -13624,6 +14655,7 @@
       <c r="O1018" s="68" t="n"/>
       <c r="P1018" s="61" t="n"/>
       <c r="Q1018" s="61" t="n"/>
+      <c r="R1018" s="89" t="n"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1" s="69">
       <c r="F1019" s="65" t="n"/>
@@ -13634,6 +14666,7 @@
       <c r="O1019" s="68" t="n"/>
       <c r="P1019" s="61" t="n"/>
       <c r="Q1019" s="61" t="n"/>
+      <c r="R1019" s="89" t="n"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1" s="69">
       <c r="F1020" s="65" t="n"/>
@@ -13644,6 +14677,7 @@
       <c r="O1020" s="68" t="n"/>
       <c r="P1020" s="61" t="n"/>
       <c r="Q1020" s="61" t="n"/>
+      <c r="R1020" s="89" t="n"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1" s="69">
       <c r="F1021" s="65" t="n"/>
@@ -13654,6 +14688,7 @@
       <c r="O1021" s="68" t="n"/>
       <c r="P1021" s="61" t="n"/>
       <c r="Q1021" s="61" t="n"/>
+      <c r="R1021" s="89" t="n"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1" s="69">
       <c r="F1022" s="65" t="n"/>
@@ -13664,6 +14699,7 @@
       <c r="O1022" s="68" t="n"/>
       <c r="P1022" s="61" t="n"/>
       <c r="Q1022" s="61" t="n"/>
+      <c r="R1022" s="89" t="n"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1" s="69">
       <c r="F1023" s="65" t="n"/>
@@ -13674,6 +14710,7 @@
       <c r="O1023" s="68" t="n"/>
       <c r="P1023" s="61" t="n"/>
       <c r="Q1023" s="61" t="n"/>
+      <c r="R1023" s="89" t="n"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1" s="69">
       <c r="F1024" s="65" t="n"/>
@@ -13684,6 +14721,7 @@
       <c r="O1024" s="68" t="n"/>
       <c r="P1024" s="61" t="n"/>
       <c r="Q1024" s="61" t="n"/>
+      <c r="R1024" s="89" t="n"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1" s="69">
       <c r="F1025" s="65" t="n"/>
@@ -13694,6 +14732,7 @@
       <c r="O1025" s="68" t="n"/>
       <c r="P1025" s="61" t="n"/>
       <c r="Q1025" s="61" t="n"/>
+      <c r="R1025" s="89" t="n"/>
     </row>
     <row r="1026" ht="12.75" customHeight="1" s="69">
       <c r="F1026" s="65" t="n"/>
@@ -13704,6 +14743,7 @@
       <c r="O1026" s="68" t="n"/>
       <c r="P1026" s="61" t="n"/>
       <c r="Q1026" s="61" t="n"/>
+      <c r="R1026" s="89" t="n"/>
     </row>
     <row r="1027" ht="12.75" customHeight="1" s="69">
       <c r="F1027" s="65" t="n"/>
@@ -13714,6 +14754,7 @@
       <c r="O1027" s="68" t="n"/>
       <c r="P1027" s="61" t="n"/>
       <c r="Q1027" s="61" t="n"/>
+      <c r="R1027" s="89" t="n"/>
     </row>
     <row r="1028" ht="12.75" customHeight="1" s="69">
       <c r="F1028" s="65" t="n"/>
@@ -13724,6 +14765,7 @@
       <c r="O1028" s="68" t="n"/>
       <c r="P1028" s="61" t="n"/>
       <c r="Q1028" s="61" t="n"/>
+      <c r="R1028" s="89" t="n"/>
     </row>
     <row r="1029" ht="12.75" customHeight="1" s="69">
       <c r="F1029" s="65" t="n"/>
@@ -13734,6 +14776,7 @@
       <c r="O1029" s="68" t="n"/>
       <c r="P1029" s="61" t="n"/>
       <c r="Q1029" s="61" t="n"/>
+      <c r="R1029" s="89" t="n"/>
     </row>
     <row r="1030" ht="12.75" customHeight="1" s="69">
       <c r="F1030" s="65" t="n"/>
@@ -13744,6 +14787,7 @@
       <c r="O1030" s="68" t="n"/>
       <c r="P1030" s="61" t="n"/>
       <c r="Q1030" s="61" t="n"/>
+      <c r="R1030" s="89" t="n"/>
     </row>
     <row r="1031" ht="12.75" customHeight="1" s="69">
       <c r="F1031" s="65" t="n"/>
@@ -13754,6 +14798,7 @@
       <c r="O1031" s="68" t="n"/>
       <c r="P1031" s="61" t="n"/>
       <c r="Q1031" s="61" t="n"/>
+      <c r="R1031" s="89" t="n"/>
     </row>
     <row r="1032" ht="12.75" customHeight="1" s="69">
       <c r="F1032" s="65" t="n"/>
@@ -13764,6 +14809,7 @@
       <c r="O1032" s="68" t="n"/>
       <c r="P1032" s="61" t="n"/>
       <c r="Q1032" s="61" t="n"/>
+      <c r="R1032" s="89" t="n"/>
     </row>
     <row r="1033" ht="12.75" customHeight="1" s="69">
       <c r="F1033" s="65" t="n"/>
@@ -13774,6 +14820,7 @@
       <c r="O1033" s="68" t="n"/>
       <c r="P1033" s="61" t="n"/>
       <c r="Q1033" s="61" t="n"/>
+      <c r="R1033" s="89" t="n"/>
     </row>
     <row r="1034" ht="12.75" customHeight="1" s="69">
       <c r="F1034" s="65" t="n"/>
@@ -13784,6 +14831,7 @@
       <c r="O1034" s="68" t="n"/>
       <c r="P1034" s="61" t="n"/>
       <c r="Q1034" s="61" t="n"/>
+      <c r="R1034" s="89" t="n"/>
     </row>
     <row r="1035" ht="12.75" customHeight="1" s="69">
       <c r="F1035" s="65" t="n"/>
@@ -13794,6 +14842,7 @@
       <c r="O1035" s="68" t="n"/>
       <c r="P1035" s="61" t="n"/>
       <c r="Q1035" s="61" t="n"/>
+      <c r="R1035" s="89" t="n"/>
     </row>
     <row r="1036" ht="12.75" customHeight="1" s="69">
       <c r="F1036" s="65" t="n"/>
@@ -13804,6 +14853,7 @@
       <c r="O1036" s="68" t="n"/>
       <c r="P1036" s="61" t="n"/>
       <c r="Q1036" s="61" t="n"/>
+      <c r="R1036" s="89" t="n"/>
     </row>
     <row r="1037" ht="12.75" customHeight="1" s="69">
       <c r="F1037" s="65" t="n"/>
@@ -13814,6 +14864,7 @@
       <c r="O1037" s="68" t="n"/>
       <c r="P1037" s="61" t="n"/>
       <c r="Q1037" s="61" t="n"/>
+      <c r="R1037" s="89" t="n"/>
     </row>
     <row r="1038" ht="12.75" customHeight="1" s="69">
       <c r="F1038" s="65" t="n"/>
@@ -13824,6 +14875,7 @@
       <c r="O1038" s="68" t="n"/>
       <c r="P1038" s="61" t="n"/>
       <c r="Q1038" s="61" t="n"/>
+      <c r="R1038" s="89" t="n"/>
     </row>
     <row r="1039" ht="12.75" customHeight="1" s="69">
       <c r="F1039" s="65" t="n"/>
@@ -13834,6 +14886,7 @@
       <c r="O1039" s="68" t="n"/>
       <c r="P1039" s="61" t="n"/>
       <c r="Q1039" s="61" t="n"/>
+      <c r="R1039" s="89" t="n"/>
     </row>
     <row r="1040" ht="12.75" customHeight="1" s="69">
       <c r="F1040" s="65" t="n"/>
@@ -13844,6 +14897,7 @@
       <c r="O1040" s="68" t="n"/>
       <c r="P1040" s="61" t="n"/>
       <c r="Q1040" s="61" t="n"/>
+      <c r="R1040" s="89" t="n"/>
     </row>
     <row r="1041" ht="12.75" customHeight="1" s="69">
       <c r="F1041" s="65" t="n"/>
@@ -13854,6 +14908,7 @@
       <c r="O1041" s="68" t="n"/>
       <c r="P1041" s="61" t="n"/>
       <c r="Q1041" s="61" t="n"/>
+      <c r="R1041" s="89" t="n"/>
     </row>
     <row r="1042" ht="12.75" customHeight="1" s="69">
       <c r="F1042" s="65" t="n"/>
@@ -13864,6 +14919,7 @@
       <c r="O1042" s="68" t="n"/>
       <c r="P1042" s="61" t="n"/>
       <c r="Q1042" s="61" t="n"/>
+      <c r="R1042" s="89" t="n"/>
     </row>
     <row r="1043" ht="12.75" customHeight="1" s="69">
       <c r="F1043" s="65" t="n"/>
@@ -13874,6 +14930,7 @@
       <c r="O1043" s="68" t="n"/>
       <c r="P1043" s="61" t="n"/>
       <c r="Q1043" s="61" t="n"/>
+      <c r="R1043" s="89" t="n"/>
     </row>
     <row r="1044" ht="12.75" customHeight="1" s="69">
       <c r="F1044" s="65" t="n"/>
@@ -13884,6 +14941,7 @@
       <c r="O1044" s="68" t="n"/>
       <c r="P1044" s="61" t="n"/>
       <c r="Q1044" s="61" t="n"/>
+      <c r="R1044" s="89" t="n"/>
     </row>
     <row r="1045" ht="12.75" customHeight="1" s="69">
       <c r="F1045" s="65" t="n"/>
@@ -13894,6 +14952,7 @@
       <c r="O1045" s="68" t="n"/>
       <c r="P1045" s="61" t="n"/>
       <c r="Q1045" s="61" t="n"/>
+      <c r="R1045" s="89" t="n"/>
     </row>
     <row r="1048576" ht="12.75" customHeight="1" s="69"/>
   </sheetData>
@@ -13968,7 +15027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:R1700"/>
+  <dimension ref="A1:R246"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.43359375" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24.67" customWidth="1" style="75" min="1" max="1"/>
@@ -13979,7 +15038,6 @@
     <col width="19.5" customWidth="1" style="75" min="7" max="7"/>
     <col width="71.98" customWidth="1" style="75" min="8" max="8"/>
     <col width="34.52" customWidth="1" style="75" min="9" max="9"/>
-    <col width="20" customWidth="1" style="69" min="18" max="18"/>
     <col width="11.52" customWidth="1" style="75" min="1024" max="1024"/>
   </cols>
   <sheetData>
@@ -14020,11 +15078,6 @@
           <t>Тип разрешительной документации</t>
         </is>
       </c>
-      <c r="R1" s="75" t="inlineStr">
-        <is>
-          <t>Вес в граммах</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" s="69">
       <c r="D2" s="75" t="inlineStr">
@@ -14149,7 +15202,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="160" customHeight="1" s="69">
+    <row r="6" ht="13.5" customHeight="1" s="69">
       <c r="D6" s="75" t="inlineStr">
         <is>
           <t>БАФФ</t>
@@ -14163,11 +15216,6 @@
       <c r="H6" s="72" t="inlineStr">
         <is>
           <t>АЛАНДСКИЕ ОСТРОВА</t>
-        </is>
-      </c>
-      <c r="R6" s="86" t="inlineStr">
-        <is>
-          <t>Обязательное поле: общий вес позиции, целое число больше 0. Просьба указать актуальный вес товара в ГРАММАХ для отчетности РОСПРИРОДНАДЗОР.</t>
         </is>
       </c>
     </row>
@@ -16530,1460 +17578,6 @@
     <row r="246" ht="13.5" customHeight="1" s="69">
       <c r="H246" s="72" t="n"/>
     </row>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
-    <row r="1164"/>
-    <row r="1165"/>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178"/>
-    <row r="1179"/>
-    <row r="1180"/>
-    <row r="1181"/>
-    <row r="1182"/>
-    <row r="1183"/>
-    <row r="1184"/>
-    <row r="1185"/>
-    <row r="1186"/>
-    <row r="1187"/>
-    <row r="1188"/>
-    <row r="1189"/>
-    <row r="1190"/>
-    <row r="1191"/>
-    <row r="1192"/>
-    <row r="1193"/>
-    <row r="1194"/>
-    <row r="1195"/>
-    <row r="1196"/>
-    <row r="1197"/>
-    <row r="1198"/>
-    <row r="1199"/>
-    <row r="1200"/>
-    <row r="1201"/>
-    <row r="1202"/>
-    <row r="1203"/>
-    <row r="1204"/>
-    <row r="1205"/>
-    <row r="1206"/>
-    <row r="1207"/>
-    <row r="1208"/>
-    <row r="1209"/>
-    <row r="1210"/>
-    <row r="1211"/>
-    <row r="1212"/>
-    <row r="1213"/>
-    <row r="1214"/>
-    <row r="1215"/>
-    <row r="1216"/>
-    <row r="1217"/>
-    <row r="1218"/>
-    <row r="1219"/>
-    <row r="1220"/>
-    <row r="1221"/>
-    <row r="1222"/>
-    <row r="1223"/>
-    <row r="1224"/>
-    <row r="1225"/>
-    <row r="1226"/>
-    <row r="1227"/>
-    <row r="1228"/>
-    <row r="1229"/>
-    <row r="1230"/>
-    <row r="1231"/>
-    <row r="1232"/>
-    <row r="1233"/>
-    <row r="1234"/>
-    <row r="1235"/>
-    <row r="1236"/>
-    <row r="1237"/>
-    <row r="1238"/>
-    <row r="1239"/>
-    <row r="1240"/>
-    <row r="1241"/>
-    <row r="1242"/>
-    <row r="1243"/>
-    <row r="1244"/>
-    <row r="1245"/>
-    <row r="1246"/>
-    <row r="1247"/>
-    <row r="1248"/>
-    <row r="1249"/>
-    <row r="1250"/>
-    <row r="1251"/>
-    <row r="1252"/>
-    <row r="1253"/>
-    <row r="1254"/>
-    <row r="1255"/>
-    <row r="1256"/>
-    <row r="1257"/>
-    <row r="1258"/>
-    <row r="1259"/>
-    <row r="1260"/>
-    <row r="1261"/>
-    <row r="1262"/>
-    <row r="1263"/>
-    <row r="1264"/>
-    <row r="1265"/>
-    <row r="1266"/>
-    <row r="1267"/>
-    <row r="1268"/>
-    <row r="1269"/>
-    <row r="1270"/>
-    <row r="1271"/>
-    <row r="1272"/>
-    <row r="1273"/>
-    <row r="1274"/>
-    <row r="1275"/>
-    <row r="1276"/>
-    <row r="1277"/>
-    <row r="1278"/>
-    <row r="1279"/>
-    <row r="1280"/>
-    <row r="1281"/>
-    <row r="1282"/>
-    <row r="1283"/>
-    <row r="1284"/>
-    <row r="1285"/>
-    <row r="1286"/>
-    <row r="1287"/>
-    <row r="1288"/>
-    <row r="1289"/>
-    <row r="1290"/>
-    <row r="1291"/>
-    <row r="1292"/>
-    <row r="1293"/>
-    <row r="1294"/>
-    <row r="1295"/>
-    <row r="1296"/>
-    <row r="1297"/>
-    <row r="1298"/>
-    <row r="1299"/>
-    <row r="1300"/>
-    <row r="1301"/>
-    <row r="1302"/>
-    <row r="1303"/>
-    <row r="1304"/>
-    <row r="1305"/>
-    <row r="1306"/>
-    <row r="1307"/>
-    <row r="1308"/>
-    <row r="1309"/>
-    <row r="1310"/>
-    <row r="1311"/>
-    <row r="1312"/>
-    <row r="1313"/>
-    <row r="1314"/>
-    <row r="1315"/>
-    <row r="1316"/>
-    <row r="1317"/>
-    <row r="1318"/>
-    <row r="1319"/>
-    <row r="1320"/>
-    <row r="1321"/>
-    <row r="1322"/>
-    <row r="1323"/>
-    <row r="1324"/>
-    <row r="1325"/>
-    <row r="1326"/>
-    <row r="1327"/>
-    <row r="1328"/>
-    <row r="1329"/>
-    <row r="1330"/>
-    <row r="1331"/>
-    <row r="1332"/>
-    <row r="1333"/>
-    <row r="1334"/>
-    <row r="1335"/>
-    <row r="1336"/>
-    <row r="1337"/>
-    <row r="1338"/>
-    <row r="1339"/>
-    <row r="1340"/>
-    <row r="1341"/>
-    <row r="1342"/>
-    <row r="1343"/>
-    <row r="1344"/>
-    <row r="1345"/>
-    <row r="1346"/>
-    <row r="1347"/>
-    <row r="1348"/>
-    <row r="1349"/>
-    <row r="1350"/>
-    <row r="1351"/>
-    <row r="1352"/>
-    <row r="1353"/>
-    <row r="1354"/>
-    <row r="1355"/>
-    <row r="1356"/>
-    <row r="1357"/>
-    <row r="1358"/>
-    <row r="1359"/>
-    <row r="1360"/>
-    <row r="1361"/>
-    <row r="1362"/>
-    <row r="1363"/>
-    <row r="1364"/>
-    <row r="1365"/>
-    <row r="1366"/>
-    <row r="1367"/>
-    <row r="1368"/>
-    <row r="1369"/>
-    <row r="1370"/>
-    <row r="1371"/>
-    <row r="1372"/>
-    <row r="1373"/>
-    <row r="1374"/>
-    <row r="1375"/>
-    <row r="1376"/>
-    <row r="1377"/>
-    <row r="1378"/>
-    <row r="1379"/>
-    <row r="1380"/>
-    <row r="1381"/>
-    <row r="1382"/>
-    <row r="1383"/>
-    <row r="1384"/>
-    <row r="1385"/>
-    <row r="1386"/>
-    <row r="1387"/>
-    <row r="1388"/>
-    <row r="1389"/>
-    <row r="1390"/>
-    <row r="1391"/>
-    <row r="1392"/>
-    <row r="1393"/>
-    <row r="1394"/>
-    <row r="1395"/>
-    <row r="1396"/>
-    <row r="1397"/>
-    <row r="1398"/>
-    <row r="1399"/>
-    <row r="1400"/>
-    <row r="1401"/>
-    <row r="1402"/>
-    <row r="1403"/>
-    <row r="1404"/>
-    <row r="1405"/>
-    <row r="1406"/>
-    <row r="1407"/>
-    <row r="1408"/>
-    <row r="1409"/>
-    <row r="1410"/>
-    <row r="1411"/>
-    <row r="1412"/>
-    <row r="1413"/>
-    <row r="1414"/>
-    <row r="1415"/>
-    <row r="1416"/>
-    <row r="1417"/>
-    <row r="1418"/>
-    <row r="1419"/>
-    <row r="1420"/>
-    <row r="1421"/>
-    <row r="1422"/>
-    <row r="1423"/>
-    <row r="1424"/>
-    <row r="1425"/>
-    <row r="1426"/>
-    <row r="1427"/>
-    <row r="1428"/>
-    <row r="1429"/>
-    <row r="1430"/>
-    <row r="1431"/>
-    <row r="1432"/>
-    <row r="1433"/>
-    <row r="1434"/>
-    <row r="1435"/>
-    <row r="1436"/>
-    <row r="1437"/>
-    <row r="1438"/>
-    <row r="1439"/>
-    <row r="1440"/>
-    <row r="1441"/>
-    <row r="1442"/>
-    <row r="1443"/>
-    <row r="1444"/>
-    <row r="1445"/>
-    <row r="1446"/>
-    <row r="1447"/>
-    <row r="1448"/>
-    <row r="1449"/>
-    <row r="1450"/>
-    <row r="1451"/>
-    <row r="1452"/>
-    <row r="1453"/>
-    <row r="1454"/>
-    <row r="1455"/>
-    <row r="1456"/>
-    <row r="1457"/>
-    <row r="1458"/>
-    <row r="1459"/>
-    <row r="1460"/>
-    <row r="1461"/>
-    <row r="1462"/>
-    <row r="1463"/>
-    <row r="1464"/>
-    <row r="1465"/>
-    <row r="1466"/>
-    <row r="1467"/>
-    <row r="1468"/>
-    <row r="1469"/>
-    <row r="1470"/>
-    <row r="1471"/>
-    <row r="1472"/>
-    <row r="1473"/>
-    <row r="1474"/>
-    <row r="1475"/>
-    <row r="1476"/>
-    <row r="1477"/>
-    <row r="1478"/>
-    <row r="1479"/>
-    <row r="1480"/>
-    <row r="1481"/>
-    <row r="1482"/>
-    <row r="1483"/>
-    <row r="1484"/>
-    <row r="1485"/>
-    <row r="1486"/>
-    <row r="1487"/>
-    <row r="1488"/>
-    <row r="1489"/>
-    <row r="1490"/>
-    <row r="1491"/>
-    <row r="1492"/>
-    <row r="1493"/>
-    <row r="1494"/>
-    <row r="1495"/>
-    <row r="1496"/>
-    <row r="1497"/>
-    <row r="1498"/>
-    <row r="1499"/>
-    <row r="1500"/>
-    <row r="1501"/>
-    <row r="1502"/>
-    <row r="1503"/>
-    <row r="1504"/>
-    <row r="1505"/>
-    <row r="1506"/>
-    <row r="1507"/>
-    <row r="1508"/>
-    <row r="1509"/>
-    <row r="1510"/>
-    <row r="1511"/>
-    <row r="1512"/>
-    <row r="1513"/>
-    <row r="1514"/>
-    <row r="1515"/>
-    <row r="1516"/>
-    <row r="1517"/>
-    <row r="1518"/>
-    <row r="1519"/>
-    <row r="1520"/>
-    <row r="1521"/>
-    <row r="1522"/>
-    <row r="1523"/>
-    <row r="1524"/>
-    <row r="1525"/>
-    <row r="1526"/>
-    <row r="1527"/>
-    <row r="1528"/>
-    <row r="1529"/>
-    <row r="1530"/>
-    <row r="1531"/>
-    <row r="1532"/>
-    <row r="1533"/>
-    <row r="1534"/>
-    <row r="1535"/>
-    <row r="1536"/>
-    <row r="1537"/>
-    <row r="1538"/>
-    <row r="1539"/>
-    <row r="1540"/>
-    <row r="1541"/>
-    <row r="1542"/>
-    <row r="1543"/>
-    <row r="1544"/>
-    <row r="1545"/>
-    <row r="1546"/>
-    <row r="1547"/>
-    <row r="1548"/>
-    <row r="1549"/>
-    <row r="1550"/>
-    <row r="1551"/>
-    <row r="1552"/>
-    <row r="1553"/>
-    <row r="1554"/>
-    <row r="1555"/>
-    <row r="1556"/>
-    <row r="1557"/>
-    <row r="1558"/>
-    <row r="1559"/>
-    <row r="1560"/>
-    <row r="1561"/>
-    <row r="1562"/>
-    <row r="1563"/>
-    <row r="1564"/>
-    <row r="1565"/>
-    <row r="1566"/>
-    <row r="1567"/>
-    <row r="1568"/>
-    <row r="1569"/>
-    <row r="1570"/>
-    <row r="1571"/>
-    <row r="1572"/>
-    <row r="1573"/>
-    <row r="1574"/>
-    <row r="1575"/>
-    <row r="1576"/>
-    <row r="1577"/>
-    <row r="1578"/>
-    <row r="1579"/>
-    <row r="1580"/>
-    <row r="1581"/>
-    <row r="1582"/>
-    <row r="1583"/>
-    <row r="1584"/>
-    <row r="1585"/>
-    <row r="1586"/>
-    <row r="1587"/>
-    <row r="1588"/>
-    <row r="1589"/>
-    <row r="1590"/>
-    <row r="1591"/>
-    <row r="1592"/>
-    <row r="1593"/>
-    <row r="1594"/>
-    <row r="1595"/>
-    <row r="1596"/>
-    <row r="1597"/>
-    <row r="1598"/>
-    <row r="1599"/>
-    <row r="1600"/>
-    <row r="1601"/>
-    <row r="1602"/>
-    <row r="1603"/>
-    <row r="1604"/>
-    <row r="1605"/>
-    <row r="1606"/>
-    <row r="1607"/>
-    <row r="1608"/>
-    <row r="1609"/>
-    <row r="1610"/>
-    <row r="1611"/>
-    <row r="1612"/>
-    <row r="1613"/>
-    <row r="1614"/>
-    <row r="1615"/>
-    <row r="1616"/>
-    <row r="1617"/>
-    <row r="1618"/>
-    <row r="1619"/>
-    <row r="1620"/>
-    <row r="1621"/>
-    <row r="1622"/>
-    <row r="1623"/>
-    <row r="1624"/>
-    <row r="1625"/>
-    <row r="1626"/>
-    <row r="1627"/>
-    <row r="1628"/>
-    <row r="1629"/>
-    <row r="1630"/>
-    <row r="1631"/>
-    <row r="1632"/>
-    <row r="1633"/>
-    <row r="1634"/>
-    <row r="1635"/>
-    <row r="1636"/>
-    <row r="1637"/>
-    <row r="1638"/>
-    <row r="1639"/>
-    <row r="1640"/>
-    <row r="1641"/>
-    <row r="1642"/>
-    <row r="1643"/>
-    <row r="1644"/>
-    <row r="1645"/>
-    <row r="1646"/>
-    <row r="1647"/>
-    <row r="1648"/>
-    <row r="1649"/>
-    <row r="1650"/>
-    <row r="1651"/>
-    <row r="1652"/>
-    <row r="1653"/>
-    <row r="1654"/>
-    <row r="1655"/>
-    <row r="1656"/>
-    <row r="1657"/>
-    <row r="1658"/>
-    <row r="1659"/>
-    <row r="1660"/>
-    <row r="1661"/>
-    <row r="1662"/>
-    <row r="1663"/>
-    <row r="1664"/>
-    <row r="1665"/>
-    <row r="1666"/>
-    <row r="1667"/>
-    <row r="1668"/>
-    <row r="1669"/>
-    <row r="1670"/>
-    <row r="1671"/>
-    <row r="1672"/>
-    <row r="1673"/>
-    <row r="1674"/>
-    <row r="1675"/>
-    <row r="1676"/>
-    <row r="1677"/>
-    <row r="1678"/>
-    <row r="1679"/>
-    <row r="1680"/>
-    <row r="1681"/>
-    <row r="1682"/>
-    <row r="1683"/>
-    <row r="1684"/>
-    <row r="1685"/>
-    <row r="1686"/>
-    <row r="1687"/>
-    <row r="1688"/>
-    <row r="1689"/>
-    <row r="1690"/>
-    <row r="1691"/>
-    <row r="1692"/>
-    <row r="1693"/>
-    <row r="1694"/>
-    <row r="1695"/>
-    <row r="1696"/>
-    <row r="1697"/>
-    <row r="1698"/>
-    <row r="1699"/>
-    <row r="1700"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
